--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4195E6BC-80E5-47E9-AB4D-96BBF1237994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAEAD94-2606-42FF-889C-3DF03516E4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8082" uniqueCount="3904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8111" uniqueCount="3910">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -11750,6 +11750,24 @@
   </si>
   <si>
     <t>FRS1, VBJ</t>
+  </si>
+  <si>
+    <t>HSMS-0577</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Tolbiac Rez-de-jardin: Rés. Vélins 1501</t>
+  </si>
+  <si>
+    <t>HSMS-0578</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/card?id=9b5d09a9-718d-459c-b355-8ad474abf740</t>
   </si>
 </sst>
 </file>
@@ -12560,8 +12578,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T577" totalsRowShown="0">
-  <autoFilter ref="A1:T577" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T579" totalsRowShown="0">
+  <autoFilter ref="A1:T579" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -12811,31 +12829,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T577"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T579"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="38.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="4" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" customWidth="1"/>
     <col min="14" max="14" width="45" style="1" customWidth="1"/>
-    <col min="15" max="15" width="59.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" customWidth="1"/>
-    <col min="17" max="17" width="41.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="59.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="41.28515625" style="1" customWidth="1"/>
     <col min="18" max="19" width="58" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
-    <col min="21" max="16384" width="9.33203125" style="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12897,7 +12915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -12944,7 +12962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -12989,7 +13007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -13039,7 +13057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -13081,7 +13099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -13131,7 +13149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -13181,7 +13199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>74</v>
       </c>
@@ -13228,7 +13246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -13278,7 +13296,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="144" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>91</v>
       </c>
@@ -13328,7 +13346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
@@ -13381,7 +13399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>108</v>
       </c>
@@ -13437,7 +13455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>117</v>
       </c>
@@ -13484,7 +13502,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>124</v>
       </c>
@@ -13538,7 +13556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>134</v>
       </c>
@@ -13588,7 +13606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>143</v>
       </c>
@@ -13633,7 +13651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -13680,7 +13698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
@@ -13722,7 +13740,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>163</v>
       </c>
@@ -13767,7 +13785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>170</v>
       </c>
@@ -13818,7 +13836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>177</v>
       </c>
@@ -13865,7 +13883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>186</v>
       </c>
@@ -13915,7 +13933,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>193</v>
       </c>
@@ -13962,7 +13980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>200</v>
       </c>
@@ -14009,7 +14027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -14056,7 +14074,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>213</v>
       </c>
@@ -14103,7 +14121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>220</v>
       </c>
@@ -14150,7 +14168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>226</v>
       </c>
@@ -14200,7 +14218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>235</v>
       </c>
@@ -14247,7 +14265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>242</v>
       </c>
@@ -14294,7 +14312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>249</v>
       </c>
@@ -14347,7 +14365,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>256</v>
       </c>
@@ -14394,7 +14412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>263</v>
       </c>
@@ -14445,7 +14463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>270</v>
       </c>
@@ -14493,7 +14511,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>276</v>
       </c>
@@ -14546,7 +14564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>285</v>
       </c>
@@ -14594,7 +14612,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>291</v>
       </c>
@@ -14639,7 +14657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>296</v>
       </c>
@@ -14687,7 +14705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>301</v>
       </c>
@@ -14738,7 +14756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>306</v>
       </c>
@@ -14789,7 +14807,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>312</v>
       </c>
@@ -14837,7 +14855,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>320</v>
       </c>
@@ -14893,7 +14911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>328</v>
       </c>
@@ -14941,7 +14959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>333</v>
       </c>
@@ -14989,7 +15007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>340</v>
       </c>
@@ -15037,7 +15055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>345</v>
       </c>
@@ -15085,7 +15103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>351</v>
       </c>
@@ -15141,7 +15159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>361</v>
       </c>
@@ -15189,7 +15207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>367</v>
       </c>
@@ -15237,7 +15255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>373</v>
       </c>
@@ -15285,7 +15303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>379</v>
       </c>
@@ -15338,7 +15356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>389</v>
       </c>
@@ -15383,7 +15401,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>395</v>
       </c>
@@ -15431,7 +15449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>403</v>
       </c>
@@ -15478,7 +15496,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>409</v>
       </c>
@@ -15528,7 +15546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>416</v>
       </c>
@@ -15578,7 +15596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>424</v>
       </c>
@@ -15631,7 +15649,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>431</v>
       </c>
@@ -15682,7 +15700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>441</v>
       </c>
@@ -15733,7 +15751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>447</v>
       </c>
@@ -15781,7 +15799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>452</v>
       </c>
@@ -15832,7 +15850,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>458</v>
       </c>
@@ -15886,7 +15904,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>466</v>
       </c>
@@ -15940,7 +15958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>472</v>
       </c>
@@ -15988,7 +16006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>477</v>
       </c>
@@ -16039,7 +16057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>481</v>
       </c>
@@ -16086,7 +16104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>487</v>
       </c>
@@ -16136,7 +16154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>495</v>
       </c>
@@ -16186,7 +16204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>501</v>
       </c>
@@ -16233,7 +16251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>506</v>
       </c>
@@ -16280,7 +16298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>513</v>
       </c>
@@ -16327,7 +16345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>520</v>
       </c>
@@ -16377,7 +16395,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>526</v>
       </c>
@@ -16427,7 +16445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>531</v>
       </c>
@@ -16480,7 +16498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>539</v>
       </c>
@@ -16530,7 +16548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>546</v>
       </c>
@@ -16577,7 +16595,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>552</v>
       </c>
@@ -16624,7 +16642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>558</v>
       </c>
@@ -16671,7 +16689,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>564</v>
       </c>
@@ -16718,7 +16736,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>570</v>
       </c>
@@ -16771,7 +16789,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>581</v>
       </c>
@@ -16818,7 +16836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>587</v>
       </c>
@@ -16865,7 +16883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>593</v>
       </c>
@@ -16915,7 +16933,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>602</v>
       </c>
@@ -16965,7 +16983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>611</v>
       </c>
@@ -17015,7 +17033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>618</v>
       </c>
@@ -17068,7 +17086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>625</v>
       </c>
@@ -17115,7 +17133,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>633</v>
       </c>
@@ -17165,7 +17183,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>640</v>
       </c>
@@ -17215,7 +17233,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>647</v>
       </c>
@@ -17262,7 +17280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>654</v>
       </c>
@@ -17309,7 +17327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>660</v>
       </c>
@@ -17356,7 +17374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>666</v>
       </c>
@@ -17406,7 +17424,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>674</v>
       </c>
@@ -17453,7 +17471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>682</v>
       </c>
@@ -17503,7 +17521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>690</v>
       </c>
@@ -17554,7 +17572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>696</v>
       </c>
@@ -17604,7 +17622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>704</v>
       </c>
@@ -17654,7 +17672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>711</v>
       </c>
@@ -17704,7 +17722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>717</v>
       </c>
@@ -17758,7 +17776,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>725</v>
       </c>
@@ -17811,7 +17829,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>732</v>
       </c>
@@ -17858,7 +17876,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>738</v>
       </c>
@@ -17908,7 +17926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>745</v>
       </c>
@@ -17958,7 +17976,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>754</v>
       </c>
@@ -18005,7 +18023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>762</v>
       </c>
@@ -18055,7 +18073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>770</v>
       </c>
@@ -18105,7 +18123,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>778</v>
       </c>
@@ -18155,7 +18173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>785</v>
       </c>
@@ -18205,7 +18223,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>793</v>
       </c>
@@ -18258,7 +18276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>801</v>
       </c>
@@ -18311,7 +18329,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>807</v>
       </c>
@@ -18364,7 +18382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>817</v>
       </c>
@@ -18414,7 +18432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>823</v>
       </c>
@@ -18464,7 +18482,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>829</v>
       </c>
@@ -18511,7 +18529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>835</v>
       </c>
@@ -18558,7 +18576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>842</v>
       </c>
@@ -18608,7 +18626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>848</v>
       </c>
@@ -18658,7 +18676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>854</v>
       </c>
@@ -18705,7 +18723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>861</v>
       </c>
@@ -18755,7 +18773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>868</v>
       </c>
@@ -18805,7 +18823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>873</v>
       </c>
@@ -18855,7 +18873,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>879</v>
       </c>
@@ -18908,7 +18926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>888</v>
       </c>
@@ -18958,7 +18976,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>895</v>
       </c>
@@ -19003,7 +19021,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>900</v>
       </c>
@@ -19053,7 +19071,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>909</v>
       </c>
@@ -19103,7 +19121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>917</v>
       </c>
@@ -19153,7 +19171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>924</v>
       </c>
@@ -19203,7 +19221,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>931</v>
       </c>
@@ -19253,7 +19271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>937</v>
       </c>
@@ -19298,7 +19316,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>943</v>
       </c>
@@ -19351,7 +19369,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>949</v>
       </c>
@@ -19401,7 +19419,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>955</v>
       </c>
@@ -19451,7 +19469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>962</v>
       </c>
@@ -19507,7 +19525,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>971</v>
       </c>
@@ -19561,7 +19579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>978</v>
       </c>
@@ -19608,7 +19626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>984</v>
       </c>
@@ -19655,7 +19673,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>991</v>
       </c>
@@ -19705,7 +19723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>1001</v>
       </c>
@@ -19755,7 +19773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>1008</v>
       </c>
@@ -19802,7 +19820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>1015</v>
       </c>
@@ -19852,7 +19870,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>1020</v>
       </c>
@@ -19899,7 +19917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>1029</v>
       </c>
@@ -19949,7 +19967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>1036</v>
       </c>
@@ -19999,7 +20017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>1044</v>
       </c>
@@ -20049,7 +20067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>1051</v>
       </c>
@@ -20096,7 +20114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>1057</v>
       </c>
@@ -20146,7 +20164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>1062</v>
       </c>
@@ -20193,7 +20211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>1069</v>
       </c>
@@ -20240,7 +20258,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>1074</v>
       </c>
@@ -20290,7 +20308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>1080</v>
       </c>
@@ -20343,7 +20361,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>1085</v>
       </c>
@@ -20390,7 +20408,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>1090</v>
       </c>
@@ -20440,7 +20458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>1097</v>
       </c>
@@ -20487,7 +20505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>1103</v>
       </c>
@@ -20532,7 +20550,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>1109</v>
       </c>
@@ -20579,7 +20597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>1116</v>
       </c>
@@ -20635,7 +20653,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>1124</v>
       </c>
@@ -20689,7 +20707,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>1134</v>
       </c>
@@ -20739,7 +20757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>1140</v>
       </c>
@@ -20792,7 +20810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>1147</v>
       </c>
@@ -20845,7 +20863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>1155</v>
       </c>
@@ -20893,7 +20911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>1161</v>
       </c>
@@ -20946,7 +20964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>1169</v>
       </c>
@@ -20999,7 +21017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>1177</v>
       </c>
@@ -21049,7 +21067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>1185</v>
       </c>
@@ -21097,7 +21115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>1190</v>
       </c>
@@ -21145,7 +21163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>1195</v>
       </c>
@@ -21195,7 +21213,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>1202</v>
       </c>
@@ -21245,7 +21263,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>1210</v>
       </c>
@@ -21295,7 +21313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>1217</v>
       </c>
@@ -21345,7 +21363,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>1223</v>
       </c>
@@ -21393,7 +21411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>1228</v>
       </c>
@@ -21443,7 +21461,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>1236</v>
       </c>
@@ -21496,7 +21514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>1242</v>
       </c>
@@ -21544,7 +21562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>1248</v>
       </c>
@@ -21600,7 +21618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>1256</v>
       </c>
@@ -21653,7 +21671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>1262</v>
       </c>
@@ -21703,7 +21721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>1267</v>
       </c>
@@ -21751,7 +21769,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>1273</v>
       </c>
@@ -21804,7 +21822,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>1279</v>
       </c>
@@ -21854,7 +21872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>1285</v>
       </c>
@@ -21904,7 +21922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>1293</v>
       </c>
@@ -21957,7 +21975,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>1301</v>
       </c>
@@ -22005,7 +22023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>1308</v>
       </c>
@@ -22050,7 +22068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>1313</v>
       </c>
@@ -22095,7 +22113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>1319</v>
       </c>
@@ -22142,7 +22160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>1327</v>
       </c>
@@ -22190,7 +22208,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22243,7 +22261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>1342</v>
       </c>
@@ -22293,7 +22311,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>1349</v>
       </c>
@@ -22340,7 +22358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>1354</v>
       </c>
@@ -22390,7 +22408,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>1360</v>
       </c>
@@ -22437,7 +22455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>1364</v>
       </c>
@@ -22487,7 +22505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>1372</v>
       </c>
@@ -22537,7 +22555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>1381</v>
       </c>
@@ -22587,7 +22605,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>1386</v>
       </c>
@@ -22637,7 +22655,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>1392</v>
       </c>
@@ -22687,7 +22705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>1398</v>
       </c>
@@ -22735,7 +22753,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>1405</v>
       </c>
@@ -22783,7 +22801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>1414</v>
       </c>
@@ -22831,7 +22849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>1421</v>
       </c>
@@ -22877,7 +22895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>1426</v>
       </c>
@@ -22924,7 +22942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>1432</v>
       </c>
@@ -22974,7 +22992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>1437</v>
       </c>
@@ -23018,7 +23036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>1440</v>
       </c>
@@ -23062,7 +23080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>1444</v>
       </c>
@@ -23110,7 +23128,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>1450</v>
       </c>
@@ -23163,7 +23181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>1456</v>
       </c>
@@ -23211,7 +23229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>1464</v>
       </c>
@@ -23261,7 +23279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>1470</v>
       </c>
@@ -23311,7 +23329,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>1476</v>
       </c>
@@ -23364,7 +23382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>1483</v>
       </c>
@@ -23420,7 +23438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>1491</v>
       </c>
@@ -23476,7 +23494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>1498</v>
       </c>
@@ -23524,7 +23542,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>1504</v>
       </c>
@@ -23577,7 +23595,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>1511</v>
       </c>
@@ -23621,7 +23639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>1515</v>
       </c>
@@ -23674,7 +23692,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1521</v>
       </c>
@@ -23724,7 +23742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>1526</v>
       </c>
@@ -23777,7 +23795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>1533</v>
       </c>
@@ -23827,7 +23845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>1539</v>
       </c>
@@ -23877,7 +23895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>1546</v>
       </c>
@@ -23930,7 +23948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>1555</v>
       </c>
@@ -23978,7 +23996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>1564</v>
       </c>
@@ -24028,7 +24046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>1571</v>
       </c>
@@ -24078,7 +24096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>1578</v>
       </c>
@@ -24128,7 +24146,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>1585</v>
       </c>
@@ -24178,7 +24196,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>1594</v>
       </c>
@@ -24228,7 +24246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>1600</v>
       </c>
@@ -24276,7 +24294,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>1604</v>
       </c>
@@ -24323,7 +24341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>1610</v>
       </c>
@@ -24373,7 +24391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>1617</v>
       </c>
@@ -24425,7 +24443,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>1625</v>
       </c>
@@ -24472,7 +24490,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1633</v>
       </c>
@@ -24522,7 +24540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>1640</v>
       </c>
@@ -24572,7 +24590,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>1646</v>
       </c>
@@ -24619,7 +24637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>1651</v>
       </c>
@@ -24666,7 +24684,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>1656</v>
       </c>
@@ -24716,7 +24734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>1660</v>
       </c>
@@ -24763,7 +24781,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>1666</v>
       </c>
@@ -24810,7 +24828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>1671</v>
       </c>
@@ -24860,7 +24878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>1677</v>
       </c>
@@ -24907,7 +24925,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>1683</v>
       </c>
@@ -24960,7 +24978,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>1691</v>
       </c>
@@ -25007,7 +25025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>1696</v>
       </c>
@@ -25054,7 +25072,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>1701</v>
       </c>
@@ -25104,7 +25122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>1707</v>
       </c>
@@ -25151,7 +25169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1713</v>
       </c>
@@ -25200,7 +25218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1719</v>
       </c>
@@ -25247,7 +25265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>1725</v>
       </c>
@@ -25294,7 +25312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>1731</v>
       </c>
@@ -25341,7 +25359,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1737</v>
       </c>
@@ -25386,7 +25404,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1742</v>
       </c>
@@ -25428,7 +25446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1747</v>
       </c>
@@ -25481,7 +25499,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1755</v>
       </c>
@@ -25528,7 +25546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1759</v>
       </c>
@@ -25575,7 +25593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1765</v>
       </c>
@@ -25625,7 +25643,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1770</v>
       </c>
@@ -25675,7 +25693,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1778</v>
       </c>
@@ -25727,7 +25745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1783</v>
       </c>
@@ -25774,7 +25792,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1787</v>
       </c>
@@ -25824,7 +25842,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1793</v>
       </c>
@@ -25874,7 +25892,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1797</v>
       </c>
@@ -25924,7 +25942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>1803</v>
       </c>
@@ -25971,7 +25989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>1806</v>
       </c>
@@ -26018,7 +26036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>1809</v>
       </c>
@@ -26065,7 +26083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>1812</v>
       </c>
@@ -26114,7 +26132,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>1818</v>
       </c>
@@ -26161,7 +26179,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>1822</v>
       </c>
@@ -26209,7 +26227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>1828</v>
       </c>
@@ -26259,7 +26277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>1833</v>
       </c>
@@ -26309,7 +26327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>1838</v>
       </c>
@@ -26354,7 +26372,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>1842</v>
       </c>
@@ -26401,7 +26419,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>1848</v>
       </c>
@@ -26451,7 +26469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>1853</v>
       </c>
@@ -26499,7 +26517,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>1858</v>
       </c>
@@ -26546,7 +26564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>1864</v>
       </c>
@@ -26596,7 +26614,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>1869</v>
       </c>
@@ -26646,7 +26664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>1875</v>
       </c>
@@ -26694,7 +26712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>1881</v>
       </c>
@@ -26742,7 +26760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>1887</v>
       </c>
@@ -26790,7 +26808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>1892</v>
       </c>
@@ -26840,7 +26858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>1897</v>
       </c>
@@ -26885,7 +26903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1902</v>
       </c>
@@ -26930,7 +26948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1908</v>
       </c>
@@ -26981,7 +26999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1915</v>
       </c>
@@ -27031,7 +27049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1921</v>
       </c>
@@ -27078,7 +27096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1925</v>
       </c>
@@ -27126,7 +27144,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="291" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1932</v>
       </c>
@@ -27176,7 +27194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="292" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1937</v>
       </c>
@@ -27228,7 +27246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="293" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1945</v>
       </c>
@@ -27275,7 +27293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="294" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1951</v>
       </c>
@@ -27325,7 +27343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1955</v>
       </c>
@@ -27370,7 +27388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="296" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1959</v>
       </c>
@@ -27420,7 +27438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="297" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1964</v>
       </c>
@@ -27465,7 +27483,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="298" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>1968</v>
       </c>
@@ -27513,7 +27531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="299" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>1974</v>
       </c>
@@ -27558,7 +27576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>1979</v>
       </c>
@@ -27608,7 +27626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="301" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>1985</v>
       </c>
@@ -27656,7 +27674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="302" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>1991</v>
       </c>
@@ -27701,7 +27719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="303" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>1996</v>
       </c>
@@ -27748,7 +27766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>2001</v>
       </c>
@@ -27798,7 +27816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>2008</v>
       </c>
@@ -27843,7 +27861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="306" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>2012</v>
       </c>
@@ -27890,7 +27908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="307" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>2018</v>
       </c>
@@ -27938,7 +27956,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>2024</v>
       </c>
@@ -27985,7 +28003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>2030</v>
       </c>
@@ -28035,7 +28053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="310" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>2034</v>
       </c>
@@ -28088,7 +28106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>2039</v>
       </c>
@@ -28138,7 +28156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="312" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>2046</v>
       </c>
@@ -28188,7 +28206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="313" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>2050</v>
       </c>
@@ -28233,7 +28251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>2055</v>
       </c>
@@ -28280,7 +28298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="315" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>2061</v>
       </c>
@@ -28330,7 +28348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="316" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>2066</v>
       </c>
@@ -28378,7 +28396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="317" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>2071</v>
       </c>
@@ -28423,7 +28441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="318" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>2075</v>
       </c>
@@ -28471,7 +28489,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="319" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>2081</v>
       </c>
@@ -28516,7 +28534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>2085</v>
       </c>
@@ -28570,7 +28588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>2091</v>
       </c>
@@ -28620,7 +28638,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="322" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>2098</v>
       </c>
@@ -28670,7 +28688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="323" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>2104</v>
       </c>
@@ -28726,7 +28744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>2109</v>
       </c>
@@ -28776,7 +28794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="325" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>2116</v>
       </c>
@@ -28821,7 +28839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="326" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>2121</v>
       </c>
@@ -28866,7 +28884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>2127</v>
       </c>
@@ -28911,7 +28929,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>2132</v>
       </c>
@@ -28959,7 +28977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>2137</v>
       </c>
@@ -29004,7 +29022,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="330" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>2141</v>
       </c>
@@ -29052,7 +29070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>2148</v>
       </c>
@@ -29103,7 +29121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="332" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>2155</v>
       </c>
@@ -29154,7 +29172,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="333" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>2162</v>
       </c>
@@ -29204,7 +29222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>2168</v>
       </c>
@@ -29257,7 +29275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="335" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>2174</v>
       </c>
@@ -29307,7 +29325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="336" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>2180</v>
       </c>
@@ -29358,7 +29376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="337" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>2186</v>
       </c>
@@ -29411,7 +29429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>2194</v>
       </c>
@@ -29464,7 +29482,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>2203</v>
       </c>
@@ -29514,7 +29532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>2210</v>
       </c>
@@ -29564,7 +29582,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="341" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>2215</v>
       </c>
@@ -29612,7 +29630,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>2223</v>
       </c>
@@ -29662,7 +29680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>2231</v>
       </c>
@@ -29709,7 +29727,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>2237</v>
       </c>
@@ -29757,7 +29775,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>2241</v>
       </c>
@@ -29810,7 +29828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>2246</v>
       </c>
@@ -29857,7 +29875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>2254</v>
       </c>
@@ -29907,7 +29925,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>2262</v>
       </c>
@@ -29952,7 +29970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>2267</v>
       </c>
@@ -30005,7 +30023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>2273</v>
       </c>
@@ -30055,7 +30073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>2279</v>
       </c>
@@ -30105,7 +30123,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>2287</v>
       </c>
@@ -30150,7 +30168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>2294</v>
       </c>
@@ -30200,7 +30218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="354" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>2302</v>
       </c>
@@ -30253,7 +30271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>2308</v>
       </c>
@@ -30306,7 +30324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>2314</v>
       </c>
@@ -30356,7 +30374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>2322</v>
       </c>
@@ -30406,7 +30424,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>2330</v>
       </c>
@@ -30453,7 +30471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>2336</v>
       </c>
@@ -30503,7 +30521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>2345</v>
       </c>
@@ -30553,7 +30571,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>2352</v>
       </c>
@@ -30600,7 +30618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="362" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>2357</v>
       </c>
@@ -30650,7 +30668,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="363" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>2362</v>
       </c>
@@ -30698,7 +30716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="364" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>2369</v>
       </c>
@@ -30745,7 +30763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>2373</v>
       </c>
@@ -30798,7 +30816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>2379</v>
       </c>
@@ -30848,7 +30866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="367" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>2387</v>
       </c>
@@ -30901,7 +30919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="368" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>2393</v>
       </c>
@@ -30946,7 +30964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="369" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>2397</v>
       </c>
@@ -30996,7 +31014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="370" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>2403</v>
       </c>
@@ -31043,7 +31061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>2408</v>
       </c>
@@ -31087,7 +31105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>2415</v>
       </c>
@@ -31134,7 +31152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="373" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>2423</v>
       </c>
@@ -31178,7 +31196,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>2429</v>
       </c>
@@ -31222,7 +31240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="375" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>2435</v>
       </c>
@@ -31269,7 +31287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="376" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>2441</v>
       </c>
@@ -31316,7 +31334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="377" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>2447</v>
       </c>
@@ -31363,7 +31381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="378" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>2453</v>
       </c>
@@ -31407,7 +31425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="379" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>2459</v>
       </c>
@@ -31451,7 +31469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="380" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>2463</v>
       </c>
@@ -31498,7 +31516,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>2470</v>
       </c>
@@ -31545,7 +31563,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="382" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>2476</v>
       </c>
@@ -31589,7 +31607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>2481</v>
       </c>
@@ -31633,7 +31651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="384" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>2485</v>
       </c>
@@ -31677,7 +31695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>2490</v>
       </c>
@@ -31721,7 +31739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>2494</v>
       </c>
@@ -31768,7 +31786,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="387" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>2501</v>
       </c>
@@ -31815,7 +31833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="388" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>2507</v>
       </c>
@@ -31859,7 +31877,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="389" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>2511</v>
       </c>
@@ -31903,7 +31921,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>2515</v>
       </c>
@@ -31956,7 +31974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="391" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>2521</v>
       </c>
@@ -32000,7 +32018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>2527</v>
       </c>
@@ -32044,7 +32062,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>2532</v>
       </c>
@@ -32085,7 +32103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="394" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>2536</v>
       </c>
@@ -32129,7 +32147,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="395" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>2541</v>
       </c>
@@ -32170,7 +32188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="396" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>2546</v>
       </c>
@@ -32209,7 +32227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="397" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>2550</v>
       </c>
@@ -32250,7 +32268,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="398" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>2554</v>
       </c>
@@ -32291,7 +32309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>2559</v>
       </c>
@@ -32332,7 +32350,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="400" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>2563</v>
       </c>
@@ -32373,7 +32391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="401" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>2567</v>
       </c>
@@ -32414,7 +32432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="402" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>2570</v>
       </c>
@@ -32455,7 +32473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="403" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>2575</v>
       </c>
@@ -32499,7 +32517,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>2577</v>
       </c>
@@ -32543,7 +32561,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="405" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>2582</v>
       </c>
@@ -32587,7 +32605,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>2587</v>
       </c>
@@ -32634,7 +32652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>2595</v>
       </c>
@@ -32681,7 +32699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="408" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>2598</v>
       </c>
@@ -32731,7 +32749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="409" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>2604</v>
       </c>
@@ -32787,7 +32805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>2613</v>
       </c>
@@ -32837,7 +32855,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="411" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>2620</v>
       </c>
@@ -32881,7 +32899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="412" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>2624</v>
       </c>
@@ -32925,7 +32943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="413" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>2629</v>
       </c>
@@ -32972,7 +32990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="414" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>2637</v>
       </c>
@@ -33013,7 +33031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="415" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>2642</v>
       </c>
@@ -33057,7 +33075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="416" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>2647</v>
       </c>
@@ -33098,7 +33116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="417" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>2651</v>
       </c>
@@ -33142,7 +33160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="418" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>2656</v>
       </c>
@@ -33186,7 +33204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>2661</v>
       </c>
@@ -33230,7 +33248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="420" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>2666</v>
       </c>
@@ -33271,7 +33289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="421" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>2670</v>
       </c>
@@ -33312,7 +33330,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="422" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>2676</v>
       </c>
@@ -33356,7 +33374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="423" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>2679</v>
       </c>
@@ -33406,7 +33424,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="424" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="12" t="s">
         <v>2686</v>
       </c>
@@ -33451,7 +33469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="425" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>2690</v>
       </c>
@@ -33489,7 +33507,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="426" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>2694</v>
       </c>
@@ -33533,7 +33551,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="427" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>2698</v>
       </c>
@@ -33577,7 +33595,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="428" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>2704</v>
       </c>
@@ -33621,7 +33639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>2708</v>
       </c>
@@ -33662,7 +33680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>2711</v>
       </c>
@@ -33706,7 +33724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="431" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>2716</v>
       </c>
@@ -33747,7 +33765,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>2721</v>
       </c>
@@ -33800,7 +33818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>2727</v>
       </c>
@@ -33853,7 +33871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="434" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>2735</v>
       </c>
@@ -33898,7 +33916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="435" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>2741</v>
       </c>
@@ -33942,7 +33960,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="436" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>2746</v>
       </c>
@@ -33986,7 +34004,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="437" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>2752</v>
       </c>
@@ -34030,7 +34048,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="438" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>2757</v>
       </c>
@@ -34077,7 +34095,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="439" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>2765</v>
       </c>
@@ -34130,7 +34148,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="440" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>2772</v>
       </c>
@@ -34183,7 +34201,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="441" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>2779</v>
       </c>
@@ -34236,7 +34254,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="442" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>2785</v>
       </c>
@@ -34286,7 +34304,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="443" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>2792</v>
       </c>
@@ -34339,7 +34357,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="444" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>2798</v>
       </c>
@@ -34389,7 +34407,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="445" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>2804</v>
       </c>
@@ -34442,7 +34460,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="446" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>2811</v>
       </c>
@@ -34498,7 +34516,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="447" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>2819</v>
       </c>
@@ -34545,7 +34563,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="448" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>2825</v>
       </c>
@@ -34592,7 +34610,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="449" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>2832</v>
       </c>
@@ -34642,7 +34660,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="450" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>2838</v>
       </c>
@@ -34689,7 +34707,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="451" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>2844</v>
       </c>
@@ -34736,7 +34754,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="452" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>2850</v>
       </c>
@@ -34787,7 +34805,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="453" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>2856</v>
       </c>
@@ -34838,7 +34856,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="454" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>2862</v>
       </c>
@@ -34890,7 +34908,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="455" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>2867</v>
       </c>
@@ -34937,7 +34955,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="456" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>2875</v>
       </c>
@@ -34984,7 +35002,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="457" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>2882</v>
       </c>
@@ -35033,7 +35051,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="458" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>2888</v>
       </c>
@@ -35080,7 +35098,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="459" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>2893</v>
       </c>
@@ -35124,7 +35142,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="460" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>2899</v>
       </c>
@@ -35171,7 +35189,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="461" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>2902</v>
       </c>
@@ -35212,7 +35230,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="462" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>2909</v>
       </c>
@@ -35259,7 +35277,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="463" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>2914</v>
       </c>
@@ -35304,7 +35322,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="464" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>2919</v>
       </c>
@@ -35348,7 +35366,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="465" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>2923</v>
       </c>
@@ -35398,7 +35416,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="466" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>2930</v>
       </c>
@@ -35451,7 +35469,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="467" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>2936</v>
       </c>
@@ -35501,7 +35519,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="468" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>2942</v>
       </c>
@@ -35539,7 +35557,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="469" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>2948</v>
       </c>
@@ -35589,7 +35607,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="470" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>2953</v>
       </c>
@@ -35639,7 +35657,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="471" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>2958</v>
       </c>
@@ -35688,7 +35706,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="472" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>2965</v>
       </c>
@@ -35739,7 +35757,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="473" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>2972</v>
       </c>
@@ -35790,7 +35808,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="474" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>2978</v>
       </c>
@@ -35837,7 +35855,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="475" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>2984</v>
       </c>
@@ -35884,7 +35902,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="476" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>2991</v>
       </c>
@@ -35925,7 +35943,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="477" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>2995</v>
       </c>
@@ -35969,7 +35987,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="478" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>3000</v>
       </c>
@@ -36010,7 +36028,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="479" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>3006</v>
       </c>
@@ -36054,7 +36072,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="480" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>3012</v>
       </c>
@@ -36101,7 +36119,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="481" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
         <v>3018</v>
       </c>
@@ -36155,7 +36173,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="482" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482" s="16" t="s">
         <v>3028</v>
       </c>
@@ -36205,7 +36223,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="483" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>3034</v>
       </c>
@@ -36257,7 +36275,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="484" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>3042</v>
       </c>
@@ -36311,7 +36329,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="485" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>3048</v>
       </c>
@@ -36363,7 +36381,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="486" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>3054</v>
       </c>
@@ -36412,7 +36430,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="487" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>3061</v>
       </c>
@@ -36462,7 +36480,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="488" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>3067</v>
       </c>
@@ -36513,7 +36531,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="489" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>3073</v>
       </c>
@@ -36564,7 +36582,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="490" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>3078</v>
       </c>
@@ -36614,7 +36632,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="491" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>3085</v>
       </c>
@@ -36665,7 +36683,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="492" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>3091</v>
       </c>
@@ -36716,7 +36734,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="493" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>3096</v>
       </c>
@@ -36767,7 +36785,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="494" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>3101</v>
       </c>
@@ -36818,7 +36836,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="495" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>3107</v>
       </c>
@@ -36868,7 +36886,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="496" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>3115</v>
       </c>
@@ -36921,7 +36939,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="497" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>3121</v>
       </c>
@@ -36972,7 +36990,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="498" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>3125</v>
       </c>
@@ -37022,7 +37040,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="499" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>3131</v>
       </c>
@@ -37072,7 +37090,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="500" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>3137</v>
       </c>
@@ -37122,7 +37140,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="501" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>3144</v>
       </c>
@@ -37172,7 +37190,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="502" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>3150</v>
       </c>
@@ -37222,7 +37240,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="503" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>3156</v>
       </c>
@@ -37275,7 +37293,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="504" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>3161</v>
       </c>
@@ -37328,7 +37346,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="505" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>3171</v>
       </c>
@@ -37380,7 +37398,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="506" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>3176</v>
       </c>
@@ -37433,7 +37451,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="507" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>3185</v>
       </c>
@@ -37480,7 +37498,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="508" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>3192</v>
       </c>
@@ -37524,7 +37542,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="509" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>3198</v>
       </c>
@@ -37568,7 +37586,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="510" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>3203</v>
       </c>
@@ -37614,7 +37632,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="511" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>3207</v>
       </c>
@@ -37652,7 +37670,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="512" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>3211</v>
       </c>
@@ -37702,7 +37720,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="513" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>3217</v>
       </c>
@@ -37747,7 +37765,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="514" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>3222</v>
       </c>
@@ -37788,7 +37806,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="515" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>3228</v>
       </c>
@@ -37833,7 +37851,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="516" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>3233</v>
       </c>
@@ -37877,7 +37895,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="517" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>3238</v>
       </c>
@@ -37921,7 +37939,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="518" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>3243</v>
       </c>
@@ -37965,7 +37983,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="519" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>3248</v>
       </c>
@@ -38010,7 +38028,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="520" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>3253</v>
       </c>
@@ -38060,7 +38078,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="521" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>3259</v>
       </c>
@@ -38110,7 +38128,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="522" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>3264</v>
       </c>
@@ -38166,7 +38184,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>3491</v>
       </c>
@@ -38215,7 +38233,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>3504</v>
       </c>
@@ -38259,7 +38277,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>3509</v>
       </c>
@@ -38300,7 +38318,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>3511</v>
       </c>
@@ -38344,7 +38362,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>3516</v>
       </c>
@@ -38391,7 +38409,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>3519</v>
       </c>
@@ -38443,7 +38461,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>3524</v>
       </c>
@@ -38487,7 +38505,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>3525</v>
       </c>
@@ -38531,7 +38549,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>3540</v>
       </c>
@@ -38578,7 +38596,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>3544</v>
       </c>
@@ -38627,7 +38645,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>3550</v>
       </c>
@@ -38677,7 +38695,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12" t="s">
         <v>3585</v>
       </c>
@@ -38728,7 +38746,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12" t="s">
         <v>3586</v>
       </c>
@@ -38779,7 +38797,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12" t="s">
         <v>3587</v>
       </c>
@@ -38831,7 +38849,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12" t="s">
         <v>3588</v>
       </c>
@@ -38880,7 +38898,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12" t="s">
         <v>3589</v>
       </c>
@@ -38931,7 +38949,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12" t="s">
         <v>3590</v>
       </c>
@@ -38982,7 +39000,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12" t="s">
         <v>3591</v>
       </c>
@@ -39033,7 +39051,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12" t="s">
         <v>3592</v>
       </c>
@@ -39084,7 +39102,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12" t="s">
         <v>3593</v>
       </c>
@@ -39133,7 +39151,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12" t="s">
         <v>3594</v>
       </c>
@@ -39184,7 +39202,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12" t="s">
         <v>3595</v>
       </c>
@@ -39235,7 +39253,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12" t="s">
         <v>3596</v>
       </c>
@@ -39286,7 +39304,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12" t="s">
         <v>3597</v>
       </c>
@@ -39335,7 +39353,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
         <v>3598</v>
       </c>
@@ -39384,7 +39402,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12" t="s">
         <v>3599</v>
       </c>
@@ -39435,7 +39453,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12" t="s">
         <v>3600</v>
       </c>
@@ -39482,7 +39500,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12" t="s">
         <v>3601</v>
       </c>
@@ -39533,7 +39551,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12" t="s">
         <v>3602</v>
       </c>
@@ -39582,7 +39600,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12" t="s">
         <v>3603</v>
       </c>
@@ -39633,7 +39651,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12" t="s">
         <v>3604</v>
       </c>
@@ -39682,7 +39700,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12" t="s">
         <v>3605</v>
       </c>
@@ -39729,7 +39747,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12" t="s">
         <v>3606</v>
       </c>
@@ -39783,7 +39801,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12" t="s">
         <v>3620</v>
       </c>
@@ -39833,7 +39851,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12" t="s">
         <v>3634</v>
       </c>
@@ -39883,7 +39901,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12" t="s">
         <v>3639</v>
       </c>
@@ -39933,7 +39951,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12" t="s">
         <v>3663</v>
       </c>
@@ -39985,7 +40003,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12" t="s">
         <v>3682</v>
       </c>
@@ -40030,7 +40048,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12" t="s">
         <v>3702</v>
       </c>
@@ -40084,7 +40102,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12" t="s">
         <v>3703</v>
       </c>
@@ -40129,7 +40147,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12" t="s">
         <v>3704</v>
       </c>
@@ -40174,7 +40192,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12" t="s">
         <v>3705</v>
       </c>
@@ -40219,7 +40237,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12" t="s">
         <v>3706</v>
       </c>
@@ -40264,7 +40282,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12" t="s">
         <v>3707</v>
       </c>
@@ -40309,7 +40327,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12" t="s">
         <v>3733</v>
       </c>
@@ -40356,7 +40374,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12" t="s">
         <v>3742</v>
       </c>
@@ -40400,7 +40418,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12" t="s">
         <v>3752</v>
       </c>
@@ -40452,7 +40470,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12" t="s">
         <v>3773</v>
       </c>
@@ -40502,7 +40520,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12" t="s">
         <v>3781</v>
       </c>
@@ -40552,7 +40570,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12" t="s">
         <v>3783</v>
       </c>
@@ -40596,7 +40614,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12" t="s">
         <v>3811</v>
       </c>
@@ -40646,7 +40664,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12" t="s">
         <v>3823</v>
       </c>
@@ -40696,7 +40714,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12" t="s">
         <v>3826</v>
       </c>
@@ -40740,7 +40758,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12" t="s">
         <v>3832</v>
       </c>
@@ -40784,7 +40802,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12" t="s">
         <v>3845</v>
       </c>
@@ -40833,6 +40851,103 @@
       </c>
       <c r="R577" s="45"/>
       <c r="T577" s="25" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="12" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C578" s="3">
+        <v>4619</v>
+      </c>
+      <c r="E578" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F578" s="2" t="s">
+        <v>3906</v>
+      </c>
+      <c r="G578" s="2" t="s">
+        <v>3802</v>
+      </c>
+      <c r="H578" s="2" t="s">
+        <v>3802</v>
+      </c>
+      <c r="I578" s="2" t="s">
+        <v>3725</v>
+      </c>
+      <c r="J578" s="2" t="s">
+        <v>3805</v>
+      </c>
+      <c r="K578" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L578" s="2" t="s">
+        <v>3905</v>
+      </c>
+      <c r="M578" s="2" t="s">
+        <v>3801</v>
+      </c>
+      <c r="N578" s="9" t="s">
+        <v>3803</v>
+      </c>
+      <c r="Q578" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="T578" s="25" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="12" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>3721</v>
+      </c>
+      <c r="C579" s="3">
+        <v>3712</v>
+      </c>
+      <c r="E579" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F579" s="2" t="s">
+        <v>3724</v>
+      </c>
+      <c r="G579" s="2" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H579" s="2" t="s">
+        <v>3798</v>
+      </c>
+      <c r="I579" s="2" t="s">
+        <v>3725</v>
+      </c>
+      <c r="J579" s="2" t="s">
+        <v>3797</v>
+      </c>
+      <c r="K579" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L579" s="2" t="s">
+        <v>3908</v>
+      </c>
+      <c r="M579" s="2" t="s">
+        <v>3721</v>
+      </c>
+      <c r="N579" s="9" t="s">
+        <v>3796</v>
+      </c>
+      <c r="O579" s="19" t="s">
+        <v>3909</v>
+      </c>
+      <c r="Q579" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="T579" s="25" t="s">
         <v>3573</v>
       </c>
     </row>
@@ -41521,11 +41636,14 @@
     <hyperlink ref="O577" r:id="rId680" xr:uid="{AB0C783D-EA21-411D-BC7F-44F208E95187}"/>
     <hyperlink ref="N577" r:id="rId681" xr:uid="{BC2E31C9-ADD4-45CA-ACB6-06477A446689}"/>
     <hyperlink ref="O308" r:id="rId682" display="https://rbdigital.realbiblioteca.es/s/rbme/item/13689" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="N578" r:id="rId683" xr:uid="{84C6A98B-C8A3-492D-A30D-EABB6FEB2065}"/>
+    <hyperlink ref="N579" r:id="rId684" xr:uid="{5CBAD618-EFEF-4CA7-8090-715DDBADBFBD}"/>
+    <hyperlink ref="O579" r:id="rId685" xr:uid="{5826E8FF-95C7-43A7-9013-761CACC02F2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId683"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId686"/>
   <tableParts count="1">
-    <tablePart r:id="rId684"/>
+    <tablePart r:id="rId687"/>
   </tableParts>
 </worksheet>
 </file>
@@ -41533,26 +41651,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T56"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="66" style="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="31" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.42578125" style="1" customWidth="1"/>
     <col min="11" max="13" width="12" style="1" customWidth="1"/>
     <col min="14" max="14" width="77" style="1" customWidth="1"/>
     <col min="15" max="15" width="79" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="24.6640625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.33203125" style="1"/>
+    <col min="16" max="16" width="24.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -41608,7 +41726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>3271</v>
       </c>
@@ -41661,7 +41779,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41697,7 +41815,7 @@
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
     </row>
-    <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41739,7 +41857,7 @@
       <c r="Q4" s="32"/>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41781,7 +41899,7 @@
       <c r="Q5" s="32"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41829,7 +41947,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41875,7 +41993,7 @@
       <c r="Q7" s="32"/>
       <c r="R7" s="32"/>
     </row>
-    <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>3271</v>
       </c>
@@ -41932,7 +42050,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
         <v>3271</v>
       </c>
@@ -41978,7 +42096,7 @@
       <c r="Q9" s="32"/>
       <c r="R9" s="32"/>
     </row>
-    <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42024,7 +42142,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
     </row>
-    <row r="11" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42070,7 +42188,7 @@
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
     </row>
-    <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42106,7 +42224,7 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
     </row>
-    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42150,7 +42268,7 @@
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
     </row>
-    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42194,7 +42312,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
     </row>
-    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42246,7 +42364,7 @@
       </c>
       <c r="R15" s="32"/>
     </row>
-    <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42300,7 +42418,7 @@
       </c>
       <c r="R16" s="32"/>
     </row>
-    <row r="17" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42352,7 +42470,7 @@
       </c>
       <c r="R17" s="32"/>
     </row>
-    <row r="18" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42406,7 +42524,7 @@
       </c>
       <c r="R18" s="32"/>
     </row>
-    <row r="19" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42456,7 +42574,7 @@
       </c>
       <c r="R19" s="32"/>
     </row>
-    <row r="20" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42508,7 +42626,7 @@
       </c>
       <c r="R20" s="32"/>
     </row>
-    <row r="21" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42558,7 +42676,7 @@
       </c>
       <c r="R21" s="32"/>
     </row>
-    <row r="22" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42610,7 +42728,7 @@
       </c>
       <c r="R22" s="32"/>
     </row>
-    <row r="23" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42662,7 +42780,7 @@
       </c>
       <c r="R23" s="32"/>
     </row>
-    <row r="24" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42714,7 +42832,7 @@
       </c>
       <c r="R24" s="32"/>
     </row>
-    <row r="25" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42760,7 +42878,7 @@
       <c r="Q25" s="32"/>
       <c r="R25" s="32"/>
     </row>
-    <row r="26" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42802,7 +42920,7 @@
       <c r="Q26" s="32"/>
       <c r="R26" s="32"/>
     </row>
-    <row r="27" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42848,7 +42966,7 @@
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
     </row>
-    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42888,7 +43006,7 @@
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
     </row>
-    <row r="29" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
         <v>3271</v>
       </c>
@@ -42934,7 +43052,7 @@
       <c r="Q29" s="32"/>
       <c r="R29" s="32"/>
     </row>
-    <row r="30" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
         <v>1908</v>
       </c>
@@ -42982,7 +43100,7 @@
       <c r="Q30" s="32"/>
       <c r="R30" s="32"/>
     </row>
-    <row r="31" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43010,7 +43128,7 @@
       <c r="Q31" s="32"/>
       <c r="R31" s="32"/>
     </row>
-    <row r="32" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43042,7 +43160,7 @@
       </c>
       <c r="R32" s="32"/>
     </row>
-    <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43078,7 +43196,7 @@
       <c r="Q33" s="32"/>
       <c r="R33" s="32"/>
     </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43114,7 +43232,7 @@
       <c r="Q34" s="32"/>
       <c r="R34" s="32"/>
     </row>
-    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43162,7 +43280,7 @@
       </c>
       <c r="R35" s="32"/>
     </row>
-    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43208,7 +43326,7 @@
       </c>
       <c r="R36" s="32"/>
     </row>
-    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43256,7 +43374,7 @@
       </c>
       <c r="R37" s="32"/>
     </row>
-    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43300,7 +43418,7 @@
       </c>
       <c r="R38" s="32"/>
     </row>
-    <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43346,7 +43464,7 @@
       <c r="Q39" s="32"/>
       <c r="R39" s="32"/>
     </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43394,7 +43512,7 @@
         <v>3573</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43432,7 +43550,7 @@
       <c r="Q41" s="32"/>
       <c r="R41" s="32"/>
     </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
         <v>3271</v>
       </c>
@@ -43470,7 +43588,7 @@
       <c r="Q42" s="32"/>
       <c r="R42" s="32"/>
     </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56"/>
       <c r="B43" s="57" t="s">
         <v>3801</v>
@@ -43514,7 +43632,7 @@
       <c r="Q43" s="45"/>
       <c r="R43" s="45"/>
     </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
       <c r="B44" s="32" t="s">
         <v>3721</v>
@@ -43564,7 +43682,7 @@
       </c>
       <c r="R44" s="32"/>
     </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
       <c r="B45" s="32" t="s">
         <v>3722</v>
@@ -43614,7 +43732,7 @@
       </c>
       <c r="R45" s="32"/>
     </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45"/>
       <c r="B46" s="55" t="s">
         <v>3791</v>
@@ -43658,7 +43776,7 @@
       </c>
       <c r="R46" s="45"/>
     </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45"/>
       <c r="B47" s="55" t="s">
         <v>3792</v>
@@ -43702,7 +43820,7 @@
       </c>
       <c r="R47" s="45"/>
     </row>
-    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
       <c r="B48" s="45" t="s">
         <v>3741</v>
@@ -43752,10 +43870,10 @@
       <c r="Q48" s="45"/>
       <c r="R48" s="45"/>
     </row>
-    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
     </row>
-    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="45"/>
       <c r="B50" s="45" t="s">
         <v>3757</v>
@@ -43797,7 +43915,7 @@
       <c r="Q50" s="45"/>
       <c r="R50" s="45"/>
     </row>
-    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="45"/>
       <c r="B51" s="45" t="s">
         <v>3761</v>
@@ -43827,7 +43945,7 @@
       <c r="Q51" s="45"/>
       <c r="R51" s="45"/>
     </row>
-    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45"/>
       <c r="B52" s="45" t="s">
         <v>3762</v>
@@ -43857,7 +43975,7 @@
       <c r="Q52" s="45"/>
       <c r="R52" s="45"/>
     </row>
-    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="45"/>
       <c r="B53" s="53" t="s">
         <v>3763</v>
@@ -43887,7 +44005,7 @@
       <c r="Q53" s="45"/>
       <c r="R53" s="45"/>
     </row>
-    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="45"/>
       <c r="B54" s="45" t="s">
         <v>3764</v>
@@ -43917,7 +44035,7 @@
       <c r="Q54" s="45"/>
       <c r="R54" s="45"/>
     </row>
-    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="45"/>
       <c r="B55" s="1" t="s">
         <v>3838</v>
@@ -43935,7 +44053,7 @@
         <v>3839</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45"/>
     </row>
   </sheetData>
@@ -44029,16 +44147,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="26.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="26.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" style="60" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="60" customWidth="1"/>
-    <col min="5" max="16384" width="26.5546875" style="60"/>
+    <col min="1" max="1" width="34.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="60" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="60" customWidth="1"/>
+    <col min="5" max="16384" width="26.5703125" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
         <v>3612</v>
       </c>
@@ -44055,7 +44173,7 @@
         <v>3864</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="61" t="s">
         <v>3861</v>
       </c>
@@ -44069,7 +44187,7 @@
         <v>3865</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60" t="s">
         <v>3818</v>
       </c>
@@ -44086,7 +44204,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
         <v>3812</v>
       </c>
@@ -44100,7 +44218,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60" t="s">
         <v>3817</v>
       </c>
@@ -44114,7 +44232,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60" t="s">
         <v>3813</v>
       </c>
@@ -44128,7 +44246,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
         <v>3814</v>
       </c>
@@ -44142,7 +44260,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60" t="s">
         <v>3815</v>
       </c>
@@ -44156,7 +44274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
         <v>3816</v>
       </c>
@@ -44170,7 +44288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
         <v>3485</v>
       </c>
@@ -44181,7 +44299,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>3570</v>
       </c>
@@ -44192,7 +44310,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60" t="s">
         <v>3571</v>
       </c>
@@ -44203,7 +44321,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="s">
         <v>3572</v>
       </c>
@@ -44214,7 +44332,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="60" t="s">
         <v>3863</v>
       </c>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAEAD94-2606-42FF-889C-3DF03516E4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9920175-C160-4EAC-8B5E-518A1CDBC8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16770" yWindow="2370" windowWidth="18975" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8111" uniqueCount="3910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8139" uniqueCount="3926">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -11768,6 +11768,54 @@
   </si>
   <si>
     <t>https://bnedigital.bne.es/bd/card?id=9b5d09a9-718d-459c-b355-8ad474abf740</t>
+  </si>
+  <si>
+    <t>HSMS-0579</t>
+  </si>
+  <si>
+    <t>EH53</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>LJS 19</t>
+  </si>
+  <si>
+    <t>1553-06-16</t>
+  </si>
+  <si>
+    <t>https://colenda.library.upenn.edu/catalog/81431-p3n633</t>
+  </si>
+  <si>
+    <t>Pedro de la Torre</t>
+  </si>
+  <si>
+    <t>HSMS-0580</t>
+  </si>
+  <si>
+    <t>CUP</t>
+  </si>
+  <si>
+    <t>BG/8501(2)</t>
+  </si>
+  <si>
+    <t>1562-08-12</t>
+  </si>
+  <si>
+    <t>Santiago de Compostena</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>https://gredos.usal.es/handle/10366/19465</t>
+  </si>
+  <si>
+    <t>Luis de Paz</t>
   </si>
 </sst>
 </file>
@@ -12578,8 +12626,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T579" totalsRowShown="0">
-  <autoFilter ref="A1:T579" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T581" totalsRowShown="0">
+  <autoFilter ref="A1:T581" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -12829,7 +12877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T579"/>
+  <dimension ref="A1:T581"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -40948,6 +40996,94 @@
         <v>289</v>
       </c>
       <c r="T579" s="25" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="12" t="s">
+        <v>3910</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="E580" s="2" t="s">
+        <v>3913</v>
+      </c>
+      <c r="F580" s="2" t="s">
+        <v>3914</v>
+      </c>
+      <c r="G580" s="2" t="s">
+        <v>3915</v>
+      </c>
+      <c r="H580" s="2" t="s">
+        <v>3915</v>
+      </c>
+      <c r="I580" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J580" s="2" t="s">
+        <v>3917</v>
+      </c>
+      <c r="K580" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L580" s="2" t="s">
+        <v>3912</v>
+      </c>
+      <c r="M580" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="O580" s="19" t="s">
+        <v>3916</v>
+      </c>
+      <c r="Q580" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T580" s="25" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="12" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>3919</v>
+      </c>
+      <c r="E581" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F581" s="2" t="s">
+        <v>3920</v>
+      </c>
+      <c r="G581" s="2" t="s">
+        <v>3921</v>
+      </c>
+      <c r="H581" s="2" t="s">
+        <v>3921</v>
+      </c>
+      <c r="I581" s="2" t="s">
+        <v>3922</v>
+      </c>
+      <c r="J581" s="2" t="s">
+        <v>3925</v>
+      </c>
+      <c r="K581" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L581" s="2" t="s">
+        <v>3923</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>3919</v>
+      </c>
+      <c r="O581" s="19" t="s">
+        <v>3924</v>
+      </c>
+      <c r="Q581" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="T581" s="25" t="s">
         <v>3573</v>
       </c>
     </row>
@@ -41639,11 +41775,12 @@
     <hyperlink ref="N578" r:id="rId683" xr:uid="{84C6A98B-C8A3-492D-A30D-EABB6FEB2065}"/>
     <hyperlink ref="N579" r:id="rId684" xr:uid="{5CBAD618-EFEF-4CA7-8090-715DDBADBFBD}"/>
     <hyperlink ref="O579" r:id="rId685" xr:uid="{5826E8FF-95C7-43A7-9013-761CACC02F2A}"/>
+    <hyperlink ref="O581" r:id="rId686" xr:uid="{AFAF42FF-21F7-410C-B342-5325F4D2942E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId686"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId687"/>
   <tableParts count="1">
-    <tablePart r:id="rId687"/>
+    <tablePart r:id="rId688"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF702860-6A34-485A-B695-5571E3992B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834FC54-A73B-4A0D-A73A-6F16AF973643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8317" uniqueCount="3995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8318" uniqueCount="3996">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12023,6 +12023,9 @@
   </si>
   <si>
     <t>1548-02-20</t>
+  </si>
+  <si>
+    <t>https://luna.manchester.ac.uk/luna/servlet/detail/Manchester~20~20~70~231843</t>
   </si>
 </sst>
 </file>
@@ -12643,9 +12646,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -12854,6 +12854,9 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -12953,7 +12956,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviaturas HSMS"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -12968,27 +12971,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R61" totalsRowShown="0" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R61" totalsRowShown="0" dataDxfId="25">
   <autoFilter ref="A1:R61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -23103,7 +23106,9 @@
       <c r="N200" s="5" t="s">
         <v>1403</v>
       </c>
-      <c r="O200" s="5"/>
+      <c r="O200" s="9" t="s">
+        <v>3995</v>
+      </c>
       <c r="Q200" s="1" t="s">
         <v>1404</v>
       </c>
@@ -42417,11 +42422,12 @@
     <hyperlink ref="O586" r:id="rId692" xr:uid="{0E41DB0D-A7BB-4F0D-A6F7-B838FB4F83CA}"/>
     <hyperlink ref="O587" r:id="rId693" xr:uid="{6EFFE956-73E4-4041-AE81-18270142CACE}"/>
     <hyperlink ref="O588" r:id="rId694" xr:uid="{27FA91A2-A0A3-408B-AEE5-A437B11E4EFE}"/>
+    <hyperlink ref="O200" r:id="rId695" xr:uid="{E0E38542-7BD7-432F-8E02-3BE7332490AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId695"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId696"/>
   <tableParts count="1">
-    <tablePart r:id="rId696"/>
+    <tablePart r:id="rId697"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834FC54-A73B-4A0D-A73A-6F16AF973643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747115B2-B950-410A-982A-94E0AD4E0EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18675" yWindow="1515" windowWidth="21540" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8318" uniqueCount="3996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15974" uniqueCount="3998">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12026,6 +12026,12 @@
   </si>
   <si>
     <t>https://luna.manchester.ac.uk/luna/servlet/detail/Manchester~20~20~70~231843</t>
+  </si>
+  <si>
+    <t>https://www.google.com/books/edition/F%C3%A1bulas_de_Esopo/roiZZ8SkDZcC?hl=en&amp;gbpv=0</t>
+  </si>
+  <si>
+    <t>facsímil de la edición de la RAE de 1929</t>
   </si>
 </sst>
 </file>
@@ -28029,9 +28035,14 @@
       <c r="N301" s="5" t="s">
         <v>1989</v>
       </c>
-      <c r="O301" s="5"/>
+      <c r="O301" s="9" t="s">
+        <v>3996</v>
+      </c>
       <c r="Q301" s="1" t="s">
         <v>1404</v>
+      </c>
+      <c r="R301" s="1" t="s">
+        <v>3997</v>
       </c>
       <c r="T301" t="s">
         <v>30</v>
@@ -42423,11 +42434,12 @@
     <hyperlink ref="O587" r:id="rId693" xr:uid="{6EFFE956-73E4-4041-AE81-18270142CACE}"/>
     <hyperlink ref="O588" r:id="rId694" xr:uid="{27FA91A2-A0A3-408B-AEE5-A437B11E4EFE}"/>
     <hyperlink ref="O200" r:id="rId695" xr:uid="{E0E38542-7BD7-432F-8E02-3BE7332490AB}"/>
+    <hyperlink ref="O301" r:id="rId696" xr:uid="{E6D51A39-3ADA-4A56-B139-19C673495222}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId696"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId697"/>
   <tableParts count="1">
-    <tablePart r:id="rId697"/>
+    <tablePart r:id="rId698"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747115B2-B950-410A-982A-94E0AD4E0EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833FDAB2-8B86-4D8D-95EF-C179B49F6818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18675" yWindow="1515" windowWidth="21540" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15974" uniqueCount="3998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8334" uniqueCount="4003">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12032,6 +12032,21 @@
   </si>
   <si>
     <t>facsímil de la edición de la RAE de 1929</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/es/card?id=384d40c3-f904-4e37-be6b-1270a79cb05c</t>
+  </si>
+  <si>
+    <t>R/35563</t>
+  </si>
+  <si>
+    <t>1538</t>
+  </si>
+  <si>
+    <t>HSMS-0588</t>
+  </si>
+  <si>
+    <t>OBP</t>
   </si>
 </sst>
 </file>
@@ -12945,8 +12960,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T588" totalsRowShown="0">
-  <autoFilter ref="A1:T588" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T589" totalsRowShown="0">
+  <autoFilter ref="A1:T589" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13196,7 +13211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T588"/>
+  <dimension ref="A1:T589"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -41733,6 +41748,50 @@
         <v>123</v>
       </c>
       <c r="T588" s="25" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="12" t="s">
+        <v>4001</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>4002</v>
+      </c>
+      <c r="E589" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F589" s="2" t="s">
+        <v>3999</v>
+      </c>
+      <c r="G589" s="2" t="s">
+        <v>4000</v>
+      </c>
+      <c r="H589" s="2" t="s">
+        <v>4000</v>
+      </c>
+      <c r="I589" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J589" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K589" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L589" s="2" t="s">
+        <v>3645</v>
+      </c>
+      <c r="M589" s="2" t="s">
+        <v>4002</v>
+      </c>
+      <c r="O589" s="19" t="s">
+        <v>3998</v>
+      </c>
+      <c r="Q589" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T589" s="25" t="s">
         <v>3572</v>
       </c>
     </row>
@@ -42435,11 +42494,12 @@
     <hyperlink ref="O588" r:id="rId694" xr:uid="{27FA91A2-A0A3-408B-AEE5-A437B11E4EFE}"/>
     <hyperlink ref="O200" r:id="rId695" xr:uid="{E0E38542-7BD7-432F-8E02-3BE7332490AB}"/>
     <hyperlink ref="O301" r:id="rId696" xr:uid="{E6D51A39-3ADA-4A56-B139-19C673495222}"/>
+    <hyperlink ref="O589" r:id="rId697" xr:uid="{8E3B950A-60B6-4BD2-AF86-E74D5A995BD4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId697"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId698"/>
   <tableParts count="1">
-    <tablePart r:id="rId698"/>
+    <tablePart r:id="rId699"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833FDAB2-8B86-4D8D-95EF-C179B49F6818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467C1FDE-F638-4068-809F-39DDAAE7DD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8334" uniqueCount="4003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8348" uniqueCount="4007">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12047,6 +12047,18 @@
   </si>
   <si>
     <t>OBP</t>
+  </si>
+  <si>
+    <t>HSMS-0589</t>
+  </si>
+  <si>
+    <t>CBB</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/es/card?id=2a453201-3e5e-4d39-ab41-0dd741813628</t>
+  </si>
+  <si>
+    <t>R/9460</t>
   </si>
 </sst>
 </file>
@@ -12960,8 +12972,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T589" totalsRowShown="0">
-  <autoFilter ref="A1:T589" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T590" totalsRowShown="0">
+  <autoFilter ref="A1:T590" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13211,7 +13223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T589"/>
+  <dimension ref="A1:T590"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -41792,6 +41804,50 @@
         <v>123</v>
       </c>
       <c r="T589" s="25" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="12" t="s">
+        <v>4003</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>4004</v>
+      </c>
+      <c r="E590" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F590" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="G590" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="H590" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="I590" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J590" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="K590" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L590" s="2" t="s">
+        <v>3645</v>
+      </c>
+      <c r="M590" s="2" t="s">
+        <v>4004</v>
+      </c>
+      <c r="O590" s="19" t="s">
+        <v>4005</v>
+      </c>
+      <c r="Q590" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T590" s="25" t="s">
         <v>3572</v>
       </c>
     </row>
@@ -42495,11 +42551,12 @@
     <hyperlink ref="O200" r:id="rId695" xr:uid="{E0E38542-7BD7-432F-8E02-3BE7332490AB}"/>
     <hyperlink ref="O301" r:id="rId696" xr:uid="{E6D51A39-3ADA-4A56-B139-19C673495222}"/>
     <hyperlink ref="O589" r:id="rId697" xr:uid="{8E3B950A-60B6-4BD2-AF86-E74D5A995BD4}"/>
+    <hyperlink ref="O590" r:id="rId698" xr:uid="{9FA755FB-B909-43E2-A231-6E621B82B6BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId698"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId699"/>
   <tableParts count="1">
-    <tablePart r:id="rId699"/>
+    <tablePart r:id="rId700"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467C1FDE-F638-4068-809F-39DDAAE7DD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E815F00-EB91-4A0A-865B-F523222DA5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8348" uniqueCount="4007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8362" uniqueCount="4013">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12059,6 +12059,24 @@
   </si>
   <si>
     <t>R/9460</t>
+  </si>
+  <si>
+    <t>OCS</t>
+  </si>
+  <si>
+    <t>HSMS-0590</t>
+  </si>
+  <si>
+    <t>R/35649(2)</t>
+  </si>
+  <si>
+    <t>1552-02-12 ad quem</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/es/card?id=1a7bbf9e-8427-40f4-9fc4-b3f0c641518a</t>
   </si>
 </sst>
 </file>
@@ -12581,6 +12599,9 @@
   </cellStyles>
   <dxfs count="27">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -12887,9 +12908,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -12972,8 +12990,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T590" totalsRowShown="0">
-  <autoFilter ref="A1:T590" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T591" totalsRowShown="0">
+  <autoFilter ref="A1:T591" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -12989,7 +13007,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="0"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviaturas HSMS"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13004,41 +13022,41 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R61" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R61" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:R61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}" name="Table8" displayName="Table8" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}" name="Table8" displayName="Table8" ref="A1:E14" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:E14" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{70A807F1-6BCD-44E7-9513-FF3B08F2D7D7}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{44D567F9-5223-430C-941A-7D85888F8E2A}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{46719F1D-7223-4772-A29C-A44848DFC11B}" name="Column3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E2160431-E43E-45D5-8B20-49EC4CDBEDC8}" name="Column4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{95CA25D4-6F4C-4CFD-96E8-B64F999F9B75}" name="Column5" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{70A807F1-6BCD-44E7-9513-FF3B08F2D7D7}" name="Column1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{44D567F9-5223-430C-941A-7D85888F8E2A}" name="Column2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{46719F1D-7223-4772-A29C-A44848DFC11B}" name="Column3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{E2160431-E43E-45D5-8B20-49EC4CDBEDC8}" name="Column4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{95CA25D4-6F4C-4CFD-96E8-B64F999F9B75}" name="Column5" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13223,7 +13241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T590"/>
+  <dimension ref="A1:T591"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -41848,6 +41866,50 @@
         <v>123</v>
       </c>
       <c r="T590" s="25" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="12" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>4007</v>
+      </c>
+      <c r="E591" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F591" s="2" t="s">
+        <v>4009</v>
+      </c>
+      <c r="G591" s="2" t="s">
+        <v>4010</v>
+      </c>
+      <c r="H591" s="2" t="s">
+        <v>4010</v>
+      </c>
+      <c r="I591" s="2" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J591" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K591" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L591" s="2" t="s">
+        <v>4011</v>
+      </c>
+      <c r="M591" s="2" t="s">
+        <v>4007</v>
+      </c>
+      <c r="O591" s="19" t="s">
+        <v>4012</v>
+      </c>
+      <c r="Q591" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T591" s="25" t="s">
         <v>3572</v>
       </c>
     </row>
@@ -42552,11 +42614,12 @@
     <hyperlink ref="O301" r:id="rId696" xr:uid="{E6D51A39-3ADA-4A56-B139-19C673495222}"/>
     <hyperlink ref="O589" r:id="rId697" xr:uid="{8E3B950A-60B6-4BD2-AF86-E74D5A995BD4}"/>
     <hyperlink ref="O590" r:id="rId698" xr:uid="{9FA755FB-B909-43E2-A231-6E621B82B6BC}"/>
+    <hyperlink ref="O591" r:id="rId699" xr:uid="{EC81F8E4-8209-45C4-AC78-47B5116C1B07}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId699"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId700"/>
   <tableParts count="1">
-    <tablePart r:id="rId700"/>
+    <tablePart r:id="rId701"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E815F00-EB91-4A0A-865B-F523222DA5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679FDEEA-0EE8-4062-B340-F0DF8877B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8362" uniqueCount="4013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8365" uniqueCount="4016">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -10210,9 +10210,6 @@
     <t>1525-11-12</t>
   </si>
   <si>
-    <t>https://bdh.bne.es/bnesearch/detalle/bdh0000089942</t>
-  </si>
-  <si>
     <t>PEU</t>
   </si>
   <si>
@@ -12077,6 +12074,18 @@
   </si>
   <si>
     <t>https://bnedigital.bne.es/bd/es/card?id=1a7bbf9e-8427-40f4-9fc4-b3f0c641518a</t>
+  </si>
+  <si>
+    <t>HSMS-0591</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/card?id=8fb1a61b-d024-404b-b262-daf7da787a99</t>
+  </si>
+  <si>
+    <t>Susana Merillas Benito</t>
+  </si>
+  <si>
+    <t>51</t>
   </si>
 </sst>
 </file>
@@ -12599,9 +12608,6 @@
   </cellStyles>
   <dxfs count="27">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -12908,6 +12914,9 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -12990,8 +12999,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T591" totalsRowShown="0">
-  <autoFilter ref="A1:T591" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T592" totalsRowShown="0">
+  <autoFilter ref="A1:T592" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13007,7 +13016,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviaturas HSMS"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13022,41 +13031,41 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R61" totalsRowShown="0" dataDxfId="26">
-  <autoFilter ref="A1:R61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R60" totalsRowShown="0" dataDxfId="25">
+  <autoFilter ref="A1:R60" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}" name="Table8" displayName="Table8" ref="A1:E14" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}" name="Table8" displayName="Table8" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E14" xr:uid="{55C86FD9-298E-4F93-8176-0A5C737DD36C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{70A807F1-6BCD-44E7-9513-FF3B08F2D7D7}" name="Column1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{44D567F9-5223-430C-941A-7D85888F8E2A}" name="Column2" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{46719F1D-7223-4772-A29C-A44848DFC11B}" name="Column3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{E2160431-E43E-45D5-8B20-49EC4CDBEDC8}" name="Column4" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{95CA25D4-6F4C-4CFD-96E8-B64F999F9B75}" name="Column5" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{70A807F1-6BCD-44E7-9513-FF3B08F2D7D7}" name="Column1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{44D567F9-5223-430C-941A-7D85888F8E2A}" name="Column2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{46719F1D-7223-4772-A29C-A44848DFC11B}" name="Column3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E2160431-E43E-45D5-8B20-49EC4CDBEDC8}" name="Column4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{95CA25D4-6F4C-4CFD-96E8-B64F999F9B75}" name="Column5" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13241,7 +13250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T591"/>
+  <dimension ref="A1:T592"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14433,7 +14442,7 @@
         <v>205</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="T24" t="s">
         <v>30</v>
@@ -15709,7 +15718,7 @@
       </c>
       <c r="O50" s="5"/>
       <c r="Q50" s="1" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="T50" t="s">
         <v>30</v>
@@ -16205,7 +16214,7 @@
         <v>451</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="T60" t="s">
         <v>30</v>
@@ -16358,13 +16367,13 @@
         <v>470</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>471</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="T63" t="s">
         <v>30</v>
@@ -16851,7 +16860,7 @@
         <v>530</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="T73" t="s">
         <v>30</v>
@@ -17486,7 +17495,7 @@
         <v>623</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>617</v>
@@ -22278,7 +22287,7 @@
         <v>1284</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="T182" t="s">
         <v>30</v>
@@ -22614,7 +22623,7 @@
       </c>
       <c r="O189" s="5"/>
       <c r="Q189" s="1" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="T189" t="s">
         <v>30</v>
@@ -23005,7 +23014,7 @@
         <v>1384</v>
       </c>
       <c r="O197" s="5" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="Q197" s="1" t="s">
         <v>579</v>
@@ -23055,7 +23064,7 @@
         <v>1389</v>
       </c>
       <c r="O198" s="10" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="Q198" s="1" t="s">
         <v>1390</v>
@@ -23105,7 +23114,7 @@
         <v>1396</v>
       </c>
       <c r="O199" s="5" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="Q199" s="1" t="s">
         <v>1397</v>
@@ -23158,7 +23167,7 @@
         <v>1403</v>
       </c>
       <c r="O200" s="9" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="Q200" s="1" t="s">
         <v>1404</v>
@@ -23303,7 +23312,7 @@
         <v>1425</v>
       </c>
       <c r="Q203" s="1" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="T203" t="s">
         <v>30</v>
@@ -23347,7 +23356,7 @@
         <v>1430</v>
       </c>
       <c r="Q204" s="1" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>1431</v>
@@ -23488,7 +23497,7 @@
         <v>1443</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="T207" t="s">
         <v>30</v>
@@ -23687,7 +23696,7 @@
         <v>1469</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="T211" t="s">
         <v>30</v>
@@ -24182,7 +24191,7 @@
         <v>69</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>130</v>
@@ -24353,7 +24362,7 @@
         <v>1552</v>
       </c>
       <c r="P224" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q224" s="1" t="s">
         <v>1553</v>
@@ -24551,7 +24560,7 @@
         <v>1583</v>
       </c>
       <c r="O228" s="9" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="Q228" s="1" t="s">
         <v>123</v>
@@ -24601,7 +24610,7 @@
         <v>2107</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="Q229" s="1" t="s">
         <v>544</v>
@@ -24749,7 +24758,7 @@
         <v>1608</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="T232" t="s">
         <v>30</v>
@@ -25901,7 +25910,7 @@
         <v>1751</v>
       </c>
       <c r="Q256" s="1" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="R256" s="1" t="s">
         <v>1752</v>
@@ -26394,7 +26403,7 @@
         <v>1804</v>
       </c>
       <c r="O266" s="5" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="Q266" s="1" t="s">
         <v>579</v>
@@ -26441,7 +26450,7 @@
         <v>1807</v>
       </c>
       <c r="O267" s="5" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="Q267" s="1" t="s">
         <v>579</v>
@@ -26488,7 +26497,7 @@
         <v>1810</v>
       </c>
       <c r="O268" s="5" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="Q268" s="1" t="s">
         <v>579</v>
@@ -26537,7 +26546,7 @@
         <v>1816</v>
       </c>
       <c r="O269" s="5" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="Q269" s="1" t="s">
         <v>557</v>
@@ -26584,7 +26593,7 @@
         <v>1820</v>
       </c>
       <c r="O270" s="5" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="Q270" s="1" t="s">
         <v>557</v>
@@ -26679,7 +26688,7 @@
         <v>1830</v>
       </c>
       <c r="O272" s="5" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="Q272" s="1" t="s">
         <v>544</v>
@@ -26729,7 +26738,7 @@
         <v>1835</v>
       </c>
       <c r="O273" s="5" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="Q273" s="1" t="s">
         <v>557</v>
@@ -26824,7 +26833,7 @@
         <v>1846</v>
       </c>
       <c r="O275" s="5" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="Q275" s="1" t="s">
         <v>557</v>
@@ -26871,7 +26880,7 @@
         <v>1850</v>
       </c>
       <c r="O276" s="5" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="Q276" s="1" t="s">
         <v>73</v>
@@ -26969,7 +26978,7 @@
         <v>1862</v>
       </c>
       <c r="O278" s="5" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="Q278" s="1" t="s">
         <v>557</v>
@@ -27019,7 +27028,7 @@
         <v>1867</v>
       </c>
       <c r="O279" s="5" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="Q279" s="1" t="s">
         <v>557</v>
@@ -27066,7 +27075,7 @@
         <v>1872</v>
       </c>
       <c r="O280" s="5" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="Q280" s="1" t="s">
         <v>579</v>
@@ -27260,7 +27269,7 @@
         <v>1894</v>
       </c>
       <c r="O284" s="5" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="Q284" s="1" t="s">
         <v>579</v>
@@ -27404,7 +27413,7 @@
         <v>1913</v>
       </c>
       <c r="O287" s="5" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="Q287" s="1" t="s">
         <v>29</v>
@@ -27451,7 +27460,7 @@
         <v>1917</v>
       </c>
       <c r="O288" s="5" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="Q288" s="1" t="s">
         <v>1918</v>
@@ -27501,7 +27510,7 @@
         <v>1923</v>
       </c>
       <c r="O289" s="5" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="Q289" s="1" t="s">
         <v>544</v>
@@ -27596,7 +27605,7 @@
         <v>1935</v>
       </c>
       <c r="O291" s="5" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="Q291" s="1" t="s">
         <v>289</v>
@@ -27648,7 +27657,7 @@
         <v>1941</v>
       </c>
       <c r="O292" s="5" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="Q292" s="1" t="s">
         <v>1942</v>
@@ -27698,7 +27707,7 @@
         <v>1949</v>
       </c>
       <c r="O293" s="5" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="Q293" s="1" t="s">
         <v>29</v>
@@ -27745,10 +27754,10 @@
         <v>1953</v>
       </c>
       <c r="O294" s="5" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="Q294" s="1" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="R294" s="1" t="s">
         <v>769</v>
@@ -27840,7 +27849,7 @@
         <v>1961</v>
       </c>
       <c r="O296" s="5" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="Q296" s="1" t="s">
         <v>1681</v>
@@ -28028,7 +28037,7 @@
         <v>1982</v>
       </c>
       <c r="O300" s="5" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="Q300" s="1" t="s">
         <v>990</v>
@@ -28081,13 +28090,13 @@
         <v>1989</v>
       </c>
       <c r="O301" s="9" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="Q301" s="1" t="s">
         <v>1404</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="T301" t="s">
         <v>30</v>
@@ -28176,7 +28185,7 @@
         <v>1999</v>
       </c>
       <c r="O303" s="5" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="Q303" s="1" t="s">
         <v>29</v>
@@ -28223,7 +28232,7 @@
         <v>2004</v>
       </c>
       <c r="O304" s="5" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="Q304" s="1" t="s">
         <v>2005</v>
@@ -28318,7 +28327,7 @@
         <v>2015</v>
       </c>
       <c r="O306" s="5" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="Q306" s="1" t="s">
         <v>2016</v>
@@ -28413,7 +28422,7 @@
         <v>2027</v>
       </c>
       <c r="O308" s="5" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="Q308" s="1" t="s">
         <v>2028</v>
@@ -28460,7 +28469,7 @@
         <v>2032</v>
       </c>
       <c r="O309" s="5" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="Q309" s="1" t="s">
         <v>777</v>
@@ -28513,13 +28522,13 @@
         <v>2037</v>
       </c>
       <c r="O310" s="9" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="Q310" s="1" t="s">
         <v>123</v>
       </c>
       <c r="R310" s="1" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="T310" t="s">
         <v>30</v>
@@ -28563,7 +28572,7 @@
         <v>2042</v>
       </c>
       <c r="O311" s="5" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="Q311" s="1" t="s">
         <v>2043</v>
@@ -28613,7 +28622,7 @@
         <v>2048</v>
       </c>
       <c r="O312" s="5" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="Q312" s="1" t="s">
         <v>132</v>
@@ -28708,7 +28717,7 @@
         <v>2059</v>
       </c>
       <c r="O314" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="Q314" s="1" t="s">
         <v>1122</v>
@@ -28755,7 +28764,7 @@
         <v>2063</v>
       </c>
       <c r="O315" s="5" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="Q315" s="1" t="s">
         <v>29</v>
@@ -29048,7 +29057,7 @@
         <v>2095</v>
       </c>
       <c r="O321" s="5" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="Q321" s="1" t="s">
         <v>2096</v>
@@ -29086,7 +29095,7 @@
         <v>26</v>
       </c>
       <c r="L322" s="2" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="M322" s="2" t="s">
         <v>2098</v>
@@ -29095,7 +29104,7 @@
         <v>2100</v>
       </c>
       <c r="O322" s="5" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="Q322" s="1" t="s">
         <v>2101</v>
@@ -29579,7 +29588,7 @@
       </c>
       <c r="O332" s="5"/>
       <c r="Q332" s="1" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="R332" s="1" t="s">
         <v>2159</v>
@@ -29868,13 +29877,13 @@
         <v>2197</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
       <c r="I338" s="2" t="s">
         <v>197</v>
       </c>
       <c r="J338" s="2" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="K338" s="2" t="s">
         <v>47</v>
@@ -29989,7 +29998,7 @@
         <v>2213</v>
       </c>
       <c r="O340" s="5" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="Q340" s="1" t="s">
         <v>295</v>
@@ -30090,7 +30099,7 @@
         <v>2228</v>
       </c>
       <c r="O342" s="5" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="Q342" s="1" t="s">
         <v>2229</v>
@@ -30737,7 +30746,7 @@
         <v>2312</v>
       </c>
       <c r="Q355" s="1" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="T355" t="s">
         <v>30</v>
@@ -31078,7 +31087,7 @@
         <v>2360</v>
       </c>
       <c r="O362" s="5" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="Q362" s="1" t="s">
         <v>2350</v>
@@ -32387,7 +32396,7 @@
         <v>2519</v>
       </c>
       <c r="Q390" s="1" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="T390" t="s">
         <v>30</v>
@@ -33015,7 +33024,7 @@
         <v>2582</v>
       </c>
       <c r="O405" s="5" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="Q405" s="1" t="s">
         <v>2350</v>
@@ -33309,7 +33318,7 @@
         <v>2620</v>
       </c>
       <c r="O411" s="5" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="Q411" s="1" t="s">
         <v>2343</v>
@@ -33784,7 +33793,7 @@
         <v>2676</v>
       </c>
       <c r="O422" s="5" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="Q422" s="1" t="s">
         <v>2640</v>
@@ -34049,7 +34058,7 @@
         <v>2704</v>
       </c>
       <c r="O428" s="19" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="Q428" s="1" t="s">
         <v>2640</v>
@@ -35070,7 +35079,7 @@
         <v>2836</v>
       </c>
       <c r="O449" s="5" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="Q449" s="1" t="s">
         <v>123</v>
@@ -35164,7 +35173,7 @@
         <v>2847</v>
       </c>
       <c r="O451" s="5" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="Q451" s="1" t="s">
         <v>2739</v>
@@ -36400,7 +36409,7 @@
         <v>2998</v>
       </c>
       <c r="Q477" s="1" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="T477" t="s">
         <v>1133</v>
@@ -37144,7 +37153,7 @@
         <v>3094</v>
       </c>
       <c r="O492" s="5" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="Q492" s="1" t="s">
         <v>289</v>
@@ -37195,7 +37204,7 @@
         <v>3099</v>
       </c>
       <c r="O493" s="5" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="Q493" s="1" t="s">
         <v>123</v>
@@ -37400,7 +37409,7 @@
         <v>3123</v>
       </c>
       <c r="O497" s="5" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="Q497" s="1" t="s">
         <v>289</v>
@@ -37807,7 +37816,7 @@
         <v>3174</v>
       </c>
       <c r="O505" s="5" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="P505" s="1"/>
       <c r="Q505" s="1" t="s">
@@ -38605,10 +38614,10 @@
     </row>
     <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
@@ -38616,7 +38625,7 @@
         <v>2937</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="G523" s="1">
         <v>1593</v>
@@ -38625,10 +38634,10 @@
         <v>1593</v>
       </c>
       <c r="I523" s="1" t="s">
+        <v>3486</v>
+      </c>
+      <c r="J523" s="1" t="s">
         <v>3487</v>
-      </c>
-      <c r="J523" s="1" t="s">
-        <v>3488</v>
       </c>
       <c r="K523" s="1" t="s">
         <v>61</v>
@@ -38637,13 +38646,13 @@
         <v>38</v>
       </c>
       <c r="M523" s="1" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="O523" s="19" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="P523" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q523" s="1" t="s">
         <v>123</v>
@@ -38654,22 +38663,22 @@
     </row>
     <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B524" s="2" t="s">
         <v>3503</v>
-      </c>
-      <c r="B524" s="2" t="s">
-        <v>3504</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F524" s="2" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="I524" s="2" t="s">
         <v>316</v>
@@ -38684,10 +38693,10 @@
         <v>2</v>
       </c>
       <c r="M524" s="2" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="O524" s="19" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="Q524" s="1" t="s">
         <v>289</v>
@@ -38698,27 +38707,27 @@
     </row>
     <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1" t="s">
+        <v>3499</v>
+      </c>
+      <c r="F525" s="1" t="s">
         <v>3500</v>
       </c>
-      <c r="F525" s="1" t="s">
+      <c r="G525" s="1" t="s">
+        <v>3508</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>3508</v>
+      </c>
+      <c r="I525" s="1" t="s">
         <v>3501</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>3509</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>3509</v>
-      </c>
-      <c r="I525" s="1" t="s">
-        <v>3502</v>
       </c>
       <c r="J525" s="1"/>
       <c r="K525" s="1" t="s">
@@ -38728,7 +38737,7 @@
         <v>13</v>
       </c>
       <c r="M525" s="1" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="Q525" s="1" t="s">
         <v>123</v>
@@ -38739,19 +38748,19 @@
     </row>
     <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>3509</v>
+      </c>
+      <c r="B526" s="2" t="s">
         <v>3510</v>
-      </c>
-      <c r="B526" s="2" t="s">
-        <v>3511</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="H526" s="2" t="s">
         <v>2632</v>
@@ -38769,10 +38778,10 @@
         <v>8</v>
       </c>
       <c r="M526" s="2" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="O526" s="19" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="Q526" s="1" t="s">
         <v>289</v>
@@ -38783,28 +38792,28 @@
     </row>
     <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="I527" s="2" t="s">
         <v>45</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="K527" s="2" t="s">
         <v>61</v>
@@ -38813,13 +38822,13 @@
         <v>54</v>
       </c>
       <c r="M527" s="2" t="s">
+        <v>3496</v>
+      </c>
+      <c r="O527" s="19" t="s">
         <v>3497</v>
       </c>
-      <c r="O527" s="19" t="s">
-        <v>3498</v>
-      </c>
       <c r="P527" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q527" s="1" t="s">
         <v>289</v>
@@ -38830,7 +38839,7 @@
     </row>
     <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>3360</v>
@@ -38870,7 +38879,7 @@
         <v>3362</v>
       </c>
       <c r="O528" s="5" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="P528" s="1"/>
       <c r="Q528" s="1" t="s">
@@ -38882,22 +38891,22 @@
     </row>
     <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G529" s="2" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="I529" s="2" t="s">
         <v>2383</v>
@@ -38912,10 +38921,10 @@
         <v>4</v>
       </c>
       <c r="M529" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="O529" s="19" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="Q529" s="1" t="s">
         <v>289</v>
@@ -38926,22 +38935,22 @@
     </row>
     <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F530" s="2" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="I530" s="2" t="s">
         <v>2383</v>
@@ -38956,10 +38965,10 @@
         <v>4</v>
       </c>
       <c r="M530" s="2" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="O530" s="19" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="Q530" s="1" t="s">
         <v>289</v>
@@ -38970,10 +38979,10 @@
     </row>
     <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="C531" s="1">
         <v>1141</v>
@@ -38983,7 +38992,7 @@
         <v>2156</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="G531" s="1">
         <v>1301</v>
@@ -39000,16 +39009,16 @@
         <v>65</v>
       </c>
       <c r="M531" s="1" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="N531" s="9" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="Q531" s="1" t="s">
         <v>2848</v>
       </c>
       <c r="R531" s="1" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="T531" t="s">
         <v>1133</v>
@@ -39017,10 +39026,10 @@
     </row>
     <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="C532" s="1">
         <v>1106</v>
@@ -39030,17 +39039,17 @@
         <v>2156</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="I532" s="1"/>
       <c r="J532" s="1" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>26</v>
@@ -39049,16 +39058,16 @@
         <v>152</v>
       </c>
       <c r="M532" s="1" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="N532" s="9" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="Q532" s="1" t="s">
         <v>2848</v>
       </c>
       <c r="R532" s="1" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="T532" t="s">
         <v>1133</v>
@@ -39066,10 +39075,10 @@
     </row>
     <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="C533" s="3">
         <v>1504</v>
@@ -39087,10 +39096,10 @@
         <v>3311</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="K533" s="2" t="s">
         <v>26</v>
@@ -39099,13 +39108,13 @@
         <v>154</v>
       </c>
       <c r="M533" s="2" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="N533" s="9" t="s">
         <v>3312</v>
       </c>
       <c r="O533" s="19" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="Q533" s="1" t="s">
         <v>2848</v>
@@ -39116,24 +39125,24 @@
     </row>
     <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="B534" s="22" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="C534" s="22"/>
       <c r="D534" s="22"/>
       <c r="E534" s="22" t="s">
+        <v>3407</v>
+      </c>
+      <c r="F534" s="22" t="s">
         <v>3408</v>
       </c>
-      <c r="F534" s="22" t="s">
+      <c r="G534" s="12" t="s">
         <v>3409</v>
       </c>
-      <c r="G534" s="12" t="s">
-        <v>3410</v>
-      </c>
       <c r="H534" s="12" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="I534" s="22" t="s">
         <v>45</v>
@@ -39148,43 +39157,43 @@
         <v>28</v>
       </c>
       <c r="M534" s="22" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="N534" s="22"/>
       <c r="O534" s="10" t="s">
+        <v>3410</v>
+      </c>
+      <c r="P534" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q534" s="18" t="s">
         <v>3411</v>
-      </c>
-      <c r="P534" t="s">
-        <v>3491</v>
-      </c>
-      <c r="Q534" s="18" t="s">
-        <v>3412</v>
       </c>
       <c r="R534" s="17"/>
       <c r="T534" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="B535" s="22" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="C535" s="22"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F535" s="22" t="s">
+        <v>3413</v>
+      </c>
+      <c r="G535" s="12" t="s">
         <v>3414</v>
       </c>
-      <c r="G535" s="12" t="s">
-        <v>3415</v>
-      </c>
       <c r="H535" s="12" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="I535" s="22" t="s">
         <v>45</v>
@@ -39196,68 +39205,68 @@
         <v>61</v>
       </c>
       <c r="L535" s="23" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="M535" s="22" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="N535" s="22"/>
       <c r="O535" s="9" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="P535" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q535" s="22" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="R535" s="22"/>
       <c r="T535" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="B536" s="22" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="C536" s="22"/>
       <c r="D536" s="22"/>
       <c r="E536" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F536" s="22" t="s">
+        <v>3417</v>
+      </c>
+      <c r="G536" s="12" t="s">
         <v>3418</v>
       </c>
-      <c r="G536" s="12" t="s">
-        <v>3419</v>
-      </c>
       <c r="H536" s="12" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="I536" s="22" t="s">
         <v>138</v>
       </c>
       <c r="J536" s="22" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="K536" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L536" s="23" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="M536" s="22" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="N536" s="22"/>
       <c r="O536" s="9" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="P536" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q536" s="22" t="s">
         <v>366</v>
@@ -39265,23 +39274,23 @@
       <c r="R536" s="22"/>
       <c r="S536" s="12"/>
       <c r="T536" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="B537" s="22" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="C537" s="22"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22" t="s">
+        <v>3421</v>
+      </c>
+      <c r="F537" s="22" t="s">
         <v>3422</v>
-      </c>
-      <c r="F537" s="22" t="s">
-        <v>3423</v>
       </c>
       <c r="G537" s="12">
         <v>1544</v>
@@ -39299,81 +39308,81 @@
         <v>26</v>
       </c>
       <c r="L537" s="23" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="M537" s="22" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="N537" s="22"/>
       <c r="O537" s="22"/>
       <c r="P537" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q537" s="22" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="R537" s="22"/>
       <c r="T537" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="B538" s="22" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="C538" s="22"/>
       <c r="D538" s="22"/>
       <c r="E538" s="22" t="s">
+        <v>3425</v>
+      </c>
+      <c r="F538" s="22" t="s">
         <v>3426</v>
       </c>
-      <c r="F538" s="22" t="s">
+      <c r="G538" s="12" t="s">
         <v>3427</v>
       </c>
-      <c r="G538" s="12" t="s">
-        <v>3428</v>
-      </c>
       <c r="H538" s="12" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="I538" s="22" t="s">
         <v>45</v>
       </c>
       <c r="J538" s="22" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="K538" s="22" t="s">
         <v>26</v>
       </c>
       <c r="L538" s="23" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="M538" s="22" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="N538" s="22"/>
       <c r="O538" s="9" t="s">
+        <v>3428</v>
+      </c>
+      <c r="P538" s="25" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q538" s="22" t="s">
         <v>3429</v>
-      </c>
-      <c r="P538" s="25" t="s">
-        <v>3491</v>
-      </c>
-      <c r="Q538" s="22" t="s">
-        <v>3430</v>
       </c>
       <c r="R538" s="22"/>
       <c r="T538" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="B539" s="22" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="C539" s="22"/>
       <c r="D539" s="22"/>
@@ -39381,47 +39390,47 @@
         <v>2204</v>
       </c>
       <c r="F539" s="22" t="s">
+        <v>3431</v>
+      </c>
+      <c r="G539" s="12" t="s">
+        <v>3659</v>
+      </c>
+      <c r="H539" s="12" t="s">
         <v>3432</v>
-      </c>
-      <c r="G539" s="12" t="s">
-        <v>3660</v>
-      </c>
-      <c r="H539" s="12" t="s">
-        <v>3433</v>
       </c>
       <c r="I539" s="22" t="s">
         <v>45</v>
       </c>
       <c r="J539" s="22" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="K539" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L539" s="23" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="M539" s="22" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="N539" s="22"/>
       <c r="O539" s="9" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="P539" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q539" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R539" s="22"/>
       <c r="T539" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="B540" s="22" t="s">
         <v>3288</v>
@@ -39429,7 +39438,7 @@
       <c r="C540" s="22"/>
       <c r="D540" s="22"/>
       <c r="E540" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F540" s="22" t="s">
         <v>3290</v>
@@ -39460,30 +39469,30 @@
         <v>3294</v>
       </c>
       <c r="P540" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q540" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R540" s="22"/>
       <c r="T540" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="B541" s="22" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="C541" s="22"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F541" s="22" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="G541" s="12">
         <v>1555</v>
@@ -39501,32 +39510,32 @@
         <v>61</v>
       </c>
       <c r="L541" s="23" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="M541" s="22" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="N541" s="22"/>
       <c r="O541" s="9" t="s">
+        <v>3436</v>
+      </c>
+      <c r="P541" s="25" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q541" s="22" t="s">
         <v>3437</v>
-      </c>
-      <c r="P541" s="25" t="s">
-        <v>3491</v>
-      </c>
-      <c r="Q541" s="22" t="s">
-        <v>3438</v>
       </c>
       <c r="R541" s="22"/>
       <c r="T541" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="B542" s="22" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="C542" s="22"/>
       <c r="D542" s="22"/>
@@ -39534,13 +39543,13 @@
         <v>433</v>
       </c>
       <c r="F542" s="12" t="s">
+        <v>3710</v>
+      </c>
+      <c r="G542" s="12" t="s">
         <v>3711</v>
       </c>
-      <c r="G542" s="12" t="s">
-        <v>3712</v>
-      </c>
       <c r="H542" s="12" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="I542" s="13" t="s">
         <v>230</v>
@@ -39552,14 +39561,14 @@
         <v>61</v>
       </c>
       <c r="L542" s="23" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="M542" s="22" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="N542" s="22"/>
       <c r="O542" s="9" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="P542" s="25"/>
       <c r="Q542" s="22" t="s">
@@ -39567,29 +39576,29 @@
       </c>
       <c r="R542" s="22"/>
       <c r="T542" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="B543" s="22" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="C543" s="22"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F543" s="22" t="s">
+        <v>3439</v>
+      </c>
+      <c r="G543" s="12" t="s">
         <v>3440</v>
       </c>
-      <c r="G543" s="12" t="s">
-        <v>3441</v>
-      </c>
       <c r="H543" s="12" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="I543" s="22" t="s">
         <v>138</v>
@@ -39601,49 +39610,49 @@
         <v>61</v>
       </c>
       <c r="L543" s="23" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="M543" s="22" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="N543" s="22"/>
       <c r="O543" s="9" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="P543" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q543" s="22" t="s">
         <v>2343</v>
       </c>
       <c r="R543" s="22"/>
       <c r="T543" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="B544" s="22" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="C544" s="22"/>
       <c r="D544" s="22"/>
       <c r="E544" s="22" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="F544" s="22" t="s">
+        <v>3442</v>
+      </c>
+      <c r="G544" s="12" t="s">
         <v>3443</v>
       </c>
-      <c r="G544" s="12" t="s">
+      <c r="H544" s="12" t="s">
+        <v>3443</v>
+      </c>
+      <c r="I544" s="22" t="s">
         <v>3444</v>
-      </c>
-      <c r="H544" s="12" t="s">
-        <v>3444</v>
-      </c>
-      <c r="I544" s="22" t="s">
-        <v>3445</v>
       </c>
       <c r="J544" s="22" t="s">
         <v>25</v>
@@ -39652,97 +39661,97 @@
         <v>26</v>
       </c>
       <c r="L544" s="23" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="M544" s="22" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="N544" s="22"/>
       <c r="O544" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="P544" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q544" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R544" s="22"/>
       <c r="T544" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B545" s="22" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="C545" s="22"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F545" s="22" t="s">
+        <v>3447</v>
+      </c>
+      <c r="G545" s="12" t="s">
         <v>3448</v>
       </c>
-      <c r="G545" s="12" t="s">
-        <v>3449</v>
-      </c>
       <c r="H545" s="12" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="I545" s="22" t="s">
         <v>1129</v>
       </c>
       <c r="J545" s="22" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="K545" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L545" s="23" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="M545" s="22" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="N545" s="22"/>
       <c r="O545" s="9" t="s">
+        <v>3449</v>
+      </c>
+      <c r="P545" s="25" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q545" s="22" t="s">
         <v>3450</v>
-      </c>
-      <c r="P545" s="25" t="s">
-        <v>3491</v>
-      </c>
-      <c r="Q545" s="22" t="s">
-        <v>3451</v>
       </c>
       <c r="R545" s="22"/>
       <c r="T545" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="B546" s="22" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="C546" s="22"/>
       <c r="D546" s="22"/>
       <c r="E546" s="22" t="s">
+        <v>3452</v>
+      </c>
+      <c r="F546" s="22" t="s">
         <v>3453</v>
       </c>
-      <c r="F546" s="22" t="s">
+      <c r="G546" s="12" t="s">
         <v>3454</v>
       </c>
-      <c r="G546" s="12" t="s">
-        <v>3455</v>
-      </c>
       <c r="H546" s="12" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="I546" s="22"/>
       <c r="J546" s="22" t="s">
@@ -39752,46 +39761,46 @@
         <v>26</v>
       </c>
       <c r="L546" s="23" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="M546" s="22" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="N546" s="22"/>
       <c r="O546" s="9" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="P546" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q546" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R546" s="22"/>
       <c r="T546" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="B547" s="22" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="C547" s="22"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="F547" s="22" t="s">
+        <v>3457</v>
+      </c>
+      <c r="G547" s="12" t="s">
+        <v>3622</v>
+      </c>
+      <c r="H547" s="12" t="s">
         <v>3458</v>
-      </c>
-      <c r="G547" s="12" t="s">
-        <v>3623</v>
-      </c>
-      <c r="H547" s="12" t="s">
-        <v>3459</v>
       </c>
       <c r="I547" s="22"/>
       <c r="J547" s="22" t="s">
@@ -39801,32 +39810,32 @@
         <v>26</v>
       </c>
       <c r="L547" s="23" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="M547" s="22" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="N547" s="22"/>
       <c r="O547" s="9" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="P547" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q547" s="22" t="s">
         <v>536</v>
       </c>
       <c r="R547" s="22"/>
       <c r="T547" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="B548" s="22" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="C548" s="22"/>
       <c r="D548" s="22"/>
@@ -39834,10 +39843,10 @@
         <v>1126</v>
       </c>
       <c r="F548" s="22" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="G548" s="12" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="H548" s="12">
         <v>1541</v>
@@ -39852,87 +39861,87 @@
         <v>61</v>
       </c>
       <c r="L548" s="23" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M548" s="22" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="N548" s="22"/>
       <c r="O548" s="9" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="P548" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q548" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R548" s="22"/>
       <c r="T548" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B549" s="22" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="C549" s="22"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="F549" s="22" t="s">
+        <v>3464</v>
+      </c>
+      <c r="G549" s="12" t="s">
+        <v>3623</v>
+      </c>
+      <c r="H549" s="12" t="s">
+        <v>3623</v>
+      </c>
+      <c r="I549" s="22" t="s">
         <v>3465</v>
-      </c>
-      <c r="G549" s="12" t="s">
-        <v>3624</v>
-      </c>
-      <c r="H549" s="12" t="s">
-        <v>3624</v>
-      </c>
-      <c r="I549" s="22" t="s">
-        <v>3466</v>
       </c>
       <c r="J549" s="22"/>
       <c r="K549" s="22" t="s">
         <v>26</v>
       </c>
       <c r="L549" s="23" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="M549" s="22" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="N549" s="22"/>
       <c r="O549" s="22"/>
       <c r="P549" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q549" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R549" s="22"/>
       <c r="T549" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="B550" s="22" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="C550" s="22"/>
       <c r="D550" s="22"/>
       <c r="E550" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F550" s="22" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="G550" s="12">
         <v>1552</v>
@@ -39944,52 +39953,52 @@
         <v>45</v>
       </c>
       <c r="J550" s="22" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="K550" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L550" s="23" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="M550" s="22" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="N550" s="22"/>
       <c r="O550" s="9" t="s">
+        <v>3468</v>
+      </c>
+      <c r="P550" s="25" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q550" s="22" t="s">
         <v>3469</v>
-      </c>
-      <c r="P550" s="25" t="s">
-        <v>3491</v>
-      </c>
-      <c r="Q550" s="22" t="s">
-        <v>3470</v>
       </c>
       <c r="R550" s="22"/>
       <c r="T550" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="B551" s="22" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="C551" s="22"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="F551" s="22" t="s">
+        <v>3471</v>
+      </c>
+      <c r="G551" s="12" t="s">
         <v>3472</v>
       </c>
-      <c r="G551" s="12" t="s">
-        <v>3473</v>
-      </c>
       <c r="H551" s="12" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="I551" s="22"/>
       <c r="J551" s="22" t="s">
@@ -39999,40 +40008,40 @@
         <v>26</v>
       </c>
       <c r="L551" s="23" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="M551" s="22" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="N551" s="22"/>
       <c r="O551" s="9" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="P551" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q551" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R551" s="22"/>
       <c r="T551" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="B552" s="22" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="C552" s="22"/>
       <c r="D552" s="22"/>
       <c r="E552" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F552" s="22" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="G552" s="12">
         <v>1534</v>
@@ -40044,43 +40053,43 @@
         <v>45</v>
       </c>
       <c r="J552" s="22" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="K552" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L552" s="23" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="M552" s="22" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="N552" s="22"/>
       <c r="O552" s="9" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="P552" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q552" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R552" s="22"/>
       <c r="T552" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="B553" s="22" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="C553" s="22"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="F553" s="22"/>
       <c r="G553" s="12">
@@ -40090,7 +40099,7 @@
         <v>1544</v>
       </c>
       <c r="I553" s="22" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="J553" s="22" t="s">
         <v>95</v>
@@ -40099,32 +40108,32 @@
         <v>61</v>
       </c>
       <c r="L553" s="23" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="M553" s="22" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="N553" s="22"/>
       <c r="O553" s="9" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="P553" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q553" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R553" s="22"/>
       <c r="T553" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="B554" s="22" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="C554" s="22"/>
       <c r="D554" s="22"/>
@@ -40132,13 +40141,13 @@
         <v>2216</v>
       </c>
       <c r="F554" s="22" t="s">
+        <v>3574</v>
+      </c>
+      <c r="G554" s="12" t="s">
         <v>3575</v>
       </c>
-      <c r="G554" s="12" t="s">
-        <v>3576</v>
-      </c>
       <c r="H554" s="12" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="I554" s="22"/>
       <c r="J554" s="22"/>
@@ -40149,29 +40158,29 @@
         <v>58</v>
       </c>
       <c r="M554" s="22" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="N554" s="22"/>
       <c r="O554" s="19" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="P554" s="25" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q554" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R554" s="22"/>
       <c r="T554" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="C555" s="1">
         <v>2393</v>
@@ -40181,13 +40190,13 @@
         <v>433</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>230</v>
@@ -40202,13 +40211,13 @@
         <v>78</v>
       </c>
       <c r="M555" s="1" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="N555" s="9" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="O555" s="19" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="P555"/>
       <c r="Q555" s="1" t="s">
@@ -40217,15 +40226,15 @@
       <c r="R555" s="1"/>
       <c r="S555" s="1"/>
       <c r="T555" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="C556" s="3">
         <v>1754</v>
@@ -40234,13 +40243,13 @@
         <v>1618</v>
       </c>
       <c r="F556" s="2" t="s">
+        <v>3634</v>
+      </c>
+      <c r="G556" s="2" t="s">
         <v>3635</v>
       </c>
-      <c r="G556" s="2" t="s">
-        <v>3636</v>
-      </c>
       <c r="H556" s="2" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I556" s="2" t="s">
         <v>2383</v>
@@ -40252,30 +40261,30 @@
         <v>47</v>
       </c>
       <c r="L556" s="2" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="M556" s="2" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="N556" s="9" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="O556" s="19" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="Q556" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T556" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="C557" s="3">
         <v>1749</v>
@@ -40284,13 +40293,13 @@
         <v>433</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="G557" s="2" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="I557" s="2" t="s">
         <v>230</v>
@@ -40302,30 +40311,30 @@
         <v>47</v>
       </c>
       <c r="L557" s="2" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M557" s="2" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="N557" s="9" t="s">
+        <v>3647</v>
+      </c>
+      <c r="O557" s="19" t="s">
         <v>3648</v>
-      </c>
-      <c r="O557" s="19" t="s">
-        <v>3649</v>
       </c>
       <c r="Q557" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T557" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="C558" s="3">
         <v>4179</v>
@@ -40334,7 +40343,7 @@
         <v>1618</v>
       </c>
       <c r="F558" s="2" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="G558" s="2" t="s">
         <v>3117</v>
@@ -40352,40 +40361,40 @@
         <v>47</v>
       </c>
       <c r="L558" s="2" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="M558" s="2" t="s">
+        <v>3640</v>
+      </c>
+      <c r="N558" s="9" t="s">
+        <v>3646</v>
+      </c>
+      <c r="O558" s="19" t="s">
         <v>3641</v>
-      </c>
-      <c r="N558" s="9" t="s">
-        <v>3647</v>
-      </c>
-      <c r="O558" s="19" t="s">
-        <v>3642</v>
       </c>
       <c r="Q558" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T558" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="B559" s="13" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="C559" s="14">
         <v>2042</v>
       </c>
       <c r="D559" s="15"/>
       <c r="E559" s="13" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="F559" s="13" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="G559" s="13" t="s">
         <v>3063</v>
@@ -40403,38 +40412,38 @@
         <v>130</v>
       </c>
       <c r="L559" s="13" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="M559" s="13" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="N559" s="19" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="O559" s="19" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="P559" s="25"/>
       <c r="Q559" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T559" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="B560" s="12" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="C560" s="14"/>
       <c r="E560" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F560" s="12" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="G560" s="12">
         <v>1555</v>
@@ -40455,24 +40464,24 @@
         <v>4</v>
       </c>
       <c r="M560" s="12" t="s">
+        <v>3666</v>
+      </c>
+      <c r="O560" s="19" t="s">
         <v>3667</v>
-      </c>
-      <c r="O560" s="19" t="s">
-        <v>3668</v>
       </c>
       <c r="Q560" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T560" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="B561" s="12" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="C561" s="12">
         <v>3887</v>
@@ -40484,10 +40493,10 @@
         <v>433</v>
       </c>
       <c r="F561" s="12" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="G561" s="12" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
       <c r="H561" s="25" t="s">
         <v>2198</v>
@@ -40496,7 +40505,7 @@
         <v>197</v>
       </c>
       <c r="J561" s="13" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="K561" s="13" t="s">
         <v>47</v>
@@ -40505,34 +40514,34 @@
         <v>10</v>
       </c>
       <c r="M561" s="12" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="N561" s="9" t="s">
         <v>2199</v>
       </c>
       <c r="O561" s="19" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="P561" s="25"/>
       <c r="Q561" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T561" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="B562" s="12" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="E562" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F562" s="12" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="G562" s="12">
         <v>1531</v>
@@ -40553,37 +40562,37 @@
         <v>2</v>
       </c>
       <c r="M562" s="12" t="s">
+        <v>3687</v>
+      </c>
+      <c r="O562" s="19" t="s">
         <v>3688</v>
-      </c>
-      <c r="O562" s="19" t="s">
-        <v>3689</v>
       </c>
       <c r="P562" s="25"/>
       <c r="Q562" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T562" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="B563" s="12" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="E563" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F563" s="12" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="G563" s="12" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="H563" s="12" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="I563" s="13" t="s">
         <v>2383</v>
@@ -40598,31 +40607,31 @@
         <v>2</v>
       </c>
       <c r="M563" s="12" t="s">
+        <v>3681</v>
+      </c>
+      <c r="O563" s="19" t="s">
         <v>3682</v>
-      </c>
-      <c r="O563" s="19" t="s">
-        <v>3683</v>
       </c>
       <c r="P563" s="25"/>
       <c r="Q563" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T563" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="B564" s="12" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="E564" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F564" s="12" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="G564" s="12">
         <v>1577</v>
@@ -40643,43 +40652,43 @@
         <v>2</v>
       </c>
       <c r="M564" s="12" t="s">
+        <v>3685</v>
+      </c>
+      <c r="O564" s="19" t="s">
         <v>3686</v>
-      </c>
-      <c r="O564" s="19" t="s">
-        <v>3687</v>
       </c>
       <c r="P564" s="25"/>
       <c r="Q564" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T564" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="B565" s="12" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
       <c r="E565" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F565" s="12" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="G565" s="12" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="H565" s="12" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="I565" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J565" s="12" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="K565" s="12" t="s">
         <v>61</v>
@@ -40688,37 +40697,37 @@
         <v>2</v>
       </c>
       <c r="M565" s="12" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
       <c r="O565" s="19" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="P565" s="25"/>
       <c r="Q565" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T565" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="B566" s="12" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="E566" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F566" s="12" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="G566" s="12" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="H566" s="12" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="I566" s="13" t="s">
         <v>2383</v>
@@ -40733,25 +40742,25 @@
         <v>4</v>
       </c>
       <c r="M566" s="12" t="s">
+        <v>3689</v>
+      </c>
+      <c r="O566" s="19" t="s">
         <v>3690</v>
-      </c>
-      <c r="O566" s="19" t="s">
-        <v>3691</v>
       </c>
       <c r="P566" s="25"/>
       <c r="Q566" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T566" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="B567" s="47" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="C567" s="45"/>
       <c r="D567" s="45"/>
@@ -40759,13 +40768,13 @@
         <v>433</v>
       </c>
       <c r="F567" s="46" t="s">
+        <v>3728</v>
+      </c>
+      <c r="G567" s="47" t="s">
         <v>3729</v>
       </c>
-      <c r="G567" s="47" t="s">
-        <v>3730</v>
-      </c>
       <c r="H567" s="47" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
       <c r="I567" s="2" t="s">
         <v>2383</v>
@@ -40780,22 +40789,22 @@
         <v>8</v>
       </c>
       <c r="M567" s="47" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="N567" s="45"/>
       <c r="O567" s="19" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="Q567" s="47" t="s">
         <v>123</v>
       </c>
       <c r="T567" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>1146</v>
@@ -40804,13 +40813,13 @@
         <v>2216</v>
       </c>
       <c r="F568" s="2" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="G568" s="2" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="H568" s="2" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="I568" s="2" t="s">
         <v>419</v>
@@ -40822,27 +40831,27 @@
         <v>61</v>
       </c>
       <c r="L568" s="2" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="M568" s="2" t="s">
         <v>1146</v>
       </c>
       <c r="O568" s="19" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="Q568" s="47" t="s">
         <v>123</v>
       </c>
       <c r="T568" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="B569" s="45" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="C569" s="45">
         <v>1803</v>
@@ -40852,7 +40861,7 @@
         <v>433</v>
       </c>
       <c r="F569" s="45" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="G569" s="48" t="s">
         <v>2607</v>
@@ -40873,28 +40882,28 @@
         <v>82</v>
       </c>
       <c r="M569" s="45" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="N569" s="9" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="O569" s="19" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
       <c r="Q569" s="32" t="s">
         <v>123</v>
       </c>
       <c r="R569" s="45"/>
       <c r="T569" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="C570" s="3">
         <v>2528</v>
@@ -40903,48 +40912,48 @@
         <v>1748</v>
       </c>
       <c r="F570" s="2" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="G570" s="2" t="s">
+        <v>3774</v>
+      </c>
+      <c r="H570" s="2" t="s">
         <v>3775</v>
-      </c>
-      <c r="H570" s="2" t="s">
-        <v>3776</v>
       </c>
       <c r="I570" s="2" t="s">
         <v>2226</v>
       </c>
       <c r="J570" s="2" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="K570" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L570" s="2" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="M570" s="2" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="N570" s="9" t="s">
+        <v>3777</v>
+      </c>
+      <c r="O570" s="19" t="s">
         <v>3778</v>
-      </c>
-      <c r="O570" s="19" t="s">
-        <v>3779</v>
       </c>
       <c r="Q570" s="32" t="s">
         <v>123</v>
       </c>
       <c r="T570" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="B571" s="32" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="C571" s="32">
         <v>1485</v>
@@ -40954,7 +40963,7 @@
         <v>3177</v>
       </c>
       <c r="F571" s="32" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="G571" s="32" t="s">
         <v>1206</v>
@@ -40972,13 +40981,13 @@
         <v>47</v>
       </c>
       <c r="L571" s="35" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="M571" s="32" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="N571" s="34" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="O571" s="32"/>
       <c r="Q571" s="32" t="s">
@@ -40986,15 +40995,15 @@
       </c>
       <c r="R571" s="32"/>
       <c r="T571" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B572" s="2" t="s">
         <v>3782</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>3783</v>
       </c>
       <c r="C572" s="3">
         <v>1454</v>
@@ -41003,7 +41012,7 @@
         <v>2280</v>
       </c>
       <c r="F572" s="2" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="G572" s="2" t="s">
         <v>650</v>
@@ -41015,46 +41024,46 @@
         <v>26</v>
       </c>
       <c r="L572" s="2" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="M572" s="2" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="N572" s="9" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="O572" s="19" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="Q572" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T572" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="B573" s="51" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="C573" s="45">
         <v>2983</v>
       </c>
       <c r="D573" s="45"/>
       <c r="E573" s="58" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="F573" s="45">
         <v>6721</v>
       </c>
       <c r="G573" s="50" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="H573" s="50" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="I573" s="50" t="s">
         <v>197</v>
@@ -41069,10 +41078,10 @@
         <v>129</v>
       </c>
       <c r="M573" s="51" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="N573" s="9" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="O573" s="45"/>
       <c r="Q573" s="32" t="s">
@@ -41080,15 +41089,15 @@
       </c>
       <c r="R573" s="45"/>
       <c r="T573" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12" t="s">
+        <v>3821</v>
+      </c>
+      <c r="B574" s="62" t="s">
         <v>3822</v>
-      </c>
-      <c r="B574" s="62" t="s">
-        <v>3823</v>
       </c>
       <c r="C574" s="45">
         <v>3345</v>
@@ -41098,13 +41107,13 @@
         <v>3177</v>
       </c>
       <c r="F574" s="32" t="s">
+        <v>3818</v>
+      </c>
+      <c r="G574" s="61" t="s">
         <v>3819</v>
       </c>
-      <c r="G574" s="61" t="s">
-        <v>3820</v>
-      </c>
       <c r="H574" s="61" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="I574" s="61" t="s">
         <v>316</v>
@@ -41119,10 +41128,10 @@
         <v>64</v>
       </c>
       <c r="M574" s="62" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="N574" s="9" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="O574" s="45"/>
       <c r="Q574" s="61" t="s">
@@ -41130,24 +41139,24 @@
       </c>
       <c r="R574" s="45"/>
       <c r="T574" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F575" s="2" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="G575" s="2" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="H575" s="2" t="s">
         <v>2632</v>
@@ -41156,45 +41165,45 @@
         <v>197</v>
       </c>
       <c r="J575" s="2" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="K575" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L575" s="2" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="M575" s="2" t="s">
+        <v>3828</v>
+      </c>
+      <c r="O575" s="19" t="s">
         <v>3829</v>
-      </c>
-      <c r="O575" s="19" t="s">
-        <v>3830</v>
       </c>
       <c r="Q575" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T575" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B576" s="2" t="s">
         <v>3831</v>
-      </c>
-      <c r="B576" s="2" t="s">
-        <v>3832</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F576" s="2" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="G576" s="2" t="s">
+        <v>3834</v>
+      </c>
+      <c r="H576" s="2" t="s">
         <v>3835</v>
-      </c>
-      <c r="H576" s="2" t="s">
-        <v>3836</v>
       </c>
       <c r="I576" s="2" t="s">
         <v>197</v>
@@ -41206,27 +41215,27 @@
         <v>47</v>
       </c>
       <c r="L576" s="2" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="M576" s="2" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="O576" s="19" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="Q576" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T576" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="B577" s="45" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="C577" s="45">
         <v>1867</v>
@@ -41236,7 +41245,7 @@
         <v>433</v>
       </c>
       <c r="F577" s="63" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="G577" s="63" t="s">
         <v>1467</v>
@@ -41257,28 +41266,28 @@
         <v>98</v>
       </c>
       <c r="M577" s="63" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="N577" s="9" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="O577" s="19" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="Q577" s="63" t="s">
         <v>123</v>
       </c>
       <c r="R577" s="45"/>
       <c r="T577" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="C578" s="3">
         <v>4619</v>
@@ -41287,45 +41296,45 @@
         <v>1618</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="G578" s="2" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="I578" s="2" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="J578" s="2" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="K578" s="2" t="s">
         <v>130</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="M578" s="2" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="N578" s="9" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="Q578" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T578" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="C579" s="3">
         <v>3712</v>
@@ -41334,148 +41343,148 @@
         <v>433</v>
       </c>
       <c r="F579" s="2" t="s">
+        <v>3722</v>
+      </c>
+      <c r="G579" s="2" t="s">
+        <v>3796</v>
+      </c>
+      <c r="H579" s="2" t="s">
+        <v>3796</v>
+      </c>
+      <c r="I579" s="2" t="s">
         <v>3723</v>
       </c>
-      <c r="G579" s="2" t="s">
-        <v>3797</v>
-      </c>
-      <c r="H579" s="2" t="s">
-        <v>3797</v>
-      </c>
-      <c r="I579" s="2" t="s">
-        <v>3724</v>
-      </c>
       <c r="J579" s="2" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="K579" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L579" s="2" t="s">
+        <v>3906</v>
+      </c>
+      <c r="M579" s="2" t="s">
+        <v>3719</v>
+      </c>
+      <c r="N579" s="9" t="s">
+        <v>3794</v>
+      </c>
+      <c r="O579" s="19" t="s">
         <v>3907</v>
-      </c>
-      <c r="M579" s="2" t="s">
-        <v>3720</v>
-      </c>
-      <c r="N579" s="9" t="s">
-        <v>3795</v>
-      </c>
-      <c r="O579" s="19" t="s">
-        <v>3908</v>
       </c>
       <c r="Q579" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T579" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12" t="s">
+        <v>3908</v>
+      </c>
+      <c r="B580" s="2" t="s">
         <v>3909</v>
       </c>
-      <c r="B580" s="2" t="s">
-        <v>3910</v>
-      </c>
       <c r="E580" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="F580" s="2" t="s">
         <v>3912</v>
       </c>
-      <c r="F580" s="2" t="s">
+      <c r="G580" s="2" t="s">
         <v>3913</v>
       </c>
-      <c r="G580" s="2" t="s">
-        <v>3914</v>
-      </c>
       <c r="H580" s="2" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="I580" s="2" t="s">
         <v>87</v>
       </c>
       <c r="J580" s="2" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="K580" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L580" s="2" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="M580" s="2" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="O580" s="19" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="Q580" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T580" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12" t="s">
+        <v>3916</v>
+      </c>
+      <c r="B581" s="2" t="s">
         <v>3917</v>
-      </c>
-      <c r="B581" s="2" t="s">
-        <v>3918</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F581" s="2" t="s">
+        <v>3918</v>
+      </c>
+      <c r="G581" s="2" t="s">
         <v>3919</v>
       </c>
-      <c r="G581" s="2" t="s">
+      <c r="H581" s="2" t="s">
+        <v>3919</v>
+      </c>
+      <c r="I581" s="2" t="s">
         <v>3920</v>
       </c>
-      <c r="H581" s="2" t="s">
-        <v>3920</v>
-      </c>
-      <c r="I581" s="2" t="s">
-        <v>3921</v>
-      </c>
       <c r="J581" s="2" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="K581" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L581" s="2" t="s">
+        <v>3921</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>3917</v>
+      </c>
+      <c r="O581" s="19" t="s">
         <v>3922</v>
-      </c>
-      <c r="M581" s="2" t="s">
-        <v>3918</v>
-      </c>
-      <c r="O581" s="19" t="s">
-        <v>3923</v>
       </c>
       <c r="Q581" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T581" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B582" s="2" t="s">
         <v>3925</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="E582" s="2" t="s">
         <v>3926</v>
       </c>
-      <c r="E582" s="2" t="s">
+      <c r="F582" s="2" t="s">
+        <v>3930</v>
+      </c>
+      <c r="G582" s="2" t="s">
         <v>3927</v>
       </c>
-      <c r="F582" s="2" t="s">
-        <v>3931</v>
-      </c>
-      <c r="G582" s="2" t="s">
-        <v>3928</v>
-      </c>
       <c r="H582" s="2" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="I582" s="2" t="s">
         <v>230</v>
@@ -41487,39 +41496,39 @@
         <v>61</v>
       </c>
       <c r="L582" s="2" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="M582" s="2" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="O582" s="19" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="Q582" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T582" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F583" s="2" t="s">
+        <v>3939</v>
+      </c>
+      <c r="G583" s="2" t="s">
         <v>3940</v>
       </c>
-      <c r="G583" s="2" t="s">
-        <v>3941</v>
-      </c>
       <c r="H583" s="2" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="I583" s="2" t="s">
         <v>138</v>
@@ -41531,27 +41540,27 @@
         <v>61</v>
       </c>
       <c r="L583" s="2" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="M583" s="2" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="O583" s="19" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="Q583" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T583" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="B584" s="65" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="C584" s="45"/>
       <c r="D584" s="45"/>
@@ -41559,13 +41568,13 @@
         <v>1748</v>
       </c>
       <c r="F584" s="66" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="G584" s="66" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="H584" s="66" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="I584" s="65" t="s">
         <v>316</v>
@@ -41577,28 +41586,28 @@
         <v>61</v>
       </c>
       <c r="L584" s="69" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="M584" s="65" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="N584" s="45"/>
       <c r="O584" s="19" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="Q584" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T584" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="B585" s="71" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="C585" s="71"/>
       <c r="D585" s="71"/>
@@ -41606,7 +41615,7 @@
         <v>433</v>
       </c>
       <c r="F585" s="71" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="G585" s="71">
         <v>1535</v>
@@ -41624,40 +41633,40 @@
         <v>61</v>
       </c>
       <c r="L585" s="72" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M585" s="71" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="N585" s="71"/>
       <c r="O585" s="19" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="Q585" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T585" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B586" s="2" t="s">
         <v>3974</v>
-      </c>
-      <c r="B586" s="2" t="s">
-        <v>3975</v>
       </c>
       <c r="E586" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="G586" s="2" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="H586" s="2" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="I586" s="2" t="s">
         <v>197</v>
@@ -41669,30 +41678,30 @@
         <v>47</v>
       </c>
       <c r="L586" s="2" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="M586" s="2" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="N586" s="5" t="s">
         <v>2199</v>
       </c>
       <c r="O586" s="19" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="Q586" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T586" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -41700,13 +41709,13 @@
         <v>433</v>
       </c>
       <c r="F587" s="1" t="s">
+        <v>3978</v>
+      </c>
+      <c r="G587" s="1" t="s">
         <v>3979</v>
       </c>
-      <c r="G587" s="1" t="s">
-        <v>3980</v>
-      </c>
       <c r="H587" s="1" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="I587" s="70" t="s">
         <v>419</v>
@@ -41721,24 +41730,24 @@
         <v>2588</v>
       </c>
       <c r="M587" s="1" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="O587" s="19" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="Q587" s="32" t="s">
         <v>289</v>
       </c>
       <c r="T587" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B588" s="45" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="C588" s="45"/>
       <c r="D588" s="45"/>
@@ -41746,59 +41755,59 @@
         <v>2216</v>
       </c>
       <c r="F588" s="45" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="G588" s="76" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="H588" s="76" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="I588" s="71" t="s">
         <v>138</v>
       </c>
       <c r="J588" s="71" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="K588" s="71" t="s">
         <v>61</v>
       </c>
       <c r="L588" s="75" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="M588" s="71" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="N588" s="45"/>
       <c r="O588" s="19" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="P588" s="45"/>
       <c r="Q588" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T588" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B589" s="2" t="s">
         <v>4001</v>
-      </c>
-      <c r="B589" s="2" t="s">
-        <v>4002</v>
       </c>
       <c r="E589" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F589" s="2" t="s">
+        <v>3998</v>
+      </c>
+      <c r="G589" s="2" t="s">
         <v>3999</v>
       </c>
-      <c r="G589" s="2" t="s">
-        <v>4000</v>
-      </c>
       <c r="H589" s="2" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="I589" s="2" t="s">
         <v>197</v>
@@ -41810,33 +41819,33 @@
         <v>61</v>
       </c>
       <c r="L589" s="2" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M589" s="2" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="O589" s="19" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="Q589" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T589" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12" t="s">
+        <v>4002</v>
+      </c>
+      <c r="B590" s="2" t="s">
         <v>4003</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>4004</v>
       </c>
       <c r="E590" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F590" s="2" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="G590" s="2" t="s">
         <v>2339</v>
@@ -41854,39 +41863,39 @@
         <v>61</v>
       </c>
       <c r="L590" s="2" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M590" s="2" t="s">
+        <v>4003</v>
+      </c>
+      <c r="O590" s="19" t="s">
         <v>4004</v>
-      </c>
-      <c r="O590" s="19" t="s">
-        <v>4005</v>
       </c>
       <c r="Q590" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T590" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="E591" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F591" s="2" t="s">
+        <v>4008</v>
+      </c>
+      <c r="G591" s="2" t="s">
         <v>4009</v>
       </c>
-      <c r="G591" s="2" t="s">
-        <v>4010</v>
-      </c>
       <c r="H591" s="2" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="I591" s="2" t="s">
         <v>2383</v>
@@ -41898,19 +41907,66 @@
         <v>61</v>
       </c>
       <c r="L591" s="2" t="s">
+        <v>4010</v>
+      </c>
+      <c r="M591" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="O591" s="19" t="s">
         <v>4011</v>
-      </c>
-      <c r="M591" s="2" t="s">
-        <v>4007</v>
-      </c>
-      <c r="O591" s="19" t="s">
-        <v>4012</v>
       </c>
       <c r="Q591" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T591" s="25" t="s">
-        <v>3572</v>
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="592" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="12" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B592" s="32" t="s">
+        <v>3387</v>
+      </c>
+      <c r="C592" s="32"/>
+      <c r="D592" s="32"/>
+      <c r="E592" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F592" s="32" t="s">
+        <v>3388</v>
+      </c>
+      <c r="G592" s="32" t="s">
+        <v>3389</v>
+      </c>
+      <c r="H592" s="32" t="s">
+        <v>3389</v>
+      </c>
+      <c r="I592" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J592" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="K592" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L592" s="35" t="s">
+        <v>4015</v>
+      </c>
+      <c r="M592" s="32" t="s">
+        <v>3387</v>
+      </c>
+      <c r="N592" s="32"/>
+      <c r="O592" s="33" t="s">
+        <v>4013</v>
+      </c>
+      <c r="Q592" s="1" t="s">
+        <v>4014</v>
+      </c>
+      <c r="T592" s="25" t="s">
+        <v>3571</v>
       </c>
     </row>
   </sheetData>
@@ -42626,7 +42682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -43859,38 +43915,42 @@
         <v>3270</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>3387</v>
-      </c>
-      <c r="C26" s="32"/>
+        <v>3390</v>
+      </c>
+      <c r="C26" s="32">
+        <v>1820</v>
+      </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32" t="s">
-        <v>433</v>
+        <v>3391</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>3388</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>3389</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>3389</v>
+        <v>3392</v>
+      </c>
+      <c r="G26" s="32">
+        <v>1493</v>
+      </c>
+      <c r="H26" s="32">
+        <v>1493</v>
       </c>
       <c r="I26" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>239</v>
+        <v>197</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>3393</v>
       </c>
       <c r="K26" s="32" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="L26" s="32"/>
       <c r="M26" s="32" t="s">
-        <v>3387</v>
-      </c>
-      <c r="N26" s="32"/>
+        <v>3390</v>
+      </c>
+      <c r="N26" s="34" t="s">
+        <v>3394</v>
+      </c>
       <c r="O26" s="33" t="s">
-        <v>3390</v>
+        <v>3395</v>
       </c>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
@@ -43901,43 +43961,37 @@
         <v>3270</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>3391</v>
+        <v>3222</v>
       </c>
       <c r="C27" s="32">
-        <v>1820</v>
+        <v>3370</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="32" t="s">
-        <v>3392</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>3393</v>
-      </c>
+        <v>3223</v>
+      </c>
+      <c r="F27" s="32"/>
       <c r="G27" s="32">
-        <v>1493</v>
+        <v>1401</v>
       </c>
       <c r="H27" s="32">
-        <v>1493</v>
+        <v>1700</v>
       </c>
       <c r="I27" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>3394</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="J27" s="32"/>
       <c r="K27" s="32" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="L27" s="32"/>
       <c r="M27" s="32" t="s">
-        <v>3391</v>
+        <v>3222</v>
       </c>
       <c r="N27" s="34" t="s">
-        <v>3395</v>
-      </c>
-      <c r="O27" s="33" t="s">
-        <v>3396</v>
-      </c>
+        <v>3226</v>
+      </c>
+      <c r="O27" s="32"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
@@ -43947,82 +44001,90 @@
         <v>3270</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>3222</v>
+        <v>3396</v>
       </c>
       <c r="C28" s="32">
-        <v>3370</v>
+        <v>1200</v>
       </c>
       <c r="D28" s="32"/>
       <c r="E28" s="32" t="s">
-        <v>3223</v>
-      </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32">
-        <v>1401</v>
-      </c>
-      <c r="H28" s="32">
-        <v>1700</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="J28" s="32"/>
+        <v>1813</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>3397</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I28" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="35"/>
       <c r="K28" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L28" s="32"/>
+      <c r="L28" s="32">
+        <v>94</v>
+      </c>
       <c r="M28" s="32" t="s">
-        <v>3222</v>
+        <v>3396</v>
       </c>
       <c r="N28" s="34" t="s">
-        <v>3226</v>
-      </c>
-      <c r="O28" s="32"/>
+        <v>3398</v>
+      </c>
+      <c r="O28" s="33" t="s">
+        <v>3399</v>
+      </c>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>3270</v>
+        <v>1907</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>3397</v>
+        <v>3400</v>
       </c>
       <c r="C29" s="32">
-        <v>1200</v>
+        <v>1021</v>
       </c>
       <c r="D29" s="32"/>
       <c r="E29" s="32" t="s">
         <v>1813</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>3398</v>
+        <v>1909</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>399</v>
+        <v>1910</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>1447</v>
-      </c>
-      <c r="I29" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="J29" s="35"/>
+        <v>1911</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>1912</v>
+      </c>
       <c r="K29" s="32" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="32">
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="M29" s="32" t="s">
-        <v>3397</v>
+        <v>3400</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>3399</v>
+        <v>1913</v>
       </c>
       <c r="O29" s="33" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
@@ -44030,47 +44092,27 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>3401</v>
-      </c>
-      <c r="C30" s="32">
-        <v>1021</v>
-      </c>
+        <v>3270</v>
+      </c>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>1813</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>1909</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>1910</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>1911</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="J30" s="32" t="s">
-        <v>1912</v>
-      </c>
-      <c r="K30" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="32">
-        <v>233</v>
-      </c>
-      <c r="M30" s="32" t="s">
-        <v>3401</v>
-      </c>
-      <c r="N30" s="34" t="s">
-        <v>1913</v>
-      </c>
+        <v>3402</v>
+      </c>
+      <c r="F30" s="32">
+        <v>2673</v>
+      </c>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
       <c r="O30" s="33" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
@@ -44080,14 +44122,16 @@
       <c r="A31" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B31" s="32"/>
+      <c r="B31" s="32" t="s">
+        <v>3341</v>
+      </c>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="E31" s="32" t="s">
-        <v>3403</v>
-      </c>
-      <c r="F31" s="32">
-        <v>2673</v>
+        <v>278</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>3404</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
@@ -44095,117 +44139,135 @@
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="M31" s="32" t="s">
+        <v>3341</v>
+      </c>
       <c r="N31" s="32"/>
-      <c r="O31" s="33" t="s">
-        <v>3404</v>
-      </c>
+      <c r="O31" s="32"/>
       <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
+      <c r="Q31" s="32" t="s">
+        <v>3405</v>
+      </c>
       <c r="R31" s="32"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B32" s="32" t="s">
-        <v>3341</v>
-      </c>
+      <c r="B32" s="32"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="E32" s="32" t="s">
-        <v>278</v>
+        <v>433</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>3405</v>
+        <v>3491</v>
       </c>
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
+      <c r="I32" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" s="35" t="s">
+        <v>686</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="L32" s="32"/>
-      <c r="M32" s="32" t="s">
-        <v>3341</v>
-      </c>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="34" t="s">
+        <v>3493</v>
+      </c>
+      <c r="O32" s="38" t="s">
+        <v>3492</v>
+      </c>
       <c r="P32" s="32"/>
-      <c r="Q32" s="32" t="s">
-        <v>3406</v>
-      </c>
+      <c r="Q32" s="32"/>
       <c r="R32" s="32"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="B33" s="32" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C33" s="32">
+        <v>1501</v>
+      </c>
       <c r="D33" s="32"/>
       <c r="E33" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F33" s="32" t="s">
-        <v>3492</v>
+        <v>3315</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32"/>
-      <c r="I33" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" s="35" t="s">
-        <v>686</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>130</v>
-      </c>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
       <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="M33" s="32" t="s">
+        <v>3535</v>
+      </c>
       <c r="N33" s="34" t="s">
-        <v>3494</v>
+        <v>3317</v>
       </c>
       <c r="O33" s="38" t="s">
-        <v>3493</v>
+        <v>3536</v>
       </c>
       <c r="P33" s="32"/>
       <c r="Q33" s="32"/>
       <c r="R33" s="32"/>
     </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>3536</v>
+        <v>3562</v>
       </c>
       <c r="C34" s="32">
-        <v>1501</v>
+        <v>3009</v>
       </c>
       <c r="D34" s="32"/>
       <c r="E34" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>3315</v>
-      </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+        <v>3529</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>3553</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>3553</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="32" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K34" s="32" t="s">
+        <v>130</v>
+      </c>
       <c r="L34" s="32"/>
       <c r="M34" s="32" t="s">
-        <v>3536</v>
+        <v>3562</v>
       </c>
       <c r="N34" s="34" t="s">
-        <v>3317</v>
+        <v>3556</v>
       </c>
       <c r="O34" s="38" t="s">
-        <v>3537</v>
+        <v>3530</v>
       </c>
       <c r="P34" s="32"/>
-      <c r="Q34" s="32"/>
+      <c r="Q34" s="32" t="s">
+        <v>3531</v>
+      </c>
       <c r="R34" s="32"/>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -44216,14 +44278,14 @@
         <v>3563</v>
       </c>
       <c r="C35" s="32">
-        <v>3009</v>
+        <v>1724</v>
       </c>
       <c r="D35" s="32"/>
       <c r="E35" s="32" t="s">
-        <v>433</v>
+        <v>3177</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>3530</v>
+        <v>3551</v>
       </c>
       <c r="G35" s="32" t="s">
         <v>3554</v>
@@ -44232,10 +44294,10 @@
         <v>3554</v>
       </c>
       <c r="I35" s="32" t="s">
-        <v>45</v>
+        <v>316</v>
       </c>
       <c r="J35" s="32" t="s">
-        <v>3111</v>
+        <v>3552</v>
       </c>
       <c r="K35" s="32" t="s">
         <v>130</v>
@@ -44245,14 +44307,12 @@
         <v>3563</v>
       </c>
       <c r="N35" s="34" t="s">
-        <v>3557</v>
-      </c>
-      <c r="O35" s="38" t="s">
-        <v>3531</v>
-      </c>
+        <v>3555</v>
+      </c>
+      <c r="O35" s="38"/>
       <c r="P35" s="32"/>
       <c r="Q35" s="32" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="R35" s="32"/>
     </row>
@@ -44264,26 +44324,26 @@
         <v>3564</v>
       </c>
       <c r="C36" s="32">
-        <v>1724</v>
+        <v>2984</v>
       </c>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>3177</v>
+        <v>2630</v>
       </c>
       <c r="F36" s="32" t="s">
-        <v>3552</v>
+        <v>3559</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>3555</v>
+        <v>3557</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>3555</v>
+        <v>3557</v>
       </c>
       <c r="I36" s="32" t="s">
-        <v>316</v>
+        <v>197</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>3553</v>
+        <v>377</v>
       </c>
       <c r="K36" s="32" t="s">
         <v>130</v>
@@ -44293,12 +44353,14 @@
         <v>3564</v>
       </c>
       <c r="N36" s="34" t="s">
-        <v>3556</v>
-      </c>
-      <c r="O36" s="38"/>
+        <v>3565</v>
+      </c>
+      <c r="O36" s="38" t="s">
+        <v>3558</v>
+      </c>
       <c r="P36" s="32"/>
       <c r="Q36" s="32" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="R36" s="32"/>
     </row>
@@ -44307,46 +44369,42 @@
         <v>3270</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>3565</v>
-      </c>
-      <c r="C37" s="32">
-        <v>2984</v>
-      </c>
+        <v>3566</v>
+      </c>
+      <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32" t="s">
-        <v>2630</v>
+        <v>433</v>
       </c>
       <c r="F37" s="32" t="s">
-        <v>3560</v>
+        <v>3572</v>
       </c>
       <c r="G37" s="32" t="s">
-        <v>3558</v>
+        <v>3567</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>3558</v>
+        <v>3567</v>
       </c>
       <c r="I37" s="32" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>377</v>
+        <v>2264</v>
       </c>
       <c r="K37" s="32" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="L37" s="32"/>
       <c r="M37" s="32" t="s">
-        <v>3565</v>
-      </c>
-      <c r="N37" s="34" t="s">
         <v>3566</v>
       </c>
+      <c r="N37" s="32"/>
       <c r="O37" s="38" t="s">
-        <v>3559</v>
+        <v>3573</v>
       </c>
       <c r="P37" s="32"/>
       <c r="Q37" s="32" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="R37" s="32"/>
     </row>
@@ -44355,145 +44413,139 @@
         <v>3270</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>3567</v>
-      </c>
-      <c r="C38" s="32"/>
+        <v>3626</v>
+      </c>
+      <c r="C38" s="32">
+        <v>1375</v>
+      </c>
       <c r="D38" s="32"/>
       <c r="E38" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>3573</v>
+        <v>3627</v>
       </c>
       <c r="G38" s="32" t="s">
-        <v>3568</v>
+        <v>748</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>3568</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="J38" s="32" t="s">
-        <v>2264</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
       <c r="K38" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L38" s="32"/>
+        <v>26</v>
+      </c>
+      <c r="L38" s="32">
+        <v>231</v>
+      </c>
       <c r="M38" s="32" t="s">
-        <v>3567</v>
-      </c>
-      <c r="N38" s="32"/>
+        <v>3626</v>
+      </c>
+      <c r="N38" s="34" t="s">
+        <v>3629</v>
+      </c>
       <c r="O38" s="38" t="s">
-        <v>3574</v>
-      </c>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32" t="s">
-        <v>3532</v>
-      </c>
+        <v>3628</v>
+      </c>
+      <c r="P38" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q38" s="32"/>
       <c r="R38" s="32"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B39" s="32" t="s">
-        <v>3627</v>
-      </c>
-      <c r="C39" s="32">
-        <v>1375</v>
-      </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32" t="s">
-        <v>433</v>
-      </c>
-      <c r="F39" s="32" t="s">
-        <v>3628</v>
-      </c>
-      <c r="G39" s="32" t="s">
-        <v>748</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>749</v>
-      </c>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="32">
-        <v>231</v>
-      </c>
-      <c r="M39" s="32" t="s">
-        <v>3627</v>
-      </c>
-      <c r="N39" s="34" t="s">
-        <v>3630</v>
-      </c>
-      <c r="O39" s="38" t="s">
-        <v>3629</v>
-      </c>
-      <c r="P39" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
+      <c r="B39" s="39" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="39"/>
+      <c r="G39" s="41">
+        <v>1544</v>
+      </c>
+      <c r="H39" s="41">
+        <v>1544</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>3292</v>
+      </c>
+      <c r="J39" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="42"/>
+      <c r="M39" s="39" t="s">
+        <v>3481</v>
+      </c>
+      <c r="N39" s="39"/>
+      <c r="O39" s="43" t="s">
+        <v>3482</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q39" s="39" t="s">
+        <v>3490</v>
+      </c>
+      <c r="R39" s="39"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="24" t="s">
+        <v>3571</v>
+      </c>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B40" s="39" t="s">
-        <v>3482</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="39"/>
-      <c r="G40" s="41">
-        <v>1544</v>
-      </c>
-      <c r="H40" s="41">
-        <v>1544</v>
-      </c>
-      <c r="I40" s="39" t="s">
-        <v>3292</v>
-      </c>
-      <c r="J40" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="K40" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="L40" s="42"/>
-      <c r="M40" s="39" t="s">
-        <v>3482</v>
-      </c>
-      <c r="N40" s="39"/>
-      <c r="O40" s="43" t="s">
-        <v>3483</v>
-      </c>
-      <c r="P40" s="44" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q40" s="39" t="s">
-        <v>3491</v>
-      </c>
-      <c r="R40" s="39"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="24" t="s">
-        <v>3572</v>
-      </c>
+      <c r="B40" s="32" t="s">
+        <v>3693</v>
+      </c>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>3672</v>
+      </c>
+      <c r="G40" s="32">
+        <v>1554</v>
+      </c>
+      <c r="H40" s="32">
+        <v>1554</v>
+      </c>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32">
+        <v>12</v>
+      </c>
+      <c r="M40" s="32" t="s">
+        <v>3693</v>
+      </c>
+      <c r="N40" s="32"/>
+      <c r="O40" s="19" t="s">
+        <v>3671</v>
+      </c>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
@@ -44501,26 +44553,26 @@
         <v>433</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>3673</v>
+        <v>3678</v>
       </c>
       <c r="G41" s="32">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="H41" s="32">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="I41" s="32"/>
       <c r="J41" s="32"/>
       <c r="K41" s="32"/>
-      <c r="L41" s="32">
-        <v>12</v>
+      <c r="L41" s="35">
+        <v>10</v>
       </c>
       <c r="M41" s="32" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
       <c r="N41" s="32"/>
-      <c r="O41" s="19" t="s">
-        <v>3672</v>
+      <c r="O41" s="38" t="s">
+        <v>3691</v>
       </c>
       <c r="P41" s="32"/>
       <c r="Q41" s="32"/>
@@ -44530,85 +44582,99 @@
       <c r="A42" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B42" s="32" t="s">
-        <v>3693</v>
-      </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32" t="s">
-        <v>433</v>
-      </c>
-      <c r="F42" s="32" t="s">
-        <v>3679</v>
-      </c>
-      <c r="G42" s="32">
-        <v>1543</v>
-      </c>
-      <c r="H42" s="32">
-        <v>1543</v>
-      </c>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="35">
-        <v>10</v>
-      </c>
-      <c r="M42" s="32" t="s">
-        <v>3693</v>
-      </c>
-      <c r="N42" s="32"/>
-      <c r="O42" s="38" t="s">
-        <v>3692</v>
-      </c>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
+      <c r="B42" s="56" t="s">
+        <v>3799</v>
+      </c>
+      <c r="C42" s="45">
+        <v>4619</v>
+      </c>
+      <c r="D42" s="45"/>
+      <c r="E42" s="56" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>3802</v>
+      </c>
+      <c r="G42" s="56" t="s">
+        <v>3800</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>3800</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>3723</v>
+      </c>
+      <c r="J42" s="32" t="s">
+        <v>3803</v>
+      </c>
+      <c r="K42" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="L42" s="57" t="s">
+        <v>3805</v>
+      </c>
+      <c r="M42" s="56" t="s">
+        <v>3799</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>3801</v>
+      </c>
+      <c r="O42" s="54"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="45"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B43" s="56" t="s">
-        <v>3800</v>
-      </c>
-      <c r="C43" s="45">
-        <v>4619</v>
-      </c>
-      <c r="D43" s="45"/>
-      <c r="E43" s="56" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F43" s="56" t="s">
-        <v>3803</v>
-      </c>
-      <c r="G43" s="56" t="s">
-        <v>3801</v>
-      </c>
-      <c r="H43" s="56" t="s">
-        <v>3801</v>
+      <c r="B43" s="32" t="s">
+        <v>3719</v>
+      </c>
+      <c r="C43" s="32">
+        <v>3712</v>
+      </c>
+      <c r="D43" s="55"/>
+      <c r="E43" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>3722</v>
+      </c>
+      <c r="G43" s="32" t="s">
+        <v>3796</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>3796</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>3804</v>
-      </c>
-      <c r="K43" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="L43" s="57" t="s">
-        <v>3806</v>
-      </c>
-      <c r="M43" s="56" t="s">
-        <v>3800</v>
+        <v>3795</v>
+      </c>
+      <c r="K43" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="32">
+        <v>136</v>
+      </c>
+      <c r="M43" s="32" t="s">
+        <v>3719</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>3802</v>
-      </c>
-      <c r="O43" s="54"/>
-      <c r="P43" s="45"/>
-      <c r="Q43" s="45"/>
-      <c r="R43" s="45"/>
+        <v>3794</v>
+      </c>
+      <c r="O43" s="19" t="s">
+        <v>3721</v>
+      </c>
+      <c r="P43" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q43" s="32" t="s">
+        <v>3734</v>
+      </c>
+      <c r="R43" s="32"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31" t="s">
@@ -44618,26 +44684,26 @@
         <v>3720</v>
       </c>
       <c r="C44" s="32">
-        <v>3712</v>
+        <v>2452</v>
       </c>
       <c r="D44" s="55"/>
       <c r="E44" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F44" s="32" t="s">
+        <v>3725</v>
+      </c>
+      <c r="G44" s="32">
+        <v>1520</v>
+      </c>
+      <c r="H44" s="32">
+        <v>1520</v>
+      </c>
+      <c r="I44" s="32" t="s">
         <v>3723</v>
       </c>
-      <c r="G44" s="32" t="s">
-        <v>3797</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>3797</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>3724</v>
-      </c>
       <c r="J44" s="32" t="s">
-        <v>3796</v>
+        <v>3804</v>
       </c>
       <c r="K44" s="32" t="s">
         <v>61</v>
@@ -44649,16 +44715,16 @@
         <v>3720</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>3795</v>
+        <v>3797</v>
       </c>
       <c r="O44" s="19" t="s">
-        <v>3722</v>
+        <v>3724</v>
       </c>
       <c r="P44" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q44" s="32" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="R44" s="32"/>
     </row>
@@ -44666,53 +44732,47 @@
       <c r="A45" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B45" s="32" t="s">
-        <v>3721</v>
-      </c>
-      <c r="C45" s="32">
-        <v>2452</v>
-      </c>
-      <c r="D45" s="55"/>
-      <c r="E45" s="32" t="s">
-        <v>433</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>3726</v>
-      </c>
-      <c r="G45" s="32">
-        <v>1520</v>
-      </c>
-      <c r="H45" s="32">
-        <v>1520</v>
+      <c r="B45" s="55" t="s">
+        <v>3789</v>
+      </c>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="55" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>3787</v>
+      </c>
+      <c r="G45" s="45">
+        <v>1510</v>
+      </c>
+      <c r="H45" s="45">
+        <v>1510</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="J45" s="32" t="s">
-        <v>3805</v>
-      </c>
-      <c r="K45" s="32" t="s">
+        <v>3798</v>
+      </c>
+      <c r="K45" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="L45" s="32">
-        <v>136</v>
-      </c>
-      <c r="M45" s="32" t="s">
-        <v>3721</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>3798</v>
-      </c>
-      <c r="O45" s="19" t="s">
-        <v>3725</v>
-      </c>
-      <c r="P45" s="32" t="s">
-        <v>289</v>
-      </c>
+      <c r="L45" s="45">
+        <v>120</v>
+      </c>
+      <c r="M45" s="55" t="s">
+        <v>3789</v>
+      </c>
+      <c r="N45" s="45"/>
+      <c r="O45" s="54" t="s">
+        <v>3788</v>
+      </c>
+      <c r="P45" s="45"/>
       <c r="Q45" s="32" t="s">
-        <v>3735</v>
-      </c>
-      <c r="R45" s="32"/>
+        <v>3734</v>
+      </c>
+      <c r="R45" s="45"/>
     </row>
     <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31" t="s">
@@ -44724,10 +44784,10 @@
       <c r="C46" s="45"/>
       <c r="D46" s="45"/>
       <c r="E46" s="55" t="s">
-        <v>2937</v>
-      </c>
-      <c r="F46" s="45" t="s">
-        <v>3788</v>
+        <v>3791</v>
+      </c>
+      <c r="F46" s="55" t="s">
+        <v>3792</v>
       </c>
       <c r="G46" s="45">
         <v>1510</v>
@@ -44736,27 +44796,27 @@
         <v>1510</v>
       </c>
       <c r="I46" s="32" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="J46" s="32" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="K46" s="55" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="45">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="M46" s="55" t="s">
         <v>3790</v>
       </c>
       <c r="N46" s="45"/>
       <c r="O46" s="54" t="s">
-        <v>3789</v>
+        <v>3793</v>
       </c>
       <c r="P46" s="45"/>
       <c r="Q46" s="32" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="R46" s="45"/>
     </row>
@@ -44764,144 +44824,130 @@
       <c r="A47" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B47" s="55" t="s">
-        <v>3791</v>
-      </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="55" t="s">
-        <v>3792</v>
-      </c>
-      <c r="F47" s="55" t="s">
-        <v>3793</v>
-      </c>
-      <c r="G47" s="45">
-        <v>1510</v>
-      </c>
-      <c r="H47" s="45">
-        <v>1510</v>
-      </c>
-      <c r="I47" s="32" t="s">
-        <v>3724</v>
-      </c>
-      <c r="J47" s="32" t="s">
-        <v>3799</v>
-      </c>
-      <c r="K47" s="55" t="s">
-        <v>61</v>
+      <c r="B47" s="45" t="s">
+        <v>3739</v>
+      </c>
+      <c r="C47" s="45">
+        <v>2172</v>
+      </c>
+      <c r="D47" s="45">
+        <v>2304</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>3735</v>
+      </c>
+      <c r="G47" s="56" t="s">
+        <v>3807</v>
+      </c>
+      <c r="H47" s="56" t="s">
+        <v>3807</v>
+      </c>
+      <c r="I47" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="J47" s="56" t="s">
+        <v>3806</v>
+      </c>
+      <c r="K47" s="56" t="s">
+        <v>130</v>
       </c>
       <c r="L47" s="45">
-        <v>96</v>
-      </c>
-      <c r="M47" s="55" t="s">
-        <v>3791</v>
-      </c>
-      <c r="N47" s="45"/>
-      <c r="O47" s="54" t="s">
-        <v>3794</v>
-      </c>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="32" t="s">
-        <v>3735</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="M47" s="45" t="s">
+        <v>3739</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>3808</v>
+      </c>
+      <c r="O47" s="19" t="s">
+        <v>3736</v>
+      </c>
+      <c r="P47" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q47" s="45"/>
       <c r="R47" s="45"/>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B48" s="45" t="s">
-        <v>3740</v>
-      </c>
-      <c r="C48" s="45">
-        <v>2172</v>
-      </c>
-      <c r="D48" s="45">
-        <v>2304</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>433</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>3736</v>
-      </c>
-      <c r="G48" s="56" t="s">
-        <v>3808</v>
-      </c>
-      <c r="H48" s="56" t="s">
-        <v>3808</v>
-      </c>
-      <c r="I48" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="J48" s="56" t="s">
-        <v>3807</v>
-      </c>
-      <c r="K48" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="L48" s="45">
-        <v>228</v>
-      </c>
-      <c r="M48" s="45" t="s">
-        <v>3740</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>3809</v>
-      </c>
-      <c r="O48" s="19" t="s">
-        <v>3737</v>
-      </c>
-      <c r="P48" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q48" s="45"/>
-      <c r="R48" s="45"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
         <v>3270</v>
       </c>
+      <c r="B49" s="45" t="s">
+        <v>3755</v>
+      </c>
+      <c r="C49" s="45">
+        <v>2456</v>
+      </c>
+      <c r="D49" s="45"/>
+      <c r="E49" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F49" s="52" t="s">
+        <v>3757</v>
+      </c>
+      <c r="G49" s="52" t="s">
+        <v>605</v>
+      </c>
+      <c r="H49" s="52" t="s">
+        <v>606</v>
+      </c>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="45">
+        <v>340</v>
+      </c>
+      <c r="M49" s="52" t="s">
+        <v>3755</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>3756</v>
+      </c>
+      <c r="O49" s="19" t="s">
+        <v>3758</v>
+      </c>
+      <c r="P49" s="45"/>
+      <c r="Q49" s="45"/>
+      <c r="R49" s="45"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>3756</v>
-      </c>
-      <c r="C50" s="45">
-        <v>2456</v>
-      </c>
+        <v>3759</v>
+      </c>
+      <c r="C50" s="45"/>
       <c r="D50" s="45"/>
-      <c r="E50" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F50" s="52" t="s">
-        <v>3758</v>
-      </c>
-      <c r="G50" s="52" t="s">
-        <v>605</v>
-      </c>
-      <c r="H50" s="52" t="s">
-        <v>606</v>
-      </c>
+      <c r="E50" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>3763</v>
+      </c>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
       <c r="I50" s="45"/>
       <c r="J50" s="45"/>
-      <c r="K50" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="45">
-        <v>340</v>
-      </c>
-      <c r="M50" s="52" t="s">
-        <v>3756</v>
-      </c>
-      <c r="N50" s="9" t="s">
-        <v>3757</v>
-      </c>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45" t="s">
+        <v>3759</v>
+      </c>
+      <c r="N50" s="45"/>
       <c r="O50" s="19" t="s">
-        <v>3759</v>
+        <v>3770</v>
       </c>
       <c r="P50" s="45"/>
       <c r="Q50" s="45"/>
@@ -44916,8 +44962,8 @@
       </c>
       <c r="C51" s="45"/>
       <c r="D51" s="45"/>
-      <c r="E51" s="45" t="s">
-        <v>433</v>
+      <c r="E51" s="53" t="s">
+        <v>2280</v>
       </c>
       <c r="F51" s="53" t="s">
         <v>3764</v>
@@ -44933,7 +44979,7 @@
       </c>
       <c r="N51" s="45"/>
       <c r="O51" s="19" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
       <c r="P51" s="45"/>
       <c r="Q51" s="45"/>
@@ -44943,7 +44989,7 @@
       <c r="A52" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B52" s="45" t="s">
+      <c r="B52" s="53" t="s">
         <v>3761</v>
       </c>
       <c r="C52" s="45"/>
@@ -44960,12 +45006,12 @@
       <c r="J52" s="45"/>
       <c r="K52" s="45"/>
       <c r="L52" s="45"/>
-      <c r="M52" s="45" t="s">
+      <c r="M52" s="53" t="s">
         <v>3761</v>
       </c>
       <c r="N52" s="45"/>
       <c r="O52" s="19" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
       <c r="P52" s="45"/>
       <c r="Q52" s="45"/>
@@ -44975,7 +45021,7 @@
       <c r="A53" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B53" s="53" t="s">
+      <c r="B53" s="45" t="s">
         <v>3762</v>
       </c>
       <c r="C53" s="45"/>
@@ -44992,12 +45038,12 @@
       <c r="J53" s="45"/>
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
-      <c r="M53" s="53" t="s">
+      <c r="M53" s="45" t="s">
         <v>3762</v>
       </c>
       <c r="N53" s="45"/>
       <c r="O53" s="19" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
       <c r="P53" s="45"/>
       <c r="Q53" s="45"/>
@@ -45007,141 +45053,155 @@
       <c r="A54" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B54" s="45" t="s">
-        <v>3763</v>
-      </c>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="53" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F54" s="53" t="s">
-        <v>3767</v>
-      </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="45"/>
-      <c r="M54" s="45" t="s">
-        <v>3763</v>
-      </c>
-      <c r="N54" s="45"/>
+      <c r="B54" s="1" t="s">
+        <v>3836</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>3735</v>
+      </c>
       <c r="O54" s="19" t="s">
-        <v>3768</v>
-      </c>
-      <c r="P54" s="45"/>
-      <c r="Q54" s="45"/>
-      <c r="R54" s="45"/>
+        <v>3838</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>3837</v>
+      </c>
     </row>
     <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3837</v>
-      </c>
-      <c r="E55" s="45" t="s">
-        <v>433</v>
+        <v>3932</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2047</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>3933</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>3736</v>
-      </c>
-      <c r="O55" s="19" t="s">
-        <v>3839</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>3838</v>
+        <v>3934</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>3935</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>3935</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>3931</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>3936</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>3937</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>3933</v>
-      </c>
-      <c r="C56" s="1">
-        <v>2047</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>3934</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>3935</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>3936</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>3936</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>3932</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>3937</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>3938</v>
+      <c r="B56" s="65" t="s">
+        <v>3944</v>
+      </c>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="49" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F56" s="66" t="s">
+        <v>3943</v>
+      </c>
+      <c r="G56" s="66" t="s">
+        <v>3948</v>
+      </c>
+      <c r="H56" s="66" t="s">
+        <v>3948</v>
+      </c>
+      <c r="I56" s="65" t="s">
+        <v>316</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="K56" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" s="45"/>
+      <c r="M56" s="65" t="s">
+        <v>3944</v>
+      </c>
+      <c r="N56" s="45"/>
+      <c r="O56" s="19" t="s">
+        <v>3946</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="Q56" s="65" t="s">
+        <v>3947</v>
+      </c>
+      <c r="R56" s="45"/>
     </row>
     <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="B57" s="65" t="s">
-        <v>3945</v>
+      <c r="B57" s="45" t="s">
+        <v>3949</v>
       </c>
       <c r="C57" s="45"/>
       <c r="D57" s="45"/>
-      <c r="E57" s="49" t="s">
-        <v>1748</v>
-      </c>
-      <c r="F57" s="66" t="s">
-        <v>3944</v>
-      </c>
-      <c r="G57" s="66" t="s">
+      <c r="E57" s="68" t="s">
+        <v>3950</v>
+      </c>
+      <c r="F57" s="68" t="s">
+        <v>3951</v>
+      </c>
+      <c r="G57" s="67" t="s">
+        <v>3418</v>
+      </c>
+      <c r="H57" s="67" t="s">
+        <v>3418</v>
+      </c>
+      <c r="I57" s="67" t="s">
+        <v>3954</v>
+      </c>
+      <c r="J57" s="67" t="s">
+        <v>3955</v>
+      </c>
+      <c r="K57" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" s="45"/>
+      <c r="M57" s="67" t="s">
         <v>3949</v>
-      </c>
-      <c r="H57" s="66" t="s">
-        <v>3949</v>
-      </c>
-      <c r="I57" s="65" t="s">
-        <v>316</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>2112</v>
-      </c>
-      <c r="K57" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="L57" s="45"/>
-      <c r="M57" s="65" t="s">
-        <v>3945</v>
       </c>
       <c r="N57" s="45"/>
       <c r="O57" s="19" t="s">
-        <v>3947</v>
+        <v>3952</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q57" s="65" t="s">
-        <v>3948</v>
+      <c r="Q57" t="s">
+        <v>3953</v>
       </c>
       <c r="R57" s="45"/>
     </row>
@@ -45150,172 +45210,126 @@
         <v>3270</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>3950</v>
-      </c>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="68" t="s">
-        <v>3951</v>
-      </c>
-      <c r="F58" s="68" t="s">
-        <v>3952</v>
-      </c>
-      <c r="G58" s="67" t="s">
-        <v>3419</v>
-      </c>
-      <c r="H58" s="67" t="s">
-        <v>3419</v>
-      </c>
-      <c r="I58" s="67" t="s">
-        <v>3955</v>
-      </c>
-      <c r="J58" s="67" t="s">
-        <v>3956</v>
-      </c>
-      <c r="K58" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="L58" s="45"/>
-      <c r="M58" s="67" t="s">
-        <v>3950</v>
-      </c>
-      <c r="N58" s="45"/>
+        <v>3959</v>
+      </c>
+      <c r="C58" s="45">
+        <v>4614</v>
+      </c>
+      <c r="D58" s="45">
+        <v>3002</v>
+      </c>
+      <c r="E58" s="70" t="s">
+        <v>3962</v>
+      </c>
+      <c r="F58" s="70" t="s">
+        <v>3964</v>
+      </c>
+      <c r="G58" s="70" t="s">
+        <v>3961</v>
+      </c>
+      <c r="H58" s="70" t="s">
+        <v>3961</v>
+      </c>
+      <c r="I58" s="70" t="s">
+        <v>419</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L58" s="45">
+        <v>383</v>
+      </c>
+      <c r="M58" s="70" t="s">
+        <v>3959</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>3963</v>
+      </c>
       <c r="O58" s="19" t="s">
-        <v>3953</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>3954</v>
-      </c>
+        <v>3960</v>
+      </c>
+      <c r="P58" s="45"/>
+      <c r="Q58" s="45"/>
       <c r="R58" s="45"/>
     </row>
     <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
-        <v>3270</v>
-      </c>
-      <c r="B59" s="45" t="s">
-        <v>3960</v>
-      </c>
-      <c r="C59" s="45">
-        <v>4614</v>
-      </c>
-      <c r="D59" s="45">
-        <v>3002</v>
-      </c>
-      <c r="E59" s="70" t="s">
-        <v>3963</v>
-      </c>
-      <c r="F59" s="70" t="s">
-        <v>3965</v>
-      </c>
-      <c r="G59" s="70" t="s">
-        <v>3962</v>
-      </c>
-      <c r="H59" s="70" t="s">
-        <v>3962</v>
-      </c>
-      <c r="I59" s="70" t="s">
-        <v>419</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L59" s="45">
-        <v>383</v>
-      </c>
-      <c r="M59" s="70" t="s">
-        <v>3960</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>3964</v>
-      </c>
+      <c r="A59" s="45"/>
+      <c r="B59" s="74" t="s">
+        <v>3986</v>
+      </c>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45" t="s">
+        <v>3289</v>
+      </c>
+      <c r="F59" s="73" t="s">
+        <v>3982</v>
+      </c>
+      <c r="G59" s="45">
+        <v>1777</v>
+      </c>
+      <c r="H59" s="45"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="45"/>
+      <c r="M59" s="45"/>
+      <c r="N59" s="45"/>
       <c r="O59" s="19" t="s">
-        <v>3961</v>
+        <v>3983</v>
       </c>
       <c r="P59" s="45"/>
-      <c r="Q59" s="45"/>
+      <c r="Q59" s="73" t="s">
+        <v>3984</v>
+      </c>
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
-      <c r="B60" s="74" t="s">
-        <v>3987</v>
+      <c r="B60" s="45" t="s">
+        <v>3985</v>
       </c>
       <c r="C60" s="45"/>
       <c r="D60" s="45"/>
       <c r="E60" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="F60" s="73" t="s">
-        <v>3983</v>
-      </c>
-      <c r="G60" s="45">
-        <v>1777</v>
-      </c>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="73" t="s">
-        <v>26</v>
+        <v>433</v>
+      </c>
+      <c r="F60" s="74" t="s">
+        <v>3987</v>
+      </c>
+      <c r="G60" s="74" t="s">
+        <v>3988</v>
+      </c>
+      <c r="H60" s="74" t="s">
+        <v>3988</v>
+      </c>
+      <c r="I60" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="J60" s="74" t="s">
+        <v>3989</v>
+      </c>
+      <c r="K60" s="74" t="s">
+        <v>61</v>
       </c>
       <c r="L60" s="45"/>
-      <c r="M60" s="45"/>
+      <c r="M60" s="74" t="s">
+        <v>3985</v>
+      </c>
       <c r="N60" s="45"/>
       <c r="O60" s="19" t="s">
-        <v>3984</v>
-      </c>
-      <c r="P60" s="45"/>
-      <c r="Q60" s="73" t="s">
-        <v>3985</v>
-      </c>
+        <v>3990</v>
+      </c>
+      <c r="P60" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q60" s="45"/>
       <c r="R60" s="45"/>
-    </row>
-    <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="45"/>
-      <c r="B61" s="45" t="s">
-        <v>3986</v>
-      </c>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45" t="s">
-        <v>433</v>
-      </c>
-      <c r="F61" s="74" t="s">
-        <v>3988</v>
-      </c>
-      <c r="G61" s="74" t="s">
-        <v>3989</v>
-      </c>
-      <c r="H61" s="74" t="s">
-        <v>3989</v>
-      </c>
-      <c r="I61" s="74" t="s">
-        <v>197</v>
-      </c>
-      <c r="J61" s="74" t="s">
-        <v>3990</v>
-      </c>
-      <c r="K61" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="L61" s="45"/>
-      <c r="M61" s="74" t="s">
-        <v>3986</v>
-      </c>
-      <c r="N61" s="45"/>
-      <c r="O61" s="19" t="s">
-        <v>3991</v>
-      </c>
-      <c r="P61" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q61" s="45"/>
-      <c r="R61" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="28" type="noConversion"/>
@@ -45360,54 +45374,53 @@
     <hyperlink ref="O24" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
     <hyperlink ref="N25" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
     <hyperlink ref="O25" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="O26" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="N27" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="O27" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="N28" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="N29" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="N30" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="O30" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="O31" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="O33" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="N33" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="O35" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="N34" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="O34" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="N36" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="N35" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="N37" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="O37" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="O39" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="N39" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="O42" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="O44" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="O45" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="O41" r:id="rId63" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="O48" r:id="rId64" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="N50" r:id="rId65" xr:uid="{23B55178-69CD-4A5E-B8C8-EEAB50CCF3A4}"/>
-    <hyperlink ref="O50" r:id="rId66" xr:uid="{DD9658B3-4899-4307-A572-493280AD9DCA}"/>
-    <hyperlink ref="O51" r:id="rId67" xr:uid="{409512AD-4AFB-4C08-95F6-E5409FAF0083}"/>
-    <hyperlink ref="O52" r:id="rId68" xr:uid="{84071305-5C0F-4713-9505-63E4B3450192}"/>
-    <hyperlink ref="O53" r:id="rId69" xr:uid="{713EAC2E-65D7-4C67-BED8-E6E4427B1187}"/>
-    <hyperlink ref="O54" r:id="rId70" xr:uid="{CFEBCD8C-93AE-4F63-A06D-C84590D9303A}"/>
-    <hyperlink ref="N44" r:id="rId71" xr:uid="{F4C55FB2-E9A9-4D79-88B2-0477AE0C670F}"/>
-    <hyperlink ref="N45" r:id="rId72" xr:uid="{6288BB8E-53D8-4FDD-8817-FD54CF2E1FDC}"/>
-    <hyperlink ref="N43" r:id="rId73" xr:uid="{77B777FF-06F4-4C87-8FCF-921CFC7B7392}"/>
-    <hyperlink ref="N2" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="N48" r:id="rId75" xr:uid="{9AF19D18-8C14-4B5B-B6D5-6A400CB8F9AF}"/>
-    <hyperlink ref="O55" r:id="rId76" xr:uid="{90BF12DF-5857-4919-AD21-7284BEEAA61F}"/>
-    <hyperlink ref="N56" r:id="rId77" xr:uid="{ADF10015-C010-477B-9A20-574A643565CD}"/>
-    <hyperlink ref="O58" r:id="rId78" xr:uid="{467AC07A-17A6-4EB4-AC4E-28DE935BA4BE}"/>
-    <hyperlink ref="O57" r:id="rId79" xr:uid="{6F999F56-AD02-4951-9706-C7B8148F8E2A}"/>
-    <hyperlink ref="N59" r:id="rId80" xr:uid="{46152AA1-6EC2-4483-AA15-E1CC65968977}"/>
-    <hyperlink ref="O59" r:id="rId81" xr:uid="{0F09B375-5A60-41A8-8909-6A8862B203D3}"/>
-    <hyperlink ref="O60" r:id="rId82" xr:uid="{6A39D157-F210-4892-95B6-5107F8DF777C}"/>
-    <hyperlink ref="O61" r:id="rId83" xr:uid="{96D11007-6757-4F70-AB48-16741226BC93}"/>
+    <hyperlink ref="N26" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="O26" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="N27" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="N28" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="N29" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="O29" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="O30" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="O32" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="N32" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="O34" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="N33" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="O33" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="N35" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="N34" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="N36" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="O36" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="O38" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="N38" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="O41" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="O43" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="O44" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="O40" r:id="rId62" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="O47" r:id="rId63" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="N49" r:id="rId64" xr:uid="{23B55178-69CD-4A5E-B8C8-EEAB50CCF3A4}"/>
+    <hyperlink ref="O49" r:id="rId65" xr:uid="{DD9658B3-4899-4307-A572-493280AD9DCA}"/>
+    <hyperlink ref="O50" r:id="rId66" xr:uid="{409512AD-4AFB-4C08-95F6-E5409FAF0083}"/>
+    <hyperlink ref="O51" r:id="rId67" xr:uid="{84071305-5C0F-4713-9505-63E4B3450192}"/>
+    <hyperlink ref="O52" r:id="rId68" xr:uid="{713EAC2E-65D7-4C67-BED8-E6E4427B1187}"/>
+    <hyperlink ref="O53" r:id="rId69" xr:uid="{CFEBCD8C-93AE-4F63-A06D-C84590D9303A}"/>
+    <hyperlink ref="N43" r:id="rId70" xr:uid="{F4C55FB2-E9A9-4D79-88B2-0477AE0C670F}"/>
+    <hyperlink ref="N44" r:id="rId71" xr:uid="{6288BB8E-53D8-4FDD-8817-FD54CF2E1FDC}"/>
+    <hyperlink ref="N42" r:id="rId72" xr:uid="{77B777FF-06F4-4C87-8FCF-921CFC7B7392}"/>
+    <hyperlink ref="N2" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="N47" r:id="rId74" xr:uid="{9AF19D18-8C14-4B5B-B6D5-6A400CB8F9AF}"/>
+    <hyperlink ref="O54" r:id="rId75" xr:uid="{90BF12DF-5857-4919-AD21-7284BEEAA61F}"/>
+    <hyperlink ref="N55" r:id="rId76" xr:uid="{ADF10015-C010-477B-9A20-574A643565CD}"/>
+    <hyperlink ref="O57" r:id="rId77" xr:uid="{467AC07A-17A6-4EB4-AC4E-28DE935BA4BE}"/>
+    <hyperlink ref="O56" r:id="rId78" xr:uid="{6F999F56-AD02-4951-9706-C7B8148F8E2A}"/>
+    <hyperlink ref="N58" r:id="rId79" xr:uid="{46152AA1-6EC2-4483-AA15-E1CC65968977}"/>
+    <hyperlink ref="O58" r:id="rId80" xr:uid="{0F09B375-5A60-41A8-8909-6A8862B203D3}"/>
+    <hyperlink ref="O59" r:id="rId81" xr:uid="{6A39D157-F210-4892-95B6-5107F8DF777C}"/>
+    <hyperlink ref="O60" r:id="rId82" xr:uid="{96D11007-6757-4F70-AB48-16741226BC93}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId84"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId83"/>
   <tableParts count="1">
-    <tablePart r:id="rId85"/>
+    <tablePart r:id="rId84"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45426,38 +45439,38 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
+        <v>3610</v>
+      </c>
+      <c r="B1" s="59" t="s">
         <v>3611</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="C1" s="59" t="s">
         <v>3612</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="D1" s="59" t="s">
         <v>3613</v>
       </c>
-      <c r="D1" s="59" t="s">
-        <v>3614</v>
-      </c>
       <c r="E1" s="59" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
+        <v>3859</v>
+      </c>
+      <c r="C2" s="60" t="s">
         <v>3860</v>
       </c>
-      <c r="C2" s="60" t="s">
-        <v>3861</v>
-      </c>
       <c r="D2" s="60" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="B3" s="59">
         <v>432</v>
@@ -45474,7 +45487,7 @@
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="B4" s="59">
         <v>1897</v>
@@ -45488,7 +45501,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="B5" s="59">
         <v>32</v>
@@ -45502,7 +45515,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="B6" s="59">
         <v>37</v>
@@ -45516,7 +45529,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="B7" s="59">
         <v>335</v>
@@ -45530,7 +45543,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="B8" s="59">
         <v>28</v>
@@ -45544,7 +45557,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="B9" s="59">
         <v>103</v>
@@ -45558,7 +45571,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="C10" s="59">
         <v>225</v>
@@ -45569,7 +45582,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="C11" s="59">
         <v>55</v>
@@ -45580,7 +45593,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="C12" s="59">
         <v>39</v>
@@ -45591,7 +45604,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="C13" s="59">
         <v>113</v>
@@ -45602,7 +45615,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="59" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
     </row>
   </sheetData>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679FDEEA-0EE8-4062-B340-F0DF8877B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DCED18-F276-4445-B03B-F55FE61B52B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8365" uniqueCount="4016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8393" uniqueCount="4024">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12067,9 +12067,6 @@
     <t>R/35649(2)</t>
   </si>
   <si>
-    <t>1552-02-12 ad quem</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -12086,6 +12083,33 @@
   </si>
   <si>
     <t>51</t>
+  </si>
+  <si>
+    <t>HSMS-0592</t>
+  </si>
+  <si>
+    <t>PP39</t>
+  </si>
+  <si>
+    <t>R/31788</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/card?id=fb3c34fa-b388-4569-b346-4ec2ff0bf37e</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/es/card?id=34d961a3-9c5d-47f1-88ce-f07f397e37bc</t>
+  </si>
+  <si>
+    <t>HSMS-0593</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>R/9430</t>
+  </si>
+  <si>
+    <t>1539-10-11 a quo</t>
   </si>
 </sst>
 </file>
@@ -12999,8 +13023,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T592" totalsRowShown="0">
-  <autoFilter ref="A1:T592" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T594" totalsRowShown="0">
+  <autoFilter ref="A1:T594" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13250,7 +13274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T592"/>
+  <dimension ref="A1:T594"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -41892,10 +41916,10 @@
         <v>4008</v>
       </c>
       <c r="G591" s="2" t="s">
-        <v>4009</v>
+        <v>3515</v>
       </c>
       <c r="H591" s="2" t="s">
-        <v>4009</v>
+        <v>3515</v>
       </c>
       <c r="I591" s="2" t="s">
         <v>2383</v>
@@ -41907,13 +41931,13 @@
         <v>61</v>
       </c>
       <c r="L591" s="2" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="M591" s="2" t="s">
         <v>4006</v>
       </c>
       <c r="O591" s="19" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="Q591" s="1" t="s">
         <v>123</v>
@@ -41924,7 +41948,7 @@
     </row>
     <row r="592" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B592" s="32" t="s">
         <v>3387</v>
@@ -41953,19 +41977,107 @@
         <v>61</v>
       </c>
       <c r="L592" s="35" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="M592" s="32" t="s">
         <v>3387</v>
       </c>
       <c r="N592" s="32"/>
       <c r="O592" s="33" t="s">
+        <v>4012</v>
+      </c>
+      <c r="Q592" s="1" t="s">
         <v>4013</v>
       </c>
-      <c r="Q592" s="1" t="s">
-        <v>4014</v>
-      </c>
       <c r="T592" s="25" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="593" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="12" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>4016</v>
+      </c>
+      <c r="E593" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F593" s="2" t="s">
+        <v>4017</v>
+      </c>
+      <c r="G593" s="2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="I593" s="2" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J593" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K593" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L593" s="2" t="s">
+        <v>3643</v>
+      </c>
+      <c r="M593" s="2" t="s">
+        <v>4016</v>
+      </c>
+      <c r="O593" s="19" t="s">
+        <v>4018</v>
+      </c>
+      <c r="Q593" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T593" s="25" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="12" t="s">
+        <v>4020</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>4021</v>
+      </c>
+      <c r="E594" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F594" s="2" t="s">
+        <v>4022</v>
+      </c>
+      <c r="G594" s="2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H594" s="2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="I594" s="2" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J594" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K594" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L594" s="2" t="s">
+        <v>3644</v>
+      </c>
+      <c r="M594" s="2" t="s">
+        <v>4021</v>
+      </c>
+      <c r="O594" s="19" t="s">
+        <v>4019</v>
+      </c>
+      <c r="Q594" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T594" s="25" t="s">
         <v>3571</v>
       </c>
     </row>
@@ -42671,11 +42783,13 @@
     <hyperlink ref="O589" r:id="rId697" xr:uid="{8E3B950A-60B6-4BD2-AF86-E74D5A995BD4}"/>
     <hyperlink ref="O590" r:id="rId698" xr:uid="{9FA755FB-B909-43E2-A231-6E621B82B6BC}"/>
     <hyperlink ref="O591" r:id="rId699" xr:uid="{EC81F8E4-8209-45C4-AC78-47B5116C1B07}"/>
+    <hyperlink ref="O593" r:id="rId700" xr:uid="{F3277743-3EA6-431A-9337-474B33DEDDC4}"/>
+    <hyperlink ref="O594" r:id="rId701" xr:uid="{B9D8FABB-89C6-4AB6-8550-7176B66C9ABE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId700"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId702"/>
   <tableParts count="1">
-    <tablePart r:id="rId701"/>
+    <tablePart r:id="rId703"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DCED18-F276-4445-B03B-F55FE61B52B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB7AE1B-E7BF-4152-A904-7CDD0BE63C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8393" uniqueCount="4024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8407" uniqueCount="4030">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12110,6 +12110,24 @@
   </si>
   <si>
     <t>1539-10-11 a quo</t>
+  </si>
+  <si>
+    <t>RCP</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/card?id=532ba596-66ee-4a60-b862-870f5c23b2bd</t>
+  </si>
+  <si>
+    <t>HSMS-0594</t>
+  </si>
+  <si>
+    <t>R/4459</t>
+  </si>
+  <si>
+    <t>Felipe de Junta y Juan Bautista Varesio</t>
+  </si>
+  <si>
+    <t>1597-01-16 a quo</t>
   </si>
 </sst>
 </file>
@@ -13023,8 +13041,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T594" totalsRowShown="0">
-  <autoFilter ref="A1:T594" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T595" totalsRowShown="0">
+  <autoFilter ref="A1:T595" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13274,31 +13292,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T594"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T595"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="18.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="41.6640625" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" style="4" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" customWidth="1"/>
     <col min="14" max="14" width="45" style="1" customWidth="1"/>
-    <col min="15" max="15" width="59.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" customWidth="1"/>
-    <col min="17" max="17" width="41.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="59.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="17" max="17" width="41.33203125" style="1" customWidth="1"/>
     <col min="18" max="19" width="58" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="1"/>
+    <col min="20" max="20" width="11.6640625" customWidth="1"/>
+    <col min="21" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13360,7 +13378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -13407,7 +13425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -13452,7 +13470,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -13502,7 +13520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -13544,7 +13562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -13594,7 +13612,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -13644,7 +13662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>74</v>
       </c>
@@ -13691,7 +13709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -13741,7 +13759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="150" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>91</v>
       </c>
@@ -13791,7 +13809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
@@ -13844,7 +13862,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>108</v>
       </c>
@@ -13900,7 +13918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>117</v>
       </c>
@@ -13947,7 +13965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>124</v>
       </c>
@@ -14001,7 +14019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>134</v>
       </c>
@@ -14051,7 +14069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>143</v>
       </c>
@@ -14096,7 +14114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -14143,7 +14161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
@@ -14185,7 +14203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>163</v>
       </c>
@@ -14230,7 +14248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>170</v>
       </c>
@@ -14281,7 +14299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>177</v>
       </c>
@@ -14328,7 +14346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>186</v>
       </c>
@@ -14378,7 +14396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>193</v>
       </c>
@@ -14425,7 +14443,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>200</v>
       </c>
@@ -14472,7 +14490,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -14519,7 +14537,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>213</v>
       </c>
@@ -14566,7 +14584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>220</v>
       </c>
@@ -14613,7 +14631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>226</v>
       </c>
@@ -14663,7 +14681,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>235</v>
       </c>
@@ -14710,7 +14728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>242</v>
       </c>
@@ -14757,7 +14775,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>249</v>
       </c>
@@ -14810,7 +14828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>256</v>
       </c>
@@ -14857,7 +14875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>263</v>
       </c>
@@ -14908,7 +14926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>270</v>
       </c>
@@ -14956,7 +14974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>276</v>
       </c>
@@ -15009,7 +15027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>285</v>
       </c>
@@ -15057,7 +15075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>291</v>
       </c>
@@ -15102,7 +15120,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>296</v>
       </c>
@@ -15150,7 +15168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>301</v>
       </c>
@@ -15201,7 +15219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>306</v>
       </c>
@@ -15252,7 +15270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>312</v>
       </c>
@@ -15300,7 +15318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>320</v>
       </c>
@@ -15356,7 +15374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>328</v>
       </c>
@@ -15404,7 +15422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>333</v>
       </c>
@@ -15452,7 +15470,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>340</v>
       </c>
@@ -15500,7 +15518,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>345</v>
       </c>
@@ -15548,7 +15566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>351</v>
       </c>
@@ -15604,7 +15622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>361</v>
       </c>
@@ -15652,7 +15670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>367</v>
       </c>
@@ -15700,7 +15718,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>373</v>
       </c>
@@ -15748,7 +15766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>379</v>
       </c>
@@ -15801,7 +15819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>389</v>
       </c>
@@ -15846,7 +15864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>395</v>
       </c>
@@ -15894,7 +15912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>403</v>
       </c>
@@ -15941,7 +15959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>409</v>
       </c>
@@ -15991,7 +16009,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>416</v>
       </c>
@@ -16041,7 +16059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>424</v>
       </c>
@@ -16094,7 +16112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>431</v>
       </c>
@@ -16145,7 +16163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>441</v>
       </c>
@@ -16196,7 +16214,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>447</v>
       </c>
@@ -16244,7 +16262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>452</v>
       </c>
@@ -16295,7 +16313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>458</v>
       </c>
@@ -16349,7 +16367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>466</v>
       </c>
@@ -16403,7 +16421,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>472</v>
       </c>
@@ -16451,7 +16469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>477</v>
       </c>
@@ -16502,7 +16520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>481</v>
       </c>
@@ -16549,7 +16567,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>487</v>
       </c>
@@ -16599,7 +16617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>495</v>
       </c>
@@ -16649,7 +16667,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>501</v>
       </c>
@@ -16696,7 +16714,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>506</v>
       </c>
@@ -16743,7 +16761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>513</v>
       </c>
@@ -16790,7 +16808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>520</v>
       </c>
@@ -16840,7 +16858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>526</v>
       </c>
@@ -16890,7 +16908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>531</v>
       </c>
@@ -16943,7 +16961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>539</v>
       </c>
@@ -16993,7 +17011,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>546</v>
       </c>
@@ -17040,7 +17058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>552</v>
       </c>
@@ -17087,7 +17105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>558</v>
       </c>
@@ -17134,7 +17152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>564</v>
       </c>
@@ -17181,7 +17199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>570</v>
       </c>
@@ -17234,7 +17252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>581</v>
       </c>
@@ -17281,7 +17299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>587</v>
       </c>
@@ -17328,7 +17346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>593</v>
       </c>
@@ -17378,7 +17396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>602</v>
       </c>
@@ -17428,7 +17446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>611</v>
       </c>
@@ -17478,7 +17496,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>618</v>
       </c>
@@ -17531,7 +17549,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>625</v>
       </c>
@@ -17578,7 +17596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>633</v>
       </c>
@@ -17628,7 +17646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>640</v>
       </c>
@@ -17678,7 +17696,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>647</v>
       </c>
@@ -17725,7 +17743,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>654</v>
       </c>
@@ -17772,7 +17790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>660</v>
       </c>
@@ -17819,7 +17837,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>666</v>
       </c>
@@ -17869,7 +17887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>674</v>
       </c>
@@ -17916,7 +17934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>682</v>
       </c>
@@ -17966,7 +17984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>690</v>
       </c>
@@ -18017,7 +18035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>696</v>
       </c>
@@ -18067,7 +18085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>704</v>
       </c>
@@ -18117,7 +18135,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>711</v>
       </c>
@@ -18167,7 +18185,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>717</v>
       </c>
@@ -18221,7 +18239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>725</v>
       </c>
@@ -18274,7 +18292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>732</v>
       </c>
@@ -18321,7 +18339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>738</v>
       </c>
@@ -18371,7 +18389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>745</v>
       </c>
@@ -18421,7 +18439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>754</v>
       </c>
@@ -18468,7 +18486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>762</v>
       </c>
@@ -18518,7 +18536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>770</v>
       </c>
@@ -18568,7 +18586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>778</v>
       </c>
@@ -18618,7 +18636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>785</v>
       </c>
@@ -18668,7 +18686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>793</v>
       </c>
@@ -18721,7 +18739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>801</v>
       </c>
@@ -18774,7 +18792,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>807</v>
       </c>
@@ -18827,7 +18845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>817</v>
       </c>
@@ -18877,7 +18895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>823</v>
       </c>
@@ -18927,7 +18945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>829</v>
       </c>
@@ -18974,7 +18992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>835</v>
       </c>
@@ -19021,7 +19039,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>842</v>
       </c>
@@ -19071,7 +19089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>848</v>
       </c>
@@ -19121,7 +19139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>854</v>
       </c>
@@ -19168,7 +19186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>861</v>
       </c>
@@ -19218,7 +19236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>868</v>
       </c>
@@ -19268,7 +19286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>873</v>
       </c>
@@ -19318,7 +19336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>879</v>
       </c>
@@ -19371,7 +19389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>888</v>
       </c>
@@ -19421,7 +19439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>895</v>
       </c>
@@ -19466,7 +19484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>900</v>
       </c>
@@ -19516,7 +19534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>909</v>
       </c>
@@ -19566,7 +19584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>917</v>
       </c>
@@ -19616,7 +19634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>924</v>
       </c>
@@ -19666,7 +19684,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>931</v>
       </c>
@@ -19716,7 +19734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>937</v>
       </c>
@@ -19761,7 +19779,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>943</v>
       </c>
@@ -19814,7 +19832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>949</v>
       </c>
@@ -19864,7 +19882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>955</v>
       </c>
@@ -19914,7 +19932,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>962</v>
       </c>
@@ -19970,7 +19988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>971</v>
       </c>
@@ -20024,7 +20042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>978</v>
       </c>
@@ -20071,7 +20089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>984</v>
       </c>
@@ -20118,7 +20136,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>991</v>
       </c>
@@ -20168,7 +20186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>1001</v>
       </c>
@@ -20218,7 +20236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>1008</v>
       </c>
@@ -20265,7 +20283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>1015</v>
       </c>
@@ -20315,7 +20333,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20362,7 +20380,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>1029</v>
       </c>
@@ -20412,7 +20430,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>1036</v>
       </c>
@@ -20462,7 +20480,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>1044</v>
       </c>
@@ -20512,7 +20530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>1051</v>
       </c>
@@ -20559,7 +20577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>1057</v>
       </c>
@@ -20609,7 +20627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>1062</v>
       </c>
@@ -20656,7 +20674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>1069</v>
       </c>
@@ -20703,7 +20721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>1074</v>
       </c>
@@ -20753,7 +20771,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>1080</v>
       </c>
@@ -20806,7 +20824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>1085</v>
       </c>
@@ -20853,7 +20871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>1090</v>
       </c>
@@ -20903,7 +20921,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>1097</v>
       </c>
@@ -20950,7 +20968,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>1103</v>
       </c>
@@ -20995,7 +21013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>1109</v>
       </c>
@@ -21042,7 +21060,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>1116</v>
       </c>
@@ -21098,7 +21116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>1124</v>
       </c>
@@ -21152,7 +21170,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>1134</v>
       </c>
@@ -21202,7 +21220,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>1140</v>
       </c>
@@ -21255,7 +21273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>1147</v>
       </c>
@@ -21308,7 +21326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>1155</v>
       </c>
@@ -21356,7 +21374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>1161</v>
       </c>
@@ -21409,7 +21427,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21462,7 +21480,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>1177</v>
       </c>
@@ -21512,7 +21530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>1185</v>
       </c>
@@ -21560,7 +21578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>1190</v>
       </c>
@@ -21608,7 +21626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>1195</v>
       </c>
@@ -21658,7 +21676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>1202</v>
       </c>
@@ -21708,7 +21726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>1210</v>
       </c>
@@ -21758,7 +21776,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>1217</v>
       </c>
@@ -21808,7 +21826,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>1223</v>
       </c>
@@ -21856,7 +21874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>1228</v>
       </c>
@@ -21906,7 +21924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>1236</v>
       </c>
@@ -21959,7 +21977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>1242</v>
       </c>
@@ -22007,7 +22025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>1248</v>
       </c>
@@ -22063,7 +22081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>1256</v>
       </c>
@@ -22116,7 +22134,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>1262</v>
       </c>
@@ -22166,7 +22184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>1267</v>
       </c>
@@ -22214,7 +22232,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>1273</v>
       </c>
@@ -22267,7 +22285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>1279</v>
       </c>
@@ -22317,7 +22335,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>1285</v>
       </c>
@@ -22367,7 +22385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>1293</v>
       </c>
@@ -22420,7 +22438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>1301</v>
       </c>
@@ -22468,7 +22486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>1308</v>
       </c>
@@ -22513,7 +22531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>1313</v>
       </c>
@@ -22558,7 +22576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>1319</v>
       </c>
@@ -22605,7 +22623,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>1327</v>
       </c>
@@ -22653,7 +22671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22706,7 +22724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>1342</v>
       </c>
@@ -22756,7 +22774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>1349</v>
       </c>
@@ -22803,7 +22821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>1354</v>
       </c>
@@ -22853,7 +22871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>1360</v>
       </c>
@@ -22900,7 +22918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>1364</v>
       </c>
@@ -22950,7 +22968,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>1372</v>
       </c>
@@ -23000,7 +23018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>1381</v>
       </c>
@@ -23050,7 +23068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>1386</v>
       </c>
@@ -23100,7 +23118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>1392</v>
       </c>
@@ -23150,7 +23168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>1398</v>
       </c>
@@ -23200,7 +23218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>1405</v>
       </c>
@@ -23248,7 +23266,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>1414</v>
       </c>
@@ -23296,7 +23314,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>1421</v>
       </c>
@@ -23342,7 +23360,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>1426</v>
       </c>
@@ -23389,7 +23407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>1432</v>
       </c>
@@ -23439,7 +23457,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>1437</v>
       </c>
@@ -23483,7 +23501,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>1440</v>
       </c>
@@ -23527,7 +23545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>1444</v>
       </c>
@@ -23575,7 +23593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>1450</v>
       </c>
@@ -23628,7 +23646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>1456</v>
       </c>
@@ -23676,7 +23694,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>1464</v>
       </c>
@@ -23726,7 +23744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>1470</v>
       </c>
@@ -23776,7 +23794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>1476</v>
       </c>
@@ -23829,7 +23847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>1483</v>
       </c>
@@ -23885,7 +23903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>1491</v>
       </c>
@@ -23941,7 +23959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>1498</v>
       </c>
@@ -23989,7 +24007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>1504</v>
       </c>
@@ -24042,7 +24060,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>1511</v>
       </c>
@@ -24086,7 +24104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>1515</v>
       </c>
@@ -24139,7 +24157,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>1521</v>
       </c>
@@ -24189,7 +24207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>1526</v>
       </c>
@@ -24242,7 +24260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>1532</v>
       </c>
@@ -24292,7 +24310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>1538</v>
       </c>
@@ -24342,7 +24360,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>1545</v>
       </c>
@@ -24395,7 +24413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>1554</v>
       </c>
@@ -24443,7 +24461,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>1563</v>
       </c>
@@ -24493,7 +24511,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>1570</v>
       </c>
@@ -24543,7 +24561,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>1577</v>
       </c>
@@ -24593,7 +24611,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>1584</v>
       </c>
@@ -24643,7 +24661,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>1593</v>
       </c>
@@ -24693,7 +24711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>1599</v>
       </c>
@@ -24741,7 +24759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>1603</v>
       </c>
@@ -24788,7 +24806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>1609</v>
       </c>
@@ -24838,7 +24856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>1616</v>
       </c>
@@ -24890,7 +24908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>1624</v>
       </c>
@@ -24937,7 +24955,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>1632</v>
       </c>
@@ -24987,7 +25005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>1639</v>
       </c>
@@ -25037,7 +25055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>1645</v>
       </c>
@@ -25084,7 +25102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>1650</v>
       </c>
@@ -25131,7 +25149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>1655</v>
       </c>
@@ -25181,7 +25199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>1659</v>
       </c>
@@ -25228,7 +25246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>1665</v>
       </c>
@@ -25275,7 +25293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>1670</v>
       </c>
@@ -25325,7 +25343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>1676</v>
       </c>
@@ -25372,7 +25390,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>1682</v>
       </c>
@@ -25425,7 +25443,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>1690</v>
       </c>
@@ -25472,7 +25490,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>1695</v>
       </c>
@@ -25519,7 +25537,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>1700</v>
       </c>
@@ -25569,7 +25587,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>1706</v>
       </c>
@@ -25616,7 +25634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>1712</v>
       </c>
@@ -25665,7 +25683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>1718</v>
       </c>
@@ -25712,7 +25730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>1724</v>
       </c>
@@ -25759,7 +25777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>1730</v>
       </c>
@@ -25806,7 +25824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>1736</v>
       </c>
@@ -25851,7 +25869,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>1741</v>
       </c>
@@ -25893,7 +25911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>1746</v>
       </c>
@@ -25946,7 +25964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>1754</v>
       </c>
@@ -25993,7 +26011,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>1758</v>
       </c>
@@ -26040,7 +26058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>1764</v>
       </c>
@@ -26090,7 +26108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>1769</v>
       </c>
@@ -26140,7 +26158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>1777</v>
       </c>
@@ -26192,7 +26210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>1782</v>
       </c>
@@ -26239,7 +26257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>1786</v>
       </c>
@@ -26289,7 +26307,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>1792</v>
       </c>
@@ -26339,7 +26357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>1796</v>
       </c>
@@ -26389,7 +26407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>1802</v>
       </c>
@@ -26436,7 +26454,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>1805</v>
       </c>
@@ -26483,7 +26501,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>1808</v>
       </c>
@@ -26530,7 +26548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>1811</v>
       </c>
@@ -26579,7 +26597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>1817</v>
       </c>
@@ -26626,7 +26644,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>1821</v>
       </c>
@@ -26674,7 +26692,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>1827</v>
       </c>
@@ -26724,7 +26742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>1832</v>
       </c>
@@ -26774,7 +26792,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>1837</v>
       </c>
@@ -26819,7 +26837,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>1841</v>
       </c>
@@ -26866,7 +26884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>1847</v>
       </c>
@@ -26916,7 +26934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>1852</v>
       </c>
@@ -26964,7 +26982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>1857</v>
       </c>
@@ -27011,7 +27029,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>1863</v>
       </c>
@@ -27061,7 +27079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>1868</v>
       </c>
@@ -27111,7 +27129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>1874</v>
       </c>
@@ -27159,7 +27177,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>1880</v>
       </c>
@@ -27207,7 +27225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>1886</v>
       </c>
@@ -27255,7 +27273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>1891</v>
       </c>
@@ -27305,7 +27323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>1896</v>
       </c>
@@ -27350,7 +27368,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>1901</v>
       </c>
@@ -27395,7 +27413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>1907</v>
       </c>
@@ -27446,7 +27464,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>1914</v>
       </c>
@@ -27496,7 +27514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>1920</v>
       </c>
@@ -27543,7 +27561,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>1924</v>
       </c>
@@ -27591,7 +27609,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>1931</v>
       </c>
@@ -27641,7 +27659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>1936</v>
       </c>
@@ -27693,7 +27711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>1944</v>
       </c>
@@ -27740,7 +27758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>1950</v>
       </c>
@@ -27790,7 +27808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>1954</v>
       </c>
@@ -27835,7 +27853,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>1958</v>
       </c>
@@ -27885,7 +27903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>1963</v>
       </c>
@@ -27930,7 +27948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>1967</v>
       </c>
@@ -27978,7 +27996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>1973</v>
       </c>
@@ -28023,7 +28041,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>1978</v>
       </c>
@@ -28073,7 +28091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>1984</v>
       </c>
@@ -28126,7 +28144,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>1990</v>
       </c>
@@ -28171,7 +28189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>1995</v>
       </c>
@@ -28218,7 +28236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>2000</v>
       </c>
@@ -28268,7 +28286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>2007</v>
       </c>
@@ -28313,7 +28331,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>2011</v>
       </c>
@@ -28360,7 +28378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>2017</v>
       </c>
@@ -28408,7 +28426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>2023</v>
       </c>
@@ -28455,7 +28473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>2029</v>
       </c>
@@ -28505,7 +28523,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>2033</v>
       </c>
@@ -28558,7 +28576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>2038</v>
       </c>
@@ -28608,7 +28626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>2045</v>
       </c>
@@ -28658,7 +28676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>2049</v>
       </c>
@@ -28703,7 +28721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>2054</v>
       </c>
@@ -28750,7 +28768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>2060</v>
       </c>
@@ -28800,7 +28818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>2065</v>
       </c>
@@ -28848,7 +28866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>2070</v>
       </c>
@@ -28893,7 +28911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>2074</v>
       </c>
@@ -28941,7 +28959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>2080</v>
       </c>
@@ -28986,7 +29004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>2084</v>
       </c>
@@ -29040,7 +29058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>2090</v>
       </c>
@@ -29090,7 +29108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>2097</v>
       </c>
@@ -29140,7 +29158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>2103</v>
       </c>
@@ -29196,7 +29214,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>2108</v>
       </c>
@@ -29246,7 +29264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>2115</v>
       </c>
@@ -29291,7 +29309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>2120</v>
       </c>
@@ -29336,7 +29354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>2126</v>
       </c>
@@ -29381,7 +29399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>2131</v>
       </c>
@@ -29429,7 +29447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>2136</v>
       </c>
@@ -29474,7 +29492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>2140</v>
       </c>
@@ -29522,7 +29540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>2147</v>
       </c>
@@ -29573,7 +29591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>2154</v>
       </c>
@@ -29624,7 +29642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>2161</v>
       </c>
@@ -29674,7 +29692,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>2167</v>
       </c>
@@ -29727,7 +29745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>2173</v>
       </c>
@@ -29777,7 +29795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>2179</v>
       </c>
@@ -29828,7 +29846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>2185</v>
       </c>
@@ -29881,7 +29899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>2193</v>
       </c>
@@ -29934,7 +29952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>2202</v>
       </c>
@@ -29984,7 +30002,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>2209</v>
       </c>
@@ -30034,7 +30052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>2214</v>
       </c>
@@ -30082,7 +30100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>2222</v>
       </c>
@@ -30132,7 +30150,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>2230</v>
       </c>
@@ -30179,7 +30197,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>2236</v>
       </c>
@@ -30227,7 +30245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>2240</v>
       </c>
@@ -30280,7 +30298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>2245</v>
       </c>
@@ -30327,7 +30345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>2253</v>
       </c>
@@ -30377,7 +30395,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>2261</v>
       </c>
@@ -30422,7 +30440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>2266</v>
       </c>
@@ -30475,7 +30493,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>2272</v>
       </c>
@@ -30525,7 +30543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>2278</v>
       </c>
@@ -30575,7 +30593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>2286</v>
       </c>
@@ -30620,7 +30638,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>2293</v>
       </c>
@@ -30670,7 +30688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>2301</v>
       </c>
@@ -30723,7 +30741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>2307</v>
       </c>
@@ -30776,7 +30794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>2313</v>
       </c>
@@ -30826,7 +30844,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>2321</v>
       </c>
@@ -30876,7 +30894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>2329</v>
       </c>
@@ -30923,7 +30941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>2335</v>
       </c>
@@ -30973,7 +30991,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>2344</v>
       </c>
@@ -31023,7 +31041,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>2351</v>
       </c>
@@ -31070,7 +31088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>2356</v>
       </c>
@@ -31120,7 +31138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>2361</v>
       </c>
@@ -31168,7 +31186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>2368</v>
       </c>
@@ -31215,7 +31233,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>2372</v>
       </c>
@@ -31268,7 +31286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>2378</v>
       </c>
@@ -31318,7 +31336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>2386</v>
       </c>
@@ -31371,7 +31389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>2392</v>
       </c>
@@ -31416,7 +31434,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>2396</v>
       </c>
@@ -31466,7 +31484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>2402</v>
       </c>
@@ -31513,7 +31531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>2407</v>
       </c>
@@ -31557,7 +31575,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>2414</v>
       </c>
@@ -31604,7 +31622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>2422</v>
       </c>
@@ -31648,7 +31666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>2428</v>
       </c>
@@ -31692,7 +31710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>2434</v>
       </c>
@@ -31739,7 +31757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>2440</v>
       </c>
@@ -31786,7 +31804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>2446</v>
       </c>
@@ -31833,7 +31851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>2452</v>
       </c>
@@ -31877,7 +31895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>2458</v>
       </c>
@@ -31921,7 +31939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>2462</v>
       </c>
@@ -31968,7 +31986,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>2469</v>
       </c>
@@ -32015,7 +32033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>2475</v>
       </c>
@@ -32059,7 +32077,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>2480</v>
       </c>
@@ -32103,7 +32121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>2484</v>
       </c>
@@ -32147,7 +32165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>2489</v>
       </c>
@@ -32191,7 +32209,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>2493</v>
       </c>
@@ -32238,7 +32256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>2500</v>
       </c>
@@ -32285,7 +32303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>2506</v>
       </c>
@@ -32329,7 +32347,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>2510</v>
       </c>
@@ -32373,7 +32391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>2514</v>
       </c>
@@ -32426,7 +32444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>2520</v>
       </c>
@@ -32470,7 +32488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>2526</v>
       </c>
@@ -32514,7 +32532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>2531</v>
       </c>
@@ -32555,7 +32573,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>2535</v>
       </c>
@@ -32599,7 +32617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>2540</v>
       </c>
@@ -32640,7 +32658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>2545</v>
       </c>
@@ -32679,7 +32697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>2549</v>
       </c>
@@ -32720,7 +32738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>2553</v>
       </c>
@@ -32761,7 +32779,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>2558</v>
       </c>
@@ -32802,7 +32820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>2562</v>
       </c>
@@ -32843,7 +32861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>2566</v>
       </c>
@@ -32884,7 +32902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>2569</v>
       </c>
@@ -32925,7 +32943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>2574</v>
       </c>
@@ -32969,7 +32987,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>2576</v>
       </c>
@@ -33013,7 +33031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>2581</v>
       </c>
@@ -33057,7 +33075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>2586</v>
       </c>
@@ -33104,7 +33122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>2594</v>
       </c>
@@ -33151,7 +33169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>2597</v>
       </c>
@@ -33201,7 +33219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>2603</v>
       </c>
@@ -33257,7 +33275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>2612</v>
       </c>
@@ -33307,7 +33325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>2619</v>
       </c>
@@ -33351,7 +33369,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>2623</v>
       </c>
@@ -33395,7 +33413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>2628</v>
       </c>
@@ -33442,7 +33460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>2636</v>
       </c>
@@ -33483,7 +33501,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>2641</v>
       </c>
@@ -33527,7 +33545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>2646</v>
       </c>
@@ -33568,7 +33586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>2650</v>
       </c>
@@ -33612,7 +33630,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>2655</v>
       </c>
@@ -33656,7 +33674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>2660</v>
       </c>
@@ -33700,7 +33718,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>2665</v>
       </c>
@@ -33741,7 +33759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>2669</v>
       </c>
@@ -33782,7 +33800,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>2675</v>
       </c>
@@ -33826,7 +33844,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>2678</v>
       </c>
@@ -33876,7 +33894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="424" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A424" s="12" t="s">
         <v>2685</v>
       </c>
@@ -33921,7 +33939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>2689</v>
       </c>
@@ -33959,7 +33977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>2693</v>
       </c>
@@ -34003,7 +34021,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>2697</v>
       </c>
@@ -34047,7 +34065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>2703</v>
       </c>
@@ -34091,7 +34109,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>2707</v>
       </c>
@@ -34132,7 +34150,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>2710</v>
       </c>
@@ -34176,7 +34194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>2715</v>
       </c>
@@ -34217,7 +34235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>2720</v>
       </c>
@@ -34270,7 +34288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>2726</v>
       </c>
@@ -34323,7 +34341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>2734</v>
       </c>
@@ -34368,7 +34386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>2740</v>
       </c>
@@ -34412,7 +34430,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>2745</v>
       </c>
@@ -34456,7 +34474,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>2751</v>
       </c>
@@ -34500,7 +34518,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>2756</v>
       </c>
@@ -34547,7 +34565,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>2764</v>
       </c>
@@ -34600,7 +34618,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>2771</v>
       </c>
@@ -34653,7 +34671,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>2778</v>
       </c>
@@ -34706,7 +34724,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>2784</v>
       </c>
@@ -34756,7 +34774,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>2791</v>
       </c>
@@ -34809,7 +34827,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>2797</v>
       </c>
@@ -34859,7 +34877,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>2803</v>
       </c>
@@ -34912,7 +34930,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>2810</v>
       </c>
@@ -34968,7 +34986,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>2818</v>
       </c>
@@ -35015,7 +35033,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>2824</v>
       </c>
@@ -35062,7 +35080,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>2831</v>
       </c>
@@ -35112,7 +35130,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>2837</v>
       </c>
@@ -35159,7 +35177,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>2843</v>
       </c>
@@ -35206,7 +35224,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>2849</v>
       </c>
@@ -35257,7 +35275,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>2855</v>
       </c>
@@ -35308,7 +35326,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>2861</v>
       </c>
@@ -35360,7 +35378,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>2866</v>
       </c>
@@ -35407,7 +35425,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>2874</v>
       </c>
@@ -35454,7 +35472,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>2881</v>
       </c>
@@ -35503,7 +35521,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>2887</v>
       </c>
@@ -35550,7 +35568,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>2892</v>
       </c>
@@ -35594,7 +35612,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>2898</v>
       </c>
@@ -35641,7 +35659,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>2901</v>
       </c>
@@ -35682,7 +35700,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>2908</v>
       </c>
@@ -35729,7 +35747,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>2913</v>
       </c>
@@ -35774,7 +35792,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>2918</v>
       </c>
@@ -35818,7 +35836,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>2922</v>
       </c>
@@ -35868,7 +35886,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>2929</v>
       </c>
@@ -35921,7 +35939,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>2935</v>
       </c>
@@ -35971,7 +35989,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>2941</v>
       </c>
@@ -36009,7 +36027,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>2947</v>
       </c>
@@ -36059,7 +36077,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>2952</v>
       </c>
@@ -36109,7 +36127,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>2957</v>
       </c>
@@ -36158,7 +36176,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>2964</v>
       </c>
@@ -36209,7 +36227,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>2971</v>
       </c>
@@ -36260,7 +36278,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>2977</v>
       </c>
@@ -36307,7 +36325,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>2983</v>
       </c>
@@ -36354,7 +36372,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>2990</v>
       </c>
@@ -36395,7 +36413,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>2994</v>
       </c>
@@ -36439,7 +36457,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>2999</v>
       </c>
@@ -36480,7 +36498,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>3005</v>
       </c>
@@ -36524,7 +36542,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>3011</v>
       </c>
@@ -36571,7 +36589,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A481" s="16" t="s">
         <v>3017</v>
       </c>
@@ -36625,7 +36643,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A482" s="16" t="s">
         <v>3027</v>
       </c>
@@ -36675,7 +36693,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>3033</v>
       </c>
@@ -36727,7 +36745,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>3041</v>
       </c>
@@ -36781,7 +36799,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>3047</v>
       </c>
@@ -36833,7 +36851,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>3053</v>
       </c>
@@ -36882,7 +36900,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>3060</v>
       </c>
@@ -36932,7 +36950,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>3066</v>
       </c>
@@ -36983,7 +37001,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>3072</v>
       </c>
@@ -37034,7 +37052,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>3077</v>
       </c>
@@ -37084,7 +37102,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>3084</v>
       </c>
@@ -37135,7 +37153,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>3090</v>
       </c>
@@ -37186,7 +37204,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>3095</v>
       </c>
@@ -37237,7 +37255,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>3100</v>
       </c>
@@ -37288,7 +37306,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>3106</v>
       </c>
@@ -37338,7 +37356,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>3114</v>
       </c>
@@ -37391,7 +37409,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>3120</v>
       </c>
@@ -37442,7 +37460,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>3124</v>
       </c>
@@ -37492,7 +37510,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>3130</v>
       </c>
@@ -37542,7 +37560,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>3136</v>
       </c>
@@ -37592,7 +37610,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>3143</v>
       </c>
@@ -37642,7 +37660,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>3149</v>
       </c>
@@ -37692,7 +37710,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>3155</v>
       </c>
@@ -37745,7 +37763,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>3160</v>
       </c>
@@ -37798,7 +37816,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>3170</v>
       </c>
@@ -37850,7 +37868,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>3175</v>
       </c>
@@ -37903,7 +37921,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>3184</v>
       </c>
@@ -37950,7 +37968,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>3191</v>
       </c>
@@ -37994,7 +38012,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>3197</v>
       </c>
@@ -38038,7 +38056,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>3202</v>
       </c>
@@ -38084,7 +38102,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>3206</v>
       </c>
@@ -38122,7 +38140,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>3210</v>
       </c>
@@ -38172,7 +38190,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>3216</v>
       </c>
@@ -38217,7 +38235,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>3221</v>
       </c>
@@ -38258,7 +38276,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>3227</v>
       </c>
@@ -38303,7 +38321,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>3232</v>
       </c>
@@ -38347,7 +38365,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>3237</v>
       </c>
@@ -38391,7 +38409,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>3242</v>
       </c>
@@ -38435,7 +38453,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>3247</v>
       </c>
@@ -38480,7 +38498,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>3252</v>
       </c>
@@ -38530,7 +38548,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>3258</v>
       </c>
@@ -38580,7 +38598,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>3263</v>
       </c>
@@ -38636,7 +38654,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>3489</v>
       </c>
@@ -38685,7 +38703,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>3502</v>
       </c>
@@ -38729,7 +38747,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>3507</v>
       </c>
@@ -38770,7 +38788,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>3509</v>
       </c>
@@ -38814,7 +38832,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>3514</v>
       </c>
@@ -38861,7 +38879,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>3517</v>
       </c>
@@ -38913,7 +38931,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>3522</v>
       </c>
@@ -38957,7 +38975,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>3523</v>
       </c>
@@ -39001,7 +39019,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>3538</v>
       </c>
@@ -39048,7 +39066,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>3542</v>
       </c>
@@ -39097,7 +39115,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>3548</v>
       </c>
@@ -39147,7 +39165,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="12" t="s">
         <v>3583</v>
       </c>
@@ -39198,7 +39216,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="12" t="s">
         <v>3584</v>
       </c>
@@ -39249,7 +39267,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="12" t="s">
         <v>3585</v>
       </c>
@@ -39301,7 +39319,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="12" t="s">
         <v>3586</v>
       </c>
@@ -39350,7 +39368,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="12" t="s">
         <v>3587</v>
       </c>
@@ -39401,7 +39419,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="12" t="s">
         <v>3588</v>
       </c>
@@ -39452,7 +39470,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="12" t="s">
         <v>3589</v>
       </c>
@@ -39503,7 +39521,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="12" t="s">
         <v>3590</v>
       </c>
@@ -39554,7 +39572,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="12" t="s">
         <v>3591</v>
       </c>
@@ -39603,7 +39621,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="12" t="s">
         <v>3592</v>
       </c>
@@ -39654,7 +39672,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="12" t="s">
         <v>3593</v>
       </c>
@@ -39705,7 +39723,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="12" t="s">
         <v>3594</v>
       </c>
@@ -39756,7 +39774,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="12" t="s">
         <v>3595</v>
       </c>
@@ -39805,7 +39823,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="12" t="s">
         <v>3596</v>
       </c>
@@ -39854,7 +39872,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="12" t="s">
         <v>3597</v>
       </c>
@@ -39905,7 +39923,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="12" t="s">
         <v>3598</v>
       </c>
@@ -39952,7 +39970,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="12" t="s">
         <v>3599</v>
       </c>
@@ -40003,7 +40021,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="12" t="s">
         <v>3600</v>
       </c>
@@ -40052,7 +40070,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="12" t="s">
         <v>3601</v>
       </c>
@@ -40103,7 +40121,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="12" t="s">
         <v>3602</v>
       </c>
@@ -40152,7 +40170,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="12" t="s">
         <v>3603</v>
       </c>
@@ -40199,7 +40217,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="12" t="s">
         <v>3604</v>
       </c>
@@ -40253,7 +40271,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="12" t="s">
         <v>3618</v>
       </c>
@@ -40303,7 +40321,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="12" t="s">
         <v>3632</v>
       </c>
@@ -40353,7 +40371,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="12" t="s">
         <v>3637</v>
       </c>
@@ -40403,7 +40421,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="12" t="s">
         <v>3661</v>
       </c>
@@ -40455,7 +40473,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="12" t="s">
         <v>3680</v>
       </c>
@@ -40500,7 +40518,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="12" t="s">
         <v>3700</v>
       </c>
@@ -40554,7 +40572,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="12" t="s">
         <v>3701</v>
       </c>
@@ -40599,7 +40617,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="12" t="s">
         <v>3702</v>
       </c>
@@ -40644,7 +40662,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="12" t="s">
         <v>3703</v>
       </c>
@@ -40689,7 +40707,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="12" t="s">
         <v>3704</v>
       </c>
@@ -40734,7 +40752,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="12" t="s">
         <v>3705</v>
       </c>
@@ -40779,7 +40797,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="12" t="s">
         <v>3731</v>
       </c>
@@ -40826,7 +40844,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="12" t="s">
         <v>3740</v>
       </c>
@@ -40870,7 +40888,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="12" t="s">
         <v>3750</v>
       </c>
@@ -40922,7 +40940,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="12" t="s">
         <v>3771</v>
       </c>
@@ -40972,7 +40990,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="12" t="s">
         <v>3779</v>
       </c>
@@ -41022,7 +41040,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="12" t="s">
         <v>3781</v>
       </c>
@@ -41066,7 +41084,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="12" t="s">
         <v>3809</v>
       </c>
@@ -41116,7 +41134,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="12" t="s">
         <v>3821</v>
       </c>
@@ -41166,7 +41184,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="12" t="s">
         <v>3824</v>
       </c>
@@ -41210,7 +41228,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="12" t="s">
         <v>3830</v>
       </c>
@@ -41254,7 +41272,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="12" t="s">
         <v>3843</v>
       </c>
@@ -41306,7 +41324,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="12" t="s">
         <v>3902</v>
       </c>
@@ -41353,7 +41371,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="12" t="s">
         <v>3905</v>
       </c>
@@ -41403,7 +41421,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="12" t="s">
         <v>3908</v>
       </c>
@@ -41447,7 +41465,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="12" t="s">
         <v>3916</v>
       </c>
@@ -41491,7 +41509,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="12" t="s">
         <v>3924</v>
       </c>
@@ -41535,7 +41553,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="12" t="s">
         <v>3938</v>
       </c>
@@ -41579,7 +41597,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="12" t="s">
         <v>3956</v>
       </c>
@@ -41626,7 +41644,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="12" t="s">
         <v>3972</v>
       </c>
@@ -41673,7 +41691,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="12" t="s">
         <v>3973</v>
       </c>
@@ -41720,7 +41738,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="12" t="s">
         <v>3981</v>
       </c>
@@ -41766,7 +41784,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="12" t="s">
         <v>3991</v>
       </c>
@@ -41814,7 +41832,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="12" t="s">
         <v>4000</v>
       </c>
@@ -41858,7 +41876,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="12" t="s">
         <v>4002</v>
       </c>
@@ -41902,7 +41920,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="12" t="s">
         <v>4007</v>
       </c>
@@ -41946,7 +41964,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="592" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="12" t="s">
         <v>4011</v>
       </c>
@@ -41993,7 +42011,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="593" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="12" t="s">
         <v>4015</v>
       </c>
@@ -42037,7 +42055,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="12" t="s">
         <v>4020</v>
       </c>
@@ -42078,6 +42096,50 @@
         <v>123</v>
       </c>
       <c r="T594" s="25" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A595" s="12" t="s">
+        <v>4026</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>4024</v>
+      </c>
+      <c r="E595" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F595" s="2" t="s">
+        <v>4027</v>
+      </c>
+      <c r="G595" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="H595" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="I595" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J595" s="2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="K595" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L595" s="2" t="s">
+        <v>3644</v>
+      </c>
+      <c r="M595" s="2" t="s">
+        <v>4024</v>
+      </c>
+      <c r="O595" s="19" t="s">
+        <v>4025</v>
+      </c>
+      <c r="Q595" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T595" s="25" t="s">
         <v>3571</v>
       </c>
     </row>
@@ -42785,11 +42847,12 @@
     <hyperlink ref="O591" r:id="rId699" xr:uid="{EC81F8E4-8209-45C4-AC78-47B5116C1B07}"/>
     <hyperlink ref="O593" r:id="rId700" xr:uid="{F3277743-3EA6-431A-9337-474B33DEDDC4}"/>
     <hyperlink ref="O594" r:id="rId701" xr:uid="{B9D8FABB-89C6-4AB6-8550-7176B66C9ABE}"/>
+    <hyperlink ref="O595" r:id="rId702" xr:uid="{9CAC67F9-460B-4B63-9E09-F80DBADE8E8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId702"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId703"/>
   <tableParts count="1">
-    <tablePart r:id="rId703"/>
+    <tablePart r:id="rId704"/>
   </tableParts>
 </worksheet>
 </file>
@@ -42797,26 +42860,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T60"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="66" style="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="31" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.44140625" style="1" customWidth="1"/>
     <col min="11" max="13" width="12" style="1" customWidth="1"/>
     <col min="14" max="14" width="77" style="1" customWidth="1"/>
     <col min="15" max="15" width="79" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="24.7109375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.28515625" style="1"/>
+    <col min="16" max="16" width="24.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="24.6640625" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -42872,7 +42935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>3270</v>
       </c>
@@ -42925,7 +42988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>3270</v>
       </c>
@@ -42961,7 +43024,7 @@
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43003,7 +43066,7 @@
       <c r="Q4" s="32"/>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43045,7 +43108,7 @@
       <c r="Q5" s="32"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43093,7 +43156,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43139,7 +43202,7 @@
       <c r="Q7" s="32"/>
       <c r="R7" s="32"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>3270</v>
       </c>
@@ -43196,7 +43259,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43242,7 +43305,7 @@
       <c r="Q9" s="32"/>
       <c r="R9" s="32"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43288,7 +43351,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43334,7 +43397,7 @@
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43370,7 +43433,7 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43414,7 +43477,7 @@
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43458,7 +43521,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43510,7 +43573,7 @@
       </c>
       <c r="R15" s="32"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43564,7 +43627,7 @@
       </c>
       <c r="R16" s="32"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43616,7 +43679,7 @@
       </c>
       <c r="R17" s="32"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43670,7 +43733,7 @@
       </c>
       <c r="R18" s="32"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43720,7 +43783,7 @@
       </c>
       <c r="R19" s="32"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43772,7 +43835,7 @@
       </c>
       <c r="R20" s="32"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43822,7 +43885,7 @@
       </c>
       <c r="R21" s="32"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43874,7 +43937,7 @@
       </c>
       <c r="R22" s="32"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43926,7 +43989,7 @@
       </c>
       <c r="R23" s="32"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43978,7 +44041,7 @@
       </c>
       <c r="R24" s="32"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44024,7 +44087,7 @@
       <c r="Q25" s="32"/>
       <c r="R25" s="32"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44070,7 +44133,7 @@
       <c r="Q26" s="32"/>
       <c r="R26" s="32"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44110,7 +44173,7 @@
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44156,7 +44219,7 @@
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="31" t="s">
         <v>1907</v>
       </c>
@@ -44204,7 +44267,7 @@
       <c r="Q29" s="32"/>
       <c r="R29" s="32"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44232,7 +44295,7 @@
       <c r="Q30" s="32"/>
       <c r="R30" s="32"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44264,7 +44327,7 @@
       </c>
       <c r="R31" s="32"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44300,7 +44363,7 @@
       <c r="Q32" s="32"/>
       <c r="R32" s="32"/>
     </row>
-    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44336,7 +44399,7 @@
       <c r="Q33" s="32"/>
       <c r="R33" s="32"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44384,7 +44447,7 @@
       </c>
       <c r="R34" s="32"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44430,7 +44493,7 @@
       </c>
       <c r="R35" s="32"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44478,7 +44541,7 @@
       </c>
       <c r="R36" s="32"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44522,7 +44585,7 @@
       </c>
       <c r="R37" s="32"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44568,7 +44631,7 @@
       <c r="Q38" s="32"/>
       <c r="R38" s="32"/>
     </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44616,7 +44679,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44654,7 +44717,7 @@
       <c r="Q40" s="32"/>
       <c r="R40" s="32"/>
     </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44692,7 +44755,7 @@
       <c r="Q41" s="32"/>
       <c r="R41" s="32"/>
     </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44738,7 +44801,7 @@
       <c r="Q42" s="45"/>
       <c r="R42" s="45"/>
     </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44790,7 +44853,7 @@
       </c>
       <c r="R43" s="32"/>
     </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44842,7 +44905,7 @@
       </c>
       <c r="R44" s="32"/>
     </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44888,7 +44951,7 @@
       </c>
       <c r="R45" s="45"/>
     </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44934,7 +44997,7 @@
       </c>
       <c r="R46" s="45"/>
     </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44986,12 +45049,12 @@
       <c r="Q47" s="45"/>
       <c r="R47" s="45"/>
     </row>
-    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="31" t="s">
         <v>3270</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45035,7 +45098,7 @@
       <c r="Q49" s="45"/>
       <c r="R49" s="45"/>
     </row>
-    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45067,7 +45130,7 @@
       <c r="Q50" s="45"/>
       <c r="R50" s="45"/>
     </row>
-    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45099,7 +45162,7 @@
       <c r="Q51" s="45"/>
       <c r="R51" s="45"/>
     </row>
-    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45131,7 +45194,7 @@
       <c r="Q52" s="45"/>
       <c r="R52" s="45"/>
     </row>
-    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45163,7 +45226,7 @@
       <c r="Q53" s="45"/>
       <c r="R53" s="45"/>
     </row>
-    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45183,7 +45246,7 @@
         <v>3837</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45227,7 +45290,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45273,7 +45336,7 @@
       </c>
       <c r="R56" s="45"/>
     </row>
-    <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45319,7 +45382,7 @@
       </c>
       <c r="R57" s="45"/>
     </row>
-    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45369,7 +45432,7 @@
       <c r="Q58" s="45"/>
       <c r="R58" s="45"/>
     </row>
-    <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="45"/>
       <c r="B59" s="74" t="s">
         <v>3986</v>
@@ -45403,7 +45466,7 @@
       </c>
       <c r="R59" s="45"/>
     </row>
-    <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="45"/>
       <c r="B60" s="45" t="s">
         <v>3985</v>
@@ -45542,16 +45605,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="26.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="26.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="59" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="59" customWidth="1"/>
-    <col min="5" max="16384" width="26.5703125" style="59"/>
+    <col min="1" max="1" width="34.109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="59" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="59" customWidth="1"/>
+    <col min="5" max="16384" width="26.5546875" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="59" t="s">
         <v>3610</v>
       </c>
@@ -45568,7 +45631,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="60" t="s">
         <v>3859</v>
       </c>
@@ -45582,7 +45645,7 @@
         <v>3863</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="59" t="s">
         <v>3816</v>
       </c>
@@ -45599,7 +45662,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="59" t="s">
         <v>3810</v>
       </c>
@@ -45613,7 +45676,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="s">
         <v>3815</v>
       </c>
@@ -45627,7 +45690,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59" t="s">
         <v>3811</v>
       </c>
@@ -45641,7 +45704,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59" t="s">
         <v>3812</v>
       </c>
@@ -45655,7 +45718,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59" t="s">
         <v>3813</v>
       </c>
@@ -45669,7 +45732,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59" t="s">
         <v>3814</v>
       </c>
@@ -45683,7 +45746,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
         <v>3483</v>
       </c>
@@ -45694,7 +45757,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="59" t="s">
         <v>3568</v>
       </c>
@@ -45705,7 +45768,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59" t="s">
         <v>3569</v>
       </c>
@@ -45716,7 +45779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59" t="s">
         <v>3570</v>
       </c>
@@ -45727,7 +45790,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="59" t="s">
         <v>3861</v>
       </c>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB7AE1B-E7BF-4152-A904-7CDD0BE63C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58567BEF-4712-45EB-A19F-E50D8F5DE077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8407" uniqueCount="4030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8433" uniqueCount="4040">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -11773,9 +11773,6 @@
     <t>38</t>
   </si>
   <si>
-    <t>Philadelphia</t>
-  </si>
-  <si>
     <t>LJS 19</t>
   </si>
   <si>
@@ -11785,9 +11782,6 @@
     <t>https://colenda.library.upenn.edu/catalog/81431-p3n633</t>
   </si>
   <si>
-    <t>Pedro de la Torre</t>
-  </si>
-  <si>
     <t>HSMS-0580</t>
   </si>
   <si>
@@ -12128,6 +12122,42 @@
   </si>
   <si>
     <t>1597-01-16 a quo</t>
+  </si>
+  <si>
+    <t>EH89</t>
+  </si>
+  <si>
+    <t>Philadelphia: University of Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://digitalcollections.library.upenn.edu/items/ebe5c7b4-eb59-425c-a4a5-659958d92074</t>
+  </si>
+  <si>
+    <t>EH68</t>
+  </si>
+  <si>
+    <t>MSS/19051</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/card?id=96293a91-871a-4bef-8f6a-906ef72f92d7</t>
+  </si>
+  <si>
+    <t>Oversize Ms. Codex 73</t>
+  </si>
+  <si>
+    <t>Iris Garrabeitia y Candelas Canarias?</t>
+  </si>
+  <si>
+    <t>Abreviatura HSMS2</t>
+  </si>
+  <si>
+    <t>HSMS-0595</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>1589-06-17</t>
   </si>
 </sst>
 </file>
@@ -12137,13 +12167,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -12433,9 +12470,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -12449,7 +12486,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -12458,26 +12495,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -12486,86 +12523,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12577,24 +12617,24 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -12616,28 +12656,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -13041,8 +13081,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T595" totalsRowShown="0">
-  <autoFilter ref="A1:T595" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T596" totalsRowShown="0">
+  <autoFilter ref="A1:T596" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13059,7 +13099,7 @@
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviaturas HSMS"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="subcorpus"/>
@@ -13073,8 +13113,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R60" totalsRowShown="0" dataDxfId="25">
-  <autoFilter ref="A1:R60" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="25">
+  <autoFilter ref="A1:R62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
@@ -13292,31 +13332,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T595"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T596"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="38.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="4" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" customWidth="1"/>
     <col min="14" max="14" width="45" style="1" customWidth="1"/>
-    <col min="15" max="15" width="59.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" customWidth="1"/>
-    <col min="17" max="17" width="41.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="59.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="41.28515625" style="1" customWidth="1"/>
     <col min="18" max="19" width="58" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
-    <col min="21" max="16384" width="9.33203125" style="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13354,7 +13394,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>4036</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -13378,7 +13418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -13425,7 +13465,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -13470,7 +13510,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -13520,7 +13560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -13562,7 +13602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -13612,7 +13652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -13662,7 +13702,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>74</v>
       </c>
@@ -13709,7 +13749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -13759,7 +13799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="144" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>91</v>
       </c>
@@ -13809,7 +13849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>99</v>
       </c>
@@ -13862,7 +13902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>108</v>
       </c>
@@ -13918,7 +13958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>117</v>
       </c>
@@ -13965,7 +14005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>124</v>
       </c>
@@ -14019,7 +14059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>134</v>
       </c>
@@ -14069,7 +14109,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>143</v>
       </c>
@@ -14114,7 +14154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -14161,7 +14201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
@@ -14203,7 +14243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>163</v>
       </c>
@@ -14248,7 +14288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>170</v>
       </c>
@@ -14299,7 +14339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>177</v>
       </c>
@@ -14346,7 +14386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>186</v>
       </c>
@@ -14396,7 +14436,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>193</v>
       </c>
@@ -14443,7 +14483,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>200</v>
       </c>
@@ -14490,7 +14530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
@@ -14537,7 +14577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>213</v>
       </c>
@@ -14584,7 +14624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>220</v>
       </c>
@@ -14631,7 +14671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>226</v>
       </c>
@@ -14681,7 +14721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>235</v>
       </c>
@@ -14728,7 +14768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>242</v>
       </c>
@@ -14775,7 +14815,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>249</v>
       </c>
@@ -14828,7 +14868,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>256</v>
       </c>
@@ -14875,7 +14915,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>263</v>
       </c>
@@ -14926,7 +14966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>270</v>
       </c>
@@ -14974,7 +15014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>276</v>
       </c>
@@ -15027,7 +15067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>285</v>
       </c>
@@ -15075,7 +15115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>291</v>
       </c>
@@ -15120,7 +15160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>296</v>
       </c>
@@ -15168,7 +15208,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>301</v>
       </c>
@@ -15219,7 +15259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>306</v>
       </c>
@@ -15270,7 +15310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>312</v>
       </c>
@@ -15318,7 +15358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>320</v>
       </c>
@@ -15374,7 +15414,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>328</v>
       </c>
@@ -15422,7 +15462,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>333</v>
       </c>
@@ -15470,7 +15510,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>340</v>
       </c>
@@ -15518,7 +15558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>345</v>
       </c>
@@ -15566,7 +15606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>351</v>
       </c>
@@ -15622,7 +15662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>361</v>
       </c>
@@ -15670,7 +15710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>367</v>
       </c>
@@ -15718,7 +15758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>373</v>
       </c>
@@ -15766,7 +15806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>379</v>
       </c>
@@ -15819,7 +15859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>389</v>
       </c>
@@ -15864,7 +15904,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>395</v>
       </c>
@@ -15912,7 +15952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>403</v>
       </c>
@@ -15959,7 +15999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>409</v>
       </c>
@@ -16009,7 +16049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>416</v>
       </c>
@@ -16059,7 +16099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>424</v>
       </c>
@@ -16112,7 +16152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>431</v>
       </c>
@@ -16163,7 +16203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>441</v>
       </c>
@@ -16214,7 +16254,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>447</v>
       </c>
@@ -16262,7 +16302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>452</v>
       </c>
@@ -16313,7 +16353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>458</v>
       </c>
@@ -16367,7 +16407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>466</v>
       </c>
@@ -16421,7 +16461,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>472</v>
       </c>
@@ -16469,7 +16509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>477</v>
       </c>
@@ -16520,7 +16560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>481</v>
       </c>
@@ -16567,7 +16607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>487</v>
       </c>
@@ -16617,7 +16657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>495</v>
       </c>
@@ -16667,7 +16707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>501</v>
       </c>
@@ -16714,7 +16754,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>506</v>
       </c>
@@ -16761,7 +16801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>513</v>
       </c>
@@ -16808,7 +16848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>520</v>
       </c>
@@ -16858,7 +16898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>526</v>
       </c>
@@ -16908,7 +16948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>531</v>
       </c>
@@ -16961,7 +17001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>539</v>
       </c>
@@ -17011,7 +17051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>546</v>
       </c>
@@ -17058,7 +17098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>552</v>
       </c>
@@ -17105,7 +17145,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>558</v>
       </c>
@@ -17152,7 +17192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>564</v>
       </c>
@@ -17199,7 +17239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>570</v>
       </c>
@@ -17252,7 +17292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>581</v>
       </c>
@@ -17299,7 +17339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>587</v>
       </c>
@@ -17346,7 +17386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>593</v>
       </c>
@@ -17396,7 +17436,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>602</v>
       </c>
@@ -17446,7 +17486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>611</v>
       </c>
@@ -17496,7 +17536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>618</v>
       </c>
@@ -17549,7 +17589,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>625</v>
       </c>
@@ -17596,7 +17636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>633</v>
       </c>
@@ -17646,7 +17686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>640</v>
       </c>
@@ -17696,7 +17736,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>647</v>
       </c>
@@ -17743,7 +17783,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>654</v>
       </c>
@@ -17790,7 +17830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>660</v>
       </c>
@@ -17837,7 +17877,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>666</v>
       </c>
@@ -17887,7 +17927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>674</v>
       </c>
@@ -17934,7 +17974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>682</v>
       </c>
@@ -17984,7 +18024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>690</v>
       </c>
@@ -18035,7 +18075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>696</v>
       </c>
@@ -18085,7 +18125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>704</v>
       </c>
@@ -18135,7 +18175,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>711</v>
       </c>
@@ -18185,7 +18225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>717</v>
       </c>
@@ -18239,7 +18279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>725</v>
       </c>
@@ -18292,7 +18332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>732</v>
       </c>
@@ -18339,7 +18379,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>738</v>
       </c>
@@ -18389,7 +18429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>745</v>
       </c>
@@ -18439,7 +18479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>754</v>
       </c>
@@ -18486,7 +18526,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>762</v>
       </c>
@@ -18536,7 +18576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>770</v>
       </c>
@@ -18586,7 +18626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>778</v>
       </c>
@@ -18636,7 +18676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>785</v>
       </c>
@@ -18686,7 +18726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>793</v>
       </c>
@@ -18739,7 +18779,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>801</v>
       </c>
@@ -18792,7 +18832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>807</v>
       </c>
@@ -18845,7 +18885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>817</v>
       </c>
@@ -18895,7 +18935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>823</v>
       </c>
@@ -18945,7 +18985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>829</v>
       </c>
@@ -18992,7 +19032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>835</v>
       </c>
@@ -19039,7 +19079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>842</v>
       </c>
@@ -19089,7 +19129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>848</v>
       </c>
@@ -19139,7 +19179,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>854</v>
       </c>
@@ -19186,7 +19226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>861</v>
       </c>
@@ -19236,7 +19276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>868</v>
       </c>
@@ -19286,7 +19326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>873</v>
       </c>
@@ -19336,7 +19376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>879</v>
       </c>
@@ -19389,7 +19429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>888</v>
       </c>
@@ -19439,7 +19479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>895</v>
       </c>
@@ -19484,7 +19524,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>900</v>
       </c>
@@ -19534,7 +19574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>909</v>
       </c>
@@ -19584,7 +19624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>917</v>
       </c>
@@ -19634,7 +19674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>924</v>
       </c>
@@ -19684,7 +19724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>931</v>
       </c>
@@ -19734,7 +19774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>937</v>
       </c>
@@ -19779,7 +19819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>943</v>
       </c>
@@ -19832,7 +19872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>949</v>
       </c>
@@ -19882,7 +19922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>955</v>
       </c>
@@ -19932,7 +19972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>962</v>
       </c>
@@ -19988,7 +20028,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>971</v>
       </c>
@@ -20042,7 +20082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>978</v>
       </c>
@@ -20089,7 +20129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>984</v>
       </c>
@@ -20136,7 +20176,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>991</v>
       </c>
@@ -20186,7 +20226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>1001</v>
       </c>
@@ -20236,7 +20276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>1008</v>
       </c>
@@ -20283,7 +20323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>1015</v>
       </c>
@@ -20333,7 +20373,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20380,7 +20420,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>1029</v>
       </c>
@@ -20430,7 +20470,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>1036</v>
       </c>
@@ -20480,7 +20520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>1044</v>
       </c>
@@ -20530,7 +20570,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>1051</v>
       </c>
@@ -20577,7 +20617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>1057</v>
       </c>
@@ -20627,7 +20667,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>1062</v>
       </c>
@@ -20674,7 +20714,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>1069</v>
       </c>
@@ -20721,7 +20761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>1074</v>
       </c>
@@ -20771,7 +20811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>1080</v>
       </c>
@@ -20824,7 +20864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>1085</v>
       </c>
@@ -20871,7 +20911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>1090</v>
       </c>
@@ -20921,7 +20961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>1097</v>
       </c>
@@ -20968,7 +21008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>1103</v>
       </c>
@@ -21013,7 +21053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>1109</v>
       </c>
@@ -21060,7 +21100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>1116</v>
       </c>
@@ -21116,7 +21156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>1124</v>
       </c>
@@ -21170,7 +21210,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>1134</v>
       </c>
@@ -21220,7 +21260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>1140</v>
       </c>
@@ -21273,7 +21313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>1147</v>
       </c>
@@ -21326,7 +21366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>1155</v>
       </c>
@@ -21374,7 +21414,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>1161</v>
       </c>
@@ -21427,7 +21467,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21480,7 +21520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>1177</v>
       </c>
@@ -21530,7 +21570,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>1185</v>
       </c>
@@ -21578,7 +21618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>1190</v>
       </c>
@@ -21626,7 +21666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>1195</v>
       </c>
@@ -21676,7 +21716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>1202</v>
       </c>
@@ -21726,7 +21766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>1210</v>
       </c>
@@ -21776,7 +21816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>1217</v>
       </c>
@@ -21826,7 +21866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>1223</v>
       </c>
@@ -21874,7 +21914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>1228</v>
       </c>
@@ -21924,7 +21964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>1236</v>
       </c>
@@ -21977,7 +22017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>1242</v>
       </c>
@@ -22025,7 +22065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>1248</v>
       </c>
@@ -22081,7 +22121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>1256</v>
       </c>
@@ -22134,7 +22174,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>1262</v>
       </c>
@@ -22184,7 +22224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>1267</v>
       </c>
@@ -22232,7 +22272,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>1273</v>
       </c>
@@ -22285,7 +22325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>1279</v>
       </c>
@@ -22335,7 +22375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>1285</v>
       </c>
@@ -22385,7 +22425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>1293</v>
       </c>
@@ -22438,7 +22478,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>1301</v>
       </c>
@@ -22486,7 +22526,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>1308</v>
       </c>
@@ -22531,7 +22571,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>1313</v>
       </c>
@@ -22576,7 +22616,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>1319</v>
       </c>
@@ -22623,7 +22663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>1327</v>
       </c>
@@ -22671,7 +22711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22724,7 +22764,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>1342</v>
       </c>
@@ -22774,7 +22814,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>1349</v>
       </c>
@@ -22821,7 +22861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>1354</v>
       </c>
@@ -22871,7 +22911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>1360</v>
       </c>
@@ -22918,7 +22958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>1364</v>
       </c>
@@ -22968,7 +23008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>1372</v>
       </c>
@@ -23018,7 +23058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>1381</v>
       </c>
@@ -23068,7 +23108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>1386</v>
       </c>
@@ -23118,7 +23158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>1392</v>
       </c>
@@ -23168,7 +23208,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>1398</v>
       </c>
@@ -23209,7 +23249,7 @@
         <v>1403</v>
       </c>
       <c r="O200" s="9" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
       <c r="Q200" s="1" t="s">
         <v>1404</v>
@@ -23218,7 +23258,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>1405</v>
       </c>
@@ -23266,7 +23306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>1414</v>
       </c>
@@ -23314,7 +23354,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>1421</v>
       </c>
@@ -23360,7 +23400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>1426</v>
       </c>
@@ -23407,7 +23447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>1432</v>
       </c>
@@ -23457,7 +23497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>1437</v>
       </c>
@@ -23501,7 +23541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>1440</v>
       </c>
@@ -23545,7 +23585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>1444</v>
       </c>
@@ -23593,7 +23633,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>1450</v>
       </c>
@@ -23646,7 +23686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>1456</v>
       </c>
@@ -23694,7 +23734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>1464</v>
       </c>
@@ -23744,7 +23784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>1470</v>
       </c>
@@ -23794,7 +23834,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>1476</v>
       </c>
@@ -23847,7 +23887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>1483</v>
       </c>
@@ -23903,7 +23943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>1491</v>
       </c>
@@ -23959,7 +23999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>1498</v>
       </c>
@@ -24007,7 +24047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>1504</v>
       </c>
@@ -24060,7 +24100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>1511</v>
       </c>
@@ -24104,7 +24144,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>1515</v>
       </c>
@@ -24157,7 +24197,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1521</v>
       </c>
@@ -24207,7 +24247,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>1526</v>
       </c>
@@ -24233,7 +24273,7 @@
         <v>69</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>130</v>
@@ -24260,7 +24300,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>1532</v>
       </c>
@@ -24310,7 +24350,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>1538</v>
       </c>
@@ -24360,7 +24400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>1545</v>
       </c>
@@ -24413,7 +24453,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>1554</v>
       </c>
@@ -24461,7 +24501,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>1563</v>
       </c>
@@ -24511,7 +24551,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>1570</v>
       </c>
@@ -24561,7 +24601,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>1577</v>
       </c>
@@ -24611,7 +24651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>1584</v>
       </c>
@@ -24661,7 +24701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>1593</v>
       </c>
@@ -24711,7 +24751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>1599</v>
       </c>
@@ -24759,7 +24799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>1603</v>
       </c>
@@ -24806,7 +24846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>1609</v>
       </c>
@@ -24856,7 +24896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>1616</v>
       </c>
@@ -24908,7 +24948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>1624</v>
       </c>
@@ -24955,7 +24995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1632</v>
       </c>
@@ -25005,7 +25045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>1639</v>
       </c>
@@ -25055,7 +25095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>1645</v>
       </c>
@@ -25102,7 +25142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>1650</v>
       </c>
@@ -25149,7 +25189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>1655</v>
       </c>
@@ -25199,7 +25239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>1659</v>
       </c>
@@ -25246,7 +25286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>1665</v>
       </c>
@@ -25293,7 +25333,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>1670</v>
       </c>
@@ -25343,7 +25383,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>1676</v>
       </c>
@@ -25390,7 +25430,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>1682</v>
       </c>
@@ -25443,7 +25483,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>1690</v>
       </c>
@@ -25490,7 +25530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>1695</v>
       </c>
@@ -25537,7 +25577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>1700</v>
       </c>
@@ -25587,7 +25627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>1706</v>
       </c>
@@ -25634,7 +25674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1712</v>
       </c>
@@ -25683,7 +25723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1718</v>
       </c>
@@ -25730,7 +25770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>1724</v>
       </c>
@@ -25777,7 +25817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>1730</v>
       </c>
@@ -25824,7 +25864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1736</v>
       </c>
@@ -25869,7 +25909,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1741</v>
       </c>
@@ -25911,7 +25951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1746</v>
       </c>
@@ -25964,7 +26004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1754</v>
       </c>
@@ -26011,7 +26051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1758</v>
       </c>
@@ -26058,7 +26098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1764</v>
       </c>
@@ -26108,7 +26148,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1769</v>
       </c>
@@ -26158,7 +26198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1777</v>
       </c>
@@ -26210,7 +26250,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1782</v>
       </c>
@@ -26257,7 +26297,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1786</v>
       </c>
@@ -26307,7 +26347,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1792</v>
       </c>
@@ -26357,7 +26397,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1796</v>
       </c>
@@ -26407,7 +26447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>1802</v>
       </c>
@@ -26454,7 +26494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>1805</v>
       </c>
@@ -26501,7 +26541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>1808</v>
       </c>
@@ -26548,7 +26588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>1811</v>
       </c>
@@ -26597,7 +26637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>1817</v>
       </c>
@@ -26644,7 +26684,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>1821</v>
       </c>
@@ -26692,7 +26732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>1827</v>
       </c>
@@ -26742,7 +26782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>1832</v>
       </c>
@@ -26792,7 +26832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>1837</v>
       </c>
@@ -26837,7 +26877,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>1841</v>
       </c>
@@ -26884,7 +26924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>1847</v>
       </c>
@@ -26934,7 +26974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>1852</v>
       </c>
@@ -26982,7 +27022,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>1857</v>
       </c>
@@ -27029,7 +27069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>1863</v>
       </c>
@@ -27079,7 +27119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>1868</v>
       </c>
@@ -27129,7 +27169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>1874</v>
       </c>
@@ -27177,7 +27217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>1880</v>
       </c>
@@ -27225,7 +27265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>1886</v>
       </c>
@@ -27273,7 +27313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>1891</v>
       </c>
@@ -27323,7 +27363,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>1896</v>
       </c>
@@ -27368,7 +27408,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1901</v>
       </c>
@@ -27413,7 +27453,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1907</v>
       </c>
@@ -27464,7 +27504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1914</v>
       </c>
@@ -27514,7 +27554,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1920</v>
       </c>
@@ -27561,7 +27601,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1924</v>
       </c>
@@ -27609,7 +27649,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="291" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1931</v>
       </c>
@@ -27659,7 +27699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="292" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1936</v>
       </c>
@@ -27711,7 +27751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="293" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1944</v>
       </c>
@@ -27758,7 +27798,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="294" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1950</v>
       </c>
@@ -27808,7 +27848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1954</v>
       </c>
@@ -27853,7 +27893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="296" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1958</v>
       </c>
@@ -27903,7 +27943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="297" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1963</v>
       </c>
@@ -27948,7 +27988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="298" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>1967</v>
       </c>
@@ -27996,7 +28036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="299" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>1973</v>
       </c>
@@ -28041,7 +28081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>1978</v>
       </c>
@@ -28091,7 +28131,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="301" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>1984</v>
       </c>
@@ -28132,19 +28172,19 @@
         <v>1989</v>
       </c>
       <c r="O301" s="9" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
       <c r="Q301" s="1" t="s">
         <v>1404</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
       <c r="T301" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="302" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>1990</v>
       </c>
@@ -28189,7 +28229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="303" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>1995</v>
       </c>
@@ -28236,7 +28276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>2000</v>
       </c>
@@ -28286,7 +28326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>2007</v>
       </c>
@@ -28331,7 +28371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="306" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>2011</v>
       </c>
@@ -28378,7 +28418,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="307" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>2017</v>
       </c>
@@ -28426,7 +28466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>2023</v>
       </c>
@@ -28473,7 +28513,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>2029</v>
       </c>
@@ -28523,7 +28563,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="310" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>2033</v>
       </c>
@@ -28576,7 +28616,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>2038</v>
       </c>
@@ -28626,7 +28666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="312" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>2045</v>
       </c>
@@ -28676,7 +28716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="313" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>2049</v>
       </c>
@@ -28721,7 +28761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>2054</v>
       </c>
@@ -28768,7 +28808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="315" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>2060</v>
       </c>
@@ -28818,7 +28858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="316" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>2065</v>
       </c>
@@ -28866,7 +28906,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="317" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>2070</v>
       </c>
@@ -28911,7 +28951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="318" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>2074</v>
       </c>
@@ -28959,7 +28999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="319" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>2080</v>
       </c>
@@ -29004,7 +29044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>2084</v>
       </c>
@@ -29058,7 +29098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>2090</v>
       </c>
@@ -29108,7 +29148,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="322" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>2097</v>
       </c>
@@ -29158,7 +29198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="323" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>2103</v>
       </c>
@@ -29214,7 +29254,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>2108</v>
       </c>
@@ -29264,7 +29304,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="325" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>2115</v>
       </c>
@@ -29309,7 +29349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="326" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>2120</v>
       </c>
@@ -29354,7 +29394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>2126</v>
       </c>
@@ -29399,7 +29439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>2131</v>
       </c>
@@ -29447,7 +29487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>2136</v>
       </c>
@@ -29492,7 +29532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="330" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>2140</v>
       </c>
@@ -29540,7 +29580,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>2147</v>
       </c>
@@ -29591,7 +29631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="332" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>2154</v>
       </c>
@@ -29642,7 +29682,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="333" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>2161</v>
       </c>
@@ -29692,7 +29732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>2167</v>
       </c>
@@ -29745,7 +29785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="335" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>2173</v>
       </c>
@@ -29795,7 +29835,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="336" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>2179</v>
       </c>
@@ -29846,7 +29886,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="337" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>2185</v>
       </c>
@@ -29899,7 +29939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>2193</v>
       </c>
@@ -29952,7 +29992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>2202</v>
       </c>
@@ -30002,7 +30042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>2209</v>
       </c>
@@ -30052,7 +30092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="341" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>2214</v>
       </c>
@@ -30100,7 +30140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>2222</v>
       </c>
@@ -30150,7 +30190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>2230</v>
       </c>
@@ -30197,7 +30237,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>2236</v>
       </c>
@@ -30245,7 +30285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>2240</v>
       </c>
@@ -30298,7 +30338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>2245</v>
       </c>
@@ -30345,7 +30385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>2253</v>
       </c>
@@ -30395,7 +30435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>2261</v>
       </c>
@@ -30440,7 +30480,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>2266</v>
       </c>
@@ -30493,7 +30533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>2272</v>
       </c>
@@ -30543,7 +30583,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>2278</v>
       </c>
@@ -30593,7 +30633,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>2286</v>
       </c>
@@ -30638,7 +30678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>2293</v>
       </c>
@@ -30688,7 +30728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="354" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>2301</v>
       </c>
@@ -30741,7 +30781,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>2307</v>
       </c>
@@ -30794,7 +30834,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>2313</v>
       </c>
@@ -30844,7 +30884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>2321</v>
       </c>
@@ -30894,7 +30934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>2329</v>
       </c>
@@ -30941,7 +30981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>2335</v>
       </c>
@@ -30991,7 +31031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="360" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>2344</v>
       </c>
@@ -31041,7 +31081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="361" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>2351</v>
       </c>
@@ -31088,7 +31128,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="362" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>2356</v>
       </c>
@@ -31138,7 +31178,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="363" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>2361</v>
       </c>
@@ -31186,7 +31226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="364" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>2368</v>
       </c>
@@ -31233,7 +31273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>2372</v>
       </c>
@@ -31286,7 +31326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>2378</v>
       </c>
@@ -31336,7 +31376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="367" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>2386</v>
       </c>
@@ -31389,7 +31429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="368" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>2392</v>
       </c>
@@ -31434,7 +31474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="369" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>2396</v>
       </c>
@@ -31484,7 +31524,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="370" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>2402</v>
       </c>
@@ -31531,7 +31571,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>2407</v>
       </c>
@@ -31575,7 +31615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>2414</v>
       </c>
@@ -31622,7 +31662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="373" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>2422</v>
       </c>
@@ -31666,7 +31706,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>2428</v>
       </c>
@@ -31710,7 +31750,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="375" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>2434</v>
       </c>
@@ -31757,7 +31797,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="376" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>2440</v>
       </c>
@@ -31804,7 +31844,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="377" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>2446</v>
       </c>
@@ -31851,7 +31891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="378" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>2452</v>
       </c>
@@ -31895,7 +31935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="379" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>2458</v>
       </c>
@@ -31939,7 +31979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="380" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>2462</v>
       </c>
@@ -31986,7 +32026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="381" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>2469</v>
       </c>
@@ -32033,7 +32073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="382" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>2475</v>
       </c>
@@ -32077,7 +32117,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>2480</v>
       </c>
@@ -32121,7 +32161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="384" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>2484</v>
       </c>
@@ -32165,7 +32205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>2489</v>
       </c>
@@ -32209,7 +32249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>2493</v>
       </c>
@@ -32256,7 +32296,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="387" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>2500</v>
       </c>
@@ -32303,7 +32343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="388" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>2506</v>
       </c>
@@ -32347,7 +32387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="389" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>2510</v>
       </c>
@@ -32391,7 +32431,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>2514</v>
       </c>
@@ -32444,7 +32484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="391" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>2520</v>
       </c>
@@ -32488,7 +32528,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>2526</v>
       </c>
@@ -32532,7 +32572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>2531</v>
       </c>
@@ -32573,7 +32613,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="394" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>2535</v>
       </c>
@@ -32617,7 +32657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="395" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>2540</v>
       </c>
@@ -32658,7 +32698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="396" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>2545</v>
       </c>
@@ -32697,7 +32737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="397" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>2549</v>
       </c>
@@ -32738,7 +32778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="398" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>2553</v>
       </c>
@@ -32779,7 +32819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>2558</v>
       </c>
@@ -32820,7 +32860,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="400" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>2562</v>
       </c>
@@ -32861,7 +32901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="401" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>2566</v>
       </c>
@@ -32902,7 +32942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="402" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>2569</v>
       </c>
@@ -32943,7 +32983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="403" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>2574</v>
       </c>
@@ -32987,7 +33027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>2576</v>
       </c>
@@ -33031,7 +33071,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="405" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>2581</v>
       </c>
@@ -33075,7 +33115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>2586</v>
       </c>
@@ -33122,7 +33162,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>2594</v>
       </c>
@@ -33169,7 +33209,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="408" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>2597</v>
       </c>
@@ -33219,7 +33259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="409" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>2603</v>
       </c>
@@ -33275,7 +33315,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>2612</v>
       </c>
@@ -33325,7 +33365,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="411" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>2619</v>
       </c>
@@ -33369,7 +33409,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="412" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>2623</v>
       </c>
@@ -33413,7 +33453,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="413" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>2628</v>
       </c>
@@ -33460,7 +33500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="414" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>2636</v>
       </c>
@@ -33501,7 +33541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="415" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>2641</v>
       </c>
@@ -33545,7 +33585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="416" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>2646</v>
       </c>
@@ -33586,7 +33626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="417" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>2650</v>
       </c>
@@ -33630,7 +33670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="418" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>2655</v>
       </c>
@@ -33674,7 +33714,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>2660</v>
       </c>
@@ -33718,7 +33758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="420" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>2665</v>
       </c>
@@ -33759,7 +33799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="421" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>2669</v>
       </c>
@@ -33800,7 +33840,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="422" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>2675</v>
       </c>
@@ -33844,7 +33884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="423" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>2678</v>
       </c>
@@ -33894,7 +33934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="424" spans="1:20" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="12" t="s">
         <v>2685</v>
       </c>
@@ -33939,7 +33979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="425" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>2689</v>
       </c>
@@ -33977,7 +34017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="426" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>2693</v>
       </c>
@@ -34021,7 +34061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="427" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>2697</v>
       </c>
@@ -34065,7 +34105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="428" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>2703</v>
       </c>
@@ -34109,7 +34149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>2707</v>
       </c>
@@ -34150,7 +34190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>2710</v>
       </c>
@@ -34194,7 +34234,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="431" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>2715</v>
       </c>
@@ -34235,7 +34275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>2720</v>
       </c>
@@ -34288,7 +34328,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>2726</v>
       </c>
@@ -34341,7 +34381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="434" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>2734</v>
       </c>
@@ -34386,7 +34426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="435" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>2740</v>
       </c>
@@ -34430,7 +34470,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="436" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>2745</v>
       </c>
@@ -34474,7 +34514,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="437" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>2751</v>
       </c>
@@ -34518,7 +34558,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="438" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>2756</v>
       </c>
@@ -34565,7 +34605,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="439" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>2764</v>
       </c>
@@ -34618,7 +34658,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="440" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>2771</v>
       </c>
@@ -34671,7 +34711,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="441" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>2778</v>
       </c>
@@ -34724,7 +34764,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="442" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>2784</v>
       </c>
@@ -34774,7 +34814,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="443" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>2791</v>
       </c>
@@ -34827,7 +34867,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="444" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>2797</v>
       </c>
@@ -34877,7 +34917,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="445" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>2803</v>
       </c>
@@ -34930,7 +34970,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="446" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>2810</v>
       </c>
@@ -34986,7 +35026,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="447" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>2818</v>
       </c>
@@ -35033,7 +35073,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="448" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>2824</v>
       </c>
@@ -35080,7 +35120,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="449" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>2831</v>
       </c>
@@ -35130,7 +35170,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="450" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>2837</v>
       </c>
@@ -35177,7 +35217,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="451" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>2843</v>
       </c>
@@ -35224,7 +35264,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="452" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>2849</v>
       </c>
@@ -35275,7 +35315,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="453" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>2855</v>
       </c>
@@ -35326,7 +35366,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="454" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>2861</v>
       </c>
@@ -35378,7 +35418,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="455" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>2866</v>
       </c>
@@ -35425,7 +35465,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="456" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>2874</v>
       </c>
@@ -35472,7 +35512,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="457" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>2881</v>
       </c>
@@ -35521,7 +35561,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="458" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>2887</v>
       </c>
@@ -35568,7 +35608,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="459" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>2892</v>
       </c>
@@ -35612,7 +35652,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="460" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>2898</v>
       </c>
@@ -35659,7 +35699,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="461" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>2901</v>
       </c>
@@ -35700,7 +35740,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="462" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>2908</v>
       </c>
@@ -35747,7 +35787,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="463" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>2913</v>
       </c>
@@ -35792,7 +35832,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="464" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>2918</v>
       </c>
@@ -35836,7 +35876,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="465" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>2922</v>
       </c>
@@ -35886,7 +35926,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="466" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>2929</v>
       </c>
@@ -35939,7 +35979,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="467" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>2935</v>
       </c>
@@ -35989,7 +36029,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="468" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>2941</v>
       </c>
@@ -36027,7 +36067,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="469" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>2947</v>
       </c>
@@ -36077,7 +36117,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="470" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>2952</v>
       </c>
@@ -36127,7 +36167,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="471" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>2957</v>
       </c>
@@ -36176,7 +36216,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="472" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>2964</v>
       </c>
@@ -36227,7 +36267,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="473" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>2971</v>
       </c>
@@ -36278,7 +36318,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="474" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>2977</v>
       </c>
@@ -36325,7 +36365,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="475" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>2983</v>
       </c>
@@ -36372,7 +36412,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="476" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>2990</v>
       </c>
@@ -36413,7 +36453,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="477" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>2994</v>
       </c>
@@ -36457,7 +36497,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="478" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>2999</v>
       </c>
@@ -36498,7 +36538,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="479" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>3005</v>
       </c>
@@ -36542,7 +36582,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="480" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>3011</v>
       </c>
@@ -36589,7 +36629,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="481" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
         <v>3017</v>
       </c>
@@ -36643,7 +36683,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="482" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482" s="16" t="s">
         <v>3027</v>
       </c>
@@ -36693,7 +36733,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="483" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>3033</v>
       </c>
@@ -36745,7 +36785,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="484" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>3041</v>
       </c>
@@ -36799,7 +36839,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="485" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>3047</v>
       </c>
@@ -36851,7 +36891,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="486" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>3053</v>
       </c>
@@ -36900,7 +36940,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="487" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>3060</v>
       </c>
@@ -36950,7 +36990,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="488" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>3066</v>
       </c>
@@ -37001,7 +37041,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="489" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>3072</v>
       </c>
@@ -37052,7 +37092,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="490" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>3077</v>
       </c>
@@ -37102,7 +37142,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="491" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>3084</v>
       </c>
@@ -37153,7 +37193,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="492" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>3090</v>
       </c>
@@ -37204,7 +37244,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="493" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>3095</v>
       </c>
@@ -37255,7 +37295,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="494" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>3100</v>
       </c>
@@ -37306,7 +37346,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="495" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>3106</v>
       </c>
@@ -37356,7 +37396,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="496" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>3114</v>
       </c>
@@ -37409,7 +37449,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="497" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>3120</v>
       </c>
@@ -37460,7 +37500,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="498" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>3124</v>
       </c>
@@ -37510,7 +37550,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="499" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>3130</v>
       </c>
@@ -37560,7 +37600,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="500" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>3136</v>
       </c>
@@ -37610,7 +37650,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="501" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>3143</v>
       </c>
@@ -37660,7 +37700,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="502" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>3149</v>
       </c>
@@ -37710,7 +37750,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="503" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>3155</v>
       </c>
@@ -37763,7 +37803,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="504" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>3160</v>
       </c>
@@ -37816,7 +37856,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="505" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>3170</v>
       </c>
@@ -37868,7 +37908,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="506" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>3175</v>
       </c>
@@ -37921,7 +37961,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="507" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>3184</v>
       </c>
@@ -37968,7 +38008,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="508" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>3191</v>
       </c>
@@ -38012,7 +38052,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="509" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>3197</v>
       </c>
@@ -38056,7 +38096,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="510" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>3202</v>
       </c>
@@ -38102,7 +38142,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="511" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>3206</v>
       </c>
@@ -38140,7 +38180,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="512" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>3210</v>
       </c>
@@ -38190,7 +38230,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="513" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>3216</v>
       </c>
@@ -38235,7 +38275,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="514" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>3221</v>
       </c>
@@ -38276,7 +38316,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="515" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>3227</v>
       </c>
@@ -38321,7 +38361,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="516" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>3232</v>
       </c>
@@ -38365,7 +38405,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="517" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>3237</v>
       </c>
@@ -38409,7 +38449,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="518" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>3242</v>
       </c>
@@ -38453,7 +38493,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="519" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>3247</v>
       </c>
@@ -38498,7 +38538,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="520" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>3252</v>
       </c>
@@ -38548,7 +38588,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="521" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>3258</v>
       </c>
@@ -38598,7 +38638,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="522" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>3263</v>
       </c>
@@ -38654,7 +38694,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>3489</v>
       </c>
@@ -38703,7 +38743,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>3502</v>
       </c>
@@ -38747,7 +38787,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>3507</v>
       </c>
@@ -38788,7 +38828,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>3509</v>
       </c>
@@ -38832,7 +38872,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>3514</v>
       </c>
@@ -38879,7 +38919,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>3517</v>
       </c>
@@ -38931,7 +38971,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>3522</v>
       </c>
@@ -38975,7 +39015,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>3523</v>
       </c>
@@ -39019,7 +39059,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>3538</v>
       </c>
@@ -39066,7 +39106,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>3542</v>
       </c>
@@ -39115,7 +39155,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>3548</v>
       </c>
@@ -39165,7 +39205,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12" t="s">
         <v>3583</v>
       </c>
@@ -39216,7 +39256,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12" t="s">
         <v>3584</v>
       </c>
@@ -39267,7 +39307,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12" t="s">
         <v>3585</v>
       </c>
@@ -39319,7 +39359,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12" t="s">
         <v>3586</v>
       </c>
@@ -39368,7 +39408,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12" t="s">
         <v>3587</v>
       </c>
@@ -39419,7 +39459,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12" t="s">
         <v>3588</v>
       </c>
@@ -39470,7 +39510,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12" t="s">
         <v>3589</v>
       </c>
@@ -39521,7 +39561,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12" t="s">
         <v>3590</v>
       </c>
@@ -39572,7 +39612,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12" t="s">
         <v>3591</v>
       </c>
@@ -39621,7 +39661,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12" t="s">
         <v>3592</v>
       </c>
@@ -39672,7 +39712,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12" t="s">
         <v>3593</v>
       </c>
@@ -39723,7 +39763,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12" t="s">
         <v>3594</v>
       </c>
@@ -39774,7 +39814,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12" t="s">
         <v>3595</v>
       </c>
@@ -39823,7 +39863,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
         <v>3596</v>
       </c>
@@ -39872,7 +39912,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12" t="s">
         <v>3597</v>
       </c>
@@ -39923,7 +39963,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12" t="s">
         <v>3598</v>
       </c>
@@ -39970,7 +40010,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12" t="s">
         <v>3599</v>
       </c>
@@ -40021,7 +40061,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12" t="s">
         <v>3600</v>
       </c>
@@ -40070,7 +40110,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12" t="s">
         <v>3601</v>
       </c>
@@ -40121,7 +40161,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12" t="s">
         <v>3602</v>
       </c>
@@ -40170,7 +40210,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12" t="s">
         <v>3603</v>
       </c>
@@ -40217,7 +40257,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12" t="s">
         <v>3604</v>
       </c>
@@ -40271,7 +40311,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12" t="s">
         <v>3618</v>
       </c>
@@ -40321,7 +40361,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12" t="s">
         <v>3632</v>
       </c>
@@ -40371,7 +40411,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12" t="s">
         <v>3637</v>
       </c>
@@ -40421,7 +40461,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12" t="s">
         <v>3661</v>
       </c>
@@ -40473,7 +40513,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12" t="s">
         <v>3680</v>
       </c>
@@ -40518,7 +40558,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12" t="s">
         <v>3700</v>
       </c>
@@ -40572,7 +40612,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12" t="s">
         <v>3701</v>
       </c>
@@ -40617,7 +40657,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12" t="s">
         <v>3702</v>
       </c>
@@ -40662,7 +40702,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12" t="s">
         <v>3703</v>
       </c>
@@ -40707,7 +40747,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12" t="s">
         <v>3704</v>
       </c>
@@ -40752,7 +40792,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12" t="s">
         <v>3705</v>
       </c>
@@ -40797,7 +40837,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12" t="s">
         <v>3731</v>
       </c>
@@ -40844,7 +40884,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12" t="s">
         <v>3740</v>
       </c>
@@ -40888,7 +40928,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12" t="s">
         <v>3750</v>
       </c>
@@ -40940,7 +40980,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12" t="s">
         <v>3771</v>
       </c>
@@ -40990,7 +41030,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12" t="s">
         <v>3779</v>
       </c>
@@ -41040,7 +41080,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12" t="s">
         <v>3781</v>
       </c>
@@ -41084,7 +41124,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12" t="s">
         <v>3809</v>
       </c>
@@ -41134,7 +41174,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12" t="s">
         <v>3821</v>
       </c>
@@ -41184,7 +41224,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12" t="s">
         <v>3824</v>
       </c>
@@ -41228,7 +41268,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12" t="s">
         <v>3830</v>
       </c>
@@ -41272,7 +41312,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12" t="s">
         <v>3843</v>
       </c>
@@ -41324,7 +41364,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12" t="s">
         <v>3902</v>
       </c>
@@ -41371,7 +41411,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12" t="s">
         <v>3905</v>
       </c>
@@ -41421,7 +41461,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12" t="s">
         <v>3908</v>
       </c>
@@ -41429,23 +41469,20 @@
         <v>3909</v>
       </c>
       <c r="E580" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="F580" s="2" t="s">
         <v>3911</v>
       </c>
-      <c r="F580" s="2" t="s">
+      <c r="G580" s="2" t="s">
         <v>3912</v>
       </c>
-      <c r="G580" s="2" t="s">
-        <v>3913</v>
-      </c>
       <c r="H580" s="2" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="I580" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J580" s="2" t="s">
-        <v>3915</v>
-      </c>
       <c r="K580" s="2" t="s">
         <v>26</v>
       </c>
@@ -41456,7 +41493,7 @@
         <v>3909</v>
       </c>
       <c r="O580" s="19" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="Q580" s="1" t="s">
         <v>123</v>
@@ -41465,42 +41502,42 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12" t="s">
-        <v>3916</v>
+        <v>3914</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F581" s="2" t="s">
+        <v>3916</v>
+      </c>
+      <c r="G581" s="2" t="s">
+        <v>3917</v>
+      </c>
+      <c r="H581" s="2" t="s">
+        <v>3917</v>
+      </c>
+      <c r="I581" s="2" t="s">
         <v>3918</v>
       </c>
-      <c r="G581" s="2" t="s">
-        <v>3919</v>
-      </c>
-      <c r="H581" s="2" t="s">
-        <v>3919</v>
-      </c>
-      <c r="I581" s="2" t="s">
-        <v>3920</v>
-      </c>
       <c r="J581" s="2" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
       <c r="K581" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L581" s="2" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
       <c r="M581" s="2" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
       <c r="O581" s="19" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
       <c r="Q581" s="1" t="s">
         <v>289</v>
@@ -41509,24 +41546,24 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>3923</v>
+      </c>
+      <c r="E582" s="2" t="s">
         <v>3924</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="F582" s="2" t="s">
+        <v>3928</v>
+      </c>
+      <c r="G582" s="2" t="s">
         <v>3925</v>
       </c>
-      <c r="E582" s="2" t="s">
-        <v>3926</v>
-      </c>
-      <c r="F582" s="2" t="s">
-        <v>3930</v>
-      </c>
-      <c r="G582" s="2" t="s">
-        <v>3927</v>
-      </c>
       <c r="H582" s="2" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
       <c r="I582" s="2" t="s">
         <v>230</v>
@@ -41538,13 +41575,13 @@
         <v>61</v>
       </c>
       <c r="L582" s="2" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
       <c r="M582" s="2" t="s">
-        <v>3925</v>
+        <v>3923</v>
       </c>
       <c r="O582" s="19" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
       <c r="Q582" s="1" t="s">
         <v>289</v>
@@ -41553,24 +41590,24 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F583" s="2" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
       <c r="G583" s="2" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
       <c r="H583" s="2" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
       <c r="I583" s="2" t="s">
         <v>138</v>
@@ -41582,13 +41619,13 @@
         <v>61</v>
       </c>
       <c r="L583" s="2" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
       <c r="M583" s="2" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
       <c r="O583" s="19" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="Q583" s="1" t="s">
         <v>289</v>
@@ -41597,12 +41634,12 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
       <c r="B584" s="65" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="C584" s="45"/>
       <c r="D584" s="45"/>
@@ -41610,13 +41647,13 @@
         <v>1748</v>
       </c>
       <c r="F584" s="66" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
       <c r="G584" s="66" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="H584" s="66" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="I584" s="65" t="s">
         <v>316</v>
@@ -41628,14 +41665,14 @@
         <v>61</v>
       </c>
       <c r="L584" s="69" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
       <c r="M584" s="65" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="N584" s="45"/>
       <c r="O584" s="19" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="Q584" s="1" t="s">
         <v>123</v>
@@ -41644,12 +41681,12 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
       <c r="B585" s="71" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="C585" s="71"/>
       <c r="D585" s="71"/>
@@ -41657,7 +41694,7 @@
         <v>433</v>
       </c>
       <c r="F585" s="71" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
       <c r="G585" s="71">
         <v>1535</v>
@@ -41678,11 +41715,11 @@
         <v>3644</v>
       </c>
       <c r="M585" s="71" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="N585" s="71"/>
       <c r="O585" s="19" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
       <c r="Q585" s="1" t="s">
         <v>123</v>
@@ -41691,18 +41728,18 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
       <c r="E586" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
       <c r="G586" s="2" t="s">
         <v>3834</v>
@@ -41723,13 +41760,13 @@
         <v>3655</v>
       </c>
       <c r="M586" s="2" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
       <c r="N586" s="5" t="s">
         <v>2199</v>
       </c>
       <c r="O586" s="19" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
       <c r="Q586" s="1" t="s">
         <v>289</v>
@@ -41738,12 +41775,12 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12" t="s">
-        <v>3981</v>
+        <v>3979</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -41751,13 +41788,13 @@
         <v>433</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="H587" s="1" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="I587" s="70" t="s">
         <v>419</v>
@@ -41772,10 +41809,10 @@
         <v>2588</v>
       </c>
       <c r="M587" s="1" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
       <c r="O587" s="19" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
       <c r="Q587" s="32" t="s">
         <v>289</v>
@@ -41784,12 +41821,12 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
       <c r="B588" s="45" t="s">
-        <v>3965</v>
+        <v>3963</v>
       </c>
       <c r="C588" s="45"/>
       <c r="D588" s="45"/>
@@ -41797,32 +41834,32 @@
         <v>2216</v>
       </c>
       <c r="F588" s="45" t="s">
-        <v>3966</v>
+        <v>3964</v>
       </c>
       <c r="G588" s="76" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
       <c r="H588" s="76" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
       <c r="I588" s="71" t="s">
         <v>138</v>
       </c>
       <c r="J588" s="71" t="s">
-        <v>3968</v>
+        <v>3966</v>
       </c>
       <c r="K588" s="71" t="s">
         <v>61</v>
       </c>
       <c r="L588" s="75" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
       <c r="M588" s="71" t="s">
-        <v>3965</v>
+        <v>3963</v>
       </c>
       <c r="N588" s="45"/>
       <c r="O588" s="19" t="s">
-        <v>3967</v>
+        <v>3965</v>
       </c>
       <c r="P588" s="45"/>
       <c r="Q588" s="1" t="s">
@@ -41832,24 +41869,24 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
       <c r="E589" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F589" s="2" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="G589" s="2" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="H589" s="2" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="I589" s="2" t="s">
         <v>197</v>
@@ -41864,10 +41901,10 @@
         <v>3644</v>
       </c>
       <c r="M589" s="2" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
       <c r="O589" s="19" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
       <c r="Q589" s="1" t="s">
         <v>123</v>
@@ -41876,18 +41913,18 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="E590" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F590" s="2" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="G590" s="2" t="s">
         <v>2339</v>
@@ -41908,10 +41945,10 @@
         <v>3644</v>
       </c>
       <c r="M590" s="2" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="O590" s="19" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="Q590" s="1" t="s">
         <v>123</v>
@@ -41920,18 +41957,18 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="E591" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F591" s="2" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="G591" s="2" t="s">
         <v>3515</v>
@@ -41949,13 +41986,13 @@
         <v>61</v>
       </c>
       <c r="L591" s="2" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="M591" s="2" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="O591" s="19" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="Q591" s="1" t="s">
         <v>123</v>
@@ -41964,9 +42001,9 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="592" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:20" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="B592" s="32" t="s">
         <v>3387</v>
@@ -41995,40 +42032,40 @@
         <v>61</v>
       </c>
       <c r="L592" s="35" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="M592" s="32" t="s">
         <v>3387</v>
       </c>
       <c r="N592" s="32"/>
       <c r="O592" s="33" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="Q592" s="1" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="T592" s="25" t="s">
         <v>3571</v>
       </c>
     </row>
-    <row r="593" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="E593" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F593" s="2" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="G593" s="2" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="I593" s="2" t="s">
         <v>2383</v>
@@ -42043,10 +42080,10 @@
         <v>3643</v>
       </c>
       <c r="M593" s="2" t="s">
+        <v>4014</v>
+      </c>
+      <c r="O593" s="19" t="s">
         <v>4016</v>
-      </c>
-      <c r="O593" s="19" t="s">
-        <v>4018</v>
       </c>
       <c r="Q593" s="1" t="s">
         <v>123</v>
@@ -42055,24 +42092,24 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="E594" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F594" s="2" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="G594" s="2" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="H594" s="2" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="I594" s="2" t="s">
         <v>2383</v>
@@ -42087,10 +42124,10 @@
         <v>3644</v>
       </c>
       <c r="M594" s="2" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="O594" s="19" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="Q594" s="1" t="s">
         <v>123</v>
@@ -42099,30 +42136,30 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="E595" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F595" s="2" t="s">
+        <v>4025</v>
+      </c>
+      <c r="G595" s="2" t="s">
         <v>4027</v>
       </c>
-      <c r="G595" s="2" t="s">
-        <v>4029</v>
-      </c>
       <c r="H595" s="2" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
       <c r="I595" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J595" s="2" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="K595" s="2" t="s">
         <v>61</v>
@@ -42131,10 +42168,10 @@
         <v>3644</v>
       </c>
       <c r="M595" s="2" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="O595" s="19" t="s">
-        <v>4025</v>
+        <v>4023</v>
       </c>
       <c r="Q595" s="1" t="s">
         <v>123</v>
@@ -42143,8 +42180,49 @@
         <v>3571</v>
       </c>
     </row>
+    <row r="596" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="12" t="s">
+        <v>4037</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="E596" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="F596" s="2" t="s">
+        <v>4034</v>
+      </c>
+      <c r="G596" s="2" t="s">
+        <v>4039</v>
+      </c>
+      <c r="H596" s="2" t="s">
+        <v>4039</v>
+      </c>
+      <c r="I596" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K596" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L596" s="2" t="s">
+        <v>4038</v>
+      </c>
+      <c r="M596" s="2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="O596" s="19" t="s">
+        <v>4030</v>
+      </c>
+      <c r="Q596" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T596" s="25" t="s">
+        <v>3571</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -42859,27 +42937,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T60"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="66" style="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="31" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.42578125" style="1" customWidth="1"/>
     <col min="11" max="13" width="12" style="1" customWidth="1"/>
     <col min="14" max="14" width="77" style="1" customWidth="1"/>
     <col min="15" max="15" width="79" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.5546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="24.6640625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.33203125" style="1"/>
+    <col min="16" max="16" width="24.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -42935,7 +43013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>3270</v>
       </c>
@@ -42988,7 +43066,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43024,7 +43102,7 @@
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
     </row>
-    <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43066,7 +43144,7 @@
       <c r="Q4" s="32"/>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43108,7 +43186,7 @@
       <c r="Q5" s="32"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43156,7 +43234,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43202,7 +43280,7 @@
       <c r="Q7" s="32"/>
       <c r="R7" s="32"/>
     </row>
-    <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>3270</v>
       </c>
@@ -43259,7 +43337,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43305,7 +43383,7 @@
       <c r="Q9" s="32"/>
       <c r="R9" s="32"/>
     </row>
-    <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43351,7 +43429,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
     </row>
-    <row r="11" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43397,7 +43475,7 @@
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
     </row>
-    <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43433,7 +43511,7 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
     </row>
-    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43477,7 +43555,7 @@
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
     </row>
-    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43521,7 +43599,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
     </row>
-    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43573,7 +43651,7 @@
       </c>
       <c r="R15" s="32"/>
     </row>
-    <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43627,7 +43705,7 @@
       </c>
       <c r="R16" s="32"/>
     </row>
-    <row r="17" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43679,7 +43757,7 @@
       </c>
       <c r="R17" s="32"/>
     </row>
-    <row r="18" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43733,7 +43811,7 @@
       </c>
       <c r="R18" s="32"/>
     </row>
-    <row r="19" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43783,7 +43861,7 @@
       </c>
       <c r="R19" s="32"/>
     </row>
-    <row r="20" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43835,7 +43913,7 @@
       </c>
       <c r="R20" s="32"/>
     </row>
-    <row r="21" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43885,7 +43963,7 @@
       </c>
       <c r="R21" s="32"/>
     </row>
-    <row r="22" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43937,7 +44015,7 @@
       </c>
       <c r="R22" s="32"/>
     </row>
-    <row r="23" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>3270</v>
       </c>
@@ -43989,7 +44067,7 @@
       </c>
       <c r="R23" s="32"/>
     </row>
-    <row r="24" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44041,7 +44119,7 @@
       </c>
       <c r="R24" s="32"/>
     </row>
-    <row r="25" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44087,7 +44165,7 @@
       <c r="Q25" s="32"/>
       <c r="R25" s="32"/>
     </row>
-    <row r="26" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44133,7 +44211,7 @@
       <c r="Q26" s="32"/>
       <c r="R26" s="32"/>
     </row>
-    <row r="27" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44173,7 +44251,7 @@
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
     </row>
-    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44219,7 +44297,7 @@
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
     </row>
-    <row r="29" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
         <v>1907</v>
       </c>
@@ -44267,7 +44345,7 @@
       <c r="Q29" s="32"/>
       <c r="R29" s="32"/>
     </row>
-    <row r="30" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44295,7 +44373,7 @@
       <c r="Q30" s="32"/>
       <c r="R30" s="32"/>
     </row>
-    <row r="31" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44327,7 +44405,7 @@
       </c>
       <c r="R31" s="32"/>
     </row>
-    <row r="32" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44363,7 +44441,7 @@
       <c r="Q32" s="32"/>
       <c r="R32" s="32"/>
     </row>
-    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44399,7 +44477,7 @@
       <c r="Q33" s="32"/>
       <c r="R33" s="32"/>
     </row>
-    <row r="34" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44447,7 +44525,7 @@
       </c>
       <c r="R34" s="32"/>
     </row>
-    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44493,7 +44571,7 @@
       </c>
       <c r="R35" s="32"/>
     </row>
-    <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44541,7 +44619,7 @@
       </c>
       <c r="R36" s="32"/>
     </row>
-    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44585,7 +44663,7 @@
       </c>
       <c r="R37" s="32"/>
     </row>
-    <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44631,7 +44709,7 @@
       <c r="Q38" s="32"/>
       <c r="R38" s="32"/>
     </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44679,7 +44757,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44717,7 +44795,7 @@
       <c r="Q40" s="32"/>
       <c r="R40" s="32"/>
     </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44755,7 +44833,7 @@
       <c r="Q41" s="32"/>
       <c r="R41" s="32"/>
     </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44801,7 +44879,7 @@
       <c r="Q42" s="45"/>
       <c r="R42" s="45"/>
     </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44853,7 +44931,7 @@
       </c>
       <c r="R43" s="32"/>
     </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44905,7 +44983,7 @@
       </c>
       <c r="R44" s="32"/>
     </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44951,7 +45029,7 @@
       </c>
       <c r="R45" s="45"/>
     </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31" t="s">
         <v>3270</v>
       </c>
@@ -44997,7 +45075,7 @@
       </c>
       <c r="R46" s="45"/>
     </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45049,12 +45127,12 @@
       <c r="Q47" s="45"/>
       <c r="R47" s="45"/>
     </row>
-    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="31" t="s">
         <v>3270</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45098,7 +45176,7 @@
       <c r="Q49" s="45"/>
       <c r="R49" s="45"/>
     </row>
-    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45130,7 +45208,7 @@
       <c r="Q50" s="45"/>
       <c r="R50" s="45"/>
     </row>
-    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45162,7 +45240,7 @@
       <c r="Q51" s="45"/>
       <c r="R51" s="45"/>
     </row>
-    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45194,7 +45272,7 @@
       <c r="Q52" s="45"/>
       <c r="R52" s="45"/>
     </row>
-    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45226,7 +45304,7 @@
       <c r="Q53" s="45"/>
       <c r="R53" s="45"/>
     </row>
-    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31" t="s">
         <v>3270</v>
       </c>
@@ -45246,30 +45324,30 @@
         <v>3837</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="C55" s="1">
         <v>2047</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>405</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>45</v>
@@ -45278,24 +45356,24 @@
         <v>130</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B56" s="65" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="45"/>
@@ -45303,13 +45381,13 @@
         <v>1748</v>
       </c>
       <c r="F56" s="66" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
       <c r="G56" s="66" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="H56" s="66" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="I56" s="65" t="s">
         <v>316</v>
@@ -45322,34 +45400,34 @@
       </c>
       <c r="L56" s="45"/>
       <c r="M56" s="65" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="N56" s="45"/>
       <c r="O56" s="19" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q56" s="65" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
       <c r="R56" s="45"/>
     </row>
-    <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
       <c r="C57" s="45"/>
       <c r="D57" s="45"/>
       <c r="E57" s="68" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
       <c r="F57" s="68" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
       <c r="G57" s="67" t="s">
         <v>3418</v>
@@ -45358,36 +45436,36 @@
         <v>3418</v>
       </c>
       <c r="I57" s="67" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
       <c r="J57" s="67" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
       <c r="K57" s="67" t="s">
         <v>61</v>
       </c>
       <c r="L57" s="45"/>
       <c r="M57" s="67" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
       <c r="N57" s="45"/>
       <c r="O57" s="19" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q57" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
       <c r="R57" s="45"/>
     </row>
-    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31" t="s">
         <v>3270</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
       <c r="C58" s="45">
         <v>4614</v>
@@ -45396,16 +45474,16 @@
         <v>3002</v>
       </c>
       <c r="E58" s="70" t="s">
+        <v>3960</v>
+      </c>
+      <c r="F58" s="70" t="s">
         <v>3962</v>
       </c>
-      <c r="F58" s="70" t="s">
-        <v>3964</v>
-      </c>
       <c r="G58" s="70" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
       <c r="H58" s="70" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
       <c r="I58" s="70" t="s">
         <v>419</v>
@@ -45420,22 +45498,22 @@
         <v>383</v>
       </c>
       <c r="M58" s="70" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>3963</v>
+        <v>3961</v>
       </c>
       <c r="O58" s="19" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
       <c r="P58" s="45"/>
       <c r="Q58" s="45"/>
       <c r="R58" s="45"/>
     </row>
-    <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45"/>
       <c r="B59" s="74" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
       <c r="C59" s="45"/>
       <c r="D59" s="45"/>
@@ -45443,7 +45521,7 @@
         <v>3289</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>3982</v>
+        <v>3980</v>
       </c>
       <c r="G59" s="45">
         <v>1777</v>
@@ -45458,18 +45536,18 @@
       <c r="M59" s="45"/>
       <c r="N59" s="45"/>
       <c r="O59" s="19" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
       <c r="P59" s="45"/>
       <c r="Q59" s="73" t="s">
-        <v>3984</v>
+        <v>3982</v>
       </c>
       <c r="R59" s="45"/>
     </row>
-    <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
       <c r="B60" s="45" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
       <c r="C60" s="45"/>
       <c r="D60" s="45"/>
@@ -45477,30 +45555,30 @@
         <v>433</v>
       </c>
       <c r="F60" s="74" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="G60" s="74" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="H60" s="74" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="I60" s="74" t="s">
         <v>197</v>
       </c>
       <c r="J60" s="74" t="s">
-        <v>3989</v>
+        <v>3987</v>
       </c>
       <c r="K60" s="74" t="s">
         <v>61</v>
       </c>
       <c r="L60" s="45"/>
       <c r="M60" s="74" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
       <c r="N60" s="45"/>
       <c r="O60" s="19" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
       <c r="P60" s="74" t="s">
         <v>289</v>
@@ -45508,8 +45586,76 @@
       <c r="Q60" s="45"/>
       <c r="R60" s="45"/>
     </row>
+    <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="45"/>
+      <c r="B61" s="45" t="s">
+        <v>4028</v>
+      </c>
+      <c r="C61" s="45"/>
+      <c r="D61" s="45"/>
+      <c r="E61" s="2" t="s">
+        <v>4029</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>4034</v>
+      </c>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="45"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="45"/>
+      <c r="M61" s="77" t="s">
+        <v>4028</v>
+      </c>
+      <c r="N61" s="45"/>
+      <c r="O61" s="45" t="s">
+        <v>4030</v>
+      </c>
+      <c r="P61" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q61" s="45"/>
+      <c r="R61" s="45"/>
+    </row>
+    <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="45"/>
+      <c r="B62" s="45" t="s">
+        <v>4031</v>
+      </c>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F62" s="77" t="s">
+        <v>4032</v>
+      </c>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="45"/>
+      <c r="J62" s="45"/>
+      <c r="K62" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="45"/>
+      <c r="M62" s="77" t="s">
+        <v>4031</v>
+      </c>
+      <c r="N62" s="45"/>
+      <c r="O62" s="45" t="s">
+        <v>4033</v>
+      </c>
+      <c r="P62" s="77" t="s">
+        <v>4035</v>
+      </c>
+      <c r="Q62" s="45"/>
+      <c r="R62" s="45"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
@@ -45605,16 +45751,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="26.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="26.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" style="59" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="59" customWidth="1"/>
-    <col min="5" max="16384" width="26.5546875" style="59"/>
+    <col min="1" max="1" width="34.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="59" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="59" customWidth="1"/>
+    <col min="5" max="16384" width="26.5703125" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
         <v>3610</v>
       </c>
@@ -45631,7 +45777,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
         <v>3859</v>
       </c>
@@ -45645,7 +45791,7 @@
         <v>3863</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>3816</v>
       </c>
@@ -45662,7 +45808,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
         <v>3810</v>
       </c>
@@ -45676,7 +45822,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
         <v>3815</v>
       </c>
@@ -45690,7 +45836,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
         <v>3811</v>
       </c>
@@ -45704,7 +45850,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
         <v>3812</v>
       </c>
@@ -45718,7 +45864,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
         <v>3813</v>
       </c>
@@ -45732,7 +45878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
         <v>3814</v>
       </c>
@@ -45746,7 +45892,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
         <v>3483</v>
       </c>
@@ -45757,7 +45903,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
         <v>3568</v>
       </c>
@@ -45768,7 +45914,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
         <v>3569</v>
       </c>
@@ -45779,7 +45925,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
         <v>3570</v>
       </c>
@@ -45790,13 +45936,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="59" t="s">
         <v>3861</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58567BEF-4712-45EB-A19F-E50D8F5DE077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC25A752-B08A-49C3-B283-1E792AE5CE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18825" yWindow="1170" windowWidth="21045" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8433" uniqueCount="4040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8436" uniqueCount="4045">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12158,6 +12158,21 @@
   </si>
   <si>
     <t>1589-06-17</t>
+  </si>
+  <si>
+    <t>PS30</t>
+  </si>
+  <si>
+    <t>R/39732</t>
+  </si>
+  <si>
+    <t>1530-01-15</t>
+  </si>
+  <si>
+    <t>https://bnedigital.bne.es/bd/es/card?id=4a66a620-1295-4b8b-acf0-73025095c7c1</t>
+  </si>
+  <si>
+    <t>PG30</t>
   </si>
 </sst>
 </file>
@@ -12167,13 +12182,27 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -12470,9 +12499,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -12486,7 +12515,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -12495,26 +12524,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -12523,86 +12552,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12611,27 +12646,27 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -12650,10 +12685,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -12665,16 +12703,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12786,6 +12821,9 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -12996,9 +13034,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -13098,7 +13133,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13113,27 +13148,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:R62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -42222,7 +42257,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -45589,15 +45624,15 @@
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45"/>
       <c r="B61" s="45" t="s">
-        <v>4028</v>
+        <v>4031</v>
       </c>
       <c r="C61" s="45"/>
       <c r="D61" s="45"/>
-      <c r="E61" s="2" t="s">
-        <v>4029</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>4034</v>
+      <c r="E61" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="F61" s="77" t="s">
+        <v>4032</v>
       </c>
       <c r="G61" s="45"/>
       <c r="H61" s="45"/>
@@ -45608,54 +45643,60 @@
       </c>
       <c r="L61" s="45"/>
       <c r="M61" s="77" t="s">
-        <v>4028</v>
+        <v>4031</v>
       </c>
       <c r="N61" s="45"/>
-      <c r="O61" s="45" t="s">
-        <v>4030</v>
+      <c r="O61" s="19" t="s">
+        <v>4033</v>
       </c>
       <c r="P61" s="77" t="s">
-        <v>123</v>
+        <v>4035</v>
       </c>
       <c r="Q61" s="45"/>
       <c r="R61" s="45"/>
     </row>
     <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45"/>
-      <c r="B62" s="45" t="s">
-        <v>4031</v>
+      <c r="B62" s="79" t="s">
+        <v>4044</v>
       </c>
       <c r="C62" s="45"/>
       <c r="D62" s="45"/>
       <c r="E62" s="45" t="s">
         <v>433</v>
       </c>
-      <c r="F62" s="77" t="s">
-        <v>4032</v>
-      </c>
-      <c r="G62" s="45"/>
-      <c r="H62" s="45"/>
-      <c r="I62" s="45"/>
-      <c r="J62" s="45"/>
-      <c r="K62" s="77" t="s">
-        <v>26</v>
+      <c r="F62" s="78" t="s">
+        <v>4041</v>
+      </c>
+      <c r="G62" s="78" t="s">
+        <v>4042</v>
+      </c>
+      <c r="H62" s="78" t="s">
+        <v>4042</v>
+      </c>
+      <c r="I62" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="J62" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="K62" s="78" t="s">
+        <v>61</v>
       </c>
       <c r="L62" s="45"/>
-      <c r="M62" s="77" t="s">
-        <v>4031</v>
+      <c r="M62" s="78" t="s">
+        <v>4040</v>
       </c>
       <c r="N62" s="45"/>
-      <c r="O62" s="45" t="s">
-        <v>4033</v>
-      </c>
-      <c r="P62" s="77" t="s">
-        <v>4035</v>
-      </c>
+      <c r="O62" s="19" t="s">
+        <v>4043</v>
+      </c>
+      <c r="P62" s="45"/>
       <c r="Q62" s="45"/>
       <c r="R62" s="45"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
@@ -45739,11 +45780,13 @@
     <hyperlink ref="O58" r:id="rId80" xr:uid="{0F09B375-5A60-41A8-8909-6A8862B203D3}"/>
     <hyperlink ref="O59" r:id="rId81" xr:uid="{6A39D157-F210-4892-95B6-5107F8DF777C}"/>
     <hyperlink ref="O60" r:id="rId82" xr:uid="{96D11007-6757-4F70-AB48-16741226BC93}"/>
+    <hyperlink ref="O62" r:id="rId83" xr:uid="{F1C65028-1D8D-40A8-9F1E-722A1F4F4126}"/>
+    <hyperlink ref="O61" r:id="rId84" xr:uid="{AA86DDB8-EC9F-44B4-81DD-DD4BD3F68872}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId83"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId85"/>
   <tableParts count="1">
-    <tablePart r:id="rId84"/>
+    <tablePart r:id="rId86"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45942,7 +45985,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC25A752-B08A-49C3-B283-1E792AE5CE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1DDD63-6E60-49FF-81A0-9FAE22EEABB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18825" yWindow="1170" windowWidth="21045" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1845" windowWidth="21045" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -11743,9 +11743,6 @@
     <t>Lloyd A. Kasten, John Nitti, Wilhelmina Jonxis-Henkemans, Xenia Bonch-Bruevich</t>
   </si>
   <si>
-    <t>FRS1, VBJ</t>
-  </si>
-  <si>
     <t>HSMS-0577</t>
   </si>
   <si>
@@ -12173,6 +12170,9 @@
   </si>
   <si>
     <t>PG30</t>
+  </si>
+  <si>
+    <t>S77</t>
   </si>
 </sst>
 </file>
@@ -12823,9 +12823,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -13034,6 +13031,9 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -13133,7 +13133,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13148,27 +13148,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="25">
   <autoFilter ref="A1:R62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13429,7 +13429,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -23284,7 +23284,7 @@
         <v>1403</v>
       </c>
       <c r="O200" s="9" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="Q200" s="1" t="s">
         <v>1404</v>
@@ -24308,7 +24308,7 @@
         <v>69</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>130</v>
@@ -28207,13 +28207,13 @@
         <v>1989</v>
       </c>
       <c r="O301" s="9" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="Q301" s="1" t="s">
         <v>1404</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="T301" t="s">
         <v>30</v>
@@ -41020,7 +41020,7 @@
         <v>3771</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>3901</v>
+        <v>4044</v>
       </c>
       <c r="C570" s="3">
         <v>2528</v>
@@ -41050,7 +41050,7 @@
         <v>3773</v>
       </c>
       <c r="M570" s="2" t="s">
-        <v>3901</v>
+        <v>4044</v>
       </c>
       <c r="N570" s="9" t="s">
         <v>3777</v>
@@ -41401,7 +41401,7 @@
     </row>
     <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>3799</v>
@@ -41413,7 +41413,7 @@
         <v>1618</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="G578" s="2" t="s">
         <v>3800</v>
@@ -41431,7 +41431,7 @@
         <v>130</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="M578" s="2" t="s">
         <v>3799</v>
@@ -41448,7 +41448,7 @@
     </row>
     <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>3719</v>
@@ -41478,7 +41478,7 @@
         <v>47</v>
       </c>
       <c r="L579" s="2" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="M579" s="2" t="s">
         <v>3719</v>
@@ -41487,7 +41487,7 @@
         <v>3794</v>
       </c>
       <c r="O579" s="19" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="Q579" s="1" t="s">
         <v>289</v>
@@ -41498,22 +41498,22 @@
     </row>
     <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B580" s="2" t="s">
         <v>3908</v>
       </c>
-      <c r="B580" s="2" t="s">
-        <v>3909</v>
-      </c>
       <c r="E580" s="2" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="F580" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="G580" s="2" t="s">
         <v>3911</v>
       </c>
-      <c r="G580" s="2" t="s">
-        <v>3912</v>
-      </c>
       <c r="H580" s="2" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="I580" s="2" t="s">
         <v>87</v>
@@ -41522,13 +41522,13 @@
         <v>26</v>
       </c>
       <c r="L580" s="2" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="M580" s="2" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="O580" s="19" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="Q580" s="1" t="s">
         <v>123</v>
@@ -41539,40 +41539,40 @@
     </row>
     <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B581" s="2" t="s">
         <v>3914</v>
-      </c>
-      <c r="B581" s="2" t="s">
-        <v>3915</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F581" s="2" t="s">
+        <v>3915</v>
+      </c>
+      <c r="G581" s="2" t="s">
         <v>3916</v>
       </c>
-      <c r="G581" s="2" t="s">
+      <c r="H581" s="2" t="s">
+        <v>3916</v>
+      </c>
+      <c r="I581" s="2" t="s">
         <v>3917</v>
       </c>
-      <c r="H581" s="2" t="s">
-        <v>3917</v>
-      </c>
-      <c r="I581" s="2" t="s">
-        <v>3918</v>
-      </c>
       <c r="J581" s="2" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="K581" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L581" s="2" t="s">
+        <v>3918</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>3914</v>
+      </c>
+      <c r="O581" s="19" t="s">
         <v>3919</v>
-      </c>
-      <c r="M581" s="2" t="s">
-        <v>3915</v>
-      </c>
-      <c r="O581" s="19" t="s">
-        <v>3920</v>
       </c>
       <c r="Q581" s="1" t="s">
         <v>289</v>
@@ -41583,22 +41583,22 @@
     </row>
     <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12" t="s">
+        <v>3921</v>
+      </c>
+      <c r="B582" s="2" t="s">
         <v>3922</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="E582" s="2" t="s">
         <v>3923</v>
       </c>
-      <c r="E582" s="2" t="s">
+      <c r="F582" s="2" t="s">
+        <v>3927</v>
+      </c>
+      <c r="G582" s="2" t="s">
         <v>3924</v>
       </c>
-      <c r="F582" s="2" t="s">
-        <v>3928</v>
-      </c>
-      <c r="G582" s="2" t="s">
-        <v>3925</v>
-      </c>
       <c r="H582" s="2" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="I582" s="2" t="s">
         <v>230</v>
@@ -41610,13 +41610,13 @@
         <v>61</v>
       </c>
       <c r="L582" s="2" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="M582" s="2" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="O582" s="19" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="Q582" s="1" t="s">
         <v>289</v>
@@ -41627,22 +41627,22 @@
     </row>
     <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F583" s="2" t="s">
+        <v>3936</v>
+      </c>
+      <c r="G583" s="2" t="s">
         <v>3937</v>
       </c>
-      <c r="G583" s="2" t="s">
-        <v>3938</v>
-      </c>
       <c r="H583" s="2" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="I583" s="2" t="s">
         <v>138</v>
@@ -41654,13 +41654,13 @@
         <v>61</v>
       </c>
       <c r="L583" s="2" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="M583" s="2" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="O583" s="19" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="Q583" s="1" t="s">
         <v>289</v>
@@ -41671,10 +41671,10 @@
     </row>
     <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="B584" s="65" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="C584" s="45"/>
       <c r="D584" s="45"/>
@@ -41682,13 +41682,13 @@
         <v>1748</v>
       </c>
       <c r="F584" s="66" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="G584" s="66" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="H584" s="66" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="I584" s="65" t="s">
         <v>316</v>
@@ -41700,14 +41700,14 @@
         <v>61</v>
       </c>
       <c r="L584" s="69" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="M584" s="65" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="N584" s="45"/>
       <c r="O584" s="19" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="Q584" s="1" t="s">
         <v>123</v>
@@ -41718,10 +41718,10 @@
     </row>
     <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B585" s="71" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="C585" s="71"/>
       <c r="D585" s="71"/>
@@ -41729,7 +41729,7 @@
         <v>433</v>
       </c>
       <c r="F585" s="71" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="G585" s="71">
         <v>1535</v>
@@ -41750,11 +41750,11 @@
         <v>3644</v>
       </c>
       <c r="M585" s="71" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="N585" s="71"/>
       <c r="O585" s="19" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="Q585" s="1" t="s">
         <v>123</v>
@@ -41765,16 +41765,16 @@
     </row>
     <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B586" s="2" t="s">
         <v>3971</v>
-      </c>
-      <c r="B586" s="2" t="s">
-        <v>3972</v>
       </c>
       <c r="E586" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="G586" s="2" t="s">
         <v>3834</v>
@@ -41795,13 +41795,13 @@
         <v>3655</v>
       </c>
       <c r="M586" s="2" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="N586" s="5" t="s">
         <v>2199</v>
       </c>
       <c r="O586" s="19" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="Q586" s="1" t="s">
         <v>289</v>
@@ -41812,10 +41812,10 @@
     </row>
     <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -41823,13 +41823,13 @@
         <v>433</v>
       </c>
       <c r="F587" s="1" t="s">
+        <v>3975</v>
+      </c>
+      <c r="G587" s="1" t="s">
         <v>3976</v>
       </c>
-      <c r="G587" s="1" t="s">
-        <v>3977</v>
-      </c>
       <c r="H587" s="1" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="I587" s="70" t="s">
         <v>419</v>
@@ -41844,10 +41844,10 @@
         <v>2588</v>
       </c>
       <c r="M587" s="1" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="O587" s="19" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="Q587" s="32" t="s">
         <v>289</v>
@@ -41858,10 +41858,10 @@
     </row>
     <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="B588" s="45" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="C588" s="45"/>
       <c r="D588" s="45"/>
@@ -41869,32 +41869,32 @@
         <v>2216</v>
       </c>
       <c r="F588" s="45" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="G588" s="76" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="H588" s="76" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="I588" s="71" t="s">
         <v>138</v>
       </c>
       <c r="J588" s="71" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="K588" s="71" t="s">
         <v>61</v>
       </c>
       <c r="L588" s="75" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="M588" s="71" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="N588" s="45"/>
       <c r="O588" s="19" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="P588" s="45"/>
       <c r="Q588" s="1" t="s">
@@ -41906,22 +41906,22 @@
     </row>
     <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B589" s="2" t="s">
         <v>3998</v>
-      </c>
-      <c r="B589" s="2" t="s">
-        <v>3999</v>
       </c>
       <c r="E589" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F589" s="2" t="s">
+        <v>3995</v>
+      </c>
+      <c r="G589" s="2" t="s">
         <v>3996</v>
       </c>
-      <c r="G589" s="2" t="s">
-        <v>3997</v>
-      </c>
       <c r="H589" s="2" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="I589" s="2" t="s">
         <v>197</v>
@@ -41936,10 +41936,10 @@
         <v>3644</v>
       </c>
       <c r="M589" s="2" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="O589" s="19" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="Q589" s="1" t="s">
         <v>123</v>
@@ -41950,16 +41950,16 @@
     </row>
     <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B590" s="2" t="s">
         <v>4000</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>4001</v>
       </c>
       <c r="E590" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F590" s="2" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="G590" s="2" t="s">
         <v>2339</v>
@@ -41980,10 +41980,10 @@
         <v>3644</v>
       </c>
       <c r="M590" s="2" t="s">
+        <v>4000</v>
+      </c>
+      <c r="O590" s="19" t="s">
         <v>4001</v>
-      </c>
-      <c r="O590" s="19" t="s">
-        <v>4002</v>
       </c>
       <c r="Q590" s="1" t="s">
         <v>123</v>
@@ -41994,16 +41994,16 @@
     </row>
     <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="E591" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F591" s="2" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="G591" s="2" t="s">
         <v>3515</v>
@@ -42021,13 +42021,13 @@
         <v>61</v>
       </c>
       <c r="L591" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="M591" s="2" t="s">
+        <v>4003</v>
+      </c>
+      <c r="O591" s="19" t="s">
         <v>4007</v>
-      </c>
-      <c r="M591" s="2" t="s">
-        <v>4004</v>
-      </c>
-      <c r="O591" s="19" t="s">
-        <v>4008</v>
       </c>
       <c r="Q591" s="1" t="s">
         <v>123</v>
@@ -42038,7 +42038,7 @@
     </row>
     <row r="592" spans="1:20" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="B592" s="32" t="s">
         <v>3387</v>
@@ -42067,17 +42067,17 @@
         <v>61</v>
       </c>
       <c r="L592" s="35" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="M592" s="32" t="s">
         <v>3387</v>
       </c>
       <c r="N592" s="32"/>
       <c r="O592" s="33" t="s">
+        <v>4009</v>
+      </c>
+      <c r="Q592" s="1" t="s">
         <v>4010</v>
-      </c>
-      <c r="Q592" s="1" t="s">
-        <v>4011</v>
       </c>
       <c r="T592" s="25" t="s">
         <v>3571</v>
@@ -42085,22 +42085,22 @@
     </row>
     <row r="593" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B593" s="2" t="s">
         <v>4013</v>
-      </c>
-      <c r="B593" s="2" t="s">
-        <v>4014</v>
       </c>
       <c r="E593" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F593" s="2" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="G593" s="2" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="I593" s="2" t="s">
         <v>2383</v>
@@ -42115,10 +42115,10 @@
         <v>3643</v>
       </c>
       <c r="M593" s="2" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="O593" s="19" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="Q593" s="1" t="s">
         <v>123</v>
@@ -42129,22 +42129,22 @@
     </row>
     <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B594" s="2" t="s">
         <v>4018</v>
-      </c>
-      <c r="B594" s="2" t="s">
-        <v>4019</v>
       </c>
       <c r="E594" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F594" s="2" t="s">
+        <v>4019</v>
+      </c>
+      <c r="G594" s="2" t="s">
         <v>4020</v>
       </c>
-      <c r="G594" s="2" t="s">
-        <v>4021</v>
-      </c>
       <c r="H594" s="2" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="I594" s="2" t="s">
         <v>2383</v>
@@ -42159,10 +42159,10 @@
         <v>3644</v>
       </c>
       <c r="M594" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="O594" s="19" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="Q594" s="1" t="s">
         <v>123</v>
@@ -42173,28 +42173,28 @@
     </row>
     <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="E595" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F595" s="2" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G595" s="2" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="H595" s="2" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="I595" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J595" s="2" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="K595" s="2" t="s">
         <v>61</v>
@@ -42203,10 +42203,10 @@
         <v>3644</v>
       </c>
       <c r="M595" s="2" t="s">
+        <v>4021</v>
+      </c>
+      <c r="O595" s="19" t="s">
         <v>4022</v>
-      </c>
-      <c r="O595" s="19" t="s">
-        <v>4023</v>
       </c>
       <c r="Q595" s="1" t="s">
         <v>123</v>
@@ -42217,22 +42217,22 @@
     </row>
     <row r="596" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="12" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="B596" s="2" t="s">
+        <v>4027</v>
+      </c>
+      <c r="E596" s="2" t="s">
         <v>4028</v>
       </c>
-      <c r="E596" s="2" t="s">
-        <v>4029</v>
-      </c>
       <c r="F596" s="2" t="s">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="G596" s="2" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="H596" s="2" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="I596" s="2" t="s">
         <v>87</v>
@@ -42241,13 +42241,13 @@
         <v>26</v>
       </c>
       <c r="L596" s="2" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="M596" s="2" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="O596" s="19" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="Q596" s="1" t="s">
         <v>123</v>
@@ -45364,25 +45364,25 @@
         <v>3270</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="C55" s="1">
         <v>2047</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>405</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>3931</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>3932</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>3933</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>45</v>
@@ -45391,13 +45391,13 @@
         <v>130</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>3933</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>3934</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>3935</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>123</v>
@@ -45408,7 +45408,7 @@
         <v>3270</v>
       </c>
       <c r="B56" s="65" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="45"/>
@@ -45416,13 +45416,13 @@
         <v>1748</v>
       </c>
       <c r="F56" s="66" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="G56" s="66" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="H56" s="66" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="I56" s="65" t="s">
         <v>316</v>
@@ -45435,17 +45435,17 @@
       </c>
       <c r="L56" s="45"/>
       <c r="M56" s="65" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="N56" s="45"/>
       <c r="O56" s="19" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q56" s="65" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="R56" s="45"/>
     </row>
@@ -45454,15 +45454,15 @@
         <v>3270</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="C57" s="45"/>
       <c r="D57" s="45"/>
       <c r="E57" s="68" t="s">
+        <v>3947</v>
+      </c>
+      <c r="F57" s="68" t="s">
         <v>3948</v>
-      </c>
-      <c r="F57" s="68" t="s">
-        <v>3949</v>
       </c>
       <c r="G57" s="67" t="s">
         <v>3418</v>
@@ -45471,27 +45471,27 @@
         <v>3418</v>
       </c>
       <c r="I57" s="67" t="s">
+        <v>3951</v>
+      </c>
+      <c r="J57" s="67" t="s">
         <v>3952</v>
-      </c>
-      <c r="J57" s="67" t="s">
-        <v>3953</v>
       </c>
       <c r="K57" s="67" t="s">
         <v>61</v>
       </c>
       <c r="L57" s="45"/>
       <c r="M57" s="67" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="N57" s="45"/>
       <c r="O57" s="19" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q57" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="R57" s="45"/>
     </row>
@@ -45500,7 +45500,7 @@
         <v>3270</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="C58" s="45">
         <v>4614</v>
@@ -45509,16 +45509,16 @@
         <v>3002</v>
       </c>
       <c r="E58" s="70" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="F58" s="70" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="G58" s="70" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="H58" s="70" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="I58" s="70" t="s">
         <v>419</v>
@@ -45533,13 +45533,13 @@
         <v>383</v>
       </c>
       <c r="M58" s="70" t="s">
+        <v>3956</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>3960</v>
+      </c>
+      <c r="O58" s="19" t="s">
         <v>3957</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>3961</v>
-      </c>
-      <c r="O58" s="19" t="s">
-        <v>3958</v>
       </c>
       <c r="P58" s="45"/>
       <c r="Q58" s="45"/>
@@ -45548,7 +45548,7 @@
     <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45"/>
       <c r="B59" s="74" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="C59" s="45"/>
       <c r="D59" s="45"/>
@@ -45556,7 +45556,7 @@
         <v>3289</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="G59" s="45">
         <v>1777</v>
@@ -45571,18 +45571,18 @@
       <c r="M59" s="45"/>
       <c r="N59" s="45"/>
       <c r="O59" s="19" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="P59" s="45"/>
       <c r="Q59" s="73" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
       <c r="B60" s="45" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="C60" s="45"/>
       <c r="D60" s="45"/>
@@ -45590,30 +45590,30 @@
         <v>433</v>
       </c>
       <c r="F60" s="74" t="s">
+        <v>3984</v>
+      </c>
+      <c r="G60" s="74" t="s">
         <v>3985</v>
       </c>
-      <c r="G60" s="74" t="s">
-        <v>3986</v>
-      </c>
       <c r="H60" s="74" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="I60" s="74" t="s">
         <v>197</v>
       </c>
       <c r="J60" s="74" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="K60" s="74" t="s">
         <v>61</v>
       </c>
       <c r="L60" s="45"/>
       <c r="M60" s="74" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="N60" s="45"/>
       <c r="O60" s="19" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="P60" s="74" t="s">
         <v>289</v>
@@ -45624,7 +45624,7 @@
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45"/>
       <c r="B61" s="45" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="C61" s="45"/>
       <c r="D61" s="45"/>
@@ -45632,7 +45632,7 @@
         <v>433</v>
       </c>
       <c r="F61" s="77" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="G61" s="45"/>
       <c r="H61" s="45"/>
@@ -45643,14 +45643,14 @@
       </c>
       <c r="L61" s="45"/>
       <c r="M61" s="77" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="N61" s="45"/>
       <c r="O61" s="19" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="P61" s="77" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="Q61" s="45"/>
       <c r="R61" s="45"/>
@@ -45658,7 +45658,7 @@
     <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45"/>
       <c r="B62" s="79" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="C62" s="45"/>
       <c r="D62" s="45"/>
@@ -45666,13 +45666,13 @@
         <v>433</v>
       </c>
       <c r="F62" s="78" t="s">
+        <v>4040</v>
+      </c>
+      <c r="G62" s="78" t="s">
         <v>4041</v>
       </c>
-      <c r="G62" s="78" t="s">
-        <v>4042</v>
-      </c>
       <c r="H62" s="78" t="s">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="I62" s="78" t="s">
         <v>45</v>
@@ -45685,11 +45685,11 @@
       </c>
       <c r="L62" s="45"/>
       <c r="M62" s="78" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="N62" s="45"/>
       <c r="O62" s="19" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="P62" s="45"/>
       <c r="Q62" s="45"/>

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1DDD63-6E60-49FF-81A0-9FAE22EEABB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F37DD7-EC28-4619-BB5C-BC9F24C2CFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1845" windowWidth="21045" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15555" yWindow="2190" windowWidth="21045" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8436" uniqueCount="4045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8449" uniqueCount="4050">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12173,6 +12173,21 @@
   </si>
   <si>
     <t>S77</t>
+  </si>
+  <si>
+    <t>https://americana.jcblibrary.org/search/?query=B554+.H557m</t>
+  </si>
+  <si>
+    <t>B554 .H557m</t>
+  </si>
+  <si>
+    <t>EFG</t>
+  </si>
+  <si>
+    <t>HSMS-0596</t>
+  </si>
+  <si>
+    <t>1554-09-22 a quo</t>
   </si>
 </sst>
 </file>
@@ -12182,13 +12197,27 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -12499,9 +12528,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -12515,7 +12544,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -12524,26 +12553,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -12552,86 +12581,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12640,27 +12675,27 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -12679,10 +12714,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -12694,16 +12732,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12821,6 +12856,9 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -13031,9 +13069,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -13116,8 +13151,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T596" totalsRowShown="0">
-  <autoFilter ref="A1:T596" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T597" totalsRowShown="0">
+  <autoFilter ref="A1:T597" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13133,7 +13168,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13148,27 +13183,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:R62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13367,7 +13402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T596"/>
+  <dimension ref="A1:T598"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -42256,8 +42291,60 @@
         <v>3571</v>
       </c>
     </row>
+    <row r="597" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="12" t="s">
+        <v>4048</v>
+      </c>
+      <c r="B597" s="80" t="s">
+        <v>4047</v>
+      </c>
+      <c r="E597" s="80" t="s">
+        <v>3289</v>
+      </c>
+      <c r="F597" s="45" t="s">
+        <v>4046</v>
+      </c>
+      <c r="G597" s="81" t="s">
+        <v>4049</v>
+      </c>
+      <c r="H597" s="81" t="s">
+        <v>4049</v>
+      </c>
+      <c r="I597" s="81" t="s">
+        <v>45</v>
+      </c>
+      <c r="J597" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="K597" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="L597" s="45">
+        <v>4</v>
+      </c>
+      <c r="M597" s="81" t="s">
+        <v>4047</v>
+      </c>
+      <c r="N597" s="45"/>
+      <c r="O597" s="19" t="s">
+        <v>4045</v>
+      </c>
+      <c r="P597" s="45"/>
+      <c r="Q597" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R597" s="45"/>
+      <c r="T597" s="25" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="598" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="45"/>
+      <c r="C598" s="45"/>
+      <c r="D598" s="45"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="31" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -42961,11 +43048,12 @@
     <hyperlink ref="O593" r:id="rId700" xr:uid="{F3277743-3EA6-431A-9337-474B33DEDDC4}"/>
     <hyperlink ref="O594" r:id="rId701" xr:uid="{B9D8FABB-89C6-4AB6-8550-7176B66C9ABE}"/>
     <hyperlink ref="O595" r:id="rId702" xr:uid="{9CAC67F9-460B-4B63-9E09-F80DBADE8E8E}"/>
+    <hyperlink ref="O597" r:id="rId703" xr:uid="{E48D0676-4901-43E0-9DFF-5BB11C0848C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId703"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId704"/>
   <tableParts count="1">
-    <tablePart r:id="rId704"/>
+    <tablePart r:id="rId705"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45696,7 +45784,7 @@
       <c r="R62" s="45"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="31" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
@@ -45985,7 +46073,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="31" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F37DD7-EC28-4619-BB5C-BC9F24C2CFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D48B5B2-CCD4-46EB-B23F-78963EE10E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15555" yWindow="2190" windowWidth="21045" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26550" yWindow="2745" windowWidth="21045" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8449" uniqueCount="4050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8463" uniqueCount="4055">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -12175,9 +12175,6 @@
     <t>S77</t>
   </si>
   <si>
-    <t>https://americana.jcblibrary.org/search/?query=B554+.H557m</t>
-  </si>
-  <si>
     <t>B554 .H557m</t>
   </si>
   <si>
@@ -12188,6 +12185,24 @@
   </si>
   <si>
     <t>1554-09-22 a quo</t>
+  </si>
+  <si>
+    <t>VPM</t>
+  </si>
+  <si>
+    <t>https://americana.jcblibrary.org/search/object/jcbcap-991008745489706966-obranueuamenteco00flor/</t>
+  </si>
+  <si>
+    <t>1-SIZE B571 .F634o</t>
+  </si>
+  <si>
+    <t>Hernando Díaz</t>
+  </si>
+  <si>
+    <t>HSMS-0597</t>
+  </si>
+  <si>
+    <t>https://americana.jcblibrary.org/search/object/jcbcap-991004401109706966-lamuylamentabled00hern/</t>
   </si>
 </sst>
 </file>
@@ -12197,13 +12212,34 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -12528,9 +12564,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -12544,7 +12580,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -12553,77 +12589,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -12633,63 +12611,130 @@
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -12705,7 +12750,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12714,25 +12759,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12750,7 +12795,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -12856,9 +12901,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -13069,6 +13111,9 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -13151,8 +13196,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T597" totalsRowShown="0">
-  <autoFilter ref="A1:T597" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T598" totalsRowShown="0">
+  <autoFilter ref="A1:T598" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13168,7 +13213,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13183,27 +13228,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R62" totalsRowShown="0" dataDxfId="26">
-  <autoFilter ref="A1:R62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R63" totalsRowShown="0" dataDxfId="25">
+  <autoFilter ref="A1:R63" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -42293,22 +42338,22 @@
     </row>
     <row r="597" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="12" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="B597" s="80" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="E597" s="80" t="s">
         <v>3289</v>
       </c>
       <c r="F597" s="45" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="G597" s="81" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="H597" s="81" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="I597" s="81" t="s">
         <v>45</v>
@@ -42323,13 +42368,15 @@
         <v>4</v>
       </c>
       <c r="M597" s="81" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="N597" s="45"/>
       <c r="O597" s="19" t="s">
-        <v>4045</v>
-      </c>
-      <c r="P597" s="45"/>
+        <v>4054</v>
+      </c>
+      <c r="P597" s="83" t="s">
+        <v>3490</v>
+      </c>
       <c r="Q597" s="1" t="s">
         <v>123</v>
       </c>
@@ -42339,12 +42386,58 @@
       </c>
     </row>
     <row r="598" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="45"/>
-      <c r="C598" s="45"/>
-      <c r="D598" s="45"/>
+      <c r="A598" s="12" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B598" s="82" t="s">
+        <v>4049</v>
+      </c>
+      <c r="C598" s="82"/>
+      <c r="D598" s="82"/>
+      <c r="E598" s="82" t="s">
+        <v>3289</v>
+      </c>
+      <c r="F598" t="s">
+        <v>4051</v>
+      </c>
+      <c r="G598" s="82">
+        <v>1571</v>
+      </c>
+      <c r="H598" s="82">
+        <v>1571</v>
+      </c>
+      <c r="I598" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="J598" s="82" t="s">
+        <v>4052</v>
+      </c>
+      <c r="K598" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="L598" s="84" t="s">
+        <v>3644</v>
+      </c>
+      <c r="M598" s="82" t="s">
+        <v>4049</v>
+      </c>
+      <c r="N598" s="82"/>
+      <c r="O598" s="19" t="s">
+        <v>4050</v>
+      </c>
+      <c r="P598" s="83" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q598" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R598" s="82"/>
+      <c r="T598" s="25" t="s">
+        <v>3571</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -43049,18 +43142,19 @@
     <hyperlink ref="O594" r:id="rId701" xr:uid="{B9D8FABB-89C6-4AB6-8550-7176B66C9ABE}"/>
     <hyperlink ref="O595" r:id="rId702" xr:uid="{9CAC67F9-460B-4B63-9E09-F80DBADE8E8E}"/>
     <hyperlink ref="O597" r:id="rId703" xr:uid="{E48D0676-4901-43E0-9DFF-5BB11C0848C1}"/>
+    <hyperlink ref="O598" r:id="rId704" xr:uid="{DB6E7717-0A77-4E3E-9C1A-57C675C32B2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId704"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId705"/>
   <tableParts count="1">
-    <tablePart r:id="rId705"/>
+    <tablePart r:id="rId706"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -45783,8 +45877,11 @@
       <c r="Q62" s="45"/>
       <c r="R62" s="45"/>
     </row>
+    <row r="63" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="82"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="N4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
@@ -46073,7 +46170,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CC0E01-C2A2-442F-A774-D9FD759C05C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103DC1C4-225C-4882-963A-31987D600EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="38700" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8499" uniqueCount="4072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8532" uniqueCount="4087">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -9991,9 +9991,6 @@
     <t>GE3</t>
   </si>
   <si>
-    <t>https://bibliotecavirtualmadrid.comunidad.madrid/bvmadrid_publicacion/es/consulta/registro.do?id=13691</t>
-  </si>
-  <si>
     <t>ACZ</t>
   </si>
   <si>
@@ -12254,6 +12251,54 @@
   </si>
   <si>
     <t>HSMS-0599</t>
+  </si>
+  <si>
+    <t>https://philobiblon.upf.edu/xtf/servlet/org.cdlib.xtf.dynaXML.DynaXML?source=/unified/Display/1062BETA.MsEd.xml&amp;style=MsEd.xsl</t>
+  </si>
+  <si>
+    <t>Évora: Bibliotec Pública de Évora</t>
+  </si>
+  <si>
+    <t>CXXV/2-3</t>
+  </si>
+  <si>
+    <t>HSMS-0600</t>
+  </si>
+  <si>
+    <t>HSMS-0601</t>
+  </si>
+  <si>
+    <t>MP66</t>
+  </si>
+  <si>
+    <t>MP68</t>
+  </si>
+  <si>
+    <t>B568 .C783d</t>
+  </si>
+  <si>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>Miguel Martínez</t>
+  </si>
+  <si>
+    <t>Pau Cortey</t>
+  </si>
+  <si>
+    <t>1566</t>
+  </si>
+  <si>
+    <t>https://americana.jcblibrary.org/search/object/jcbcap-991004409549706966-copiadevnacartav00unse/</t>
+  </si>
+  <si>
+    <t>https://nlpdl.nlp.gov.ph/elib1/3/879/home.htm</t>
+  </si>
+  <si>
+    <t>el facsímil digital es el de la edición facimilar de 1958</t>
+  </si>
+  <si>
+    <t>Desconocido</t>
   </si>
 </sst>
 </file>
@@ -12581,6 +12626,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12588,6 +12634,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12983,6 +13030,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -13191,9 +13241,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -13276,8 +13323,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T600" totalsRowShown="0">
-  <autoFilter ref="A1:T600" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T602" totalsRowShown="0">
+  <autoFilter ref="A1:T602" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T573">
     <sortCondition ref="A2:A573"/>
   </sortState>
@@ -13293,7 +13340,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Lugar específico de producción"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="productor específico"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="formato"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="número folios" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Abreviatura HSMS2"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PhiloBiblonlink"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="facsímildigital"/>
@@ -13308,27 +13355,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R64" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:R64" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:R64" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="HSMS ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Abreviatura HSMS" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="BETA manid" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="BETA copid" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Biblioteca" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Signatura" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="SPDT-inicio" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="SPDT-fin" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Lugar específico de producción" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="productor específico" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="formato" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="número folios" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Abreviaturas HSMS" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="PhiloBiblonlink" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="facsímildigital" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="transcriptor" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="notas" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="duplicado" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13527,7 +13574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T600"/>
+  <dimension ref="A1:T602"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13589,7 +13636,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -14719,7 +14766,7 @@
         <v>205</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="T24" t="s">
         <v>30</v>
@@ -15995,7 +16042,7 @@
       </c>
       <c r="O50" s="5"/>
       <c r="Q50" s="1" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="T50" t="s">
         <v>30</v>
@@ -16491,7 +16538,7 @@
         <v>451</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="T60" t="s">
         <v>30</v>
@@ -16644,13 +16691,13 @@
         <v>470</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>471</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="T63" t="s">
         <v>30</v>
@@ -17137,7 +17184,7 @@
         <v>530</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="T73" t="s">
         <v>30</v>
@@ -17772,7 +17819,7 @@
         <v>623</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>617</v>
@@ -22564,7 +22611,7 @@
         <v>1284</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="T182" t="s">
         <v>30</v>
@@ -22900,7 +22947,7 @@
       </c>
       <c r="O189" s="5"/>
       <c r="Q189" s="1" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="T189" t="s">
         <v>30</v>
@@ -23291,7 +23338,7 @@
         <v>1384</v>
       </c>
       <c r="O197" s="5" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="Q197" s="1" t="s">
         <v>579</v>
@@ -23341,7 +23388,7 @@
         <v>1389</v>
       </c>
       <c r="O198" s="10" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="Q198" s="1" t="s">
         <v>1390</v>
@@ -23391,7 +23438,7 @@
         <v>1396</v>
       </c>
       <c r="O199" s="5" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="Q199" s="1" t="s">
         <v>1397</v>
@@ -23444,7 +23491,7 @@
         <v>1403</v>
       </c>
       <c r="O200" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="Q200" s="1" t="s">
         <v>1404</v>
@@ -23589,7 +23636,7 @@
         <v>1425</v>
       </c>
       <c r="Q203" s="1" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="T203" t="s">
         <v>30</v>
@@ -23633,7 +23680,7 @@
         <v>1430</v>
       </c>
       <c r="Q204" s="1" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>1431</v>
@@ -23774,7 +23821,7 @@
         <v>1443</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="T207" t="s">
         <v>30</v>
@@ -23973,7 +24020,7 @@
         <v>1469</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="T211" t="s">
         <v>30</v>
@@ -24468,7 +24515,7 @@
         <v>69</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>130</v>
@@ -24639,7 +24686,7 @@
         <v>1552</v>
       </c>
       <c r="P224" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q224" s="1" t="s">
         <v>1553</v>
@@ -24837,7 +24884,7 @@
         <v>1583</v>
       </c>
       <c r="O228" s="9" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="Q228" s="1" t="s">
         <v>123</v>
@@ -24887,7 +24934,7 @@
         <v>2107</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Q229" s="1" t="s">
         <v>544</v>
@@ -25035,7 +25082,7 @@
         <v>1608</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="T232" t="s">
         <v>30</v>
@@ -26187,7 +26234,7 @@
         <v>1751</v>
       </c>
       <c r="Q256" s="1" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="R256" s="1" t="s">
         <v>1752</v>
@@ -26680,7 +26727,7 @@
         <v>1804</v>
       </c>
       <c r="O266" s="5" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="Q266" s="1" t="s">
         <v>579</v>
@@ -26727,7 +26774,7 @@
         <v>1807</v>
       </c>
       <c r="O267" s="5" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="Q267" s="1" t="s">
         <v>579</v>
@@ -26774,7 +26821,7 @@
         <v>1810</v>
       </c>
       <c r="O268" s="5" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="Q268" s="1" t="s">
         <v>579</v>
@@ -26823,7 +26870,7 @@
         <v>1816</v>
       </c>
       <c r="O269" s="5" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="Q269" s="1" t="s">
         <v>557</v>
@@ -26870,7 +26917,7 @@
         <v>1820</v>
       </c>
       <c r="O270" s="5" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="Q270" s="1" t="s">
         <v>557</v>
@@ -26965,7 +27012,7 @@
         <v>1830</v>
       </c>
       <c r="O272" s="5" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="Q272" s="1" t="s">
         <v>544</v>
@@ -27015,7 +27062,7 @@
         <v>1835</v>
       </c>
       <c r="O273" s="5" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="Q273" s="1" t="s">
         <v>557</v>
@@ -27110,7 +27157,7 @@
         <v>1846</v>
       </c>
       <c r="O275" s="5" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="Q275" s="1" t="s">
         <v>557</v>
@@ -27157,7 +27204,7 @@
         <v>1850</v>
       </c>
       <c r="O276" s="5" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="Q276" s="1" t="s">
         <v>73</v>
@@ -27255,7 +27302,7 @@
         <v>1862</v>
       </c>
       <c r="O278" s="5" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="Q278" s="1" t="s">
         <v>557</v>
@@ -27305,7 +27352,7 @@
         <v>1867</v>
       </c>
       <c r="O279" s="5" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="Q279" s="1" t="s">
         <v>557</v>
@@ -27352,7 +27399,7 @@
         <v>1872</v>
       </c>
       <c r="O280" s="5" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="Q280" s="1" t="s">
         <v>579</v>
@@ -27546,7 +27593,7 @@
         <v>1894</v>
       </c>
       <c r="O284" s="5" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="Q284" s="1" t="s">
         <v>579</v>
@@ -27690,7 +27737,7 @@
         <v>1913</v>
       </c>
       <c r="O287" s="5" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="Q287" s="1" t="s">
         <v>29</v>
@@ -27737,7 +27784,7 @@
         <v>1917</v>
       </c>
       <c r="O288" s="5" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="Q288" s="1" t="s">
         <v>1918</v>
@@ -27787,7 +27834,7 @@
         <v>1923</v>
       </c>
       <c r="O289" s="5" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="Q289" s="1" t="s">
         <v>544</v>
@@ -27882,7 +27929,7 @@
         <v>1935</v>
       </c>
       <c r="O291" s="5" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="Q291" s="1" t="s">
         <v>289</v>
@@ -27934,7 +27981,7 @@
         <v>1941</v>
       </c>
       <c r="O292" s="5" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="Q292" s="1" t="s">
         <v>1942</v>
@@ -27984,7 +28031,7 @@
         <v>1949</v>
       </c>
       <c r="O293" s="5" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="Q293" s="1" t="s">
         <v>29</v>
@@ -28031,10 +28078,10 @@
         <v>1953</v>
       </c>
       <c r="O294" s="5" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="Q294" s="1" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="R294" s="1" t="s">
         <v>769</v>
@@ -28126,7 +28173,7 @@
         <v>1961</v>
       </c>
       <c r="O296" s="5" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="Q296" s="1" t="s">
         <v>1681</v>
@@ -28314,7 +28361,7 @@
         <v>1982</v>
       </c>
       <c r="O300" s="5" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="Q300" s="1" t="s">
         <v>990</v>
@@ -28367,13 +28414,13 @@
         <v>1989</v>
       </c>
       <c r="O301" s="9" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="Q301" s="1" t="s">
         <v>1404</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="T301" t="s">
         <v>30</v>
@@ -28462,7 +28509,7 @@
         <v>1999</v>
       </c>
       <c r="O303" s="5" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="Q303" s="1" t="s">
         <v>29</v>
@@ -28509,7 +28556,7 @@
         <v>2004</v>
       </c>
       <c r="O304" s="5" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="Q304" s="1" t="s">
         <v>2005</v>
@@ -28604,7 +28651,7 @@
         <v>2015</v>
       </c>
       <c r="O306" s="5" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="Q306" s="1" t="s">
         <v>2016</v>
@@ -28699,7 +28746,7 @@
         <v>2027</v>
       </c>
       <c r="O308" s="5" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="Q308" s="1" t="s">
         <v>2028</v>
@@ -28746,7 +28793,7 @@
         <v>2032</v>
       </c>
       <c r="O309" s="5" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="Q309" s="1" t="s">
         <v>777</v>
@@ -28799,13 +28846,13 @@
         <v>2037</v>
       </c>
       <c r="O310" s="9" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="Q310" s="1" t="s">
         <v>123</v>
       </c>
       <c r="R310" s="1" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="T310" t="s">
         <v>30</v>
@@ -28849,7 +28896,7 @@
         <v>2042</v>
       </c>
       <c r="O311" s="5" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="Q311" s="1" t="s">
         <v>2043</v>
@@ -28899,7 +28946,7 @@
         <v>2048</v>
       </c>
       <c r="O312" s="5" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="Q312" s="1" t="s">
         <v>132</v>
@@ -28994,7 +29041,7 @@
         <v>2059</v>
       </c>
       <c r="O314" s="5" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="Q314" s="1" t="s">
         <v>1122</v>
@@ -29041,7 +29088,7 @@
         <v>2063</v>
       </c>
       <c r="O315" s="5" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="Q315" s="1" t="s">
         <v>29</v>
@@ -29334,7 +29381,7 @@
         <v>2095</v>
       </c>
       <c r="O321" s="5" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="Q321" s="1" t="s">
         <v>2096</v>
@@ -29372,7 +29419,7 @@
         <v>26</v>
       </c>
       <c r="L322" s="2" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="M322" s="2" t="s">
         <v>2098</v>
@@ -29381,7 +29428,7 @@
         <v>2100</v>
       </c>
       <c r="O322" s="5" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="Q322" s="1" t="s">
         <v>2101</v>
@@ -29865,7 +29912,7 @@
       </c>
       <c r="O332" s="5"/>
       <c r="Q332" s="1" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="R332" s="1" t="s">
         <v>2159</v>
@@ -30095,7 +30142,7 @@
         <v>2187</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>2188</v>
@@ -30119,10 +30166,10 @@
         <v>2186</v>
       </c>
       <c r="N337" s="9" t="s">
+        <v>4060</v>
+      </c>
+      <c r="O337" s="9" t="s">
         <v>4061</v>
-      </c>
-      <c r="O337" s="9" t="s">
-        <v>4062</v>
       </c>
       <c r="Q337" s="1" t="s">
         <v>464</v>
@@ -30154,13 +30201,13 @@
         <v>2194</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="I338" s="2" t="s">
         <v>197</v>
       </c>
       <c r="J338" s="2" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
       <c r="K338" s="2" t="s">
         <v>47</v>
@@ -30275,7 +30322,7 @@
         <v>2210</v>
       </c>
       <c r="O340" s="5" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="Q340" s="1" t="s">
         <v>295</v>
@@ -30376,7 +30423,7 @@
         <v>2225</v>
       </c>
       <c r="O342" s="5" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="Q342" s="1" t="s">
         <v>2226</v>
@@ -31023,7 +31070,7 @@
         <v>2309</v>
       </c>
       <c r="Q355" s="1" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="T355" t="s">
         <v>30</v>
@@ -31364,7 +31411,7 @@
         <v>2357</v>
       </c>
       <c r="O362" s="5" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="Q362" s="1" t="s">
         <v>2347</v>
@@ -32673,7 +32720,7 @@
         <v>2516</v>
       </c>
       <c r="Q390" s="1" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="T390" t="s">
         <v>30</v>
@@ -33301,7 +33348,7 @@
         <v>2579</v>
       </c>
       <c r="O405" s="5" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="Q405" s="1" t="s">
         <v>2347</v>
@@ -33595,7 +33642,7 @@
         <v>2617</v>
       </c>
       <c r="O411" s="5" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="Q411" s="1" t="s">
         <v>2340</v>
@@ -34070,7 +34117,7 @@
         <v>2673</v>
       </c>
       <c r="O422" s="5" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="Q422" s="1" t="s">
         <v>2637</v>
@@ -34335,7 +34382,7 @@
         <v>2701</v>
       </c>
       <c r="O428" s="19" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="Q428" s="1" t="s">
         <v>2637</v>
@@ -35356,7 +35403,7 @@
         <v>2833</v>
       </c>
       <c r="O449" s="5" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="Q449" s="1" t="s">
         <v>123</v>
@@ -35450,7 +35497,7 @@
         <v>2844</v>
       </c>
       <c r="O451" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="Q451" s="1" t="s">
         <v>2736</v>
@@ -36686,7 +36733,7 @@
         <v>2995</v>
       </c>
       <c r="Q477" s="1" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="T477" t="s">
         <v>1133</v>
@@ -37430,7 +37477,7 @@
         <v>3091</v>
       </c>
       <c r="O492" s="5" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="Q492" s="1" t="s">
         <v>289</v>
@@ -37481,7 +37528,7 @@
         <v>3096</v>
       </c>
       <c r="O493" s="5" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="Q493" s="1" t="s">
         <v>123</v>
@@ -37686,7 +37733,7 @@
         <v>3120</v>
       </c>
       <c r="O497" s="5" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="Q497" s="1" t="s">
         <v>289</v>
@@ -38093,7 +38140,7 @@
         <v>3171</v>
       </c>
       <c r="O505" s="5" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="P505" s="1"/>
       <c r="Q505" s="1" t="s">
@@ -38891,10 +38938,10 @@
     </row>
     <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
@@ -38902,7 +38949,7 @@
         <v>2934</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="G523" s="1">
         <v>1593</v>
@@ -38911,10 +38958,10 @@
         <v>1593</v>
       </c>
       <c r="I523" s="1" t="s">
+        <v>3482</v>
+      </c>
+      <c r="J523" s="1" t="s">
         <v>3483</v>
-      </c>
-      <c r="J523" s="1" t="s">
-        <v>3484</v>
       </c>
       <c r="K523" s="1" t="s">
         <v>61</v>
@@ -38923,13 +38970,13 @@
         <v>38</v>
       </c>
       <c r="M523" s="1" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="O523" s="19" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="P523" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q523" s="1" t="s">
         <v>123</v>
@@ -38940,22 +38987,22 @@
     </row>
     <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B524" s="2" t="s">
         <v>3499</v>
-      </c>
-      <c r="B524" s="2" t="s">
-        <v>3500</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F524" s="2" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="I524" s="2" t="s">
         <v>316</v>
@@ -38970,10 +39017,10 @@
         <v>2</v>
       </c>
       <c r="M524" s="2" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="O524" s="19" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="Q524" s="1" t="s">
         <v>289</v>
@@ -38984,27 +39031,27 @@
     </row>
     <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1" t="s">
+        <v>3495</v>
+      </c>
+      <c r="F525" s="1" t="s">
         <v>3496</v>
       </c>
-      <c r="F525" s="1" t="s">
+      <c r="G525" s="1" t="s">
+        <v>3504</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>3504</v>
+      </c>
+      <c r="I525" s="1" t="s">
         <v>3497</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>3505</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>3505</v>
-      </c>
-      <c r="I525" s="1" t="s">
-        <v>3498</v>
       </c>
       <c r="J525" s="1"/>
       <c r="K525" s="1" t="s">
@@ -39014,7 +39061,7 @@
         <v>13</v>
       </c>
       <c r="M525" s="1" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="Q525" s="1" t="s">
         <v>123</v>
@@ -39025,19 +39072,19 @@
     </row>
     <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B526" s="2" t="s">
         <v>3506</v>
-      </c>
-      <c r="B526" s="2" t="s">
-        <v>3507</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="H526" s="2" t="s">
         <v>2629</v>
@@ -39055,10 +39102,10 @@
         <v>8</v>
       </c>
       <c r="M526" s="2" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="O526" s="19" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="Q526" s="1" t="s">
         <v>289</v>
@@ -39069,28 +39116,28 @@
     </row>
     <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="I527" s="2" t="s">
         <v>45</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="K527" s="2" t="s">
         <v>61</v>
@@ -39099,13 +39146,13 @@
         <v>54</v>
       </c>
       <c r="M527" s="2" t="s">
+        <v>3492</v>
+      </c>
+      <c r="O527" s="19" t="s">
         <v>3493</v>
       </c>
-      <c r="O527" s="19" t="s">
-        <v>3494</v>
-      </c>
       <c r="P527" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q527" s="1" t="s">
         <v>289</v>
@@ -39116,10 +39163,10 @@
     </row>
     <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="C528" s="1">
         <v>2041</v>
@@ -39129,7 +39176,7 @@
         <v>433</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="G528" s="1">
         <v>1493</v>
@@ -39150,13 +39197,13 @@
         <v>100</v>
       </c>
       <c r="M528" s="1" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="N528" s="9" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="O528" s="5" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="P528" s="1"/>
       <c r="Q528" s="1" t="s">
@@ -39168,22 +39215,22 @@
     </row>
     <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="G529" s="2" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="I529" s="2" t="s">
         <v>2380</v>
@@ -39198,10 +39245,10 @@
         <v>4</v>
       </c>
       <c r="M529" s="2" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="O529" s="19" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="Q529" s="1" t="s">
         <v>289</v>
@@ -39212,22 +39259,22 @@
     </row>
     <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F530" s="2" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="I530" s="2" t="s">
         <v>2380</v>
@@ -39242,10 +39289,10 @@
         <v>4</v>
       </c>
       <c r="M530" s="2" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="O530" s="19" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="Q530" s="1" t="s">
         <v>289</v>
@@ -39256,10 +39303,10 @@
     </row>
     <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="C531" s="1">
         <v>1141</v>
@@ -39269,7 +39316,7 @@
         <v>2156</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="G531" s="1">
         <v>1301</v>
@@ -39286,16 +39333,16 @@
         <v>65</v>
       </c>
       <c r="M531" s="1" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="N531" s="9" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="Q531" s="1" t="s">
         <v>2845</v>
       </c>
       <c r="R531" s="1" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="T531" t="s">
         <v>1133</v>
@@ -39303,10 +39350,10 @@
     </row>
     <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="C532" s="1">
         <v>1106</v>
@@ -39316,17 +39363,17 @@
         <v>2156</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="I532" s="1"/>
       <c r="J532" s="1" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="K532" s="1" t="s">
         <v>26</v>
@@ -39335,16 +39382,16 @@
         <v>152</v>
       </c>
       <c r="M532" s="1" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="N532" s="9" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="Q532" s="1" t="s">
         <v>2845</v>
       </c>
       <c r="R532" s="1" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="T532" t="s">
         <v>1133</v>
@@ -39352,10 +39399,10 @@
     </row>
     <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="C533" s="3">
         <v>1504</v>
@@ -39373,10 +39420,10 @@
         <v>3308</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="K533" s="2" t="s">
         <v>26</v>
@@ -39385,13 +39432,13 @@
         <v>154</v>
       </c>
       <c r="M533" s="2" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="N533" s="9" t="s">
         <v>3309</v>
       </c>
       <c r="O533" s="19" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="Q533" s="1" t="s">
         <v>2845</v>
@@ -39402,24 +39449,24 @@
     </row>
     <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="B534" s="22" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="C534" s="22"/>
       <c r="D534" s="22"/>
       <c r="E534" s="22" t="s">
+        <v>3403</v>
+      </c>
+      <c r="F534" s="22" t="s">
         <v>3404</v>
       </c>
-      <c r="F534" s="22" t="s">
+      <c r="G534" s="12" t="s">
         <v>3405</v>
       </c>
-      <c r="G534" s="12" t="s">
-        <v>3406</v>
-      </c>
       <c r="H534" s="12" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="I534" s="22" t="s">
         <v>45</v>
@@ -39434,43 +39481,43 @@
         <v>28</v>
       </c>
       <c r="M534" s="22" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="N534" s="22"/>
       <c r="O534" s="10" t="s">
+        <v>3406</v>
+      </c>
+      <c r="P534" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q534" s="18" t="s">
         <v>3407</v>
-      </c>
-      <c r="P534" t="s">
-        <v>3487</v>
-      </c>
-      <c r="Q534" s="18" t="s">
-        <v>3408</v>
       </c>
       <c r="R534" s="17"/>
       <c r="T534" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="535" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="B535" s="22" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="C535" s="22"/>
       <c r="D535" s="22"/>
       <c r="E535" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F535" s="22" t="s">
+        <v>3409</v>
+      </c>
+      <c r="G535" s="12" t="s">
         <v>3410</v>
       </c>
-      <c r="G535" s="12" t="s">
-        <v>3411</v>
-      </c>
       <c r="H535" s="12" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="I535" s="22" t="s">
         <v>45</v>
@@ -39482,68 +39529,68 @@
         <v>61</v>
       </c>
       <c r="L535" s="23" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="M535" s="22" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="N535" s="22"/>
       <c r="O535" s="9" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="P535" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q535" s="22" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="R535" s="22"/>
       <c r="T535" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="536" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="B536" s="22" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="C536" s="22"/>
       <c r="D536" s="22"/>
       <c r="E536" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F536" s="22" t="s">
+        <v>3413</v>
+      </c>
+      <c r="G536" s="12" t="s">
         <v>3414</v>
       </c>
-      <c r="G536" s="12" t="s">
-        <v>3415</v>
-      </c>
       <c r="H536" s="12" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="I536" s="22" t="s">
         <v>138</v>
       </c>
       <c r="J536" s="22" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="K536" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L536" s="23" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="M536" s="22" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="N536" s="22"/>
       <c r="O536" s="9" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="P536" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q536" s="22" t="s">
         <v>366</v>
@@ -39551,23 +39598,23 @@
       <c r="R536" s="22"/>
       <c r="S536" s="12"/>
       <c r="T536" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="537" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="B537" s="22" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="C537" s="22"/>
       <c r="D537" s="22"/>
       <c r="E537" s="22" t="s">
+        <v>3417</v>
+      </c>
+      <c r="F537" s="22" t="s">
         <v>3418</v>
-      </c>
-      <c r="F537" s="22" t="s">
-        <v>3419</v>
       </c>
       <c r="G537" s="12">
         <v>1544</v>
@@ -39585,81 +39632,81 @@
         <v>26</v>
       </c>
       <c r="L537" s="23" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="M537" s="22" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="N537" s="22"/>
       <c r="O537" s="22"/>
       <c r="P537" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q537" s="22" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="R537" s="22"/>
       <c r="T537" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="538" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="B538" s="22" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="C538" s="22"/>
       <c r="D538" s="22"/>
       <c r="E538" s="22" t="s">
+        <v>3421</v>
+      </c>
+      <c r="F538" s="22" t="s">
         <v>3422</v>
       </c>
-      <c r="F538" s="22" t="s">
+      <c r="G538" s="12" t="s">
         <v>3423</v>
       </c>
-      <c r="G538" s="12" t="s">
-        <v>3424</v>
-      </c>
       <c r="H538" s="12" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="I538" s="22" t="s">
         <v>45</v>
       </c>
       <c r="J538" s="22" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="K538" s="22" t="s">
         <v>26</v>
       </c>
       <c r="L538" s="23" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="M538" s="22" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="N538" s="22"/>
       <c r="O538" s="9" t="s">
+        <v>3424</v>
+      </c>
+      <c r="P538" s="25" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q538" s="22" t="s">
         <v>3425</v>
-      </c>
-      <c r="P538" s="25" t="s">
-        <v>3487</v>
-      </c>
-      <c r="Q538" s="22" t="s">
-        <v>3426</v>
       </c>
       <c r="R538" s="22"/>
       <c r="T538" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="539" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="B539" s="22" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="C539" s="22"/>
       <c r="D539" s="22"/>
@@ -39667,47 +39714,47 @@
         <v>2201</v>
       </c>
       <c r="F539" s="22" t="s">
+        <v>3427</v>
+      </c>
+      <c r="G539" s="12" t="s">
+        <v>3655</v>
+      </c>
+      <c r="H539" s="12" t="s">
         <v>3428</v>
-      </c>
-      <c r="G539" s="12" t="s">
-        <v>3656</v>
-      </c>
-      <c r="H539" s="12" t="s">
-        <v>3429</v>
       </c>
       <c r="I539" s="22" t="s">
         <v>45</v>
       </c>
       <c r="J539" s="22" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="K539" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L539" s="23" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="M539" s="22" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="N539" s="22"/>
       <c r="O539" s="9" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="P539" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q539" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R539" s="22"/>
       <c r="T539" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="540" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="B540" s="22" t="s">
         <v>3285</v>
@@ -39715,7 +39762,7 @@
       <c r="C540" s="22"/>
       <c r="D540" s="22"/>
       <c r="E540" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F540" s="22" t="s">
         <v>3287</v>
@@ -39746,30 +39793,30 @@
         <v>3291</v>
       </c>
       <c r="P540" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q540" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R540" s="22"/>
       <c r="T540" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="541" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="B541" s="22" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="C541" s="22"/>
       <c r="D541" s="22"/>
       <c r="E541" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F541" s="22" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="G541" s="12">
         <v>1555</v>
@@ -39787,32 +39834,32 @@
         <v>61</v>
       </c>
       <c r="L541" s="23" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="M541" s="22" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="N541" s="22"/>
       <c r="O541" s="9" t="s">
+        <v>3432</v>
+      </c>
+      <c r="P541" s="25" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q541" s="22" t="s">
         <v>3433</v>
-      </c>
-      <c r="P541" s="25" t="s">
-        <v>3487</v>
-      </c>
-      <c r="Q541" s="22" t="s">
-        <v>3434</v>
       </c>
       <c r="R541" s="22"/>
       <c r="T541" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="542" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="B542" s="22" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="C542" s="22"/>
       <c r="D542" s="22"/>
@@ -39820,13 +39867,13 @@
         <v>433</v>
       </c>
       <c r="F542" s="12" t="s">
+        <v>3706</v>
+      </c>
+      <c r="G542" s="12" t="s">
         <v>3707</v>
       </c>
-      <c r="G542" s="12" t="s">
-        <v>3708</v>
-      </c>
       <c r="H542" s="12" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="I542" s="13" t="s">
         <v>230</v>
@@ -39838,14 +39885,14 @@
         <v>61</v>
       </c>
       <c r="L542" s="23" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="M542" s="22" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="N542" s="22"/>
       <c r="O542" s="9" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="P542" s="25"/>
       <c r="Q542" s="22" t="s">
@@ -39853,29 +39900,29 @@
       </c>
       <c r="R542" s="22"/>
       <c r="T542" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="543" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="B543" s="22" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="C543" s="22"/>
       <c r="D543" s="22"/>
       <c r="E543" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F543" s="22" t="s">
+        <v>3435</v>
+      </c>
+      <c r="G543" s="12" t="s">
         <v>3436</v>
       </c>
-      <c r="G543" s="12" t="s">
-        <v>3437</v>
-      </c>
       <c r="H543" s="12" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="I543" s="22" t="s">
         <v>138</v>
@@ -39887,49 +39934,49 @@
         <v>61</v>
       </c>
       <c r="L543" s="23" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="M543" s="22" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="N543" s="22"/>
       <c r="O543" s="9" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="P543" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q543" s="22" t="s">
         <v>2340</v>
       </c>
       <c r="R543" s="22"/>
       <c r="T543" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="544" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="B544" s="22" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="C544" s="22"/>
       <c r="D544" s="22"/>
       <c r="E544" s="22" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="F544" s="22" t="s">
+        <v>3438</v>
+      </c>
+      <c r="G544" s="12" t="s">
         <v>3439</v>
       </c>
-      <c r="G544" s="12" t="s">
+      <c r="H544" s="12" t="s">
+        <v>3439</v>
+      </c>
+      <c r="I544" s="22" t="s">
         <v>3440</v>
-      </c>
-      <c r="H544" s="12" t="s">
-        <v>3440</v>
-      </c>
-      <c r="I544" s="22" t="s">
-        <v>3441</v>
       </c>
       <c r="J544" s="22" t="s">
         <v>25</v>
@@ -39938,97 +39985,97 @@
         <v>26</v>
       </c>
       <c r="L544" s="23" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="M544" s="22" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="N544" s="22"/>
       <c r="O544" s="9" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="P544" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q544" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R544" s="22"/>
       <c r="T544" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="545" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="B545" s="22" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="C545" s="22"/>
       <c r="D545" s="22"/>
       <c r="E545" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F545" s="22" t="s">
+        <v>3443</v>
+      </c>
+      <c r="G545" s="12" t="s">
         <v>3444</v>
       </c>
-      <c r="G545" s="12" t="s">
-        <v>3445</v>
-      </c>
       <c r="H545" s="12" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I545" s="22" t="s">
         <v>1129</v>
       </c>
       <c r="J545" s="22" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="K545" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L545" s="23" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="M545" s="22" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="N545" s="22"/>
       <c r="O545" s="9" t="s">
+        <v>3445</v>
+      </c>
+      <c r="P545" s="25" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q545" s="22" t="s">
         <v>3446</v>
-      </c>
-      <c r="P545" s="25" t="s">
-        <v>3487</v>
-      </c>
-      <c r="Q545" s="22" t="s">
-        <v>3447</v>
       </c>
       <c r="R545" s="22"/>
       <c r="T545" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="546" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="B546" s="22" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="C546" s="22"/>
       <c r="D546" s="22"/>
       <c r="E546" s="22" t="s">
+        <v>3448</v>
+      </c>
+      <c r="F546" s="22" t="s">
         <v>3449</v>
       </c>
-      <c r="F546" s="22" t="s">
+      <c r="G546" s="12" t="s">
         <v>3450</v>
       </c>
-      <c r="G546" s="12" t="s">
-        <v>3451</v>
-      </c>
       <c r="H546" s="12" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="I546" s="22"/>
       <c r="J546" s="22" t="s">
@@ -40038,46 +40085,46 @@
         <v>26</v>
       </c>
       <c r="L546" s="23" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="M546" s="22" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="N546" s="22"/>
       <c r="O546" s="9" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="P546" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q546" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R546" s="22"/>
       <c r="T546" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="547" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="B547" s="22" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="C547" s="22"/>
       <c r="D547" s="22"/>
       <c r="E547" s="22" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="F547" s="22" t="s">
+        <v>3453</v>
+      </c>
+      <c r="G547" s="12" t="s">
+        <v>3618</v>
+      </c>
+      <c r="H547" s="12" t="s">
         <v>3454</v>
-      </c>
-      <c r="G547" s="12" t="s">
-        <v>3619</v>
-      </c>
-      <c r="H547" s="12" t="s">
-        <v>3455</v>
       </c>
       <c r="I547" s="22"/>
       <c r="J547" s="22" t="s">
@@ -40087,32 +40134,32 @@
         <v>26</v>
       </c>
       <c r="L547" s="23" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="M547" s="22" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="N547" s="22"/>
       <c r="O547" s="9" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="P547" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q547" s="22" t="s">
         <v>536</v>
       </c>
       <c r="R547" s="22"/>
       <c r="T547" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="548" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="B548" s="22" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="C548" s="22"/>
       <c r="D548" s="22"/>
@@ -40120,10 +40167,10 @@
         <v>1126</v>
       </c>
       <c r="F548" s="22" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="G548" s="12" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="H548" s="12">
         <v>1541</v>
@@ -40138,87 +40185,87 @@
         <v>61</v>
       </c>
       <c r="L548" s="23" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M548" s="22" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="N548" s="22"/>
       <c r="O548" s="9" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="P548" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q548" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R548" s="22"/>
       <c r="T548" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="549" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B549" s="22" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="C549" s="22"/>
       <c r="D549" s="22"/>
       <c r="E549" s="22" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="F549" s="22" t="s">
+        <v>3460</v>
+      </c>
+      <c r="G549" s="12" t="s">
+        <v>3619</v>
+      </c>
+      <c r="H549" s="12" t="s">
+        <v>3619</v>
+      </c>
+      <c r="I549" s="22" t="s">
         <v>3461</v>
-      </c>
-      <c r="G549" s="12" t="s">
-        <v>3620</v>
-      </c>
-      <c r="H549" s="12" t="s">
-        <v>3620</v>
-      </c>
-      <c r="I549" s="22" t="s">
-        <v>3462</v>
       </c>
       <c r="J549" s="22"/>
       <c r="K549" s="22" t="s">
         <v>26</v>
       </c>
       <c r="L549" s="23" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="M549" s="22" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="N549" s="22"/>
       <c r="O549" s="22"/>
       <c r="P549" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q549" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R549" s="22"/>
       <c r="T549" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="550" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="B550" s="22" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="C550" s="22"/>
       <c r="D550" s="22"/>
       <c r="E550" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F550" s="22" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G550" s="12">
         <v>1552</v>
@@ -40230,52 +40277,52 @@
         <v>45</v>
       </c>
       <c r="J550" s="22" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="K550" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L550" s="23" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="M550" s="22" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="N550" s="22"/>
       <c r="O550" s="9" t="s">
+        <v>3464</v>
+      </c>
+      <c r="P550" s="25" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q550" s="22" t="s">
         <v>3465</v>
-      </c>
-      <c r="P550" s="25" t="s">
-        <v>3487</v>
-      </c>
-      <c r="Q550" s="22" t="s">
-        <v>3466</v>
       </c>
       <c r="R550" s="22"/>
       <c r="T550" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="551" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="B551" s="22" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="C551" s="22"/>
       <c r="D551" s="22"/>
       <c r="E551" s="22" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F551" s="22" t="s">
+        <v>3467</v>
+      </c>
+      <c r="G551" s="12" t="s">
         <v>3468</v>
       </c>
-      <c r="G551" s="12" t="s">
-        <v>3469</v>
-      </c>
       <c r="H551" s="12" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="I551" s="22"/>
       <c r="J551" s="22" t="s">
@@ -40285,40 +40332,40 @@
         <v>26</v>
       </c>
       <c r="L551" s="23" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="M551" s="22" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="N551" s="22"/>
       <c r="O551" s="9" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="P551" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q551" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R551" s="22"/>
       <c r="T551" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="552" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="B552" s="22" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="C552" s="22"/>
       <c r="D552" s="22"/>
       <c r="E552" s="22" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="F552" s="22" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="G552" s="12">
         <v>1534</v>
@@ -40330,43 +40377,43 @@
         <v>45</v>
       </c>
       <c r="J552" s="22" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="K552" s="22" t="s">
         <v>61</v>
       </c>
       <c r="L552" s="23" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="M552" s="22" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="N552" s="22"/>
       <c r="O552" s="9" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="P552" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q552" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R552" s="22"/>
       <c r="T552" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="553" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B553" s="22" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="C553" s="22"/>
       <c r="D553" s="22"/>
       <c r="E553" s="22" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="F553" s="22"/>
       <c r="G553" s="12">
@@ -40376,7 +40423,7 @@
         <v>1544</v>
       </c>
       <c r="I553" s="22" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="J553" s="22" t="s">
         <v>95</v>
@@ -40385,32 +40432,32 @@
         <v>61</v>
       </c>
       <c r="L553" s="23" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="M553" s="22" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="N553" s="22"/>
       <c r="O553" s="9" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="P553" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q553" s="22" t="s">
         <v>123</v>
       </c>
       <c r="R553" s="22"/>
       <c r="T553" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="554" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="B554" s="22" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="C554" s="22"/>
       <c r="D554" s="22"/>
@@ -40418,13 +40465,13 @@
         <v>2213</v>
       </c>
       <c r="F554" s="22" t="s">
+        <v>3570</v>
+      </c>
+      <c r="G554" s="12" t="s">
         <v>3571</v>
       </c>
-      <c r="G554" s="12" t="s">
-        <v>3572</v>
-      </c>
       <c r="H554" s="12" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="I554" s="22"/>
       <c r="J554" s="22"/>
@@ -40435,29 +40482,29 @@
         <v>58</v>
       </c>
       <c r="M554" s="22" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="N554" s="22"/>
       <c r="O554" s="19" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="P554" s="25" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q554" s="22" t="s">
         <v>366</v>
       </c>
       <c r="R554" s="22"/>
       <c r="T554" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="555" spans="1:20" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="C555" s="1">
         <v>2393</v>
@@ -40467,13 +40514,13 @@
         <v>433</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>230</v>
@@ -40488,13 +40535,13 @@
         <v>78</v>
       </c>
       <c r="M555" s="1" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="N555" s="9" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="O555" s="19" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="P555"/>
       <c r="Q555" s="1" t="s">
@@ -40503,15 +40550,15 @@
       <c r="R555" s="1"/>
       <c r="S555" s="1"/>
       <c r="T555" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="C556" s="3">
         <v>1754</v>
@@ -40520,13 +40567,13 @@
         <v>1618</v>
       </c>
       <c r="F556" s="2" t="s">
+        <v>3630</v>
+      </c>
+      <c r="G556" s="2" t="s">
         <v>3631</v>
       </c>
-      <c r="G556" s="2" t="s">
-        <v>3632</v>
-      </c>
       <c r="H556" s="2" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="I556" s="2" t="s">
         <v>2380</v>
@@ -40538,30 +40585,30 @@
         <v>47</v>
       </c>
       <c r="L556" s="2" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="M556" s="2" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="N556" s="9" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="O556" s="19" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="Q556" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T556" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="C557" s="3">
         <v>1749</v>
@@ -40570,13 +40617,13 @@
         <v>433</v>
       </c>
       <c r="F557" s="2" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="G557" s="2" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="I557" s="2" t="s">
         <v>230</v>
@@ -40588,30 +40635,30 @@
         <v>47</v>
       </c>
       <c r="L557" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M557" s="2" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="N557" s="9" t="s">
+        <v>3643</v>
+      </c>
+      <c r="O557" s="19" t="s">
         <v>3644</v>
-      </c>
-      <c r="O557" s="19" t="s">
-        <v>3645</v>
       </c>
       <c r="Q557" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T557" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="C558" s="3">
         <v>4179</v>
@@ -40620,7 +40667,7 @@
         <v>1618</v>
       </c>
       <c r="F558" s="2" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="G558" s="2" t="s">
         <v>3114</v>
@@ -40638,40 +40685,40 @@
         <v>47</v>
       </c>
       <c r="L558" s="2" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="M558" s="2" t="s">
+        <v>3636</v>
+      </c>
+      <c r="N558" s="9" t="s">
+        <v>3642</v>
+      </c>
+      <c r="O558" s="19" t="s">
         <v>3637</v>
-      </c>
-      <c r="N558" s="9" t="s">
-        <v>3643</v>
-      </c>
-      <c r="O558" s="19" t="s">
-        <v>3638</v>
       </c>
       <c r="Q558" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T558" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="559" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="B559" s="13" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="C559" s="14">
         <v>2042</v>
       </c>
       <c r="D559" s="15"/>
       <c r="E559" s="13" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="F559" s="13" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="G559" s="13" t="s">
         <v>3060</v>
@@ -40689,38 +40736,38 @@
         <v>130</v>
       </c>
       <c r="L559" s="13" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="M559" s="13" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="N559" s="19" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="O559" s="19" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="P559" s="25"/>
       <c r="Q559" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T559" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="560" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="B560" s="12" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="C560" s="14"/>
       <c r="E560" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F560" s="12" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="G560" s="12">
         <v>1555</v>
@@ -40741,24 +40788,24 @@
         <v>4</v>
       </c>
       <c r="M560" s="12" t="s">
+        <v>3662</v>
+      </c>
+      <c r="O560" s="19" t="s">
         <v>3663</v>
-      </c>
-      <c r="O560" s="19" t="s">
-        <v>3664</v>
       </c>
       <c r="Q560" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T560" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="561" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="B561" s="12" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
       <c r="C561" s="12">
         <v>3887</v>
@@ -40770,10 +40817,10 @@
         <v>433</v>
       </c>
       <c r="F561" s="12" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="G561" s="12" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="H561" s="25" t="s">
         <v>2195</v>
@@ -40782,7 +40829,7 @@
         <v>197</v>
       </c>
       <c r="J561" s="13" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
       <c r="K561" s="13" t="s">
         <v>47</v>
@@ -40791,34 +40838,34 @@
         <v>10</v>
       </c>
       <c r="M561" s="12" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
       <c r="N561" s="9" t="s">
         <v>2196</v>
       </c>
       <c r="O561" s="19" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="P561" s="25"/>
       <c r="Q561" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T561" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="562" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="B562" s="12" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="E562" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F562" s="12" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="G562" s="12">
         <v>1531</v>
@@ -40839,37 +40886,37 @@
         <v>2</v>
       </c>
       <c r="M562" s="12" t="s">
+        <v>3683</v>
+      </c>
+      <c r="O562" s="19" t="s">
         <v>3684</v>
-      </c>
-      <c r="O562" s="19" t="s">
-        <v>3685</v>
       </c>
       <c r="P562" s="25"/>
       <c r="Q562" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T562" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="563" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
       <c r="B563" s="12" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="E563" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F563" s="12" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="G563" s="12" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="H563" s="12" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="I563" s="13" t="s">
         <v>2380</v>
@@ -40884,31 +40931,31 @@
         <v>2</v>
       </c>
       <c r="M563" s="12" t="s">
+        <v>3677</v>
+      </c>
+      <c r="O563" s="19" t="s">
         <v>3678</v>
-      </c>
-      <c r="O563" s="19" t="s">
-        <v>3679</v>
       </c>
       <c r="P563" s="25"/>
       <c r="Q563" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T563" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="564" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
       <c r="B564" s="12" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="E564" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F564" s="12" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="G564" s="12">
         <v>1577</v>
@@ -40929,43 +40976,43 @@
         <v>2</v>
       </c>
       <c r="M564" s="12" t="s">
+        <v>3681</v>
+      </c>
+      <c r="O564" s="19" t="s">
         <v>3682</v>
-      </c>
-      <c r="O564" s="19" t="s">
-        <v>3683</v>
       </c>
       <c r="P564" s="25"/>
       <c r="Q564" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T564" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="565" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="B565" s="12" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="E565" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F565" s="12" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="G565" s="12" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="H565" s="12" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="I565" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J565" s="12" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="K565" s="12" t="s">
         <v>61</v>
@@ -40974,37 +41021,37 @@
         <v>2</v>
       </c>
       <c r="M565" s="12" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="O565" s="19" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="P565" s="25"/>
       <c r="Q565" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T565" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="566" spans="1:20" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="B566" s="12" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="E566" s="12" t="s">
         <v>433</v>
       </c>
       <c r="F566" s="12" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="G566" s="12" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="H566" s="12" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="I566" s="13" t="s">
         <v>2380</v>
@@ -41019,25 +41066,25 @@
         <v>4</v>
       </c>
       <c r="M566" s="12" t="s">
+        <v>3685</v>
+      </c>
+      <c r="O566" s="19" t="s">
         <v>3686</v>
-      </c>
-      <c r="O566" s="19" t="s">
-        <v>3687</v>
       </c>
       <c r="P566" s="25"/>
       <c r="Q566" s="12" t="s">
         <v>289</v>
       </c>
       <c r="T566" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="B567" s="47" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="C567" s="45"/>
       <c r="D567" s="45"/>
@@ -41045,13 +41092,13 @@
         <v>433</v>
       </c>
       <c r="F567" s="46" t="s">
+        <v>3724</v>
+      </c>
+      <c r="G567" s="47" t="s">
         <v>3725</v>
       </c>
-      <c r="G567" s="47" t="s">
-        <v>3726</v>
-      </c>
       <c r="H567" s="47" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="I567" s="2" t="s">
         <v>2380</v>
@@ -41066,22 +41113,22 @@
         <v>8</v>
       </c>
       <c r="M567" s="47" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="N567" s="45"/>
       <c r="O567" s="19" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="Q567" s="47" t="s">
         <v>123</v>
       </c>
       <c r="T567" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>1146</v>
@@ -41090,13 +41137,13 @@
         <v>2213</v>
       </c>
       <c r="F568" s="2" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="G568" s="2" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
       <c r="H568" s="2" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
       <c r="I568" s="2" t="s">
         <v>419</v>
@@ -41108,27 +41155,27 @@
         <v>61</v>
       </c>
       <c r="L568" s="2" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="M568" s="2" t="s">
         <v>1146</v>
       </c>
       <c r="O568" s="19" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
       <c r="Q568" s="47" t="s">
         <v>123</v>
       </c>
       <c r="T568" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="B569" s="45" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
       <c r="C569" s="45">
         <v>1803</v>
@@ -41138,7 +41185,7 @@
         <v>433</v>
       </c>
       <c r="F569" s="45" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
       <c r="G569" s="48" t="s">
         <v>2604</v>
@@ -41159,28 +41206,28 @@
         <v>82</v>
       </c>
       <c r="M569" s="45" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
       <c r="N569" s="9" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="O569" s="19" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="Q569" s="32" t="s">
         <v>123</v>
       </c>
       <c r="R569" s="45"/>
       <c r="T569" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="C570" s="3">
         <v>2528</v>
@@ -41189,48 +41236,48 @@
         <v>1748</v>
       </c>
       <c r="F570" s="2" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="G570" s="2" t="s">
+        <v>3770</v>
+      </c>
+      <c r="H570" s="2" t="s">
         <v>3771</v>
-      </c>
-      <c r="H570" s="2" t="s">
-        <v>3772</v>
       </c>
       <c r="I570" s="2" t="s">
         <v>2223</v>
       </c>
       <c r="J570" s="2" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="K570" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L570" s="2" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="M570" s="2" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="N570" s="9" t="s">
+        <v>3773</v>
+      </c>
+      <c r="O570" s="19" t="s">
         <v>3774</v>
-      </c>
-      <c r="O570" s="19" t="s">
-        <v>3775</v>
       </c>
       <c r="Q570" s="32" t="s">
         <v>123</v>
       </c>
       <c r="T570" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="B571" s="32" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="C571" s="32">
         <v>1485</v>
@@ -41240,7 +41287,7 @@
         <v>3174</v>
       </c>
       <c r="F571" s="32" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="G571" s="32" t="s">
         <v>1206</v>
@@ -41258,13 +41305,13 @@
         <v>47</v>
       </c>
       <c r="L571" s="35" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="M571" s="32" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="N571" s="34" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="O571" s="32"/>
       <c r="Q571" s="32" t="s">
@@ -41272,15 +41319,15 @@
       </c>
       <c r="R571" s="32"/>
       <c r="T571" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12" t="s">
+        <v>3777</v>
+      </c>
+      <c r="B572" s="2" t="s">
         <v>3778</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>3779</v>
       </c>
       <c r="C572" s="3">
         <v>1454</v>
@@ -41289,7 +41336,7 @@
         <v>2277</v>
       </c>
       <c r="F572" s="2" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="G572" s="2" t="s">
         <v>650</v>
@@ -41301,46 +41348,46 @@
         <v>26</v>
       </c>
       <c r="L572" s="2" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="M572" s="2" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="N572" s="9" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="O572" s="19" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="Q572" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T572" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="B573" s="51" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="C573" s="45">
         <v>2983</v>
       </c>
       <c r="D573" s="45"/>
       <c r="E573" s="58" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="F573" s="45">
         <v>6721</v>
       </c>
       <c r="G573" s="50" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="H573" s="50" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="I573" s="50" t="s">
         <v>197</v>
@@ -41355,10 +41402,10 @@
         <v>129</v>
       </c>
       <c r="M573" s="51" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="N573" s="9" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="O573" s="45"/>
       <c r="Q573" s="32" t="s">
@@ -41366,15 +41413,15 @@
       </c>
       <c r="R573" s="45"/>
       <c r="T573" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12" t="s">
+        <v>3817</v>
+      </c>
+      <c r="B574" s="62" t="s">
         <v>3818</v>
-      </c>
-      <c r="B574" s="62" t="s">
-        <v>3819</v>
       </c>
       <c r="C574" s="45">
         <v>3345</v>
@@ -41384,13 +41431,13 @@
         <v>3174</v>
       </c>
       <c r="F574" s="32" t="s">
+        <v>3814</v>
+      </c>
+      <c r="G574" s="61" t="s">
         <v>3815</v>
       </c>
-      <c r="G574" s="61" t="s">
-        <v>3816</v>
-      </c>
       <c r="H574" s="61" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="I574" s="61" t="s">
         <v>316</v>
@@ -41405,10 +41452,10 @@
         <v>64</v>
       </c>
       <c r="M574" s="62" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="N574" s="9" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="O574" s="45"/>
       <c r="Q574" s="61" t="s">
@@ -41416,24 +41463,24 @@
       </c>
       <c r="R574" s="45"/>
       <c r="T574" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F575" s="2" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="G575" s="2" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="H575" s="2" t="s">
         <v>2629</v>
@@ -41442,45 +41489,45 @@
         <v>197</v>
       </c>
       <c r="J575" s="2" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="K575" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L575" s="2" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="M575" s="2" t="s">
+        <v>3824</v>
+      </c>
+      <c r="O575" s="19" t="s">
         <v>3825</v>
-      </c>
-      <c r="O575" s="19" t="s">
-        <v>3826</v>
       </c>
       <c r="Q575" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T575" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12" t="s">
+        <v>3826</v>
+      </c>
+      <c r="B576" s="2" t="s">
         <v>3827</v>
-      </c>
-      <c r="B576" s="2" t="s">
-        <v>3828</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F576" s="2" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="G576" s="2" t="s">
+        <v>3830</v>
+      </c>
+      <c r="H576" s="2" t="s">
         <v>3831</v>
-      </c>
-      <c r="H576" s="2" t="s">
-        <v>3832</v>
       </c>
       <c r="I576" s="2" t="s">
         <v>197</v>
@@ -41492,27 +41539,27 @@
         <v>47</v>
       </c>
       <c r="L576" s="2" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="M576" s="2" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="O576" s="19" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="Q576" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T576" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="B577" s="45" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="C577" s="45">
         <v>1867</v>
@@ -41522,7 +41569,7 @@
         <v>433</v>
       </c>
       <c r="F577" s="63" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="G577" s="63" t="s">
         <v>1467</v>
@@ -41543,28 +41590,28 @@
         <v>98</v>
       </c>
       <c r="M577" s="63" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="N577" s="9" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="O577" s="19" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="Q577" s="63" t="s">
         <v>123</v>
       </c>
       <c r="R577" s="45"/>
       <c r="T577" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="C578" s="3">
         <v>4619</v>
@@ -41573,45 +41620,45 @@
         <v>1618</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="G578" s="2" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="I578" s="2" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="J578" s="2" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="K578" s="2" t="s">
         <v>130</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="M578" s="2" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="N578" s="9" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="Q578" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T578" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="C579" s="3">
         <v>3712</v>
@@ -41620,60 +41667,60 @@
         <v>433</v>
       </c>
       <c r="F579" s="2" t="s">
+        <v>3718</v>
+      </c>
+      <c r="G579" s="2" t="s">
+        <v>3792</v>
+      </c>
+      <c r="H579" s="2" t="s">
+        <v>3792</v>
+      </c>
+      <c r="I579" s="2" t="s">
         <v>3719</v>
       </c>
-      <c r="G579" s="2" t="s">
-        <v>3793</v>
-      </c>
-      <c r="H579" s="2" t="s">
-        <v>3793</v>
-      </c>
-      <c r="I579" s="2" t="s">
-        <v>3720</v>
-      </c>
       <c r="J579" s="2" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K579" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L579" s="2" t="s">
+        <v>3901</v>
+      </c>
+      <c r="M579" s="2" t="s">
+        <v>3715</v>
+      </c>
+      <c r="N579" s="9" t="s">
+        <v>3790</v>
+      </c>
+      <c r="O579" s="19" t="s">
         <v>3902</v>
-      </c>
-      <c r="M579" s="2" t="s">
-        <v>3716</v>
-      </c>
-      <c r="N579" s="9" t="s">
-        <v>3791</v>
-      </c>
-      <c r="O579" s="19" t="s">
-        <v>3903</v>
       </c>
       <c r="Q579" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T579" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12" t="s">
+        <v>3903</v>
+      </c>
+      <c r="B580" s="2" t="s">
         <v>3904</v>
       </c>
-      <c r="B580" s="2" t="s">
-        <v>3905</v>
-      </c>
       <c r="E580" s="2" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="F580" s="2" t="s">
+        <v>3906</v>
+      </c>
+      <c r="G580" s="2" t="s">
         <v>3907</v>
       </c>
-      <c r="G580" s="2" t="s">
-        <v>3908</v>
-      </c>
       <c r="H580" s="2" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="I580" s="2" t="s">
         <v>87</v>
@@ -41682,83 +41729,83 @@
         <v>26</v>
       </c>
       <c r="L580" s="2" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="M580" s="2" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="O580" s="19" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="Q580" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T580" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B581" s="2" t="s">
         <v>3910</v>
-      </c>
-      <c r="B581" s="2" t="s">
-        <v>3911</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F581" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="G581" s="2" t="s">
         <v>3912</v>
       </c>
-      <c r="G581" s="2" t="s">
+      <c r="H581" s="2" t="s">
+        <v>3912</v>
+      </c>
+      <c r="I581" s="2" t="s">
         <v>3913</v>
       </c>
-      <c r="H581" s="2" t="s">
-        <v>3913</v>
-      </c>
-      <c r="I581" s="2" t="s">
-        <v>3914</v>
-      </c>
       <c r="J581" s="2" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="K581" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L581" s="2" t="s">
+        <v>3914</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="O581" s="19" t="s">
         <v>3915</v>
-      </c>
-      <c r="M581" s="2" t="s">
-        <v>3911</v>
-      </c>
-      <c r="O581" s="19" t="s">
-        <v>3916</v>
       </c>
       <c r="Q581" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T581" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B582" s="2" t="s">
         <v>3918</v>
       </c>
-      <c r="B582" s="2" t="s">
+      <c r="E582" s="2" t="s">
         <v>3919</v>
       </c>
-      <c r="E582" s="2" t="s">
+      <c r="F582" s="2" t="s">
+        <v>3923</v>
+      </c>
+      <c r="G582" s="2" t="s">
         <v>3920</v>
       </c>
-      <c r="F582" s="2" t="s">
-        <v>3924</v>
-      </c>
-      <c r="G582" s="2" t="s">
-        <v>3921</v>
-      </c>
       <c r="H582" s="2" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="I582" s="2" t="s">
         <v>230</v>
@@ -41770,39 +41817,39 @@
         <v>61</v>
       </c>
       <c r="L582" s="2" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="M582" s="2" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="O582" s="19" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="Q582" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T582" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="F583" s="2" t="s">
+        <v>3932</v>
+      </c>
+      <c r="G583" s="2" t="s">
         <v>3933</v>
       </c>
-      <c r="G583" s="2" t="s">
-        <v>3934</v>
-      </c>
       <c r="H583" s="2" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="I583" s="2" t="s">
         <v>138</v>
@@ -41814,27 +41861,27 @@
         <v>61</v>
       </c>
       <c r="L583" s="2" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="M583" s="2" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="O583" s="19" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="Q583" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T583" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="B584" s="65" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="C584" s="45"/>
       <c r="D584" s="45"/>
@@ -41842,13 +41889,13 @@
         <v>1748</v>
       </c>
       <c r="F584" s="66" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="G584" s="66" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="H584" s="66" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="I584" s="65" t="s">
         <v>316</v>
@@ -41860,28 +41907,28 @@
         <v>61</v>
       </c>
       <c r="L584" s="69" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="M584" s="65" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="N584" s="45"/>
       <c r="O584" s="19" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="Q584" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T584" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="B585" s="71" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="C585" s="71"/>
       <c r="D585" s="71"/>
@@ -41889,7 +41936,7 @@
         <v>433</v>
       </c>
       <c r="F585" s="71" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="G585" s="71">
         <v>1535</v>
@@ -41907,28 +41954,28 @@
         <v>61</v>
       </c>
       <c r="L585" s="72" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M585" s="71" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="N585" s="71"/>
       <c r="O585" s="19" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="Q585" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T585" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12" t="s">
+        <v>3966</v>
+      </c>
+      <c r="B586" s="2" t="s">
         <v>3967</v>
-      </c>
-      <c r="B586" s="2" t="s">
-        <v>3968</v>
       </c>
       <c r="C586" s="3">
         <v>3887</v>
@@ -41937,13 +41984,13 @@
         <v>433</v>
       </c>
       <c r="F586" s="2" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="G586" s="2" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="H586" s="2" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="I586" s="2" t="s">
         <v>197</v>
@@ -41955,30 +42002,30 @@
         <v>47</v>
       </c>
       <c r="L586" s="2" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="M586" s="2" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="N586" s="5" t="s">
         <v>2196</v>
       </c>
       <c r="O586" s="19" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="Q586" s="1" t="s">
         <v>289</v>
       </c>
       <c r="T586" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -41986,13 +42033,13 @@
         <v>433</v>
       </c>
       <c r="F587" s="1" t="s">
+        <v>3971</v>
+      </c>
+      <c r="G587" s="1" t="s">
         <v>3972</v>
       </c>
-      <c r="G587" s="1" t="s">
-        <v>3973</v>
-      </c>
       <c r="H587" s="1" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="I587" s="70" t="s">
         <v>419</v>
@@ -42007,24 +42054,24 @@
         <v>2585</v>
       </c>
       <c r="M587" s="1" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="O587" s="19" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="Q587" s="32" t="s">
         <v>289</v>
       </c>
       <c r="T587" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="B588" s="45" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="C588" s="45"/>
       <c r="D588" s="45"/>
@@ -42032,59 +42079,59 @@
         <v>2213</v>
       </c>
       <c r="F588" s="45" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="G588" s="76" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="H588" s="76" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="I588" s="71" t="s">
         <v>138</v>
       </c>
       <c r="J588" s="71" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="K588" s="71" t="s">
         <v>61</v>
       </c>
       <c r="L588" s="75" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="M588" s="71" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N588" s="45"/>
       <c r="O588" s="19" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="P588" s="45"/>
       <c r="Q588" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T588" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B589" s="2" t="s">
         <v>3994</v>
-      </c>
-      <c r="B589" s="2" t="s">
-        <v>3995</v>
       </c>
       <c r="E589" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F589" s="2" t="s">
+        <v>3991</v>
+      </c>
+      <c r="G589" s="2" t="s">
         <v>3992</v>
       </c>
-      <c r="G589" s="2" t="s">
-        <v>3993</v>
-      </c>
       <c r="H589" s="2" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="I589" s="2" t="s">
         <v>197</v>
@@ -42096,33 +42143,33 @@
         <v>61</v>
       </c>
       <c r="L589" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M589" s="2" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="O589" s="19" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="Q589" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T589" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12" t="s">
+        <v>3995</v>
+      </c>
+      <c r="B590" s="2" t="s">
         <v>3996</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>3997</v>
       </c>
       <c r="E590" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F590" s="2" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="G590" s="2" t="s">
         <v>2336</v>
@@ -42140,39 +42187,39 @@
         <v>61</v>
       </c>
       <c r="L590" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M590" s="2" t="s">
+        <v>3996</v>
+      </c>
+      <c r="O590" s="19" t="s">
         <v>3997</v>
-      </c>
-      <c r="O590" s="19" t="s">
-        <v>3998</v>
       </c>
       <c r="Q590" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T590" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="E591" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F591" s="2" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="G591" s="2" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="H591" s="2" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="I591" s="2" t="s">
         <v>2380</v>
@@ -42184,27 +42231,27 @@
         <v>61</v>
       </c>
       <c r="L591" s="2" t="s">
+        <v>4002</v>
+      </c>
+      <c r="M591" s="2" t="s">
+        <v>3999</v>
+      </c>
+      <c r="O591" s="19" t="s">
         <v>4003</v>
-      </c>
-      <c r="M591" s="2" t="s">
-        <v>4000</v>
-      </c>
-      <c r="O591" s="19" t="s">
-        <v>4004</v>
       </c>
       <c r="Q591" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T591" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="592" spans="1:20" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B592" s="32" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="C592" s="32"/>
       <c r="D592" s="32"/>
@@ -42212,13 +42259,13 @@
         <v>433</v>
       </c>
       <c r="F592" s="32" t="s">
+        <v>3384</v>
+      </c>
+      <c r="G592" s="32" t="s">
         <v>3385</v>
       </c>
-      <c r="G592" s="32" t="s">
-        <v>3386</v>
-      </c>
       <c r="H592" s="32" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="I592" s="32" t="s">
         <v>45</v>
@@ -42230,40 +42277,40 @@
         <v>61</v>
       </c>
       <c r="L592" s="35" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="M592" s="32" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="N592" s="32"/>
       <c r="O592" s="33" t="s">
+        <v>4005</v>
+      </c>
+      <c r="Q592" s="1" t="s">
         <v>4006</v>
       </c>
-      <c r="Q592" s="1" t="s">
-        <v>4007</v>
-      </c>
       <c r="T592" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="593" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B593" s="2" t="s">
         <v>4009</v>
-      </c>
-      <c r="B593" s="2" t="s">
-        <v>4010</v>
       </c>
       <c r="E593" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F593" s="2" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="G593" s="2" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="I593" s="2" t="s">
         <v>2380</v>
@@ -42275,39 +42322,39 @@
         <v>61</v>
       </c>
       <c r="L593" s="2" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="M593" s="2" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="O593" s="19" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="Q593" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T593" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B594" s="2" t="s">
         <v>4014</v>
-      </c>
-      <c r="B594" s="2" t="s">
-        <v>4015</v>
       </c>
       <c r="E594" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F594" s="2" t="s">
+        <v>4015</v>
+      </c>
+      <c r="G594" s="2" t="s">
         <v>4016</v>
       </c>
-      <c r="G594" s="2" t="s">
-        <v>4017</v>
-      </c>
       <c r="H594" s="2" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="I594" s="2" t="s">
         <v>2380</v>
@@ -42319,83 +42366,83 @@
         <v>61</v>
       </c>
       <c r="L594" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M594" s="2" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="O594" s="19" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="Q594" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T594" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="E595" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F595" s="2" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="G595" s="2" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="H595" s="2" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="I595" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J595" s="2" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="K595" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L595" s="2" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M595" s="2" t="s">
+        <v>4017</v>
+      </c>
+      <c r="O595" s="19" t="s">
         <v>4018</v>
-      </c>
-      <c r="O595" s="19" t="s">
-        <v>4019</v>
       </c>
       <c r="Q595" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T595" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="596" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="12" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B596" s="2" t="s">
+        <v>4023</v>
+      </c>
+      <c r="E596" s="2" t="s">
         <v>4024</v>
       </c>
-      <c r="E596" s="2" t="s">
-        <v>4025</v>
-      </c>
       <c r="F596" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="G596" s="2" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="H596" s="2" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="I596" s="2" t="s">
         <v>87</v>
@@ -42404,39 +42451,39 @@
         <v>26</v>
       </c>
       <c r="L596" s="2" t="s">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="M596" s="2" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="O596" s="19" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="Q596" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T596" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="597" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="12" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B597" s="80" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="E597" s="80" t="s">
         <v>3286</v>
       </c>
       <c r="F597" s="45" t="s">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="G597" s="81" t="s">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="H597" s="81" t="s">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="I597" s="81" t="s">
         <v>45</v>
@@ -42451,29 +42498,29 @@
         <v>4</v>
       </c>
       <c r="M597" s="81" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="N597" s="45"/>
       <c r="O597" s="19" t="s">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="P597" s="83" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q597" s="1" t="s">
         <v>123</v>
       </c>
       <c r="R597" s="45"/>
       <c r="T597" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="598" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="12" t="s">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="B598" s="82" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="C598" s="82"/>
       <c r="D598" s="82"/>
@@ -42481,7 +42528,7 @@
         <v>3286</v>
       </c>
       <c r="F598" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="G598" s="82">
         <v>1571</v>
@@ -42493,90 +42540,90 @@
         <v>45</v>
       </c>
       <c r="J598" s="82" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="K598" s="82" t="s">
         <v>61</v>
       </c>
       <c r="L598" s="84" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="M598" s="82" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="N598" s="82"/>
       <c r="O598" s="19" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="P598" s="83" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="Q598" s="1" t="s">
         <v>123</v>
       </c>
       <c r="R598" s="82"/>
       <c r="T598" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="599" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="12" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B599" s="2" t="s">
         <v>4064</v>
-      </c>
-      <c r="B599" s="2" t="s">
-        <v>4065</v>
       </c>
       <c r="E599" s="32" t="s">
         <v>433</v>
       </c>
       <c r="F599" s="2" t="s">
+        <v>4065</v>
+      </c>
+      <c r="G599" s="2" t="s">
         <v>4066</v>
       </c>
-      <c r="G599" s="2" t="s">
-        <v>4067</v>
-      </c>
       <c r="H599" s="2" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="I599" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J599" s="2" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="K599" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L599" s="2" t="s">
+        <v>4068</v>
+      </c>
+      <c r="M599" s="2" t="s">
+        <v>4064</v>
+      </c>
+      <c r="O599" s="19" t="s">
         <v>4069</v>
-      </c>
-      <c r="M599" s="2" t="s">
-        <v>4065</v>
-      </c>
-      <c r="O599" s="19" t="s">
-        <v>4070</v>
       </c>
       <c r="Q599" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T599" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="600" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="12" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="B600" s="86" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="C600" s="45"/>
       <c r="D600" s="45"/>
       <c r="E600" s="86" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="F600" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="G600" s="87">
         <v>1527</v>
@@ -42588,7 +42635,7 @@
         <v>2380</v>
       </c>
       <c r="J600" s="1" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="K600" s="86" t="s">
         <v>61</v>
@@ -42597,17 +42644,111 @@
         <v>34</v>
       </c>
       <c r="M600" s="86" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="N600" s="45"/>
       <c r="O600" s="19" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="Q600" s="1" t="s">
         <v>123</v>
       </c>
       <c r="T600" s="25" t="s">
-        <v>3568</v>
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="601" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="12" t="s">
+        <v>4074</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>4076</v>
+      </c>
+      <c r="E601" s="2" t="s">
+        <v>4086</v>
+      </c>
+      <c r="G601" s="2" t="s">
+        <v>4082</v>
+      </c>
+      <c r="H601" s="2" t="s">
+        <v>4082</v>
+      </c>
+      <c r="I601" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J601" s="2" t="s">
+        <v>4081</v>
+      </c>
+      <c r="K601" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="L601" s="2" t="s">
+        <v>3639</v>
+      </c>
+      <c r="M601" s="2" t="s">
+        <v>4076</v>
+      </c>
+      <c r="O601" s="19" t="s">
+        <v>4084</v>
+      </c>
+      <c r="P601" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q601" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R601" s="1" t="s">
+        <v>4085</v>
+      </c>
+      <c r="T601" s="25" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="602" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="12" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>4077</v>
+      </c>
+      <c r="E602" s="82" t="s">
+        <v>3286</v>
+      </c>
+      <c r="F602" s="2" t="s">
+        <v>4078</v>
+      </c>
+      <c r="G602" s="2" t="s">
+        <v>4079</v>
+      </c>
+      <c r="H602" s="2" t="s">
+        <v>2716</v>
+      </c>
+      <c r="I602" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J602" s="2" t="s">
+        <v>4080</v>
+      </c>
+      <c r="K602" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="L602" s="2" t="s">
+        <v>3639</v>
+      </c>
+      <c r="M602" s="2" t="s">
+        <v>4077</v>
+      </c>
+      <c r="O602" s="19" t="s">
+        <v>4083</v>
+      </c>
+      <c r="P602" t="s">
+        <v>3486</v>
+      </c>
+      <c r="Q602" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T602" s="25" t="s">
+        <v>3567</v>
       </c>
     </row>
   </sheetData>
@@ -43317,11 +43458,13 @@
     <hyperlink ref="O597" r:id="rId702" xr:uid="{E48D0676-4901-43E0-9DFF-5BB11C0848C1}"/>
     <hyperlink ref="O598" r:id="rId703" xr:uid="{DB6E7717-0A77-4E3E-9C1A-57C675C32B2A}"/>
     <hyperlink ref="O599" r:id="rId704" xr:uid="{8658DF67-CFB0-4C09-AB13-DA4E9D3EC276}"/>
+    <hyperlink ref="O602" r:id="rId705" xr:uid="{4371940C-29F7-4297-A3AA-6C12E1DA4C65}"/>
+    <hyperlink ref="O601" r:id="rId706" xr:uid="{30F84109-39A3-4344-A5D1-2F2A694B8D82}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId705"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId707"/>
   <tableParts count="1">
-    <tablePart r:id="rId706"/>
+    <tablePart r:id="rId708"/>
   </tableParts>
 </worksheet>
 </file>
@@ -43876,13 +44019,17 @@
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32" t="s">
-        <v>1335</v>
-      </c>
-      <c r="F12" s="32">
-        <v>6</v>
-      </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
+        <v>4072</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>4073</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>78</v>
+      </c>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32" t="s">
@@ -43892,10 +44039,10 @@
       <c r="M12" s="32" t="s">
         <v>3316</v>
       </c>
-      <c r="N12" s="32"/>
-      <c r="O12" s="33" t="s">
-        <v>3317</v>
-      </c>
+      <c r="N12" s="32" t="s">
+        <v>4071</v>
+      </c>
+      <c r="O12" s="33"/>
       <c r="P12" s="32" t="s">
         <v>123</v>
       </c>
@@ -43907,7 +44054,7 @@
         <v>3267</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="C13" s="32">
         <v>2885</v>
@@ -43917,7 +44064,7 @@
         <v>433</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>77</v>
@@ -43932,13 +44079,13 @@
       </c>
       <c r="L13" s="32"/>
       <c r="M13" s="32" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="N13" s="34" t="s">
+        <v>3319</v>
+      </c>
+      <c r="O13" s="33" t="s">
         <v>3320</v>
-      </c>
-      <c r="O13" s="33" t="s">
-        <v>3321</v>
       </c>
       <c r="P13" s="32" t="s">
         <v>123</v>
@@ -43951,7 +44098,7 @@
         <v>3267</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="C14" s="32">
         <v>1039</v>
@@ -43961,7 +44108,7 @@
         <v>3174</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="G14" s="32">
         <v>1301</v>
@@ -43978,14 +44125,14 @@
         <v>97</v>
       </c>
       <c r="M14" s="32" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="N14" s="34" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="O14" s="32"/>
       <c r="P14" s="32" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
@@ -43995,7 +44142,7 @@
         <v>3267</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="C15" s="32">
         <v>2430</v>
@@ -44005,13 +44152,13 @@
         <v>1374</v>
       </c>
       <c r="F15" s="32" t="s">
+        <v>3326</v>
+      </c>
+      <c r="G15" s="32" t="s">
         <v>3327</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>3328</v>
-      </c>
       <c r="H15" s="32" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>230</v>
@@ -44026,19 +44173,19 @@
         <v>34</v>
       </c>
       <c r="M15" s="32" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="N15" s="34" t="s">
+        <v>3328</v>
+      </c>
+      <c r="O15" s="33" t="s">
         <v>3329</v>
-      </c>
-      <c r="O15" s="33" t="s">
-        <v>3330</v>
       </c>
       <c r="P15" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q15" s="32" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="R15" s="32"/>
     </row>
@@ -44047,7 +44194,7 @@
         <v>3267</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="C16" s="32">
         <v>1807</v>
@@ -44059,13 +44206,13 @@
         <v>433</v>
       </c>
       <c r="F16" s="32" t="s">
+        <v>3332</v>
+      </c>
+      <c r="G16" s="32" t="s">
         <v>3333</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>3334</v>
-      </c>
       <c r="H16" s="32" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="I16" s="32" t="s">
         <v>45</v>
@@ -44080,19 +44227,19 @@
         <v>256</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="N16" s="34" t="s">
+        <v>3334</v>
+      </c>
+      <c r="O16" s="33" t="s">
         <v>3335</v>
-      </c>
-      <c r="O16" s="33" t="s">
-        <v>3336</v>
       </c>
       <c r="P16" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q16" s="32" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="R16" s="32"/>
     </row>
@@ -44101,7 +44248,7 @@
         <v>3267</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="C17" s="32">
         <v>3338</v>
@@ -44111,13 +44258,13 @@
         <v>278</v>
       </c>
       <c r="F17" s="32" t="s">
+        <v>3338</v>
+      </c>
+      <c r="G17" s="32" t="s">
         <v>3339</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>3340</v>
-      </c>
       <c r="H17" s="32" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="I17" s="32" t="s">
         <v>45</v>
@@ -44132,19 +44279,19 @@
         <v>197</v>
       </c>
       <c r="M17" s="32" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="N17" s="34" t="s">
+        <v>3340</v>
+      </c>
+      <c r="O17" s="33" t="s">
         <v>3341</v>
-      </c>
-      <c r="O17" s="33" t="s">
-        <v>3342</v>
       </c>
       <c r="P17" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q17" s="32" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="R17" s="32"/>
     </row>
@@ -44153,7 +44300,7 @@
         <v>3267</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="C18" s="32">
         <v>1694</v>
@@ -44165,13 +44312,13 @@
         <v>433</v>
       </c>
       <c r="F18" s="32" t="s">
+        <v>3344</v>
+      </c>
+      <c r="G18" s="32" t="s">
         <v>3345</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>3346</v>
-      </c>
       <c r="H18" s="32" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>45</v>
@@ -44186,19 +44333,19 @@
         <v>129</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="N18" s="34" t="s">
+        <v>3346</v>
+      </c>
+      <c r="O18" s="33" t="s">
         <v>3347</v>
-      </c>
-      <c r="O18" s="33" t="s">
-        <v>3348</v>
       </c>
       <c r="P18" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q18" s="32" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="R18" s="32"/>
     </row>
@@ -44207,7 +44354,7 @@
         <v>3267</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="C19" s="32">
         <v>2757</v>
@@ -44236,7 +44383,7 @@
       </c>
       <c r="L19" s="32"/>
       <c r="M19" s="32" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="N19" s="34" t="s">
         <v>3101</v>
@@ -44248,7 +44395,7 @@
         <v>289</v>
       </c>
       <c r="Q19" s="32" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="R19" s="32"/>
     </row>
@@ -44257,7 +44404,7 @@
         <v>3267</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="C20" s="32">
         <v>2061</v>
@@ -44269,13 +44416,13 @@
         <v>57</v>
       </c>
       <c r="F20" s="32" t="s">
+        <v>3352</v>
+      </c>
+      <c r="G20" s="32" t="s">
         <v>3353</v>
       </c>
-      <c r="G20" s="32" t="s">
-        <v>3354</v>
-      </c>
       <c r="H20" s="32" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="I20" s="32" t="s">
         <v>128</v>
@@ -44288,19 +44435,19 @@
       </c>
       <c r="L20" s="32"/>
       <c r="M20" s="32" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="N20" s="34" t="s">
         <v>3155</v>
       </c>
       <c r="O20" s="33" t="s">
+        <v>3354</v>
+      </c>
+      <c r="P20" s="32" t="s">
+        <v>3324</v>
+      </c>
+      <c r="Q20" s="32" t="s">
         <v>3355</v>
-      </c>
-      <c r="P20" s="32" t="s">
-        <v>3325</v>
-      </c>
-      <c r="Q20" s="32" t="s">
-        <v>3356</v>
       </c>
       <c r="R20" s="32"/>
     </row>
@@ -44309,7 +44456,7 @@
         <v>3267</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="C21" s="32">
         <v>3397</v>
@@ -44319,7 +44466,7 @@
         <v>57</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="G21" s="32" t="s">
         <v>2881</v>
@@ -44338,19 +44485,19 @@
       </c>
       <c r="L21" s="32"/>
       <c r="M21" s="32" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="N21" s="34" t="s">
+        <v>3361</v>
+      </c>
+      <c r="O21" s="33" t="s">
         <v>3362</v>
-      </c>
-      <c r="O21" s="33" t="s">
-        <v>3363</v>
       </c>
       <c r="P21" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q21" s="32" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="R21" s="32"/>
     </row>
@@ -44359,7 +44506,7 @@
         <v>3267</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="C22" s="32">
         <v>1622</v>
@@ -44371,13 +44518,13 @@
         <v>2934</v>
       </c>
       <c r="F22" s="32" t="s">
+        <v>3365</v>
+      </c>
+      <c r="G22" s="32" t="s">
         <v>3366</v>
       </c>
-      <c r="G22" s="32" t="s">
-        <v>3367</v>
-      </c>
       <c r="H22" s="32" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="I22" s="32" t="s">
         <v>230</v>
@@ -44390,19 +44537,19 @@
       </c>
       <c r="L22" s="32"/>
       <c r="M22" s="32" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="N22" s="34" t="s">
+        <v>3367</v>
+      </c>
+      <c r="O22" s="33" t="s">
         <v>3368</v>
-      </c>
-      <c r="O22" s="33" t="s">
-        <v>3369</v>
       </c>
       <c r="P22" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q22" s="32" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="R22" s="32"/>
     </row>
@@ -44411,7 +44558,7 @@
         <v>3267</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="C23" s="32">
         <v>1932</v>
@@ -44423,13 +44570,13 @@
         <v>2934</v>
       </c>
       <c r="F23" s="32" t="s">
+        <v>3365</v>
+      </c>
+      <c r="G23" s="32" t="s">
         <v>3366</v>
       </c>
-      <c r="G23" s="32" t="s">
-        <v>3367</v>
-      </c>
       <c r="H23" s="32" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="I23" s="32" t="s">
         <v>230</v>
@@ -44442,19 +44589,19 @@
       </c>
       <c r="L23" s="32"/>
       <c r="M23" s="32" t="s">
+        <v>3370</v>
+      </c>
+      <c r="N23" s="34" t="s">
         <v>3371</v>
       </c>
-      <c r="N23" s="34" t="s">
+      <c r="O23" s="33" t="s">
+        <v>3368</v>
+      </c>
+      <c r="P23" s="32" t="s">
+        <v>3324</v>
+      </c>
+      <c r="Q23" s="32" t="s">
         <v>3372</v>
-      </c>
-      <c r="O23" s="33" t="s">
-        <v>3369</v>
-      </c>
-      <c r="P23" s="32" t="s">
-        <v>3325</v>
-      </c>
-      <c r="Q23" s="32" t="s">
-        <v>3373</v>
       </c>
       <c r="R23" s="32"/>
     </row>
@@ -44463,7 +44610,7 @@
         <v>3267</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="C24" s="32">
         <v>3043</v>
@@ -44472,10 +44619,10 @@
         <v>2889</v>
       </c>
       <c r="E24" s="32" t="s">
+        <v>3374</v>
+      </c>
+      <c r="F24" s="32" t="s">
         <v>3375</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>3376</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>2881</v>
@@ -44494,19 +44641,19 @@
       </c>
       <c r="L24" s="32"/>
       <c r="M24" s="32" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="N24" s="34" t="s">
+        <v>3376</v>
+      </c>
+      <c r="O24" s="33" t="s">
         <v>3377</v>
-      </c>
-      <c r="O24" s="33" t="s">
-        <v>3378</v>
       </c>
       <c r="P24" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q24" s="32" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="R24" s="32"/>
     </row>
@@ -44515,7 +44662,7 @@
         <v>3267</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="C25" s="32">
         <v>2993</v>
@@ -44525,13 +44672,13 @@
         <v>433</v>
       </c>
       <c r="F25" s="32" t="s">
+        <v>3379</v>
+      </c>
+      <c r="G25" s="32" t="s">
         <v>3380</v>
       </c>
-      <c r="G25" s="32" t="s">
-        <v>3381</v>
-      </c>
       <c r="H25" s="32" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="I25" s="32" t="s">
         <v>128</v>
@@ -44544,13 +44691,13 @@
       </c>
       <c r="L25" s="32"/>
       <c r="M25" s="32" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="N25" s="34" t="s">
+        <v>3381</v>
+      </c>
+      <c r="O25" s="33" t="s">
         <v>3382</v>
-      </c>
-      <c r="O25" s="33" t="s">
-        <v>3383</v>
       </c>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
@@ -44561,17 +44708,17 @@
         <v>3267</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="C26" s="32">
         <v>1820</v>
       </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32" t="s">
+        <v>3387</v>
+      </c>
+      <c r="F26" s="32" t="s">
         <v>3388</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>3389</v>
       </c>
       <c r="G26" s="32">
         <v>1493</v>
@@ -44583,20 +44730,20 @@
         <v>197</v>
       </c>
       <c r="J26" s="32" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="K26" s="32" t="s">
         <v>130</v>
       </c>
       <c r="L26" s="32"/>
       <c r="M26" s="32" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="N26" s="34" t="s">
+        <v>3390</v>
+      </c>
+      <c r="O26" s="33" t="s">
         <v>3391</v>
-      </c>
-      <c r="O26" s="33" t="s">
-        <v>3392</v>
       </c>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
@@ -44647,7 +44794,7 @@
         <v>3267</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="C28" s="32">
         <v>1200</v>
@@ -44657,7 +44804,7 @@
         <v>1813</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>399</v>
@@ -44676,13 +44823,13 @@
         <v>94</v>
       </c>
       <c r="M28" s="32" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="N28" s="34" t="s">
+        <v>3394</v>
+      </c>
+      <c r="O28" s="33" t="s">
         <v>3395</v>
-      </c>
-      <c r="O28" s="33" t="s">
-        <v>3396</v>
       </c>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
@@ -44693,7 +44840,7 @@
         <v>1907</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="C29" s="32">
         <v>1021</v>
@@ -44724,13 +44871,13 @@
         <v>233</v>
       </c>
       <c r="M29" s="32" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="N29" s="34" t="s">
         <v>1913</v>
       </c>
       <c r="O29" s="33" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
@@ -44744,7 +44891,7 @@
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="F30" s="32">
         <v>2673</v>
@@ -44758,7 +44905,7 @@
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
       <c r="O30" s="33" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
@@ -44769,7 +44916,7 @@
         <v>3267</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
@@ -44777,7 +44924,7 @@
         <v>278</v>
       </c>
       <c r="F31" s="32" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
@@ -44786,13 +44933,13 @@
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="M31" s="32" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="N31" s="32"/>
       <c r="O31" s="32"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="R31" s="32"/>
     </row>
@@ -44807,7 +44954,7 @@
         <v>433</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
@@ -44823,10 +44970,10 @@
       <c r="L32" s="32"/>
       <c r="M32" s="32"/>
       <c r="N32" s="34" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="O32" s="38" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
@@ -44837,7 +44984,7 @@
         <v>3267</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="C33" s="32">
         <v>1501</v>
@@ -44856,13 +45003,13 @@
       <c r="K33" s="32"/>
       <c r="L33" s="32"/>
       <c r="M33" s="32" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="N33" s="34" t="s">
         <v>3314</v>
       </c>
       <c r="O33" s="38" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="P33" s="32"/>
       <c r="Q33" s="32"/>
@@ -44873,7 +45020,7 @@
         <v>3267</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="C34" s="32">
         <v>3009</v>
@@ -44883,13 +45030,13 @@
         <v>433</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="G34" s="32" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="I34" s="32" t="s">
         <v>45</v>
@@ -44902,17 +45049,17 @@
       </c>
       <c r="L34" s="32"/>
       <c r="M34" s="32" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="N34" s="34" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="O34" s="38" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="P34" s="32"/>
       <c r="Q34" s="32" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="R34" s="32"/>
     </row>
@@ -44921,7 +45068,7 @@
         <v>3267</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="C35" s="32">
         <v>1724</v>
@@ -44931,34 +45078,34 @@
         <v>3174</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="G35" s="32" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="I35" s="32" t="s">
         <v>316</v>
       </c>
       <c r="J35" s="32" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="K35" s="32" t="s">
         <v>130</v>
       </c>
       <c r="L35" s="32"/>
       <c r="M35" s="32" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="N35" s="34" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="O35" s="38"/>
       <c r="P35" s="32"/>
       <c r="Q35" s="32" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="R35" s="32"/>
     </row>
@@ -44967,7 +45114,7 @@
         <v>3267</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="C36" s="32">
         <v>2984</v>
@@ -44977,13 +45124,13 @@
         <v>2627</v>
       </c>
       <c r="F36" s="32" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="I36" s="32" t="s">
         <v>197</v>
@@ -44996,17 +45143,17 @@
       </c>
       <c r="L36" s="32"/>
       <c r="M36" s="32" t="s">
+        <v>3560</v>
+      </c>
+      <c r="N36" s="34" t="s">
         <v>3561</v>
       </c>
-      <c r="N36" s="34" t="s">
-        <v>3562</v>
-      </c>
       <c r="O36" s="38" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="P36" s="32"/>
       <c r="Q36" s="32" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="R36" s="32"/>
     </row>
@@ -45015,7 +45162,7 @@
         <v>3267</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
@@ -45023,13 +45170,13 @@
         <v>433</v>
       </c>
       <c r="F37" s="32" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="G37" s="32" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="I37" s="32" t="s">
         <v>230</v>
@@ -45042,15 +45189,15 @@
       </c>
       <c r="L37" s="32"/>
       <c r="M37" s="32" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="N37" s="32"/>
       <c r="O37" s="38" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="P37" s="32"/>
       <c r="Q37" s="32" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="R37" s="32"/>
     </row>
@@ -45059,7 +45206,7 @@
         <v>3267</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="C38" s="32">
         <v>1375</v>
@@ -45069,7 +45216,7 @@
         <v>433</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="G38" s="32" t="s">
         <v>748</v>
@@ -45086,13 +45233,13 @@
         <v>231</v>
       </c>
       <c r="M38" s="32" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="N38" s="34" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="O38" s="38" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="P38" s="32" t="s">
         <v>123</v>
@@ -45105,7 +45252,7 @@
         <v>3267</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -45130,22 +45277,22 @@
       </c>
       <c r="L39" s="42"/>
       <c r="M39" s="39" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="N39" s="39"/>
       <c r="O39" s="43" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="P39" s="44" t="s">
         <v>366</v>
       </c>
       <c r="Q39" s="39" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="R39" s="39"/>
       <c r="S39" s="20"/>
       <c r="T39" s="24" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45153,7 +45300,7 @@
         <v>3267</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
@@ -45161,7 +45308,7 @@
         <v>433</v>
       </c>
       <c r="F40" s="32" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="G40" s="32">
         <v>1554</v>
@@ -45176,11 +45323,11 @@
         <v>12</v>
       </c>
       <c r="M40" s="32" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="N40" s="32"/>
       <c r="O40" s="19" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="P40" s="32"/>
       <c r="Q40" s="32"/>
@@ -45191,7 +45338,7 @@
         <v>3267</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
@@ -45199,7 +45346,7 @@
         <v>433</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="G41" s="32">
         <v>1543</v>
@@ -45214,11 +45361,11 @@
         <v>10</v>
       </c>
       <c r="M41" s="32" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="N41" s="32"/>
       <c r="O41" s="38" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="P41" s="32"/>
       <c r="Q41" s="32"/>
@@ -45229,7 +45376,7 @@
         <v>3267</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="C42" s="45">
         <v>4619</v>
@@ -45239,31 +45386,31 @@
         <v>1618</v>
       </c>
       <c r="F42" s="56" t="s">
+        <v>3798</v>
+      </c>
+      <c r="G42" s="56" t="s">
+        <v>3796</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>3796</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>3719</v>
+      </c>
+      <c r="J42" s="32" t="s">
         <v>3799</v>
-      </c>
-      <c r="G42" s="56" t="s">
-        <v>3797</v>
-      </c>
-      <c r="H42" s="56" t="s">
-        <v>3797</v>
-      </c>
-      <c r="I42" s="32" t="s">
-        <v>3720</v>
-      </c>
-      <c r="J42" s="32" t="s">
-        <v>3800</v>
       </c>
       <c r="K42" s="56" t="s">
         <v>130</v>
       </c>
       <c r="L42" s="57" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="M42" s="56" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="O42" s="54"/>
       <c r="P42" s="45"/>
@@ -45275,7 +45422,7 @@
         <v>3267</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="C43" s="32">
         <v>3712</v>
@@ -45285,19 +45432,19 @@
         <v>433</v>
       </c>
       <c r="F43" s="32" t="s">
+        <v>3718</v>
+      </c>
+      <c r="G43" s="32" t="s">
+        <v>3792</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>3792</v>
+      </c>
+      <c r="I43" s="32" t="s">
         <v>3719</v>
       </c>
-      <c r="G43" s="32" t="s">
-        <v>3793</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>3793</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>3720</v>
-      </c>
       <c r="J43" s="32" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K43" s="32" t="s">
         <v>61</v>
@@ -45306,19 +45453,19 @@
         <v>136</v>
       </c>
       <c r="M43" s="32" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="O43" s="19" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="P43" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q43" s="32" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="R43" s="32"/>
     </row>
@@ -45327,7 +45474,7 @@
         <v>3267</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="C44" s="32">
         <v>2452</v>
@@ -45337,7 +45484,7 @@
         <v>433</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="G44" s="32">
         <v>1520</v>
@@ -45346,10 +45493,10 @@
         <v>1520</v>
       </c>
       <c r="I44" s="32" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="J44" s="32" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="K44" s="32" t="s">
         <v>61</v>
@@ -45358,19 +45505,19 @@
         <v>136</v>
       </c>
       <c r="M44" s="32" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="O44" s="19" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="P44" s="32" t="s">
         <v>289</v>
       </c>
       <c r="Q44" s="32" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="R44" s="32"/>
     </row>
@@ -45379,7 +45526,7 @@
         <v>3267</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="C45" s="45"/>
       <c r="D45" s="45"/>
@@ -45387,7 +45534,7 @@
         <v>2934</v>
       </c>
       <c r="F45" s="45" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="G45" s="45">
         <v>1510</v>
@@ -45396,10 +45543,10 @@
         <v>1510</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="J45" s="32" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="K45" s="55" t="s">
         <v>61</v>
@@ -45408,15 +45555,15 @@
         <v>120</v>
       </c>
       <c r="M45" s="55" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="N45" s="45"/>
       <c r="O45" s="54" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="P45" s="45"/>
       <c r="Q45" s="32" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="R45" s="45"/>
     </row>
@@ -45425,15 +45572,15 @@
         <v>3267</v>
       </c>
       <c r="B46" s="55" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="C46" s="45"/>
       <c r="D46" s="45"/>
       <c r="E46" s="55" t="s">
+        <v>3787</v>
+      </c>
+      <c r="F46" s="55" t="s">
         <v>3788</v>
-      </c>
-      <c r="F46" s="55" t="s">
-        <v>3789</v>
       </c>
       <c r="G46" s="45">
         <v>1510</v>
@@ -45442,10 +45589,10 @@
         <v>1510</v>
       </c>
       <c r="I46" s="32" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="J46" s="32" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="K46" s="55" t="s">
         <v>61</v>
@@ -45454,15 +45601,15 @@
         <v>96</v>
       </c>
       <c r="M46" s="55" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="N46" s="45"/>
       <c r="O46" s="54" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="P46" s="45"/>
       <c r="Q46" s="32" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="R46" s="45"/>
     </row>
@@ -45471,7 +45618,7 @@
         <v>3267</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="C47" s="45">
         <v>2172</v>
@@ -45483,19 +45630,19 @@
         <v>433</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="H47" s="56" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="I47" s="56" t="s">
         <v>87</v>
       </c>
       <c r="J47" s="56" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="K47" s="56" t="s">
         <v>130</v>
@@ -45504,13 +45651,13 @@
         <v>228</v>
       </c>
       <c r="M47" s="45" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="O47" s="19" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="P47" s="32" t="s">
         <v>123</v>
@@ -45528,7 +45675,7 @@
         <v>3267</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="C49" s="45">
         <v>2456</v>
@@ -45538,7 +45685,7 @@
         <v>1618</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="G49" s="52" t="s">
         <v>605</v>
@@ -45555,13 +45702,13 @@
         <v>340</v>
       </c>
       <c r="M49" s="52" t="s">
+        <v>3751</v>
+      </c>
+      <c r="N49" s="9" t="s">
         <v>3752</v>
       </c>
-      <c r="N49" s="9" t="s">
-        <v>3753</v>
-      </c>
       <c r="O49" s="19" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="P49" s="45"/>
       <c r="Q49" s="45"/>
@@ -45572,7 +45719,7 @@
         <v>3267</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="C50" s="45"/>
       <c r="D50" s="45"/>
@@ -45580,7 +45727,7 @@
         <v>433</v>
       </c>
       <c r="F50" s="53" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="G50" s="45"/>
       <c r="H50" s="45"/>
@@ -45589,11 +45736,11 @@
       <c r="K50" s="45"/>
       <c r="L50" s="45"/>
       <c r="M50" s="45" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="N50" s="45"/>
       <c r="O50" s="19" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="P50" s="45"/>
       <c r="Q50" s="45"/>
@@ -45604,7 +45751,7 @@
         <v>3267</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="C51" s="45"/>
       <c r="D51" s="45"/>
@@ -45612,7 +45759,7 @@
         <v>2277</v>
       </c>
       <c r="F51" s="53" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="G51" s="45"/>
       <c r="H51" s="45"/>
@@ -45621,11 +45768,11 @@
       <c r="K51" s="45"/>
       <c r="L51" s="45"/>
       <c r="M51" s="45" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="N51" s="45"/>
       <c r="O51" s="19" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="P51" s="45"/>
       <c r="Q51" s="45"/>
@@ -45636,7 +45783,7 @@
         <v>3267</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="C52" s="45"/>
       <c r="D52" s="45"/>
@@ -45644,7 +45791,7 @@
         <v>2277</v>
       </c>
       <c r="F52" s="53" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="G52" s="45"/>
       <c r="H52" s="45"/>
@@ -45653,11 +45800,11 @@
       <c r="K52" s="45"/>
       <c r="L52" s="45"/>
       <c r="M52" s="53" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="N52" s="45"/>
       <c r="O52" s="19" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="P52" s="45"/>
       <c r="Q52" s="45"/>
@@ -45668,7 +45815,7 @@
         <v>3267</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="C53" s="45"/>
       <c r="D53" s="45"/>
@@ -45676,7 +45823,7 @@
         <v>2277</v>
       </c>
       <c r="F53" s="53" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="G53" s="45"/>
       <c r="H53" s="45"/>
@@ -45685,11 +45832,11 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
       <c r="M53" s="45" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="N53" s="45"/>
       <c r="O53" s="19" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="P53" s="45"/>
       <c r="Q53" s="45"/>
@@ -45700,19 +45847,19 @@
         <v>3267</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="E54" s="45" t="s">
         <v>433</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="O54" s="19" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45720,25 +45867,25 @@
         <v>3267</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="C55" s="1">
         <v>2047</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>405</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>3927</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>3928</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>3929</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>45</v>
@@ -45747,13 +45894,13 @@
         <v>130</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>3929</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>3930</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>3931</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>123</v>
@@ -45764,7 +45911,7 @@
         <v>3267</v>
       </c>
       <c r="B56" s="65" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="45"/>
@@ -45772,13 +45919,13 @@
         <v>1748</v>
       </c>
       <c r="F56" s="66" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="G56" s="66" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="H56" s="66" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="I56" s="65" t="s">
         <v>316</v>
@@ -45791,17 +45938,17 @@
       </c>
       <c r="L56" s="45"/>
       <c r="M56" s="65" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="N56" s="45"/>
       <c r="O56" s="19" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q56" s="65" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="R56" s="45"/>
     </row>
@@ -45810,44 +45957,44 @@
         <v>3267</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="C57" s="45"/>
       <c r="D57" s="45"/>
       <c r="E57" s="68" t="s">
+        <v>3943</v>
+      </c>
+      <c r="F57" s="68" t="s">
         <v>3944</v>
       </c>
-      <c r="F57" s="68" t="s">
-        <v>3945</v>
-      </c>
       <c r="G57" s="67" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="H57" s="67" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="I57" s="67" t="s">
+        <v>3947</v>
+      </c>
+      <c r="J57" s="67" t="s">
         <v>3948</v>
-      </c>
-      <c r="J57" s="67" t="s">
-        <v>3949</v>
       </c>
       <c r="K57" s="67" t="s">
         <v>61</v>
       </c>
       <c r="L57" s="45"/>
       <c r="M57" s="67" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N57" s="45"/>
       <c r="O57" s="19" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q57" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="R57" s="45"/>
     </row>
@@ -45856,7 +46003,7 @@
         <v>3267</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="C58" s="45">
         <v>4614</v>
@@ -45865,16 +46012,16 @@
         <v>3002</v>
       </c>
       <c r="E58" s="70" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="F58" s="70" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="G58" s="70" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="H58" s="70" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="I58" s="70" t="s">
         <v>419</v>
@@ -45889,13 +46036,13 @@
         <v>383</v>
       </c>
       <c r="M58" s="70" t="s">
+        <v>3952</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>3956</v>
+      </c>
+      <c r="O58" s="19" t="s">
         <v>3953</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>3957</v>
-      </c>
-      <c r="O58" s="19" t="s">
-        <v>3954</v>
       </c>
       <c r="P58" s="45"/>
       <c r="Q58" s="45"/>
@@ -45904,7 +46051,7 @@
     <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45"/>
       <c r="B59" s="74" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="C59" s="45"/>
       <c r="D59" s="45"/>
@@ -45912,7 +46059,7 @@
         <v>3286</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="G59" s="45">
         <v>1777</v>
@@ -45925,22 +46072,22 @@
       </c>
       <c r="L59" s="45"/>
       <c r="M59" s="85" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="N59" s="45"/>
       <c r="O59" s="19" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="P59" s="45"/>
       <c r="Q59" s="73" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
       <c r="B60" s="45" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="C60" s="45"/>
       <c r="D60" s="45"/>
@@ -45948,30 +46095,30 @@
         <v>433</v>
       </c>
       <c r="F60" s="74" t="s">
+        <v>3980</v>
+      </c>
+      <c r="G60" s="74" t="s">
         <v>3981</v>
       </c>
-      <c r="G60" s="74" t="s">
-        <v>3982</v>
-      </c>
       <c r="H60" s="74" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="I60" s="74" t="s">
         <v>197</v>
       </c>
       <c r="J60" s="74" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="K60" s="74" t="s">
         <v>61</v>
       </c>
       <c r="L60" s="45"/>
       <c r="M60" s="74" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="N60" s="45"/>
       <c r="O60" s="19" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="P60" s="74" t="s">
         <v>289</v>
@@ -45982,7 +46129,7 @@
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45"/>
       <c r="B61" s="45" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="C61" s="45"/>
       <c r="D61" s="45"/>
@@ -45990,7 +46137,7 @@
         <v>433</v>
       </c>
       <c r="F61" s="77" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="G61" s="45"/>
       <c r="H61" s="45"/>
@@ -46001,14 +46148,14 @@
       </c>
       <c r="L61" s="45"/>
       <c r="M61" s="77" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="N61" s="45"/>
       <c r="O61" s="19" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="P61" s="77" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="Q61" s="45"/>
       <c r="R61" s="45"/>
@@ -46016,7 +46163,7 @@
     <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45"/>
       <c r="B62" s="79" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="C62" s="45"/>
       <c r="D62" s="45"/>
@@ -46024,13 +46171,13 @@
         <v>433</v>
       </c>
       <c r="F62" s="78" t="s">
+        <v>4036</v>
+      </c>
+      <c r="G62" s="78" t="s">
         <v>4037</v>
       </c>
-      <c r="G62" s="78" t="s">
-        <v>4038</v>
-      </c>
       <c r="H62" s="78" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="I62" s="78" t="s">
         <v>45</v>
@@ -46043,11 +46190,11 @@
       </c>
       <c r="L62" s="45"/>
       <c r="M62" s="78" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="N62" s="45"/>
       <c r="O62" s="19" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="P62" s="45"/>
       <c r="Q62" s="45"/>
@@ -46056,13 +46203,13 @@
     <row r="63" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="82"/>
       <c r="B63" s="1" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>2334</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="G63" s="1">
         <v>1528</v>
@@ -46074,7 +46221,7 @@
         <v>2380</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>61</v>
@@ -46083,16 +46230,16 @@
         <v>73</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="O63" s="19" t="s">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>4056</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46130,80 +46277,79 @@
     <hyperlink ref="N10" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
     <hyperlink ref="O10" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
     <hyperlink ref="N11" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="O12" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="N13" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="O13" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="N14" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="N15" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="O15" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="N16" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="O16" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="N17" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="N18" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="O18" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="N19" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="O19" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="N20" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="O20" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="N21" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="O21" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="N22" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="O22" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="N23" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="O23" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="N24" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="O24" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="N25" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="O25" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="N26" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="O26" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="N27" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="N28" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="N29" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="O29" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="O30" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="O32" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="N32" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="O34" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="N33" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="O33" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="N35" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="N34" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="N36" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="O36" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="O38" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="N38" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="O41" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="O43" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="O44" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="O40" r:id="rId62" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="O47" r:id="rId63" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="N49" r:id="rId64" xr:uid="{23B55178-69CD-4A5E-B8C8-EEAB50CCF3A4}"/>
-    <hyperlink ref="O49" r:id="rId65" xr:uid="{DD9658B3-4899-4307-A572-493280AD9DCA}"/>
-    <hyperlink ref="O50" r:id="rId66" xr:uid="{409512AD-4AFB-4C08-95F6-E5409FAF0083}"/>
-    <hyperlink ref="O51" r:id="rId67" xr:uid="{84071305-5C0F-4713-9505-63E4B3450192}"/>
-    <hyperlink ref="O52" r:id="rId68" xr:uid="{713EAC2E-65D7-4C67-BED8-E6E4427B1187}"/>
-    <hyperlink ref="O53" r:id="rId69" xr:uid="{CFEBCD8C-93AE-4F63-A06D-C84590D9303A}"/>
-    <hyperlink ref="N43" r:id="rId70" xr:uid="{F4C55FB2-E9A9-4D79-88B2-0477AE0C670F}"/>
-    <hyperlink ref="N44" r:id="rId71" xr:uid="{6288BB8E-53D8-4FDD-8817-FD54CF2E1FDC}"/>
-    <hyperlink ref="N42" r:id="rId72" xr:uid="{77B777FF-06F4-4C87-8FCF-921CFC7B7392}"/>
-    <hyperlink ref="N2" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="N47" r:id="rId74" xr:uid="{9AF19D18-8C14-4B5B-B6D5-6A400CB8F9AF}"/>
-    <hyperlink ref="O54" r:id="rId75" xr:uid="{90BF12DF-5857-4919-AD21-7284BEEAA61F}"/>
-    <hyperlink ref="N55" r:id="rId76" xr:uid="{ADF10015-C010-477B-9A20-574A643565CD}"/>
-    <hyperlink ref="O57" r:id="rId77" xr:uid="{467AC07A-17A6-4EB4-AC4E-28DE935BA4BE}"/>
-    <hyperlink ref="O56" r:id="rId78" xr:uid="{6F999F56-AD02-4951-9706-C7B8148F8E2A}"/>
-    <hyperlink ref="N58" r:id="rId79" xr:uid="{46152AA1-6EC2-4483-AA15-E1CC65968977}"/>
-    <hyperlink ref="O58" r:id="rId80" xr:uid="{0F09B375-5A60-41A8-8909-6A8862B203D3}"/>
-    <hyperlink ref="O59" r:id="rId81" xr:uid="{6A39D157-F210-4892-95B6-5107F8DF777C}"/>
-    <hyperlink ref="O60" r:id="rId82" xr:uid="{96D11007-6757-4F70-AB48-16741226BC93}"/>
-    <hyperlink ref="O62" r:id="rId83" xr:uid="{F1C65028-1D8D-40A8-9F1E-722A1F4F4126}"/>
-    <hyperlink ref="O61" r:id="rId84" xr:uid="{AA86DDB8-EC9F-44B4-81DD-DD4BD3F68872}"/>
+    <hyperlink ref="N13" r:id="rId16" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="O13" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="N14" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="N15" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="O15" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="N16" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="O16" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="N17" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="N18" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="O18" r:id="rId25" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="N19" r:id="rId26" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="O19" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="N20" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="O20" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="N21" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="O21" r:id="rId31" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="N22" r:id="rId32" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="O22" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="N23" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="O23" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="N24" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="O24" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="N25" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="O25" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="N26" r:id="rId40" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="O26" r:id="rId41" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="N27" r:id="rId42" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="N28" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="N29" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="O29" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="O30" r:id="rId46" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="O32" r:id="rId47" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="N32" r:id="rId48" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="O34" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="N33" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="O33" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="N35" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="N34" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="N36" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="O36" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="O38" r:id="rId56" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="N38" r:id="rId57" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="O41" r:id="rId58" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="O43" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="O44" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="O40" r:id="rId61" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="O47" r:id="rId62" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="N49" r:id="rId63" xr:uid="{23B55178-69CD-4A5E-B8C8-EEAB50CCF3A4}"/>
+    <hyperlink ref="O49" r:id="rId64" xr:uid="{DD9658B3-4899-4307-A572-493280AD9DCA}"/>
+    <hyperlink ref="O50" r:id="rId65" xr:uid="{409512AD-4AFB-4C08-95F6-E5409FAF0083}"/>
+    <hyperlink ref="O51" r:id="rId66" xr:uid="{84071305-5C0F-4713-9505-63E4B3450192}"/>
+    <hyperlink ref="O52" r:id="rId67" xr:uid="{713EAC2E-65D7-4C67-BED8-E6E4427B1187}"/>
+    <hyperlink ref="O53" r:id="rId68" xr:uid="{CFEBCD8C-93AE-4F63-A06D-C84590D9303A}"/>
+    <hyperlink ref="N43" r:id="rId69" xr:uid="{F4C55FB2-E9A9-4D79-88B2-0477AE0C670F}"/>
+    <hyperlink ref="N44" r:id="rId70" xr:uid="{6288BB8E-53D8-4FDD-8817-FD54CF2E1FDC}"/>
+    <hyperlink ref="N42" r:id="rId71" xr:uid="{77B777FF-06F4-4C87-8FCF-921CFC7B7392}"/>
+    <hyperlink ref="N2" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="N47" r:id="rId73" xr:uid="{9AF19D18-8C14-4B5B-B6D5-6A400CB8F9AF}"/>
+    <hyperlink ref="O54" r:id="rId74" xr:uid="{90BF12DF-5857-4919-AD21-7284BEEAA61F}"/>
+    <hyperlink ref="N55" r:id="rId75" xr:uid="{ADF10015-C010-477B-9A20-574A643565CD}"/>
+    <hyperlink ref="O57" r:id="rId76" xr:uid="{467AC07A-17A6-4EB4-AC4E-28DE935BA4BE}"/>
+    <hyperlink ref="O56" r:id="rId77" xr:uid="{6F999F56-AD02-4951-9706-C7B8148F8E2A}"/>
+    <hyperlink ref="N58" r:id="rId78" xr:uid="{46152AA1-6EC2-4483-AA15-E1CC65968977}"/>
+    <hyperlink ref="O58" r:id="rId79" xr:uid="{0F09B375-5A60-41A8-8909-6A8862B203D3}"/>
+    <hyperlink ref="O59" r:id="rId80" xr:uid="{6A39D157-F210-4892-95B6-5107F8DF777C}"/>
+    <hyperlink ref="O60" r:id="rId81" xr:uid="{96D11007-6757-4F70-AB48-16741226BC93}"/>
+    <hyperlink ref="O62" r:id="rId82" xr:uid="{F1C65028-1D8D-40A8-9F1E-722A1F4F4126}"/>
+    <hyperlink ref="O61" r:id="rId83" xr:uid="{AA86DDB8-EC9F-44B4-81DD-DD4BD3F68872}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId85"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId84"/>
   <tableParts count="1">
-    <tablePart r:id="rId86"/>
+    <tablePart r:id="rId85"/>
   </tableParts>
 </worksheet>
 </file>
@@ -46222,38 +46368,38 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
+        <v>3606</v>
+      </c>
+      <c r="B1" s="59" t="s">
         <v>3607</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="C1" s="59" t="s">
         <v>3608</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="D1" s="59" t="s">
         <v>3609</v>
       </c>
-      <c r="D1" s="59" t="s">
-        <v>3610</v>
-      </c>
       <c r="E1" s="59" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
+        <v>3855</v>
+      </c>
+      <c r="C2" s="60" t="s">
         <v>3856</v>
       </c>
-      <c r="C2" s="60" t="s">
-        <v>3857</v>
-      </c>
       <c r="D2" s="60" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="B3" s="59">
         <v>432</v>
@@ -46270,7 +46416,7 @@
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="B4" s="59">
         <v>1897</v>
@@ -46284,7 +46430,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="B5" s="59">
         <v>32</v>
@@ -46298,7 +46444,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="B6" s="59">
         <v>37</v>
@@ -46312,7 +46458,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="B7" s="59">
         <v>335</v>
@@ -46326,7 +46472,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="B8" s="59">
         <v>28</v>
@@ -46340,7 +46486,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="B9" s="59">
         <v>103</v>
@@ -46354,7 +46500,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="C10" s="59">
         <v>225</v>
@@ -46365,7 +46511,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="C11" s="59">
         <v>55</v>
@@ -46376,7 +46522,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="C12" s="59">
         <v>39</v>
@@ -46387,7 +46533,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="C13" s="59">
         <v>113</v>
@@ -46398,7 +46544,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="59" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
     </row>
   </sheetData>
